--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8BC278-E082-42DC-BA89-27F5916E9EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF601E-1A94-489D-820F-9092E6386520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{3366F5A6-D48D-4B7C-80E0-46CFBEDC9F48}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Produtividade" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtividade!$A$1:$O$575</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtividade!$A$1:$O$620</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22514,7 +22514,7 @@
         <v>CRÍTICO</v>
       </c>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="7">
         <v>46162</v>
       </c>
@@ -22565,7 +22565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="7">
         <v>46162</v>
       </c>
@@ -22615,7 +22615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="7">
         <v>46162</v>
       </c>
@@ -22666,7 +22666,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="7">
         <v>46162</v>
       </c>
@@ -22717,7 +22717,7 @@
         <v>15.38</v>
       </c>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="7">
         <v>46162</v>
       </c>
@@ -22768,7 +22768,7 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="7">
         <v>46162</v>
       </c>
@@ -22819,7 +22819,7 @@
         <v>12.81</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="7">
         <v>46162</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="7">
         <v>46162</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>18.18</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="7">
         <v>46162</v>
       </c>
@@ -22972,7 +22972,7 @@
         <v>16.45</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="7">
         <v>46162</v>
       </c>
@@ -23023,7 +23023,7 @@
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="7">
         <v>46162</v>
       </c>
@@ -23074,7 +23074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="7">
         <v>46162</v>
       </c>
@@ -23125,7 +23125,7 @@
         <v>18.059999999999999</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="7">
         <v>46162</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>18.68</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="7">
         <v>46162</v>
       </c>
@@ -23227,7 +23227,7 @@
         <v>42.11</v>
       </c>
     </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="7">
         <v>46162</v>
       </c>
@@ -23278,7 +23278,7 @@
         <v>13.58</v>
       </c>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="7">
         <v>46162</v>
       </c>
@@ -23329,7 +23329,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="7">
         <v>46162</v>
       </c>
@@ -23380,7 +23380,7 @@
         <v>17.239999999999998</v>
       </c>
     </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="7">
         <v>46162</v>
       </c>
@@ -23431,7 +23431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="7">
         <v>46162</v>
       </c>
@@ -23482,7 +23482,7 @@
         <v>14.78</v>
       </c>
     </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="7">
         <v>46162</v>
       </c>
@@ -23533,7 +23533,7 @@
         <v>12.04</v>
       </c>
     </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="7">
         <v>46162</v>
       </c>
@@ -23584,7 +23584,7 @@
         <v>14.47</v>
       </c>
     </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="7">
         <v>46162</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>17.09</v>
       </c>
     </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="7">
         <v>46162</v>
       </c>
@@ -23686,7 +23686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="7">
         <v>46162</v>
       </c>
@@ -23737,7 +23737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="7">
         <v>46162</v>
       </c>
@@ -23788,7 +23788,7 @@
         <v>12.82</v>
       </c>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="7">
         <v>46162</v>
       </c>
@@ -23839,7 +23839,7 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="7">
         <v>46162</v>
       </c>
@@ -23890,7 +23890,7 @@
         <v>14.47</v>
       </c>
     </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="7">
         <v>46162</v>
       </c>
@@ -23941,7 +23941,7 @@
         <v>11.56</v>
       </c>
     </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="7">
         <v>46162</v>
       </c>
@@ -23992,7 +23992,7 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="7">
         <v>46162</v>
       </c>
@@ -24043,7 +24043,7 @@
         <v>17.11</v>
       </c>
     </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="7">
         <v>46162</v>
       </c>
@@ -24094,7 +24094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="7">
         <v>46162</v>
       </c>
@@ -24145,7 +24145,7 @@
         <v>16.89</v>
       </c>
     </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="7">
         <v>46162</v>
       </c>
@@ -24196,7 +24196,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="7">
         <v>46162</v>
       </c>
@@ -24247,7 +24247,7 @@
         <v>29.17</v>
       </c>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="7">
         <v>46162</v>
       </c>
@@ -24298,7 +24298,7 @@
         <v>16.62</v>
       </c>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="7">
         <v>46162</v>
       </c>
@@ -24349,7 +24349,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="7">
         <v>46162</v>
       </c>
@@ -24400,7 +24400,7 @@
         <v>13.83</v>
       </c>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="7">
         <v>46162</v>
       </c>
@@ -24451,7 +24451,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="7">
         <v>46162</v>
       </c>
@@ -24502,7 +24502,7 @@
         <v>17.02</v>
       </c>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="7">
         <v>46162</v>
       </c>
@@ -24553,7 +24553,7 @@
         <v>13.04</v>
       </c>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="7">
         <v>46162</v>
       </c>
@@ -24604,7 +24604,7 @@
         <v>19.32</v>
       </c>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="7">
         <v>46162</v>
       </c>
@@ -24655,7 +24655,7 @@
         <v>15.74</v>
       </c>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="7">
         <v>46162</v>
       </c>
@@ -24706,7 +24706,7 @@
         <v>19.32</v>
       </c>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="7">
         <v>46162</v>
       </c>
@@ -24757,7 +24757,7 @@
         <v>13.02</v>
       </c>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="7">
         <v>46162</v>
       </c>
@@ -27104,14 +27104,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O575" xr:uid="{B156EF58-AF9E-4A91-B7D8-7B3B50610D55}">
+  <autoFilter ref="A1:O620" xr:uid="{B156EF58-AF9E-4A91-B7D8-7B3B50610D55}">
     <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2026" month="5" day="20" dateTimeGrouping="day"/>
+        <dateGroupItem year="2026" month="5" day="21" dateTimeGrouping="day"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A531:O575">
-      <sortCondition ref="B1:B575"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A590:O590">
+      <sortCondition ref="B1:B620"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -623,7 +623,7 @@
         <v>100</v>
       </c>
       <c r="O2" s="9" t="n">
-        <v>16.67</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="3" hidden="1">
@@ -666,13 +666,13 @@
         <v/>
       </c>
       <c r="M3" s="9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N3" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O3" s="9" t="n">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" hidden="1">
@@ -718,13 +718,13 @@
         <v/>
       </c>
       <c r="M4" s="9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N4" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>21.8</v>
+        <v>25.71428571428571</v>
       </c>
     </row>
     <row r="5" hidden="1">
@@ -770,13 +770,13 @@
         <v/>
       </c>
       <c r="M5" s="9" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="N5" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>15.79</v>
+        <v>38.70967741935484</v>
       </c>
     </row>
     <row r="6" hidden="1">
@@ -825,13 +825,13 @@
         <v/>
       </c>
       <c r="M6" s="9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N6" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>33.33</v>
+        <v>10.3448275862069</v>
       </c>
     </row>
     <row r="7" hidden="1">
@@ -877,13 +877,13 @@
         <v/>
       </c>
       <c r="M7" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" hidden="1">
@@ -929,13 +929,13 @@
         <v/>
       </c>
       <c r="M8" s="9" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="N8" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>11.76</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
     <row r="9" hidden="1">
@@ -981,13 +981,13 @@
         <v/>
       </c>
       <c r="M9" s="9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N9" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>5.88</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="10" hidden="1">
@@ -1033,13 +1033,13 @@
         <v/>
       </c>
       <c r="M10" s="9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N10" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>17.39</v>
+        <v>20.68965517241379</v>
       </c>
     </row>
     <row r="11" hidden="1">
@@ -1085,13 +1085,13 @@
         <v/>
       </c>
       <c r="M11" s="9" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N11" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>8.33</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="12" hidden="1">
@@ -1137,13 +1137,13 @@
         <v/>
       </c>
       <c r="M12" s="9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N12" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>10.53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" hidden="1">
@@ -1189,13 +1189,13 @@
         <v/>
       </c>
       <c r="M13" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>29.41</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="14" hidden="1">
@@ -1241,13 +1241,13 @@
         <v/>
       </c>
       <c r="M14" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N14" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" hidden="1">
@@ -1293,13 +1293,13 @@
         <v/>
       </c>
       <c r="M15" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N15" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16" hidden="1">
@@ -1449,13 +1449,13 @@
         <v/>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>0</v>
+        <v>20.68965517241379</v>
       </c>
     </row>
     <row r="19" hidden="1">
@@ -1501,13 +1501,13 @@
         <v/>
       </c>
       <c r="M19" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>0</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="20" hidden="1">
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>0</v>
+        <v>12.12121212121212</v>
       </c>
     </row>
     <row r="21" hidden="1">
@@ -1605,13 +1605,13 @@
         <v/>
       </c>
       <c r="M21" s="9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N21" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>0</v>
+        <v>4.347826086956522</v>
       </c>
     </row>
     <row r="22" hidden="1">
@@ -1657,13 +1657,13 @@
         <v/>
       </c>
       <c r="M22" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N22" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="23" hidden="1">
@@ -1709,13 +1709,13 @@
         <v/>
       </c>
       <c r="M23" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N23" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>0</v>
+        <v>9.67741935483871</v>
       </c>
     </row>
     <row r="24" hidden="1">
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="9" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v/>
       </c>
       <c r="M25" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N25" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="26" hidden="1">
@@ -1865,13 +1865,13 @@
         <v/>
       </c>
       <c r="M26" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" hidden="1">
@@ -1917,13 +1917,13 @@
         <v/>
       </c>
       <c r="M27" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N27" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>0</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="28" hidden="1">
@@ -1969,13 +1969,13 @@
         <v/>
       </c>
       <c r="M28" s="9" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N28" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>22.86</v>
+        <v>14.81481481481481</v>
       </c>
     </row>
     <row r="29" hidden="1">
@@ -2021,13 +2021,13 @@
         <v/>
       </c>
       <c r="M29" s="9" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="N29" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>16.67</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="30" hidden="1">
@@ -2073,12 +2073,14 @@
         <v/>
       </c>
       <c r="M30" s="9" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N30" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="O30" s="9" t="n"/>
+      <c r="O30" s="9" t="n">
+        <v>6.451612903225806</v>
+      </c>
     </row>
     <row r="31" hidden="1">
       <c r="A31" s="5" t="n">
@@ -2123,13 +2125,13 @@
         <v/>
       </c>
       <c r="M31" s="9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>91.67</v>
+        <v>0</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" hidden="1">
@@ -2175,13 +2177,13 @@
         <v/>
       </c>
       <c r="M32" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>16.67</v>
+        <v>23.07692307692308</v>
       </c>
     </row>
     <row r="33" hidden="1">
@@ -2230,13 +2232,13 @@
         <v/>
       </c>
       <c r="M33" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>71.43000000000001</v>
+        <v>0</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" hidden="1">
@@ -2285,13 +2287,13 @@
         <v/>
       </c>
       <c r="M34" s="9" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>11.11</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="35" hidden="1">
@@ -2337,13 +2339,13 @@
         <v/>
       </c>
       <c r="M35" s="9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>30.77</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="36" hidden="1">
@@ -2389,13 +2391,13 @@
         <v/>
       </c>
       <c r="M36" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>13.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" hidden="1">
@@ -2441,13 +2443,13 @@
         <v/>
       </c>
       <c r="M37" s="9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N37" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" hidden="1">
@@ -2493,13 +2495,13 @@
         <v/>
       </c>
       <c r="M38" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N38" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>27.78</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="39" hidden="1">
@@ -2545,13 +2547,13 @@
         <v/>
       </c>
       <c r="M39" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>17.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" hidden="1">
@@ -2597,13 +2599,13 @@
         <v/>
       </c>
       <c r="M40" s="9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>3.85</v>
+        <v>4.761904761904762</v>
       </c>
     </row>
     <row r="41" hidden="1">
@@ -2652,13 +2654,13 @@
         <v/>
       </c>
       <c r="M41" s="9" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="N41" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>19.35</v>
+        <v>41.66666666666667</v>
       </c>
     </row>
     <row r="42" hidden="1">
@@ -2704,13 +2706,13 @@
         <v/>
       </c>
       <c r="M42" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>19.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" hidden="1">
@@ -2756,13 +2758,13 @@
         <v/>
       </c>
       <c r="M43" s="9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N43" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>23.33</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="44" hidden="1">
@@ -2808,13 +2810,13 @@
         <v/>
       </c>
       <c r="M44" s="9" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="N44" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>6.06</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" hidden="1">
@@ -2863,13 +2865,13 @@
         <v/>
       </c>
       <c r="M45" s="9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="N45" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>35</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="46" hidden="1">
@@ -2915,13 +2917,13 @@
         <v/>
       </c>
       <c r="M46" s="3" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>7.69</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="47" hidden="1">
@@ -2967,13 +2969,13 @@
         <v/>
       </c>
       <c r="M47" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N47" s="9" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" hidden="1">
@@ -3019,13 +3021,13 @@
         <v/>
       </c>
       <c r="M48" s="3" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.76</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="49" hidden="1">
@@ -3071,13 +3073,13 @@
         <v/>
       </c>
       <c r="M49" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>18.52</v>
+        <v>7.692307692307693</v>
       </c>
     </row>
     <row r="50" hidden="1">
@@ -3126,13 +3128,13 @@
         <v/>
       </c>
       <c r="M50" s="3" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>16</v>
+        <v>42.42424242424242</v>
       </c>
     </row>
     <row r="51" hidden="1">
@@ -3178,13 +3180,13 @@
         <v/>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="52" hidden="1">
@@ -3233,13 +3235,13 @@
         <v/>
       </c>
       <c r="M52" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -3285,10 +3287,10 @@
         <v/>
       </c>
       <c r="M53" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
@@ -3337,13 +3339,13 @@
         <v/>
       </c>
       <c r="M54" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>37.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" hidden="1">
@@ -3389,13 +3391,13 @@
         <v/>
       </c>
       <c r="M55" s="3" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>18.18</v>
+        <v>7.407407407407407</v>
       </c>
     </row>
     <row r="56" hidden="1">
@@ -3444,13 +3446,13 @@
         <v/>
       </c>
       <c r="M56" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" hidden="1">
@@ -3499,13 +3501,13 @@
         <v/>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>33.33</v>
+        <v>5.555555555555555</v>
       </c>
     </row>
     <row r="58" hidden="1">
@@ -3551,13 +3553,13 @@
         <v/>
       </c>
       <c r="M58" s="3" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N58" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>13.79</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="59" hidden="1">
@@ -3603,13 +3605,13 @@
         <v/>
       </c>
       <c r="M59" s="3" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>24.14</v>
+        <v>17.39130434782609</v>
       </c>
     </row>
     <row r="60" hidden="1">
@@ -3655,13 +3657,13 @@
         <v/>
       </c>
       <c r="M60" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N60" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>16.67</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="61" hidden="1">
@@ -3713,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>22.22</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="62" hidden="1">
@@ -3759,13 +3761,13 @@
         <v/>
       </c>
       <c r="M62" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>3.85</v>
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="63" hidden="1">
@@ -3811,13 +3813,13 @@
         <v/>
       </c>
       <c r="M63" s="3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" hidden="1">
@@ -3863,13 +3865,13 @@
         <v/>
       </c>
       <c r="M64" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" hidden="1">
@@ -3915,13 +3917,13 @@
         <v/>
       </c>
       <c r="M65" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N65" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" hidden="1">
@@ -3967,13 +3969,13 @@
         <v/>
       </c>
       <c r="M66" s="3" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>0</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="67" hidden="1">
@@ -4019,13 +4021,13 @@
         <v/>
       </c>
       <c r="M67" s="3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>20.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" hidden="1">
@@ -4071,13 +4073,13 @@
         <v/>
       </c>
       <c r="M68" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>18.6</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="69" hidden="1">
@@ -4123,13 +4125,13 @@
         <v/>
       </c>
       <c r="M69" s="3" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>17.14</v>
+        <v>4.878048780487805</v>
       </c>
     </row>
     <row r="70" hidden="1">
@@ -4175,13 +4177,13 @@
         <v/>
       </c>
       <c r="M70" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>19.35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" hidden="1">
@@ -4227,13 +4229,13 @@
         <v/>
       </c>
       <c r="M71" s="3" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" hidden="1">
@@ -4279,13 +4281,13 @@
         <v/>
       </c>
       <c r="M72" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>6.67</v>
+        <v>14.81481481481481</v>
       </c>
     </row>
     <row r="73" hidden="1">
@@ -4331,13 +4333,13 @@
         <v/>
       </c>
       <c r="M73" s="3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>23.53</v>
+        <v>31.81818181818182</v>
       </c>
     </row>
     <row r="74" hidden="1">
@@ -4383,13 +4385,13 @@
         <v/>
       </c>
       <c r="M74" s="3" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3.33</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="75" hidden="1">
@@ -4435,13 +4437,13 @@
         <v/>
       </c>
       <c r="M75" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>9.09</v>
+        <v>3.125</v>
       </c>
     </row>
     <row r="76" hidden="1">
@@ -4487,13 +4489,13 @@
         <v/>
       </c>
       <c r="M76" s="3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>9.52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" hidden="1">
@@ -4539,13 +4541,13 @@
         <v/>
       </c>
       <c r="M77" s="3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>9.52</v>
+        <v>5.405405405405405</v>
       </c>
     </row>
     <row r="78" hidden="1">
@@ -4591,13 +4593,13 @@
         <v/>
       </c>
       <c r="M78" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N78" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" hidden="1">
@@ -4643,13 +4645,13 @@
         <v/>
       </c>
       <c r="M79" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" hidden="1">
@@ -4704,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>28.57</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
     <row r="81" hidden="1">
@@ -4750,13 +4752,13 @@
         <v/>
       </c>
       <c r="M81" s="3" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="N81" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>11.11</v>
+        <v>2.702702702702703</v>
       </c>
     </row>
     <row r="82" hidden="1">
@@ -4802,13 +4804,13 @@
         <v/>
       </c>
       <c r="M82" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" hidden="1">
@@ -4854,13 +4856,13 @@
         <v/>
       </c>
       <c r="M83" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>22.22</v>
+        <v>9.523809523809524</v>
       </c>
     </row>
     <row r="84" hidden="1">
@@ -4906,13 +4908,13 @@
         <v/>
       </c>
       <c r="M84" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" hidden="1">
@@ -4958,13 +4960,13 @@
         <v/>
       </c>
       <c r="M85" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>15.38</v>
+        <v>10.52631578947368</v>
       </c>
     </row>
     <row r="86" hidden="1">
@@ -5010,13 +5012,13 @@
         <v/>
       </c>
       <c r="M86" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" hidden="1">
@@ -5062,13 +5064,13 @@
         <v/>
       </c>
       <c r="M87" s="3" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="N87" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>21.05</v>
+        <v>16.3265306122449</v>
       </c>
     </row>
     <row r="88" hidden="1">
@@ -5114,13 +5116,13 @@
         <v/>
       </c>
       <c r="M88" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N88" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" hidden="1">
@@ -5169,13 +5171,13 @@
         <v/>
       </c>
       <c r="M89" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>3.45</v>
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="90" hidden="1">
@@ -5218,13 +5220,13 @@
         <v/>
       </c>
       <c r="M90" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>3.85</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="91" hidden="1">
@@ -5270,13 +5272,13 @@
         <v/>
       </c>
       <c r="M91" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N91" s="9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O91" s="9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" hidden="1">
@@ -5319,13 +5321,13 @@
         <v/>
       </c>
       <c r="M92" s="3" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>4</v>
+        <v>16.27906976744186</v>
       </c>
     </row>
     <row r="93" hidden="1">
@@ -5368,13 +5370,13 @@
         <v/>
       </c>
       <c r="M93" s="3" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N93" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>42.86</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="94" hidden="1">
@@ -5417,13 +5419,13 @@
         <v/>
       </c>
       <c r="M94" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" hidden="1">
@@ -5466,13 +5468,13 @@
         <v/>
       </c>
       <c r="M95" s="3" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>33.33</v>
+        <v>19.35483870967742</v>
       </c>
     </row>
     <row r="96" hidden="1">
@@ -5518,13 +5520,13 @@
         <v/>
       </c>
       <c r="M96" s="3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>11.11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" hidden="1">
@@ -5567,13 +5569,13 @@
         <v/>
       </c>
       <c r="M97" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" hidden="1">
@@ -5619,7 +5621,7 @@
         <v/>
       </c>
       <c r="M98" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98" s="3" t="n">
         <v>0</v>
@@ -5668,13 +5670,13 @@
         <v/>
       </c>
       <c r="M99" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="100" hidden="1">
@@ -5717,10 +5719,10 @@
         <v/>
       </c>
       <c r="M100" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
         <v>0</v>
@@ -5766,13 +5768,13 @@
         <v/>
       </c>
       <c r="M101" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>33.33</v>
+        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="102" hidden="1">
@@ -5815,13 +5817,13 @@
         <v/>
       </c>
       <c r="M102" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>12.5</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="103" hidden="1">
@@ -5864,13 +5866,13 @@
         <v/>
       </c>
       <c r="M103" s="3" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>24.39024390243902</v>
       </c>
     </row>
     <row r="104" hidden="1">
@@ -5913,13 +5915,13 @@
         <v/>
       </c>
       <c r="M104" s="3" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>14.29</v>
+        <v>10.3448275862069</v>
       </c>
     </row>
     <row r="105" hidden="1">
@@ -5962,13 +5964,13 @@
         <v/>
       </c>
       <c r="M105" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N105" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>0</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="106" hidden="1">
@@ -6011,13 +6013,13 @@
         <v/>
       </c>
       <c r="M106" s="3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>13.79</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="107" hidden="1">
@@ -6060,13 +6062,13 @@
         <v/>
       </c>
       <c r="M107" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" hidden="1">
@@ -6112,13 +6114,13 @@
         <v/>
       </c>
       <c r="M108" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>13.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" hidden="1">
@@ -6164,13 +6166,13 @@
         <v/>
       </c>
       <c r="M109" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N109" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O109" s="3" t="n">
-        <v>17.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" hidden="1">
@@ -6213,13 +6215,13 @@
         <v/>
       </c>
       <c r="M110" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>33.33</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="111" hidden="1">
@@ -6262,13 +6264,13 @@
         <v/>
       </c>
       <c r="M111" s="3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>4.76</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="112" hidden="1">
@@ -6311,13 +6313,13 @@
         <v/>
       </c>
       <c r="M112" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>24</v>
+        <v>12.72727272727273</v>
       </c>
     </row>
     <row r="113" hidden="1">
@@ -6363,10 +6365,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O113" s="3" t="n">
-        <v>11.54</v>
+        <v>11.53846153846154</v>
       </c>
     </row>
     <row r="114" hidden="1">
@@ -6409,13 +6411,13 @@
         <v/>
       </c>
       <c r="M114" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>20</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="115" hidden="1">
@@ -6461,13 +6463,13 @@
         <v/>
       </c>
       <c r="M115" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" hidden="1">
@@ -6516,7 +6518,7 @@
         <v>100</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>9.09</v>
+        <v>22.72727272727273</v>
       </c>
     </row>
     <row r="117" hidden="1">
@@ -6559,13 +6561,13 @@
         <v/>
       </c>
       <c r="M117" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="O117" s="3" t="n">
-        <v>10.53</v>
+        <v>23.07692307692308</v>
       </c>
     </row>
     <row r="118" hidden="1">
@@ -6608,13 +6610,13 @@
         <v/>
       </c>
       <c r="M118" s="3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>13.64</v>
+        <v>5.88235294117647</v>
       </c>
     </row>
     <row r="119" hidden="1">
@@ -6657,13 +6659,13 @@
         <v/>
       </c>
       <c r="M119" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O119" s="3" t="n">
-        <v>18.75</v>
+        <v>19.44444444444445</v>
       </c>
     </row>
     <row r="120" hidden="1">
@@ -6706,13 +6708,13 @@
         <v/>
       </c>
       <c r="M120" s="3" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" hidden="1">
@@ -6755,13 +6757,13 @@
         <v/>
       </c>
       <c r="M121" s="3" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>24.39</v>
+        <v>7.142857142857142</v>
       </c>
     </row>
     <row r="122" hidden="1">
@@ -6807,13 +6809,13 @@
         <v/>
       </c>
       <c r="M122" s="3" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="N122" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" hidden="1">
@@ -6856,13 +6858,13 @@
         <v/>
       </c>
       <c r="M123" s="3" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="N123" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>28</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="124" hidden="1">
@@ -6911,10 +6913,10 @@
         <v>31</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>90</v>
+        <v>88.89</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>25.81</v>
+        <v>29.03225806451613</v>
       </c>
     </row>
     <row r="125" hidden="1">
@@ -6957,13 +6959,13 @@
         <v/>
       </c>
       <c r="M125" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>9.09</v>
+        <v>25.80645161290322</v>
       </c>
     </row>
     <row r="126" hidden="1">
@@ -7009,13 +7011,13 @@
         <v/>
       </c>
       <c r="M126" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" hidden="1">
@@ -7058,13 +7060,13 @@
         <v/>
       </c>
       <c r="M127" s="3" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="N127" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>50</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="128" hidden="1">
@@ -7107,13 +7109,13 @@
         <v/>
       </c>
       <c r="M128" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N128" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O128" s="3" t="n">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" hidden="1">
@@ -7156,13 +7158,13 @@
         <v/>
       </c>
       <c r="M129" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="O129" s="3" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="130" hidden="1">
@@ -7205,13 +7207,13 @@
         <v/>
       </c>
       <c r="M130" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N130" s="3" t="n">
-        <v>91.67</v>
+        <v>0</v>
       </c>
       <c r="O130" s="3" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" hidden="1">
@@ -7254,13 +7256,13 @@
         <v/>
       </c>
       <c r="M131" s="3" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N131" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O131" s="3" t="n">
-        <v>4.76</v>
+        <v>27.02702702702703</v>
       </c>
     </row>
     <row r="132" hidden="1">
@@ -7303,13 +7305,13 @@
         <v/>
       </c>
       <c r="M132" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="N132" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>16</v>
+        <v>5.555555555555555</v>
       </c>
     </row>
     <row r="133" hidden="1">
@@ -7352,13 +7354,13 @@
         <v/>
       </c>
       <c r="M133" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N133" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>30.77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" hidden="1">
@@ -7401,13 +7403,13 @@
         <v/>
       </c>
       <c r="M134" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>10.36</v>
+        <v>26.31578947368421</v>
       </c>
     </row>
     <row r="135" hidden="1">
@@ -7453,13 +7455,13 @@
         <v/>
       </c>
       <c r="M135" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N135" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O135" s="9" t="n">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" hidden="1">
@@ -7502,13 +7504,13 @@
         <v/>
       </c>
       <c r="M136" s="3" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>12.5</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="137" hidden="1">
@@ -7551,13 +7553,13 @@
         <v/>
       </c>
       <c r="M137" s="3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="N137" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>13.64</v>
+        <v>21.21212121212121</v>
       </c>
     </row>
     <row r="138" hidden="1">
@@ -7600,13 +7602,13 @@
         <v/>
       </c>
       <c r="M138" s="3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O138" s="3" t="n">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" hidden="1">
@@ -7649,13 +7651,13 @@
         <v/>
       </c>
       <c r="M139" s="3" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="N139" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>7.69</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="140" hidden="1">
@@ -7701,13 +7703,13 @@
         <v/>
       </c>
       <c r="M140" s="3" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>5.88</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="141" hidden="1">
@@ -7750,13 +7752,13 @@
         <v/>
       </c>
       <c r="M141" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>6.67</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="142" hidden="1">
@@ -7799,10 +7801,10 @@
         <v/>
       </c>
       <c r="M142" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O142" s="3" t="n">
         <v>0</v>
@@ -7851,10 +7853,10 @@
         <v/>
       </c>
       <c r="M143" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O143" s="3" t="n">
         <v>0</v>
@@ -7900,13 +7902,13 @@
         <v/>
       </c>
       <c r="M144" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O144" s="3" t="n">
-        <v>0</v>
+        <v>13.04347826086956</v>
       </c>
     </row>
     <row r="145" hidden="1">
@@ -7949,13 +7951,13 @@
         <v/>
       </c>
       <c r="M145" s="3" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="N145" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O145" s="3" t="n">
-        <v>18.75</v>
+        <v>26.31578947368421</v>
       </c>
     </row>
     <row r="146" hidden="1">
@@ -7998,13 +8000,13 @@
         <v/>
       </c>
       <c r="M146" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>27.78</v>
+        <v>36.84210526315789</v>
       </c>
     </row>
     <row r="147" hidden="1">
@@ -8047,13 +8049,13 @@
         <v/>
       </c>
       <c r="M147" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N147" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>15.38</v>
+        <v>26.31578947368421</v>
       </c>
     </row>
     <row r="148" hidden="1">
@@ -8096,13 +8098,13 @@
         <v/>
       </c>
       <c r="M148" s="3" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N148" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O148" s="3" t="n">
-        <v>26.32</v>
+        <v>20.68965517241379</v>
       </c>
     </row>
     <row r="149" hidden="1">
@@ -8145,13 +8147,13 @@
         <v/>
       </c>
       <c r="M149" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N149" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O149" s="3" t="n">
-        <v>18.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" hidden="1">
@@ -8197,13 +8199,13 @@
         <v/>
       </c>
       <c r="M150" s="3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N150" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O150" s="3" t="n">
-        <v>15.79</v>
+        <v>30.76923076923077</v>
       </c>
     </row>
     <row r="151" hidden="1">
@@ -8246,13 +8248,13 @@
         <v/>
       </c>
       <c r="M151" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O151" s="3" t="n">
-        <v>29.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" hidden="1">
@@ -8298,13 +8300,13 @@
         <v/>
       </c>
       <c r="M152" s="3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N152" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" hidden="1">
@@ -8350,13 +8352,13 @@
         <v/>
       </c>
       <c r="M153" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" hidden="1">
@@ -8399,13 +8401,13 @@
         <v/>
       </c>
       <c r="M154" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N154" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>15.79</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="155" hidden="1">
@@ -8448,13 +8450,13 @@
         <v/>
       </c>
       <c r="M155" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>11.11</v>
+        <v>18.18181818181818</v>
       </c>
     </row>
     <row r="156" hidden="1">
@@ -8497,13 +8499,13 @@
         <v/>
       </c>
       <c r="M156" s="3" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="N156" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>6.67</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="157" hidden="1">
@@ -8546,13 +8548,13 @@
         <v/>
       </c>
       <c r="M157" s="3" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="N157" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>0</v>
+        <v>12.19512195121951</v>
       </c>
     </row>
     <row r="158" hidden="1">
@@ -8595,13 +8597,13 @@
         <v/>
       </c>
       <c r="M158" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O158" s="3" t="n">
-        <v>4</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="159" hidden="1">
@@ -8647,13 +8649,13 @@
         <v/>
       </c>
       <c r="M159" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" hidden="1">
@@ -8696,13 +8698,13 @@
         <v/>
       </c>
       <c r="M160" s="3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="N160" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>28.12</v>
+        <v>13.63636363636363</v>
       </c>
     </row>
     <row r="161" hidden="1">
@@ -8745,13 +8747,13 @@
         <v/>
       </c>
       <c r="M161" s="3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N161" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>6.9</v>
+        <v>17.39130434782609</v>
       </c>
     </row>
     <row r="162" hidden="1">
@@ -8794,13 +8796,13 @@
         <v/>
       </c>
       <c r="M162" s="3" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>27.27</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="163" hidden="1">
@@ -8892,13 +8894,13 @@
         <v/>
       </c>
       <c r="M164" s="3" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N164" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O164" s="3" t="n">
-        <v>18.52</v>
+        <v>15.68627450980392</v>
       </c>
     </row>
     <row r="165" hidden="1">
@@ -8941,13 +8943,13 @@
         <v/>
       </c>
       <c r="M165" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O165" s="3" t="n">
-        <v>23.81</v>
+        <v>26.92307692307692</v>
       </c>
     </row>
     <row r="166" hidden="1">
@@ -8993,13 +8995,13 @@
         <v/>
       </c>
       <c r="M166" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N166" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" hidden="1">
@@ -9042,13 +9044,13 @@
         <v/>
       </c>
       <c r="M167" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>26.09</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" hidden="1">
@@ -9094,13 +9096,13 @@
         <v/>
       </c>
       <c r="M168" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O168" s="3" t="n">
-        <v>0</v>
+        <v>8.571428571428571</v>
       </c>
     </row>
     <row r="169" hidden="1">
@@ -9143,13 +9145,13 @@
         <v/>
       </c>
       <c r="M169" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O169" s="3" t="n">
-        <v>0</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="170" hidden="1">
@@ -9198,7 +9200,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>0</v>
@@ -9244,13 +9246,13 @@
         <v/>
       </c>
       <c r="M171" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N171" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="172" hidden="1">
@@ -9342,13 +9344,13 @@
         <v/>
       </c>
       <c r="M173" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" hidden="1">
@@ -9394,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="N174" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O174" s="3" t="n">
         <v>0</v>
@@ -9440,13 +9442,13 @@
         <v/>
       </c>
       <c r="M175" s="3" t="n">
-        <v>66.67</v>
+        <v>37</v>
       </c>
       <c r="N175" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>50</v>
+        <v>18.91891891891892</v>
       </c>
     </row>
     <row r="176" hidden="1">
@@ -9489,13 +9491,13 @@
         <v/>
       </c>
       <c r="M176" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N176" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177" hidden="1">
@@ -9541,13 +9543,13 @@
         <v/>
       </c>
       <c r="M177" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N177" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O177" s="3" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="178" hidden="1">
@@ -9599,7 +9601,7 @@
         <v>100</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>33.33</v>
+        <v>4.761904761904762</v>
       </c>
     </row>
     <row r="179" hidden="1">
@@ -9648,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="N179" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O179" s="9" t="n">
         <v>0</v>
@@ -9697,13 +9699,13 @@
         <v/>
       </c>
       <c r="M180" s="3" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>21.05</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="181" hidden="1">
@@ -9748,6 +9750,15 @@
         <f>IF(K181&lt;-5,"CRÍTICO",IF(K181&lt;0,"ATENÇÃO",IF(K181&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M181" t="n">
+        <v>20</v>
+      </c>
+      <c r="N181" t="n">
+        <v>100</v>
+      </c>
+      <c r="O181" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="182" hidden="1">
       <c r="A182" s="5" t="n">
@@ -9791,6 +9802,15 @@
         <f>IF(K182&lt;-5,"CRÍTICO",IF(K182&lt;0,"ATENÇÃO",IF(K182&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183" hidden="1">
       <c r="A183" s="5" t="n">
@@ -9834,6 +9854,15 @@
         <f>IF(K183&lt;-5,"CRÍTICO",IF(K183&lt;0,"ATENÇÃO",IF(K183&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M183" t="n">
+        <v>12</v>
+      </c>
+      <c r="N183" t="n">
+        <v>100</v>
+      </c>
+      <c r="O183" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="184" hidden="1">
       <c r="A184" s="5" t="n">
@@ -9877,6 +9906,15 @@
         <f>IF(K184&lt;-5,"CRÍTICO",IF(K184&lt;0,"ATENÇÃO",IF(K184&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M184" t="n">
+        <v>27</v>
+      </c>
+      <c r="N184" t="n">
+        <v>100</v>
+      </c>
+      <c r="O184" t="n">
+        <v>25.92592592592592</v>
+      </c>
     </row>
     <row r="185" hidden="1">
       <c r="A185" s="5" t="n">
@@ -9920,6 +9958,15 @@
         <f>IF(K185&lt;-5,"CRÍTICO",IF(K185&lt;0,"ATENÇÃO",IF(K185&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M185" t="n">
+        <v>25</v>
+      </c>
+      <c r="N185" t="n">
+        <v>100</v>
+      </c>
+      <c r="O185" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="186" hidden="1">
       <c r="A186" s="5" t="n">
@@ -9963,6 +10010,15 @@
         <f>IF(K186&lt;-5,"CRÍTICO",IF(K186&lt;0,"ATENÇÃO",IF(K186&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M186" t="n">
+        <v>16</v>
+      </c>
+      <c r="N186" t="n">
+        <v>100</v>
+      </c>
+      <c r="O186" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="187" hidden="1">
       <c r="A187" s="5" t="n">
@@ -10006,6 +10062,15 @@
         <f>IF(K187&lt;-5,"CRÍTICO",IF(K187&lt;0,"ATENÇÃO",IF(K187&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M187" t="n">
+        <v>11</v>
+      </c>
+      <c r="N187" t="n">
+        <v>100</v>
+      </c>
+      <c r="O187" t="n">
+        <v>9.090909090909092</v>
+      </c>
     </row>
     <row r="188" hidden="1">
       <c r="A188" s="5" t="n">
@@ -10049,6 +10114,15 @@
         <f>IF(K188&lt;-5,"CRÍTICO",IF(K188&lt;0,"ATENÇÃO",IF(K188&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M188" t="n">
+        <v>22</v>
+      </c>
+      <c r="N188" t="n">
+        <v>100</v>
+      </c>
+      <c r="O188" t="n">
+        <v>40.90909090909091</v>
+      </c>
     </row>
     <row r="189" hidden="1">
       <c r="A189" s="5" t="n">
@@ -10092,6 +10166,15 @@
         <f>IF(K189&lt;-5,"CRÍTICO",IF(K189&lt;0,"ATENÇÃO",IF(K189&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M189" t="n">
+        <v>29</v>
+      </c>
+      <c r="N189" t="n">
+        <v>100</v>
+      </c>
+      <c r="O189" t="n">
+        <v>10.3448275862069</v>
+      </c>
     </row>
     <row r="190" hidden="1">
       <c r="A190" s="5" t="n">
@@ -10135,6 +10218,15 @@
         <f>IF(K190&lt;-5,"CRÍTICO",IF(K190&lt;0,"ATENÇÃO",IF(K190&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M190" t="n">
+        <v>7</v>
+      </c>
+      <c r="N190" t="n">
+        <v>100</v>
+      </c>
+      <c r="O190" t="n">
+        <v>28.57142857142857</v>
+      </c>
     </row>
     <row r="191" hidden="1">
       <c r="A191" s="5" t="n">
@@ -10178,6 +10270,15 @@
         <f>IF(K191&lt;-5,"CRÍTICO",IF(K191&lt;0,"ATENÇÃO",IF(K191&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M191" t="n">
+        <v>6</v>
+      </c>
+      <c r="N191" t="n">
+        <v>100</v>
+      </c>
+      <c r="O191" t="n">
+        <v>66.66666666666666</v>
+      </c>
     </row>
     <row r="192" hidden="1">
       <c r="A192" s="5" t="n">
@@ -10221,6 +10322,15 @@
         <f>IF(K192&lt;-5,"CRÍTICO",IF(K192&lt;0,"ATENÇÃO",IF(K192&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193" hidden="1">
       <c r="A193" s="5" t="n">
@@ -10264,6 +10374,15 @@
         <f>IF(K193&lt;-5,"CRÍTICO",IF(K193&lt;0,"ATENÇÃO",IF(K193&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194" hidden="1">
       <c r="A194" s="5" t="n">
@@ -10307,6 +10426,15 @@
         <f>IF(K194&lt;-5,"CRÍTICO",IF(K194&lt;0,"ATENÇÃO",IF(K194&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195" hidden="1">
       <c r="A195" s="5" t="n">
@@ -10350,6 +10478,15 @@
         <f>IF(K195&lt;-5,"CRÍTICO",IF(K195&lt;0,"ATENÇÃO",IF(K195&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M195" t="n">
+        <v>11</v>
+      </c>
+      <c r="N195" t="n">
+        <v>100</v>
+      </c>
+      <c r="O195" t="n">
+        <v>18.18181818181818</v>
+      </c>
     </row>
     <row r="196" hidden="1">
       <c r="A196" s="5" t="n">
@@ -10393,6 +10530,15 @@
         <f>IF(K196&lt;-5,"CRÍTICO",IF(K196&lt;0,"ATENÇÃO",IF(K196&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197" hidden="1">
       <c r="A197" s="5" t="n">
@@ -10436,6 +10582,15 @@
         <f>IF(K197&lt;-5,"CRÍTICO",IF(K197&lt;0,"ATENÇÃO",IF(K197&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>100</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198" hidden="1">
       <c r="A198" s="5" t="n">
@@ -10479,6 +10634,15 @@
         <f>IF(K198&lt;-5,"CRÍTICO",IF(K198&lt;0,"ATENÇÃO",IF(K198&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>100</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199" hidden="1">
       <c r="A199" s="5" t="n">
@@ -10522,6 +10686,15 @@
         <f>IF(K199&lt;-5,"CRÍTICO",IF(K199&lt;0,"ATENÇÃO",IF(K199&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>100</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200" hidden="1">
       <c r="A200" s="5" t="n">
@@ -10565,6 +10738,15 @@
         <f>IF(K200&lt;-5,"CRÍTICO",IF(K200&lt;0,"ATENÇÃO",IF(K200&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M200" t="n">
+        <v>22</v>
+      </c>
+      <c r="N200" t="n">
+        <v>100</v>
+      </c>
+      <c r="O200" t="n">
+        <v>22.72727272727273</v>
+      </c>
     </row>
     <row r="201" hidden="1">
       <c r="A201" s="5" t="n">
@@ -10608,6 +10790,15 @@
         <f>IF(K201&lt;-5,"CRÍTICO",IF(K201&lt;0,"ATENÇÃO",IF(K201&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M201" t="n">
+        <v>41</v>
+      </c>
+      <c r="N201" t="n">
+        <v>100</v>
+      </c>
+      <c r="O201" t="n">
+        <v>29.26829268292683</v>
+      </c>
     </row>
     <row r="202" hidden="1">
       <c r="A202" s="5" t="n">
@@ -10651,6 +10842,15 @@
         <f>IF(K202&lt;-5,"CRÍTICO",IF(K202&lt;0,"ATENÇÃO",IF(K202&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M202" t="n">
+        <v>21</v>
+      </c>
+      <c r="N202" t="n">
+        <v>100</v>
+      </c>
+      <c r="O202" t="n">
+        <v>4.761904761904762</v>
+      </c>
     </row>
     <row r="203" hidden="1">
       <c r="A203" s="5" t="n">
@@ -10694,6 +10894,15 @@
         <f>IF(K203&lt;-5,"CRÍTICO",IF(K203&lt;0,"ATENÇÃO",IF(K203&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M203" t="n">
+        <v>24</v>
+      </c>
+      <c r="N203" t="n">
+        <v>100</v>
+      </c>
+      <c r="O203" t="n">
+        <v>8.333333333333332</v>
+      </c>
     </row>
     <row r="204" hidden="1">
       <c r="A204" s="5" t="n">
@@ -10737,6 +10946,15 @@
         <f>IF(K204&lt;-5,"CRÍTICO",IF(K204&lt;0,"ATENÇÃO",IF(K204&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205" hidden="1">
       <c r="A205" s="5" t="n">
@@ -10780,6 +10998,15 @@
         <f>IF(K205&lt;-5,"CRÍTICO",IF(K205&lt;0,"ATENÇÃO",IF(K205&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M205" t="n">
+        <v>16</v>
+      </c>
+      <c r="N205" t="n">
+        <v>100</v>
+      </c>
+      <c r="O205" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="206" hidden="1">
       <c r="A206" s="5" t="n">
@@ -10823,6 +11050,15 @@
         <f>IF(K206&lt;-5,"CRÍTICO",IF(K206&lt;0,"ATENÇÃO",IF(K206&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M206" t="n">
+        <v>4</v>
+      </c>
+      <c r="N206" t="n">
+        <v>100</v>
+      </c>
+      <c r="O206" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="207" hidden="1">
       <c r="A207" s="5" t="n">
@@ -10866,6 +11102,15 @@
         <f>IF(K207&lt;-5,"CRÍTICO",IF(K207&lt;0,"ATENÇÃO",IF(K207&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M207" t="n">
+        <v>14</v>
+      </c>
+      <c r="N207" t="n">
+        <v>100</v>
+      </c>
+      <c r="O207" t="n">
+        <v>7.142857142857142</v>
+      </c>
     </row>
     <row r="208" hidden="1">
       <c r="A208" s="5" t="n">
@@ -10909,6 +11154,15 @@
         <f>IF(K208&lt;-5,"CRÍTICO",IF(K208&lt;0,"ATENÇÃO",IF(K208&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M208" t="n">
+        <v>24</v>
+      </c>
+      <c r="N208" t="n">
+        <v>100</v>
+      </c>
+      <c r="O208" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="209" hidden="1">
       <c r="A209" s="5" t="n">
@@ -10952,6 +11206,15 @@
         <f>IF(K209&lt;-5,"CRÍTICO",IF(K209&lt;0,"ATENÇÃO",IF(K209&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M209" t="n">
+        <v>18</v>
+      </c>
+      <c r="N209" t="n">
+        <v>100</v>
+      </c>
+      <c r="O209" t="n">
+        <v>22.22222222222222</v>
+      </c>
     </row>
     <row r="210" hidden="1">
       <c r="A210" s="5" t="n">
@@ -10995,6 +11258,15 @@
         <f>IF(K210&lt;-5,"CRÍTICO",IF(K210&lt;0,"ATENÇÃO",IF(K210&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M210" t="n">
+        <v>21</v>
+      </c>
+      <c r="N210" t="n">
+        <v>100</v>
+      </c>
+      <c r="O210" t="n">
+        <v>19.04761904761905</v>
+      </c>
     </row>
     <row r="211" hidden="1">
       <c r="A211" s="5" t="n">
@@ -11038,6 +11310,15 @@
         <f>IF(K211&lt;-5,"CRÍTICO",IF(K211&lt;0,"ATENÇÃO",IF(K211&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212" hidden="1">
       <c r="A212" s="5" t="n">
@@ -11081,6 +11362,15 @@
         <f>IF(K212&lt;-5,"CRÍTICO",IF(K212&lt;0,"ATENÇÃO",IF(K212&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M212" t="n">
+        <v>23</v>
+      </c>
+      <c r="N212" t="n">
+        <v>75</v>
+      </c>
+      <c r="O212" t="n">
+        <v>34.78260869565217</v>
+      </c>
     </row>
     <row r="213" hidden="1">
       <c r="A213" s="5" t="n">
@@ -11124,6 +11414,15 @@
         <f>IF(K213&lt;-5,"CRÍTICO",IF(K213&lt;0,"ATENÇÃO",IF(K213&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M213" t="n">
+        <v>21</v>
+      </c>
+      <c r="N213" t="n">
+        <v>100</v>
+      </c>
+      <c r="O213" t="n">
+        <v>9.523809523809524</v>
+      </c>
     </row>
     <row r="214" hidden="1">
       <c r="A214" s="5" t="n">
@@ -11167,6 +11466,15 @@
         <f>IF(K214&lt;-5,"CRÍTICO",IF(K214&lt;0,"ATENÇÃO",IF(K214&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M214" t="n">
+        <v>23</v>
+      </c>
+      <c r="N214" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O214" t="n">
+        <v>34.78260869565217</v>
+      </c>
     </row>
     <row r="215" hidden="1">
       <c r="A215" s="5" t="n">
@@ -11210,6 +11518,15 @@
         <f>IF(K215&lt;-5,"CRÍTICO",IF(K215&lt;0,"ATENÇÃO",IF(K215&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216" hidden="1">
       <c r="A216" s="5" t="n">
@@ -11253,6 +11570,15 @@
         <f>IF(K216&lt;-5,"CRÍTICO",IF(K216&lt;0,"ATENÇÃO",IF(K216&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M216" t="n">
+        <v>17</v>
+      </c>
+      <c r="N216" t="n">
+        <v>100</v>
+      </c>
+      <c r="O216" t="n">
+        <v>11.76470588235294</v>
+      </c>
     </row>
     <row r="217" hidden="1">
       <c r="A217" s="5" t="n">
@@ -11296,6 +11622,15 @@
         <f>IF(K217&lt;-5,"CRÍTICO",IF(K217&lt;0,"ATENÇÃO",IF(K217&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218" hidden="1">
       <c r="A218" s="5" t="n">
@@ -11339,6 +11674,15 @@
         <f>IF(K218&lt;-5,"CRÍTICO",IF(K218&lt;0,"ATENÇÃO",IF(K218&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M218" t="n">
+        <v>16</v>
+      </c>
+      <c r="N218" t="n">
+        <v>100</v>
+      </c>
+      <c r="O218" t="n">
+        <v>6.25</v>
+      </c>
     </row>
     <row r="219" hidden="1">
       <c r="A219" s="5" t="n">
@@ -11382,6 +11726,15 @@
         <f>IF(K219&lt;-5,"CRÍTICO",IF(K219&lt;0,"ATENÇÃO",IF(K219&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220" hidden="1">
       <c r="A220" s="5" t="n">
@@ -11425,6 +11778,15 @@
         <f>IF(K220&lt;-5,"CRÍTICO",IF(K220&lt;0,"ATENÇÃO",IF(K220&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M220" t="n">
+        <v>26</v>
+      </c>
+      <c r="N220" t="n">
+        <v>100</v>
+      </c>
+      <c r="O220" t="n">
+        <v>23.07692307692308</v>
+      </c>
     </row>
     <row r="221" hidden="1">
       <c r="A221" s="5" t="n">
@@ -11468,6 +11830,15 @@
         <f>IF(K221&lt;-5,"CRÍTICO",IF(K221&lt;0,"ATENÇÃO",IF(K221&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>100</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222" hidden="1">
       <c r="A222" s="5" t="n">
@@ -11511,6 +11882,15 @@
         <f>IF(K222&lt;-5,"CRÍTICO",IF(K222&lt;0,"ATENÇÃO",IF(K222&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M222" t="n">
+        <v>25</v>
+      </c>
+      <c r="N222" t="n">
+        <v>100</v>
+      </c>
+      <c r="O222" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="223" hidden="1">
       <c r="A223" s="5" t="n">
@@ -11558,7 +11938,7 @@
         <v>100</v>
       </c>
       <c r="O223" s="3" t="n">
-        <v>11.11</v>
+        <v>27.77777777777778</v>
       </c>
     </row>
     <row r="224" hidden="1">
@@ -11607,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="N224" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O224" s="9" t="n">
         <v>0</v>
@@ -11653,13 +12033,13 @@
         <v/>
       </c>
       <c r="M225" s="3" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N225" s="3" t="n">
-        <v>87.5</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="O225" s="3" t="n">
-        <v>11.11</v>
+        <v>18.42105263157895</v>
       </c>
     </row>
     <row r="226" hidden="1">
@@ -11698,6 +12078,15 @@
         <f>IF(K226&lt;-5,"CRÍTICO",IF(K226&lt;0,"ATENÇÃO",IF(K226&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M226" t="n">
+        <v>13</v>
+      </c>
+      <c r="N226" t="n">
+        <v>100</v>
+      </c>
+      <c r="O226" t="n">
+        <v>30.76923076923077</v>
+      </c>
     </row>
     <row r="227" hidden="1">
       <c r="A227" s="5" t="n">
@@ -11738,6 +12127,15 @@
         <f>IF(K227&lt;-5,"CRÍTICO",IF(K227&lt;0,"ATENÇÃO",IF(K227&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228" hidden="1">
       <c r="A228" s="5" t="n">
@@ -11778,6 +12176,15 @@
         <f>IF(K228&lt;-5,"CRÍTICO",IF(K228&lt;0,"ATENÇÃO",IF(K228&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M228" t="n">
+        <v>26</v>
+      </c>
+      <c r="N228" t="n">
+        <v>100</v>
+      </c>
+      <c r="O228" t="n">
+        <v>11.53846153846154</v>
+      </c>
     </row>
     <row r="229" hidden="1">
       <c r="A229" s="5" t="n">
@@ -11818,6 +12225,15 @@
         <f>IF(K229&lt;-5,"CRÍTICO",IF(K229&lt;0,"ATENÇÃO",IF(K229&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M229" t="n">
+        <v>21</v>
+      </c>
+      <c r="N229" t="n">
+        <v>100</v>
+      </c>
+      <c r="O229" t="n">
+        <v>28.57142857142857</v>
+      </c>
     </row>
     <row r="230" hidden="1">
       <c r="A230" s="5" t="n">
@@ -11855,6 +12271,15 @@
         <f>IF(K230&lt;-5,"CRÍTICO",IF(K230&lt;0,"ATENÇÃO",IF(K230&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M230" t="n">
+        <v>31</v>
+      </c>
+      <c r="N230" t="n">
+        <v>90</v>
+      </c>
+      <c r="O230" t="n">
+        <v>32.25806451612903</v>
+      </c>
     </row>
     <row r="231" hidden="1">
       <c r="A231" s="5" t="n">
@@ -11895,6 +12320,15 @@
         <f>IF(K231&lt;-5,"CRÍTICO",IF(K231&lt;0,"ATENÇÃO",IF(K231&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M231" t="n">
+        <v>22</v>
+      </c>
+      <c r="N231" t="n">
+        <v>100</v>
+      </c>
+      <c r="O231" t="n">
+        <v>31.81818181818182</v>
+      </c>
     </row>
     <row r="232" hidden="1">
       <c r="A232" s="5" t="n">
@@ -11935,6 +12369,15 @@
         <f>IF(K232&lt;-5,"CRÍTICO",IF(K232&lt;0,"ATENÇÃO",IF(K232&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M232" t="n">
+        <v>19</v>
+      </c>
+      <c r="N232" t="n">
+        <v>100</v>
+      </c>
+      <c r="O232" t="n">
+        <v>15.78947368421053</v>
+      </c>
     </row>
     <row r="233" hidden="1">
       <c r="A233" s="5" t="n">
@@ -11972,6 +12415,15 @@
         <f>IF(K233&lt;-5,"CRÍTICO",IF(K233&lt;0,"ATENÇÃO",IF(K233&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M233" t="n">
+        <v>25</v>
+      </c>
+      <c r="N233" t="n">
+        <v>100</v>
+      </c>
+      <c r="O233" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="234" hidden="1">
       <c r="A234" s="5" t="n">
@@ -12015,6 +12467,15 @@
         <f>IF(K234&lt;-5,"CRÍTICO",IF(K234&lt;0,"ATENÇÃO",IF(K234&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M234" t="n">
+        <v>29</v>
+      </c>
+      <c r="N234" t="n">
+        <v>100</v>
+      </c>
+      <c r="O234" t="n">
+        <v>13.79310344827586</v>
+      </c>
     </row>
     <row r="235" hidden="1">
       <c r="A235" s="5" t="n">
@@ -12052,6 +12513,15 @@
         <f>IF(K235&lt;-5,"CRÍTICO",IF(K235&lt;0,"ATENÇÃO",IF(K235&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
+      <c r="N235" t="n">
+        <v>100</v>
+      </c>
+      <c r="O235" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="236" hidden="1">
       <c r="A236" s="5" t="n">
@@ -12089,6 +12559,15 @@
         <f>IF(K236&lt;-5,"CRÍTICO",IF(K236&lt;0,"ATENÇÃO",IF(K236&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M236" t="n">
+        <v>2</v>
+      </c>
+      <c r="N236" t="n">
+        <v>100</v>
+      </c>
+      <c r="O236" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="237" hidden="1">
       <c r="A237" s="5" t="n">
@@ -12129,6 +12608,15 @@
         <f>IF(K237&lt;-5,"CRÍTICO",IF(K237&lt;0,"ATENÇÃO",IF(K237&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238" hidden="1">
       <c r="A238" s="5" t="n">
@@ -12172,6 +12660,15 @@
         <f>IF(K238&lt;-5,"CRÍTICO",IF(K238&lt;0,"ATENÇÃO",IF(K238&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>100</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239" hidden="1">
       <c r="A239" s="5" t="n">
@@ -12215,6 +12712,15 @@
         <f>IF(K239&lt;-5,"CRÍTICO",IF(K239&lt;0,"ATENÇÃO",IF(K239&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>100</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240" hidden="1">
       <c r="A240" s="5" t="n">
@@ -12258,6 +12764,15 @@
         <f>IF(K240&lt;-5,"CRÍTICO",IF(K240&lt;0,"ATENÇÃO",IF(K240&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M240" t="n">
+        <v>4</v>
+      </c>
+      <c r="N240" t="n">
+        <v>100</v>
+      </c>
+      <c r="O240" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="241" hidden="1">
       <c r="A241" s="5" t="n">
@@ -12295,6 +12810,15 @@
         <f>IF(K241&lt;-5,"CRÍTICO",IF(K241&lt;0,"ATENÇÃO",IF(K241&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242" hidden="1">
       <c r="A242" s="5" t="n">
@@ -12332,6 +12856,15 @@
         <f>IF(K242&lt;-5,"CRÍTICO",IF(K242&lt;0,"ATENÇÃO",IF(K242&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M242" t="n">
+        <v>15</v>
+      </c>
+      <c r="N242" t="n">
+        <v>100</v>
+      </c>
+      <c r="O242" t="n">
+        <v>6.666666666666667</v>
+      </c>
     </row>
     <row r="243" hidden="1">
       <c r="A243" s="5" t="n">
@@ -12372,6 +12905,15 @@
         <f>IF(K243&lt;-5,"CRÍTICO",IF(K243&lt;0,"ATENÇÃO",IF(K243&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M243" t="n">
+        <v>23</v>
+      </c>
+      <c r="N243" t="n">
+        <v>100</v>
+      </c>
+      <c r="O243" t="n">
+        <v>17.39130434782609</v>
+      </c>
     </row>
     <row r="244" hidden="1">
       <c r="A244" s="5" t="n">
@@ -12409,6 +12951,15 @@
         <f>IF(K244&lt;-5,"CRÍTICO",IF(K244&lt;0,"ATENÇÃO",IF(K244&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M244" t="n">
+        <v>23</v>
+      </c>
+      <c r="N244" t="n">
+        <v>100</v>
+      </c>
+      <c r="O244" t="n">
+        <v>17.39130434782609</v>
+      </c>
     </row>
     <row r="245" hidden="1">
       <c r="A245" s="5" t="n">
@@ -12449,6 +13000,15 @@
         <f>IF(K245&lt;-5,"CRÍTICO",IF(K245&lt;0,"ATENÇÃO",IF(K245&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M245" t="n">
+        <v>44</v>
+      </c>
+      <c r="N245" t="n">
+        <v>100</v>
+      </c>
+      <c r="O245" t="n">
+        <v>22.72727272727273</v>
+      </c>
     </row>
     <row r="246" hidden="1">
       <c r="A246" s="5" t="n">
@@ -12489,6 +13049,15 @@
         <f>IF(K246&lt;-5,"CRÍTICO",IF(K246&lt;0,"ATENÇÃO",IF(K246&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M246" t="n">
+        <v>17</v>
+      </c>
+      <c r="N246" t="n">
+        <v>100</v>
+      </c>
+      <c r="O246" t="n">
+        <v>17.64705882352941</v>
+      </c>
     </row>
     <row r="247" hidden="1">
       <c r="A247" s="5" t="n">
@@ -12529,6 +13098,15 @@
         <f>IF(K247&lt;-5,"CRÍTICO",IF(K247&lt;0,"ATENÇÃO",IF(K247&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M247" t="n">
+        <v>25</v>
+      </c>
+      <c r="N247" t="n">
+        <v>100</v>
+      </c>
+      <c r="O247" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="248" hidden="1">
       <c r="A248" s="5" t="n">
@@ -12572,6 +13150,15 @@
         <f>IF(K248&lt;-5,"CRÍTICO",IF(K248&lt;0,"ATENÇÃO",IF(K248&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249" hidden="1">
       <c r="A249" s="5" t="n">
@@ -12612,6 +13199,15 @@
         <f>IF(K249&lt;-5,"CRÍTICO",IF(K249&lt;0,"ATENÇÃO",IF(K249&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M249" t="n">
+        <v>18</v>
+      </c>
+      <c r="N249" t="n">
+        <v>100</v>
+      </c>
+      <c r="O249" t="n">
+        <v>16.66666666666666</v>
+      </c>
     </row>
     <row r="250" hidden="1">
       <c r="A250" s="5" t="n">
@@ -12652,6 +13248,15 @@
         <f>IF(K250&lt;-5,"CRÍTICO",IF(K250&lt;0,"ATENÇÃO",IF(K250&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M250" t="n">
+        <v>23</v>
+      </c>
+      <c r="N250" t="n">
+        <v>100</v>
+      </c>
+      <c r="O250" t="n">
+        <v>13.04347826086956</v>
+      </c>
     </row>
     <row r="251" hidden="1">
       <c r="A251" s="5" t="n">
@@ -12692,6 +13297,15 @@
         <f>IF(K251&lt;-5,"CRÍTICO",IF(K251&lt;0,"ATENÇÃO",IF(K251&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M251" t="n">
+        <v>11</v>
+      </c>
+      <c r="N251" t="n">
+        <v>100</v>
+      </c>
+      <c r="O251" t="n">
+        <v>27.27272727272727</v>
+      </c>
     </row>
     <row r="252" hidden="1">
       <c r="A252" s="5" t="n">
@@ -12732,6 +13346,15 @@
         <f>IF(K252&lt;-5,"CRÍTICO",IF(K252&lt;0,"ATENÇÃO",IF(K252&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M252" t="n">
+        <v>29</v>
+      </c>
+      <c r="N252" t="n">
+        <v>100</v>
+      </c>
+      <c r="O252" t="n">
+        <v>20.68965517241379</v>
+      </c>
     </row>
     <row r="253" hidden="1">
       <c r="A253" s="5" t="n">
@@ -12772,6 +13395,15 @@
         <f>IF(K253&lt;-5,"CRÍTICO",IF(K253&lt;0,"ATENÇÃO",IF(K253&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M253" t="n">
+        <v>21</v>
+      </c>
+      <c r="N253" t="n">
+        <v>100</v>
+      </c>
+      <c r="O253" t="n">
+        <v>23.80952380952381</v>
+      </c>
     </row>
     <row r="254" hidden="1">
       <c r="A254" s="5" t="n">
@@ -12809,6 +13441,15 @@
         <f>IF(K254&lt;-5,"CRÍTICO",IF(K254&lt;0,"ATENÇÃO",IF(K254&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M254" t="n">
+        <v>25</v>
+      </c>
+      <c r="N254" t="n">
+        <v>100</v>
+      </c>
+      <c r="O254" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="255" hidden="1">
       <c r="A255" s="5" t="n">
@@ -12852,6 +13493,15 @@
         <f>IF(K255&lt;-5,"CRÍTICO",IF(K255&lt;0,"ATENÇÃO",IF(K255&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256" hidden="1">
       <c r="A256" s="5" t="n">
@@ -12892,6 +13542,15 @@
         <f>IF(K256&lt;-5,"CRÍTICO",IF(K256&lt;0,"ATENÇÃO",IF(K256&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M256" t="n">
+        <v>25</v>
+      </c>
+      <c r="N256" t="n">
+        <v>100</v>
+      </c>
+      <c r="O256" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="257" hidden="1">
       <c r="A257" s="5" t="n">
@@ -12932,6 +13591,15 @@
         <f>IF(K257&lt;-5,"CRÍTICO",IF(K257&lt;0,"ATENÇÃO",IF(K257&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M257" t="n">
+        <v>27</v>
+      </c>
+      <c r="N257" t="n">
+        <v>100</v>
+      </c>
+      <c r="O257" t="n">
+        <v>18.51851851851852</v>
+      </c>
     </row>
     <row r="258" hidden="1">
       <c r="A258" s="5" t="n">
@@ -12972,6 +13640,15 @@
         <f>IF(K258&lt;-5,"CRÍTICO",IF(K258&lt;0,"ATENÇÃO",IF(K258&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M258" t="n">
+        <v>26</v>
+      </c>
+      <c r="N258" t="n">
+        <v>100</v>
+      </c>
+      <c r="O258" t="n">
+        <v>19.23076923076923</v>
+      </c>
     </row>
     <row r="259" hidden="1">
       <c r="A259" s="5" t="n">
@@ -13009,6 +13686,15 @@
         <f>IF(K259&lt;-5,"CRÍTICO",IF(K259&lt;0,"ATENÇÃO",IF(K259&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260" hidden="1">
       <c r="A260" s="5" t="n">
@@ -13046,6 +13732,15 @@
         <f>IF(K260&lt;-5,"CRÍTICO",IF(K260&lt;0,"ATENÇÃO",IF(K260&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M260" t="n">
+        <v>7</v>
+      </c>
+      <c r="N260" t="n">
+        <v>100</v>
+      </c>
+      <c r="O260" t="n">
+        <v>71.42857142857143</v>
+      </c>
     </row>
     <row r="261" hidden="1">
       <c r="A261" s="5" t="n">
@@ -13083,6 +13778,15 @@
         <f>IF(K261&lt;-5,"CRÍTICO",IF(K261&lt;0,"ATENÇÃO",IF(K261&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262" hidden="1">
       <c r="A262" s="5" t="n">
@@ -13123,6 +13827,15 @@
         <f>IF(K262&lt;-5,"CRÍTICO",IF(K262&lt;0,"ATENÇÃO",IF(K262&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M262" t="n">
+        <v>17</v>
+      </c>
+      <c r="N262" t="n">
+        <v>100</v>
+      </c>
+      <c r="O262" t="n">
+        <v>11.76470588235294</v>
+      </c>
     </row>
     <row r="263" hidden="1">
       <c r="A263" s="5" t="n">
@@ -13163,6 +13876,15 @@
         <f>IF(K263&lt;-5,"CRÍTICO",IF(K263&lt;0,"ATENÇÃO",IF(K263&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264" hidden="1">
       <c r="A264" s="5" t="n">
@@ -13203,6 +13925,15 @@
         <f>IF(K264&lt;-5,"CRÍTICO",IF(K264&lt;0,"ATENÇÃO",IF(K264&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M264" t="n">
+        <v>17</v>
+      </c>
+      <c r="N264" t="n">
+        <v>100</v>
+      </c>
+      <c r="O264" t="n">
+        <v>17.64705882352941</v>
+      </c>
     </row>
     <row r="265" hidden="1">
       <c r="A265" s="5" t="n">
@@ -13243,6 +13974,15 @@
         <f>IF(K265&lt;-5,"CRÍTICO",IF(K265&lt;0,"ATENÇÃO",IF(K265&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M265" t="n">
+        <v>15</v>
+      </c>
+      <c r="N265" t="n">
+        <v>100</v>
+      </c>
+      <c r="O265" t="n">
+        <v>26.66666666666667</v>
+      </c>
     </row>
     <row r="266" hidden="1">
       <c r="A266" s="5" t="n">
@@ -13280,6 +14020,15 @@
         <f>IF(K266&lt;-5,"CRÍTICO",IF(K266&lt;0,"ATENÇÃO",IF(K266&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M266" t="n">
+        <v>16</v>
+      </c>
+      <c r="N266" t="n">
+        <v>100</v>
+      </c>
+      <c r="O266" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="267" hidden="1">
       <c r="A267" s="5" t="n">
@@ -13327,7 +14076,7 @@
         <v>100</v>
       </c>
       <c r="O267" s="3" t="n">
-        <v>11.76</v>
+        <v>35.29411764705883</v>
       </c>
     </row>
     <row r="268" hidden="1">
@@ -13376,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="N268" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O268" s="9" t="n">
         <v>0</v>
@@ -13422,13 +14171,13 @@
         <v/>
       </c>
       <c r="M269" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N269" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O269" s="3" t="n">
-        <v>30.77</v>
+        <v>29.62962962962963</v>
       </c>
     </row>
     <row r="270" hidden="1">
@@ -13470,6 +14219,15 @@
         <f>IF(K270&lt;-5,"CRÍTICO",IF(K270&lt;0,"ATENÇÃO",IF(K270&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M270" t="n">
+        <v>25</v>
+      </c>
+      <c r="N270" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O270" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="271" hidden="1">
       <c r="A271" s="5" t="n">
@@ -13510,6 +14268,15 @@
         <f>IF(K271&lt;-5,"CRÍTICO",IF(K271&lt;0,"ATENÇÃO",IF(K271&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272" hidden="1">
       <c r="A272" s="5" t="n">
@@ -13547,6 +14314,15 @@
         <f>IF(K272&lt;-5,"CRÍTICO",IF(K272&lt;0,"ATENÇÃO",IF(K272&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M272" t="n">
+        <v>24</v>
+      </c>
+      <c r="N272" t="n">
+        <v>100</v>
+      </c>
+      <c r="O272" t="n">
+        <v>45.83333333333333</v>
+      </c>
     </row>
     <row r="273" hidden="1">
       <c r="A273" s="5" t="n">
@@ -13587,6 +14363,15 @@
         <f>IF(K273&lt;-5,"CRÍTICO",IF(K273&lt;0,"ATENÇÃO",IF(K273&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M273" t="n">
+        <v>25</v>
+      </c>
+      <c r="N273" t="n">
+        <v>100</v>
+      </c>
+      <c r="O273" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="274" hidden="1">
       <c r="A274" s="5" t="n">
@@ -13624,6 +14409,15 @@
         <f>IF(K274&lt;-5,"CRÍTICO",IF(K274&lt;0,"ATENÇÃO",IF(K274&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M274" t="n">
+        <v>33</v>
+      </c>
+      <c r="N274" t="n">
+        <v>100</v>
+      </c>
+      <c r="O274" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="275" hidden="1">
       <c r="A275" s="5" t="n">
@@ -13661,6 +14455,15 @@
         <f>IF(K275&lt;-5,"CRÍTICO",IF(K275&lt;0,"ATENÇÃO",IF(K275&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M275" t="n">
+        <v>27</v>
+      </c>
+      <c r="N275" t="n">
+        <v>100</v>
+      </c>
+      <c r="O275" t="n">
+        <v>18.51851851851852</v>
+      </c>
     </row>
     <row r="276" hidden="1">
       <c r="A276" s="5" t="n">
@@ -13698,6 +14501,15 @@
         <f>IF(K276&lt;-5,"CRÍTICO",IF(K276&lt;0,"ATENÇÃO",IF(K276&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M276" t="n">
+        <v>17</v>
+      </c>
+      <c r="N276" t="n">
+        <v>100</v>
+      </c>
+      <c r="O276" t="n">
+        <v>64.70588235294117</v>
+      </c>
     </row>
     <row r="277" hidden="1">
       <c r="A277" s="5" t="n">
@@ -13738,6 +14550,15 @@
         <f>IF(K277&lt;-5,"CRÍTICO",IF(K277&lt;0,"ATENÇÃO",IF(K277&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M277" t="n">
+        <v>27</v>
+      </c>
+      <c r="N277" t="n">
+        <v>100</v>
+      </c>
+      <c r="O277" t="n">
+        <v>29.62962962962963</v>
+      </c>
     </row>
     <row r="278" hidden="1">
       <c r="A278" s="5" t="n">
@@ -13778,6 +14599,15 @@
         <f>IF(K278&lt;-5,"CRÍTICO",IF(K278&lt;0,"ATENÇÃO",IF(K278&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="279" hidden="1">
       <c r="A279" s="5" t="n">
@@ -13821,6 +14651,15 @@
         <f>IF(K279&lt;-5,"CRÍTICO",IF(K279&lt;0,"ATENÇÃO",IF(K279&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>100</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280" hidden="1">
       <c r="A280" s="5" t="n">
@@ -13864,6 +14703,15 @@
         <f>IF(K280&lt;-5,"CRÍTICO",IF(K280&lt;0,"ATENÇÃO",IF(K280&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>100</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281" hidden="1">
       <c r="A281" s="5" t="n">
@@ -13901,6 +14749,15 @@
         <f>IF(K281&lt;-5,"CRÍTICO",IF(K281&lt;0,"ATENÇÃO",IF(K281&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M281" t="n">
+        <v>18</v>
+      </c>
+      <c r="N281" t="n">
+        <v>100</v>
+      </c>
+      <c r="O281" t="n">
+        <v>61.11111111111111</v>
+      </c>
     </row>
     <row r="282" hidden="1">
       <c r="A282" s="5" t="n">
@@ -13941,6 +14798,15 @@
         <f>IF(K282&lt;-5,"CRÍTICO",IF(K282&lt;0,"ATENÇÃO",IF(K282&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M282" t="n">
+        <v>24</v>
+      </c>
+      <c r="N282" t="n">
+        <v>100</v>
+      </c>
+      <c r="O282" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="283" hidden="1">
       <c r="A283" s="5" t="n">
@@ -13978,6 +14844,15 @@
         <f>IF(K283&lt;-5,"CRÍTICO",IF(K283&lt;0,"ATENÇÃO",IF(K283&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M283" t="n">
+        <v>18</v>
+      </c>
+      <c r="N283" t="n">
+        <v>100</v>
+      </c>
+      <c r="O283" t="n">
+        <v>38.88888888888889</v>
+      </c>
     </row>
     <row r="284" hidden="1">
       <c r="A284" s="5" t="n">
@@ -14018,6 +14893,15 @@
         <f>IF(K284&lt;-5,"CRÍTICO",IF(K284&lt;0,"ATENÇÃO",IF(K284&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M284" t="n">
+        <v>45</v>
+      </c>
+      <c r="N284" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O284" t="n">
+        <v>17.77777777777778</v>
+      </c>
     </row>
     <row r="285" hidden="1">
       <c r="A285" s="5" t="n">
@@ -14058,6 +14942,15 @@
         <f>IF(K285&lt;-5,"CRÍTICO",IF(K285&lt;0,"ATENÇÃO",IF(K285&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M285" t="n">
+        <v>37</v>
+      </c>
+      <c r="N285" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O285" t="n">
+        <v>21.62162162162162</v>
+      </c>
     </row>
     <row r="286" hidden="1">
       <c r="A286" s="5" t="n">
@@ -14098,6 +14991,15 @@
         <f>IF(K286&lt;-5,"CRÍTICO",IF(K286&lt;0,"ATENÇÃO",IF(K286&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M286" t="n">
+        <v>26</v>
+      </c>
+      <c r="N286" t="n">
+        <v>100</v>
+      </c>
+      <c r="O286" t="n">
+        <v>19.23076923076923</v>
+      </c>
     </row>
     <row r="287" hidden="1">
       <c r="A287" s="5" t="n">
@@ -14141,6 +15043,15 @@
         <f>IF(K287&lt;-5,"CRÍTICO",IF(K287&lt;0,"ATENÇÃO",IF(K287&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288" hidden="1">
       <c r="A288" s="5" t="n">
@@ -14178,6 +15089,15 @@
         <f>IF(K288&lt;-5,"CRÍTICO",IF(K288&lt;0,"ATENÇÃO",IF(K288&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M288" t="n">
+        <v>22</v>
+      </c>
+      <c r="N288" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O288" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="289" hidden="1">
       <c r="A289" s="5" t="n">
@@ -14218,6 +15138,15 @@
         <f>IF(K289&lt;-5,"CRÍTICO",IF(K289&lt;0,"ATENÇÃO",IF(K289&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M289" t="n">
+        <v>18</v>
+      </c>
+      <c r="N289" t="n">
+        <v>100</v>
+      </c>
+      <c r="O289" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="290" hidden="1">
       <c r="A290" s="5" t="n">
@@ -14258,6 +15187,15 @@
         <f>IF(K290&lt;-5,"CRÍTICO",IF(K290&lt;0,"ATENÇÃO",IF(K290&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M290" t="n">
+        <v>11</v>
+      </c>
+      <c r="N290" t="n">
+        <v>100</v>
+      </c>
+      <c r="O290" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="291" hidden="1">
       <c r="A291" s="5" t="n">
@@ -14298,6 +15236,15 @@
         <f>IF(K291&lt;-5,"CRÍTICO",IF(K291&lt;0,"ATENÇÃO",IF(K291&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M291" t="n">
+        <v>28</v>
+      </c>
+      <c r="N291" t="n">
+        <v>100</v>
+      </c>
+      <c r="O291" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="292" hidden="1">
       <c r="A292" s="5" t="n">
@@ -14338,6 +15285,15 @@
         <f>IF(K292&lt;-5,"CRÍTICO",IF(K292&lt;0,"ATENÇÃO",IF(K292&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M292" t="n">
+        <v>22</v>
+      </c>
+      <c r="N292" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="O292" t="n">
+        <v>31.81818181818182</v>
+      </c>
     </row>
     <row r="293" hidden="1">
       <c r="A293" s="5" t="n">
@@ -14375,6 +15331,15 @@
         <f>IF(K293&lt;-5,"CRÍTICO",IF(K293&lt;0,"ATENÇÃO",IF(K293&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M293" t="n">
+        <v>20</v>
+      </c>
+      <c r="N293" t="n">
+        <v>100</v>
+      </c>
+      <c r="O293" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="294" hidden="1">
       <c r="A294" s="5" t="n">
@@ -14418,6 +15383,15 @@
         <f>IF(K294&lt;-5,"CRÍTICO",IF(K294&lt;0,"ATENÇÃO",IF(K294&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295" hidden="1">
       <c r="A295" s="5" t="n">
@@ -14458,6 +15432,15 @@
         <f>IF(K295&lt;-5,"CRÍTICO",IF(K295&lt;0,"ATENÇÃO",IF(K295&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M295" t="n">
+        <v>22</v>
+      </c>
+      <c r="N295" t="n">
+        <v>100</v>
+      </c>
+      <c r="O295" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="296" hidden="1">
       <c r="A296" s="5" t="n">
@@ -14495,6 +15478,15 @@
         <f>IF(K296&lt;-5,"CRÍTICO",IF(K296&lt;0,"ATENÇÃO",IF(K296&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M296" t="n">
+        <v>6</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297" hidden="1">
       <c r="A297" s="5" t="n">
@@ -14532,6 +15524,15 @@
         <f>IF(K297&lt;-5,"CRÍTICO",IF(K297&lt;0,"ATENÇÃO",IF(K297&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="n">
+        <v>100</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="298" hidden="1">
       <c r="A298" s="5" t="n">
@@ -14569,6 +15570,15 @@
         <f>IF(K298&lt;-5,"CRÍTICO",IF(K298&lt;0,"ATENÇÃO",IF(K298&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M298" t="n">
+        <v>1</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299" hidden="1">
       <c r="A299" s="5" t="n">
@@ -14606,6 +15616,15 @@
         <f>IF(K299&lt;-5,"CRÍTICO",IF(K299&lt;0,"ATENÇÃO",IF(K299&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300" hidden="1">
       <c r="A300" s="5" t="n">
@@ -14649,6 +15668,15 @@
         <f>IF(K300&lt;-5,"CRÍTICO",IF(K300&lt;0,"ATENÇÃO",IF(K300&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M300" t="n">
+        <v>13</v>
+      </c>
+      <c r="N300" t="n">
+        <v>100</v>
+      </c>
+      <c r="O300" t="n">
+        <v>38.46153846153847</v>
+      </c>
     </row>
     <row r="301" hidden="1">
       <c r="A301" s="5" t="n">
@@ -14689,6 +15717,15 @@
         <f>IF(K301&lt;-5,"CRÍTICO",IF(K301&lt;0,"ATENÇÃO",IF(K301&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M301" t="n">
+        <v>25</v>
+      </c>
+      <c r="N301" t="n">
+        <v>100</v>
+      </c>
+      <c r="O301" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="302" hidden="1">
       <c r="A302" s="5" t="n">
@@ -14729,6 +15766,15 @@
         <f>IF(K302&lt;-5,"CRÍTICO",IF(K302&lt;0,"ATENÇÃO",IF(K302&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M302" t="n">
+        <v>28</v>
+      </c>
+      <c r="N302" t="n">
+        <v>100</v>
+      </c>
+      <c r="O302" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="303" hidden="1">
       <c r="A303" s="5" t="n">
@@ -14766,6 +15812,15 @@
         <f>IF(K303&lt;-5,"CRÍTICO",IF(K303&lt;0,"ATENÇÃO",IF(K303&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="304" hidden="1">
       <c r="A304" s="5" t="n">
@@ -14803,6 +15858,15 @@
         <f>IF(K304&lt;-5,"CRÍTICO",IF(K304&lt;0,"ATENÇÃO",IF(K304&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M304" t="n">
+        <v>22</v>
+      </c>
+      <c r="N304" t="n">
+        <v>100</v>
+      </c>
+      <c r="O304" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="305" hidden="1">
       <c r="A305" s="5" t="n">
@@ -14840,6 +15904,15 @@
         <f>IF(K305&lt;-5,"CRÍTICO",IF(K305&lt;0,"ATENÇÃO",IF(K305&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306" hidden="1">
       <c r="A306" s="5" t="n">
@@ -14877,6 +15950,15 @@
         <f>IF(K306&lt;-5,"CRÍTICO",IF(K306&lt;0,"ATENÇÃO",IF(K306&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M306" t="n">
+        <v>9</v>
+      </c>
+      <c r="N306" t="n">
+        <v>100</v>
+      </c>
+      <c r="O306" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="307" hidden="1">
       <c r="A307" s="5" t="n">
@@ -14917,6 +15999,15 @@
         <f>IF(K307&lt;-5,"CRÍTICO",IF(K307&lt;0,"ATENÇÃO",IF(K307&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="308" hidden="1">
       <c r="A308" s="5" t="n">
@@ -14957,6 +16048,15 @@
         <f>IF(K308&lt;-5,"CRÍTICO",IF(K308&lt;0,"ATENÇÃO",IF(K308&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M308" t="n">
+        <v>22</v>
+      </c>
+      <c r="N308" t="n">
+        <v>100</v>
+      </c>
+      <c r="O308" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="309" hidden="1">
       <c r="A309" s="5" t="n">
@@ -14994,6 +16094,15 @@
         <f>IF(K309&lt;-5,"CRÍTICO",IF(K309&lt;0,"ATENÇÃO",IF(K309&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M309" t="n">
+        <v>19</v>
+      </c>
+      <c r="N309" t="n">
+        <v>100</v>
+      </c>
+      <c r="O309" t="n">
+        <v>15.78947368421053</v>
+      </c>
     </row>
     <row r="310" hidden="1">
       <c r="A310" s="5" t="n">
@@ -15034,6 +16143,15 @@
         <f>IF(K310&lt;-5,"CRÍTICO",IF(K310&lt;0,"ATENÇÃO",IF(K310&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M310" t="n">
+        <v>25</v>
+      </c>
+      <c r="N310" t="n">
+        <v>100</v>
+      </c>
+      <c r="O310" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="311" hidden="1">
       <c r="A311" s="5" t="n">
@@ -15081,7 +16199,7 @@
         <v>100</v>
       </c>
       <c r="O311" s="3" t="n">
-        <v>5.88</v>
+        <v>11.76470588235294</v>
       </c>
     </row>
     <row r="312" hidden="1">
@@ -15130,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="N312" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O312" s="9" t="n">
         <v>0</v>
@@ -15176,13 +16294,13 @@
         <v/>
       </c>
       <c r="M313" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N313" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O313" s="3" t="n">
-        <v>13.04</v>
+        <v>23.07692307692308</v>
       </c>
     </row>
     <row r="314" hidden="1">
@@ -15221,6 +16339,15 @@
         <f>IF(K314&lt;-5,"CRÍTICO",IF(K314&lt;0,"ATENÇÃO",IF(K314&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M314" t="n">
+        <v>21</v>
+      </c>
+      <c r="N314" t="n">
+        <v>100</v>
+      </c>
+      <c r="O314" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="315" hidden="1">
       <c r="A315" s="5" t="n">
@@ -15261,6 +16388,15 @@
         <f>IF(K315&lt;-5,"CRÍTICO",IF(K315&lt;0,"ATENÇÃO",IF(K315&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M315" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316" hidden="1">
       <c r="A316" s="5" t="n">
@@ -15301,6 +16437,15 @@
         <f>IF(K316&lt;-5,"CRÍTICO",IF(K316&lt;0,"ATENÇÃO",IF(K316&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M316" t="n">
+        <v>19</v>
+      </c>
+      <c r="N316" t="n">
+        <v>100</v>
+      </c>
+      <c r="O316" t="n">
+        <v>36.84210526315789</v>
+      </c>
     </row>
     <row r="317" hidden="1">
       <c r="A317" s="5" t="n">
@@ -15341,6 +16486,15 @@
         <f>IF(K317&lt;-5,"CRÍTICO",IF(K317&lt;0,"ATENÇÃO",IF(K317&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M317" t="n">
+        <v>26</v>
+      </c>
+      <c r="N317" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="O317" t="n">
+        <v>26.92307692307692</v>
+      </c>
     </row>
     <row r="318" hidden="1">
       <c r="A318" s="5" t="n">
@@ -15378,6 +16532,15 @@
         <f>IF(K318&lt;-5,"CRÍTICO",IF(K318&lt;0,"ATENÇÃO",IF(K318&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M318" t="n">
+        <v>31</v>
+      </c>
+      <c r="N318" t="n">
+        <v>75</v>
+      </c>
+      <c r="O318" t="n">
+        <v>12.90322580645161</v>
+      </c>
     </row>
     <row r="319" hidden="1">
       <c r="A319" s="5" t="n">
@@ -15418,6 +16581,15 @@
         <f>IF(K319&lt;-5,"CRÍTICO",IF(K319&lt;0,"ATENÇÃO",IF(K319&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M319" t="n">
+        <v>13</v>
+      </c>
+      <c r="N319" t="n">
+        <v>100</v>
+      </c>
+      <c r="O319" t="n">
+        <v>23.07692307692308</v>
+      </c>
     </row>
     <row r="320" hidden="1">
       <c r="A320" s="5" t="n">
@@ -15458,6 +16630,15 @@
         <f>IF(K320&lt;-5,"CRÍTICO",IF(K320&lt;0,"ATENÇÃO",IF(K320&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M320" t="n">
+        <v>19</v>
+      </c>
+      <c r="N320" t="n">
+        <v>100</v>
+      </c>
+      <c r="O320" t="n">
+        <v>15.78947368421053</v>
+      </c>
     </row>
     <row r="321" hidden="1">
       <c r="A321" s="5" t="n">
@@ -15495,6 +16676,15 @@
         <f>IF(K321&lt;-5,"CRÍTICO",IF(K321&lt;0,"ATENÇÃO",IF(K321&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M321" t="n">
+        <v>21</v>
+      </c>
+      <c r="N321" t="n">
+        <v>100</v>
+      </c>
+      <c r="O321" t="n">
+        <v>76.19047619047619</v>
+      </c>
     </row>
     <row r="322" hidden="1">
       <c r="A322" s="5" t="n">
@@ -15535,6 +16725,15 @@
         <f>IF(K322&lt;-5,"CRÍTICO",IF(K322&lt;0,"ATENÇÃO",IF(K322&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M322" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323" hidden="1">
       <c r="A323" s="5" t="n">
@@ -15578,6 +16777,15 @@
         <f>IF(K323&lt;-5,"CRÍTICO",IF(K323&lt;0,"ATENÇÃO",IF(K323&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M323" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="324" hidden="1">
       <c r="A324" s="5" t="n">
@@ -15621,6 +16829,15 @@
         <f>IF(K324&lt;-5,"CRÍTICO",IF(K324&lt;0,"ATENÇÃO",IF(K324&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M324" t="n">
+        <v>0</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325" hidden="1">
       <c r="A325" s="5" t="n">
@@ -15664,6 +16881,15 @@
         <f>IF(K325&lt;-5,"CRÍTICO",IF(K325&lt;0,"ATENÇÃO",IF(K325&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M325" t="n">
+        <v>18</v>
+      </c>
+      <c r="N325" t="n">
+        <v>100</v>
+      </c>
+      <c r="O325" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="326" hidden="1">
       <c r="A326" s="5" t="n">
@@ -15704,6 +16930,15 @@
         <f>IF(K326&lt;-5,"CRÍTICO",IF(K326&lt;0,"ATENÇÃO",IF(K326&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M326" t="n">
+        <v>22</v>
+      </c>
+      <c r="N326" t="n">
+        <v>100</v>
+      </c>
+      <c r="O326" t="n">
+        <v>4.545454545454546</v>
+      </c>
     </row>
     <row r="327" hidden="1">
       <c r="A327" s="5" t="n">
@@ -15744,6 +16979,15 @@
         <f>IF(K327&lt;-5,"CRÍTICO",IF(K327&lt;0,"ATENÇÃO",IF(K327&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M327" t="n">
+        <v>37</v>
+      </c>
+      <c r="N327" t="n">
+        <v>100</v>
+      </c>
+      <c r="O327" t="n">
+        <v>27.02702702702703</v>
+      </c>
     </row>
     <row r="328" hidden="1">
       <c r="A328" s="5" t="n">
@@ -15784,6 +17028,15 @@
         <f>IF(K328&lt;-5,"CRÍTICO",IF(K328&lt;0,"ATENÇÃO",IF(K328&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M328" t="n">
+        <v>31</v>
+      </c>
+      <c r="N328" t="n">
+        <v>100</v>
+      </c>
+      <c r="O328" t="n">
+        <v>25.80645161290322</v>
+      </c>
     </row>
     <row r="329" hidden="1">
       <c r="A329" s="5" t="n">
@@ -15821,6 +17074,15 @@
         <f>IF(K329&lt;-5,"CRÍTICO",IF(K329&lt;0,"ATENÇÃO",IF(K329&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M329" t="n">
+        <v>23</v>
+      </c>
+      <c r="N329" t="n">
+        <v>100</v>
+      </c>
+      <c r="O329" t="n">
+        <v>17.39130434782609</v>
+      </c>
     </row>
     <row r="330" hidden="1">
       <c r="A330" s="5" t="n">
@@ -15864,6 +17126,15 @@
         <f>IF(K330&lt;-5,"CRÍTICO",IF(K330&lt;0,"ATENÇÃO",IF(K330&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M330" t="n">
+        <v>0</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331" hidden="1">
       <c r="A331" s="5" t="n">
@@ -15904,6 +17175,15 @@
         <f>IF(K331&lt;-5,"CRÍTICO",IF(K331&lt;0,"ATENÇÃO",IF(K331&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M331" t="n">
+        <v>18</v>
+      </c>
+      <c r="N331" t="n">
+        <v>100</v>
+      </c>
+      <c r="O331" t="n">
+        <v>16.66666666666666</v>
+      </c>
     </row>
     <row r="332" hidden="1">
       <c r="A332" s="5" t="n">
@@ -15941,6 +17221,15 @@
         <f>IF(K332&lt;-5,"CRÍTICO",IF(K332&lt;0,"ATENÇÃO",IF(K332&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M332" t="n">
+        <v>20</v>
+      </c>
+      <c r="N332" t="n">
+        <v>100</v>
+      </c>
+      <c r="O332" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="333" hidden="1">
       <c r="A333" s="5" t="n">
@@ -15984,6 +17273,15 @@
         <f>IF(K333&lt;-5,"CRÍTICO",IF(K333&lt;0,"ATENÇÃO",IF(K333&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M333" t="n">
+        <v>0</v>
+      </c>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334" hidden="1">
       <c r="A334" s="5" t="n">
@@ -16024,6 +17322,15 @@
         <f>IF(K334&lt;-5,"CRÍTICO",IF(K334&lt;0,"ATENÇÃO",IF(K334&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M334" t="n">
+        <v>26</v>
+      </c>
+      <c r="N334" t="n">
+        <v>100</v>
+      </c>
+      <c r="O334" t="n">
+        <v>23.07692307692308</v>
+      </c>
     </row>
     <row r="335" hidden="1">
       <c r="A335" s="5" t="n">
@@ -16064,6 +17371,15 @@
         <f>IF(K335&lt;-5,"CRÍTICO",IF(K335&lt;0,"ATENÇÃO",IF(K335&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M335" t="n">
+        <v>22</v>
+      </c>
+      <c r="N335" t="n">
+        <v>100</v>
+      </c>
+      <c r="O335" t="n">
+        <v>9.090909090909092</v>
+      </c>
     </row>
     <row r="336" hidden="1">
       <c r="A336" s="5" t="n">
@@ -16104,6 +17420,15 @@
         <f>IF(K336&lt;-5,"CRÍTICO",IF(K336&lt;0,"ATENÇÃO",IF(K336&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M336" t="n">
+        <v>26</v>
+      </c>
+      <c r="N336" t="n">
+        <v>100</v>
+      </c>
+      <c r="O336" t="n">
+        <v>7.692307692307693</v>
+      </c>
     </row>
     <row r="337" hidden="1">
       <c r="A337" s="5" t="n">
@@ -16147,6 +17472,15 @@
         <f>IF(K337&lt;-5,"CRÍTICO",IF(K337&lt;0,"ATENÇÃO",IF(K337&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M337" t="n">
+        <v>0</v>
+      </c>
+      <c r="N337" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="338" hidden="1">
       <c r="A338" s="5" t="n">
@@ -16187,6 +17521,15 @@
         <f>IF(K338&lt;-5,"CRÍTICO",IF(K338&lt;0,"ATENÇÃO",IF(K338&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M338" t="n">
+        <v>22</v>
+      </c>
+      <c r="N338" t="n">
+        <v>100</v>
+      </c>
+      <c r="O338" t="n">
+        <v>9.090909090909092</v>
+      </c>
     </row>
     <row r="339" hidden="1">
       <c r="A339" s="5" t="n">
@@ -16230,6 +17573,15 @@
         <f>IF(K339&lt;-5,"CRÍTICO",IF(K339&lt;0,"ATENÇÃO",IF(K339&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M339" t="n">
+        <v>18</v>
+      </c>
+      <c r="N339" t="n">
+        <v>100</v>
+      </c>
+      <c r="O339" t="n">
+        <v>27.77777777777778</v>
+      </c>
     </row>
     <row r="340" hidden="1">
       <c r="A340" s="5" t="n">
@@ -16267,6 +17619,15 @@
         <f>IF(K340&lt;-5,"CRÍTICO",IF(K340&lt;0,"ATENÇÃO",IF(K340&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M340" t="n">
+        <v>5</v>
+      </c>
+      <c r="N340" t="n">
+        <v>100</v>
+      </c>
+      <c r="O340" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="341" hidden="1">
       <c r="A341" s="5" t="n">
@@ -16304,6 +17665,15 @@
         <f>IF(K341&lt;-5,"CRÍTICO",IF(K341&lt;0,"ATENÇÃO",IF(K341&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M341" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" t="n">
+        <v>0</v>
+      </c>
+      <c r="O341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342" hidden="1">
       <c r="A342" s="5" t="n">
@@ -16347,6 +17717,15 @@
         <f>IF(K342&lt;-5,"CRÍTICO",IF(K342&lt;0,"ATENÇÃO",IF(K342&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M342" t="n">
+        <v>1</v>
+      </c>
+      <c r="N342" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="343" hidden="1">
       <c r="A343" s="5" t="n">
@@ -16384,6 +17763,15 @@
         <f>IF(K343&lt;-5,"CRÍTICO",IF(K343&lt;0,"ATENÇÃO",IF(K343&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M343" t="n">
+        <v>0</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="344" hidden="1">
       <c r="A344" s="5" t="n">
@@ -16421,6 +17809,15 @@
         <f>IF(K344&lt;-5,"CRÍTICO",IF(K344&lt;0,"ATENÇÃO",IF(K344&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M344" t="n">
+        <v>13</v>
+      </c>
+      <c r="N344" t="n">
+        <v>80</v>
+      </c>
+      <c r="O344" t="n">
+        <v>38.46153846153847</v>
+      </c>
     </row>
     <row r="345" hidden="1">
       <c r="A345" s="5" t="n">
@@ -16464,6 +17861,15 @@
         <f>IF(K345&lt;-5,"CRÍTICO",IF(K345&lt;0,"ATENÇÃO",IF(K345&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M345" t="n">
+        <v>28</v>
+      </c>
+      <c r="N345" t="n">
+        <v>100</v>
+      </c>
+      <c r="O345" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="346" hidden="1">
       <c r="A346" s="5" t="n">
@@ -16504,6 +17910,15 @@
         <f>IF(K346&lt;-5,"CRÍTICO",IF(K346&lt;0,"ATENÇÃO",IF(K346&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M346" t="n">
+        <v>29</v>
+      </c>
+      <c r="N346" t="n">
+        <v>100</v>
+      </c>
+      <c r="O346" t="n">
+        <v>24.13793103448276</v>
+      </c>
     </row>
     <row r="347" hidden="1">
       <c r="A347" s="5" t="n">
@@ -16544,6 +17959,15 @@
         <f>IF(K347&lt;-5,"CRÍTICO",IF(K347&lt;0,"ATENÇÃO",IF(K347&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M347" t="n">
+        <v>0</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="348" hidden="1">
       <c r="A348" s="5" t="n">
@@ -16581,6 +18005,15 @@
         <f>IF(K348&lt;-5,"CRÍTICO",IF(K348&lt;0,"ATENÇÃO",IF(K348&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M348" t="n">
+        <v>18</v>
+      </c>
+      <c r="N348" t="n">
+        <v>100</v>
+      </c>
+      <c r="O348" t="n">
+        <v>11.11111111111111</v>
+      </c>
     </row>
     <row r="349" hidden="1">
       <c r="A349" s="5" t="n">
@@ -16618,6 +18051,15 @@
         <f>IF(K349&lt;-5,"CRÍTICO",IF(K349&lt;0,"ATENÇÃO",IF(K349&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M349" t="n">
+        <v>0</v>
+      </c>
+      <c r="N349" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350" hidden="1">
       <c r="A350" s="5" t="n">
@@ -16658,6 +18100,15 @@
         <f>IF(K350&lt;-5,"CRÍTICO",IF(K350&lt;0,"ATENÇÃO",IF(K350&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M350" t="n">
+        <v>18</v>
+      </c>
+      <c r="N350" t="n">
+        <v>100</v>
+      </c>
+      <c r="O350" t="n">
+        <v>27.77777777777778</v>
+      </c>
     </row>
     <row r="351" hidden="1">
       <c r="A351" s="5" t="n">
@@ -16698,6 +18149,15 @@
         <f>IF(K351&lt;-5,"CRÍTICO",IF(K351&lt;0,"ATENÇÃO",IF(K351&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M351" t="n">
+        <v>0</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352" hidden="1">
       <c r="A352" s="5" t="n">
@@ -16738,6 +18198,15 @@
         <f>IF(K352&lt;-5,"CRÍTICO",IF(K352&lt;0,"ATENÇÃO",IF(K352&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M352" t="n">
+        <v>32</v>
+      </c>
+      <c r="N352" t="n">
+        <v>100</v>
+      </c>
+      <c r="O352" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="353" hidden="1">
       <c r="A353" s="5" t="n">
@@ -16778,6 +18247,15 @@
         <f>IF(K353&lt;-5,"CRÍTICO",IF(K353&lt;0,"ATENÇÃO",IF(K353&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M353" t="n">
+        <v>16</v>
+      </c>
+      <c r="N353" t="n">
+        <v>100</v>
+      </c>
+      <c r="O353" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="354" hidden="1">
       <c r="A354" s="5" t="n">
@@ -16815,6 +18293,15 @@
         <f>IF(K354&lt;-5,"CRÍTICO",IF(K354&lt;0,"ATENÇÃO",IF(K354&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M354" t="n">
+        <v>21</v>
+      </c>
+      <c r="N354" t="n">
+        <v>100</v>
+      </c>
+      <c r="O354" t="n">
+        <v>28.57142857142857</v>
+      </c>
     </row>
     <row r="355" hidden="1">
       <c r="A355" s="5" t="n">
@@ -16865,7 +18352,7 @@
         <v>100</v>
       </c>
       <c r="O355" s="3" t="n">
-        <v>17.39</v>
+        <v>52.17391304347826</v>
       </c>
     </row>
     <row r="356" hidden="1">
@@ -16914,7 +18401,7 @@
         <v>0</v>
       </c>
       <c r="N356" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O356" s="9" t="n">
         <v>0</v>
@@ -16963,13 +18450,13 @@
         <v/>
       </c>
       <c r="M357" s="3" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O357" s="3" t="n">
-        <v>11.11</v>
+        <v>43.47826086956522</v>
       </c>
     </row>
     <row r="358" hidden="1">
@@ -17014,6 +18501,15 @@
         <f>IF(K358&lt;-5,"CRÍTICO",IF(K358&lt;0,"ATENÇÃO",IF(K358&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M358" t="n">
+        <v>27</v>
+      </c>
+      <c r="N358" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="O358" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="359" hidden="1">
       <c r="A359" s="5" t="n">
@@ -17057,6 +18553,15 @@
         <f>IF(K359&lt;-5,"CRÍTICO",IF(K359&lt;0,"ATENÇÃO",IF(K359&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M359" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360" hidden="1">
       <c r="A360" s="5" t="n">
@@ -17100,6 +18605,15 @@
         <f>IF(K360&lt;-5,"CRÍTICO",IF(K360&lt;0,"ATENÇÃO",IF(K360&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M360" t="n">
+        <v>25</v>
+      </c>
+      <c r="N360" t="n">
+        <v>100</v>
+      </c>
+      <c r="O360" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="361" hidden="1">
       <c r="A361" s="5" t="n">
@@ -17143,6 +18657,15 @@
         <f>IF(K361&lt;-5,"CRÍTICO",IF(K361&lt;0,"ATENÇÃO",IF(K361&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M361" t="n">
+        <v>30</v>
+      </c>
+      <c r="N361" t="n">
+        <v>100</v>
+      </c>
+      <c r="O361" t="n">
+        <v>16.66666666666666</v>
+      </c>
     </row>
     <row r="362" hidden="1">
       <c r="A362" s="5" t="n">
@@ -17186,6 +18709,15 @@
         <f>IF(K362&lt;-5,"CRÍTICO",IF(K362&lt;0,"ATENÇÃO",IF(K362&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M362" t="n">
+        <v>14</v>
+      </c>
+      <c r="N362" t="n">
+        <v>100</v>
+      </c>
+      <c r="O362" t="n">
+        <v>107.1428571428571</v>
+      </c>
     </row>
     <row r="363" hidden="1">
       <c r="A363" s="5" t="n">
@@ -17229,6 +18761,15 @@
         <f>IF(K363&lt;-5,"CRÍTICO",IF(K363&lt;0,"ATENÇÃO",IF(K363&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M363" t="n">
+        <v>17</v>
+      </c>
+      <c r="N363" t="n">
+        <v>100</v>
+      </c>
+      <c r="O363" t="n">
+        <v>70.58823529411765</v>
+      </c>
     </row>
     <row r="364" hidden="1">
       <c r="A364" s="5" t="n">
@@ -17272,6 +18813,15 @@
         <f>IF(K364&lt;-5,"CRÍTICO",IF(K364&lt;0,"ATENÇÃO",IF(K364&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M364" t="n">
+        <v>20</v>
+      </c>
+      <c r="N364" t="n">
+        <v>100</v>
+      </c>
+      <c r="O364" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="365" hidden="1">
       <c r="A365" s="5" t="n">
@@ -17315,6 +18865,15 @@
         <f>IF(K365&lt;-5,"CRÍTICO",IF(K365&lt;0,"ATENÇÃO",IF(K365&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M365" t="n">
+        <v>26</v>
+      </c>
+      <c r="N365" t="n">
+        <v>100</v>
+      </c>
+      <c r="O365" t="n">
+        <v>26.92307692307692</v>
+      </c>
     </row>
     <row r="366" hidden="1">
       <c r="A366" s="5" t="n">
@@ -17358,6 +18917,15 @@
         <f>IF(K366&lt;-5,"CRÍTICO",IF(K366&lt;0,"ATENÇÃO",IF(K366&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M366" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367" hidden="1">
       <c r="A367" s="5" t="n">
@@ -17401,6 +18969,15 @@
         <f>IF(K367&lt;-5,"CRÍTICO",IF(K367&lt;0,"ATENÇÃO",IF(K367&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M367" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" t="n">
+        <v>100</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="368" hidden="1">
       <c r="A368" s="5" t="n">
@@ -17444,6 +19021,15 @@
         <f>IF(K368&lt;-5,"CRÍTICO",IF(K368&lt;0,"ATENÇÃO",IF(K368&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M368" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" t="n">
+        <v>100</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369" hidden="1">
       <c r="A369" s="5" t="n">
@@ -17487,6 +19073,15 @@
         <f>IF(K369&lt;-5,"CRÍTICO",IF(K369&lt;0,"ATENÇÃO",IF(K369&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M369" t="n">
+        <v>23</v>
+      </c>
+      <c r="N369" t="n">
+        <v>100</v>
+      </c>
+      <c r="O369" t="n">
+        <v>34.78260869565217</v>
+      </c>
     </row>
     <row r="370" hidden="1">
       <c r="A370" s="5" t="n">
@@ -17530,6 +19125,15 @@
         <f>IF(K370&lt;-5,"CRÍTICO",IF(K370&lt;0,"ATENÇÃO",IF(K370&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M370" t="n">
+        <v>13</v>
+      </c>
+      <c r="N370" t="n">
+        <v>100</v>
+      </c>
+      <c r="O370" t="n">
+        <v>30.76923076923077</v>
+      </c>
     </row>
     <row r="371" hidden="1">
       <c r="A371" s="5" t="n">
@@ -17573,6 +19177,15 @@
         <f>IF(K371&lt;-5,"CRÍTICO",IF(K371&lt;0,"ATENÇÃO",IF(K371&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M371" t="n">
+        <v>38</v>
+      </c>
+      <c r="N371" t="n">
+        <v>100</v>
+      </c>
+      <c r="O371" t="n">
+        <v>31.57894736842105</v>
+      </c>
     </row>
     <row r="372" hidden="1">
       <c r="A372" s="5" t="n">
@@ -17616,6 +19229,15 @@
         <f>IF(K372&lt;-5,"CRÍTICO",IF(K372&lt;0,"ATENÇÃO",IF(K372&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M372" t="n">
+        <v>44</v>
+      </c>
+      <c r="N372" t="n">
+        <v>100</v>
+      </c>
+      <c r="O372" t="n">
+        <v>27.27272727272727</v>
+      </c>
     </row>
     <row r="373" hidden="1">
       <c r="A373" s="5" t="n">
@@ -17659,6 +19281,15 @@
         <f>IF(K373&lt;-5,"CRÍTICO",IF(K373&lt;0,"ATENÇÃO",IF(K373&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M373" t="n">
+        <v>9</v>
+      </c>
+      <c r="N373" t="n">
+        <v>100</v>
+      </c>
+      <c r="O373" t="n">
+        <v>66.66666666666666</v>
+      </c>
     </row>
     <row r="374" hidden="1">
       <c r="A374" s="5" t="n">
@@ -17702,6 +19333,15 @@
         <f>IF(K374&lt;-5,"CRÍTICO",IF(K374&lt;0,"ATENÇÃO",IF(K374&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M374" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375" hidden="1">
       <c r="A375" s="5" t="n">
@@ -17745,6 +19385,15 @@
         <f>IF(K375&lt;-5,"CRÍTICO",IF(K375&lt;0,"ATENÇÃO",IF(K375&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M375" t="n">
+        <v>22</v>
+      </c>
+      <c r="N375" t="n">
+        <v>100</v>
+      </c>
+      <c r="O375" t="n">
+        <v>27.27272727272727</v>
+      </c>
     </row>
     <row r="376" hidden="1">
       <c r="A376" s="5" t="n">
@@ -17788,6 +19437,15 @@
         <f>IF(K376&lt;-5,"CRÍTICO",IF(K376&lt;0,"ATENÇÃO",IF(K376&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M376" t="n">
+        <v>28</v>
+      </c>
+      <c r="N376" t="n">
+        <v>75</v>
+      </c>
+      <c r="O376" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="377" hidden="1">
       <c r="A377" s="5" t="n">
@@ -17831,6 +19489,15 @@
         <f>IF(K377&lt;-5,"CRÍTICO",IF(K377&lt;0,"ATENÇÃO",IF(K377&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M377" t="n">
+        <v>9</v>
+      </c>
+      <c r="N377" t="n">
+        <v>100</v>
+      </c>
+      <c r="O377" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="378" hidden="1">
       <c r="A378" s="5" t="n">
@@ -17874,6 +19541,15 @@
         <f>IF(K378&lt;-5,"CRÍTICO",IF(K378&lt;0,"ATENÇÃO",IF(K378&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M378" t="n">
+        <v>23</v>
+      </c>
+      <c r="N378" t="n">
+        <v>100</v>
+      </c>
+      <c r="O378" t="n">
+        <v>43.47826086956522</v>
+      </c>
     </row>
     <row r="379" hidden="1">
       <c r="A379" s="5" t="n">
@@ -17917,6 +19593,15 @@
         <f>IF(K379&lt;-5,"CRÍTICO",IF(K379&lt;0,"ATENÇÃO",IF(K379&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M379" t="n">
+        <v>12</v>
+      </c>
+      <c r="N379" t="n">
+        <v>100</v>
+      </c>
+      <c r="O379" t="n">
+        <v>91.66666666666666</v>
+      </c>
     </row>
     <row r="380" hidden="1">
       <c r="A380" s="5" t="n">
@@ -17960,6 +19645,15 @@
         <f>IF(K380&lt;-5,"CRÍTICO",IF(K380&lt;0,"ATENÇÃO",IF(K380&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M380" t="n">
+        <v>16</v>
+      </c>
+      <c r="N380" t="n">
+        <v>100</v>
+      </c>
+      <c r="O380" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="381" hidden="1">
       <c r="A381" s="5" t="n">
@@ -18003,6 +19697,15 @@
         <f>IF(K381&lt;-5,"CRÍTICO",IF(K381&lt;0,"ATENÇÃO",IF(K381&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M381" t="n">
+        <v>0</v>
+      </c>
+      <c r="N381" t="n">
+        <v>100</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382" hidden="1">
       <c r="A382" s="5" t="n">
@@ -18046,6 +19749,15 @@
         <f>IF(K382&lt;-5,"CRÍTICO",IF(K382&lt;0,"ATENÇÃO",IF(K382&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M382" t="n">
+        <v>16</v>
+      </c>
+      <c r="N382" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="O382" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="383" hidden="1">
       <c r="A383" s="5" t="n">
@@ -18089,6 +19801,15 @@
         <f>IF(K383&lt;-5,"CRÍTICO",IF(K383&lt;0,"ATENÇÃO",IF(K383&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M383" t="n">
+        <v>26</v>
+      </c>
+      <c r="N383" t="n">
+        <v>90</v>
+      </c>
+      <c r="O383" t="n">
+        <v>38.46153846153847</v>
+      </c>
     </row>
     <row r="384" hidden="1">
       <c r="A384" s="5" t="n">
@@ -18132,6 +19853,15 @@
         <f>IF(K384&lt;-5,"CRÍTICO",IF(K384&lt;0,"ATENÇÃO",IF(K384&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M384" t="n">
+        <v>30</v>
+      </c>
+      <c r="N384" t="n">
+        <v>100</v>
+      </c>
+      <c r="O384" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="385" hidden="1">
       <c r="A385" s="5" t="n">
@@ -18175,6 +19905,15 @@
         <f>IF(K385&lt;-5,"CRÍTICO",IF(K385&lt;0,"ATENÇÃO",IF(K385&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M385" t="n">
+        <v>29</v>
+      </c>
+      <c r="N385" t="n">
+        <v>100</v>
+      </c>
+      <c r="O385" t="n">
+        <v>37.93103448275862</v>
+      </c>
     </row>
     <row r="386" hidden="1">
       <c r="A386" s="5" t="n">
@@ -18218,6 +19957,15 @@
         <f>IF(K386&lt;-5,"CRÍTICO",IF(K386&lt;0,"ATENÇÃO",IF(K386&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M386" t="n">
+        <v>6</v>
+      </c>
+      <c r="N386" t="n">
+        <v>100</v>
+      </c>
+      <c r="O386" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="387" hidden="1">
       <c r="A387" s="5" t="n">
@@ -18261,6 +20009,15 @@
         <f>IF(K387&lt;-5,"CRÍTICO",IF(K387&lt;0,"ATENÇÃO",IF(K387&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M387" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388" hidden="1">
       <c r="A388" s="5" t="n">
@@ -18304,6 +20061,15 @@
         <f>IF(K388&lt;-5,"CRÍTICO",IF(K388&lt;0,"ATENÇÃO",IF(K388&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M388" t="n">
+        <v>2</v>
+      </c>
+      <c r="N388" t="n">
+        <v>100</v>
+      </c>
+      <c r="O388" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="389" hidden="1">
       <c r="A389" s="5" t="n">
@@ -18347,6 +20113,15 @@
         <f>IF(K389&lt;-5,"CRÍTICO",IF(K389&lt;0,"ATENÇÃO",IF(K389&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M389" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390" hidden="1">
       <c r="A390" s="5" t="n">
@@ -18390,6 +20165,15 @@
         <f>IF(K390&lt;-5,"CRÍTICO",IF(K390&lt;0,"ATENÇÃO",IF(K390&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M390" t="n">
+        <v>15</v>
+      </c>
+      <c r="N390" t="n">
+        <v>100</v>
+      </c>
+      <c r="O390" t="n">
+        <v>46.66666666666666</v>
+      </c>
     </row>
     <row r="391" hidden="1">
       <c r="A391" s="5" t="n">
@@ -18433,6 +20217,15 @@
         <f>IF(K391&lt;-5,"CRÍTICO",IF(K391&lt;0,"ATENÇÃO",IF(K391&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392" hidden="1">
       <c r="A392" s="5" t="n">
@@ -18476,6 +20269,15 @@
         <f>IF(K392&lt;-5,"CRÍTICO",IF(K392&lt;0,"ATENÇÃO",IF(K392&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M392" t="n">
+        <v>23</v>
+      </c>
+      <c r="N392" t="n">
+        <v>100</v>
+      </c>
+      <c r="O392" t="n">
+        <v>17.39130434782609</v>
+      </c>
     </row>
     <row r="393" hidden="1">
       <c r="A393" s="5" t="n">
@@ -18519,6 +20321,15 @@
         <f>IF(K393&lt;-5,"CRÍTICO",IF(K393&lt;0,"ATENÇÃO",IF(K393&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M393" t="n">
+        <v>0</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394" hidden="1">
       <c r="A394" s="5" t="n">
@@ -18562,6 +20373,15 @@
         <f>IF(K394&lt;-5,"CRÍTICO",IF(K394&lt;0,"ATENÇÃO",IF(K394&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M394" t="n">
+        <v>5</v>
+      </c>
+      <c r="N394" t="n">
+        <v>100</v>
+      </c>
+      <c r="O394" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="395" hidden="1">
       <c r="A395" s="5" t="n">
@@ -18605,6 +20425,15 @@
         <f>IF(K395&lt;-5,"CRÍTICO",IF(K395&lt;0,"ATENÇÃO",IF(K395&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M395" t="n">
+        <v>0</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396" hidden="1">
       <c r="A396" s="5" t="n">
@@ -18648,6 +20477,15 @@
         <f>IF(K396&lt;-5,"CRÍTICO",IF(K396&lt;0,"ATENÇÃO",IF(K396&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M396" t="n">
+        <v>40</v>
+      </c>
+      <c r="N396" t="n">
+        <v>100</v>
+      </c>
+      <c r="O396" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="397" hidden="1">
       <c r="A397" s="5" t="n">
@@ -18691,6 +20529,15 @@
         <f>IF(K397&lt;-5,"CRÍTICO",IF(K397&lt;0,"ATENÇÃO",IF(K397&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M397" t="n">
+        <v>17</v>
+      </c>
+      <c r="N397" t="n">
+        <v>100</v>
+      </c>
+      <c r="O397" t="n">
+        <v>17.64705882352941</v>
+      </c>
     </row>
     <row r="398" hidden="1">
       <c r="A398" s="5" t="n">
@@ -18734,6 +20581,15 @@
         <f>IF(K398&lt;-5,"CRÍTICO",IF(K398&lt;0,"ATENÇÃO",IF(K398&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M398" t="n">
+        <v>21</v>
+      </c>
+      <c r="N398" t="n">
+        <v>100</v>
+      </c>
+      <c r="O398" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="399" hidden="1">
       <c r="A399" s="5" t="n">
@@ -18784,7 +20640,7 @@
         <v>100</v>
       </c>
       <c r="O399" s="3" t="n">
-        <v>8.33</v>
+        <v>8.333333333333332</v>
       </c>
     </row>
     <row r="400" hidden="1">
@@ -18833,7 +20689,7 @@
         <v>0</v>
       </c>
       <c r="N400" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O400" s="9" t="n">
         <v>0</v>
@@ -18882,13 +20738,13 @@
         <v/>
       </c>
       <c r="M401" s="3" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="N401" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O401" s="3" t="n">
-        <v>27.78</v>
+        <v>16.66666666666666</v>
       </c>
     </row>
     <row r="402" hidden="1">
@@ -18933,6 +20789,15 @@
         <f>IF(K402&lt;-5,"CRÍTICO",IF(K402&lt;0,"ATENÇÃO",IF(K402&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M402" t="n">
+        <v>25</v>
+      </c>
+      <c r="N402" t="n">
+        <v>100</v>
+      </c>
+      <c r="O402" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="403" hidden="1">
       <c r="A403" s="5" t="n">
@@ -18976,6 +20841,15 @@
         <f>IF(K403&lt;-5,"CRÍTICO",IF(K403&lt;0,"ATENÇÃO",IF(K403&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M403" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="404" hidden="1">
       <c r="A404" s="5" t="n">
@@ -19019,6 +20893,15 @@
         <f>IF(K404&lt;-5,"CRÍTICO",IF(K404&lt;0,"ATENÇÃO",IF(K404&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M404" t="n">
+        <v>29</v>
+      </c>
+      <c r="N404" t="n">
+        <v>100</v>
+      </c>
+      <c r="O404" t="n">
+        <v>13.79310344827586</v>
+      </c>
     </row>
     <row r="405" hidden="1">
       <c r="A405" s="5" t="n">
@@ -19062,6 +20945,15 @@
         <f>IF(K405&lt;-5,"CRÍTICO",IF(K405&lt;0,"ATENÇÃO",IF(K405&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M405" t="n">
+        <v>20</v>
+      </c>
+      <c r="N405" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="O405" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="406" hidden="1">
       <c r="A406" s="5" t="n">
@@ -19105,6 +20997,15 @@
         <f>IF(K406&lt;-5,"CRÍTICO",IF(K406&lt;0,"ATENÇÃO",IF(K406&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M406" t="n">
+        <v>29</v>
+      </c>
+      <c r="N406" t="n">
+        <v>100</v>
+      </c>
+      <c r="O406" t="n">
+        <v>6.896551724137931</v>
+      </c>
     </row>
     <row r="407" hidden="1">
       <c r="A407" s="5" t="n">
@@ -19148,6 +21049,15 @@
         <f>IF(K407&lt;-5,"CRÍTICO",IF(K407&lt;0,"ATENÇÃO",IF(K407&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M407" t="n">
+        <v>30</v>
+      </c>
+      <c r="N407" t="n">
+        <v>100</v>
+      </c>
+      <c r="O407" t="n">
+        <v>3.333333333333333</v>
+      </c>
     </row>
     <row r="408" hidden="1">
       <c r="A408" s="5" t="n">
@@ -19191,6 +21101,15 @@
         <f>IF(K408&lt;-5,"CRÍTICO",IF(K408&lt;0,"ATENÇÃO",IF(K408&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M408" t="n">
+        <v>19</v>
+      </c>
+      <c r="N408" t="n">
+        <v>100</v>
+      </c>
+      <c r="O408" t="n">
+        <v>15.78947368421053</v>
+      </c>
     </row>
     <row r="409" hidden="1">
       <c r="A409" s="5" t="n">
@@ -19234,6 +21153,15 @@
         <f>IF(K409&lt;-5,"CRÍTICO",IF(K409&lt;0,"ATENÇÃO",IF(K409&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M409" t="n">
+        <v>23</v>
+      </c>
+      <c r="N409" t="n">
+        <v>100</v>
+      </c>
+      <c r="O409" t="n">
+        <v>13.04347826086956</v>
+      </c>
     </row>
     <row r="410" hidden="1">
       <c r="A410" s="5" t="n">
@@ -19277,6 +21205,15 @@
         <f>IF(K410&lt;-5,"CRÍTICO",IF(K410&lt;0,"ATENÇÃO",IF(K410&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="411" hidden="1">
       <c r="A411" s="5" t="n">
@@ -19320,6 +21257,15 @@
         <f>IF(K411&lt;-5,"CRÍTICO",IF(K411&lt;0,"ATENÇÃO",IF(K411&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="412" hidden="1">
       <c r="A412" s="5" t="n">
@@ -19363,6 +21309,15 @@
         <f>IF(K412&lt;-5,"CRÍTICO",IF(K412&lt;0,"ATENÇÃO",IF(K412&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M412" t="n">
+        <v>15</v>
+      </c>
+      <c r="N412" t="n">
+        <v>100</v>
+      </c>
+      <c r="O412" t="n">
+        <v>13.33333333333333</v>
+      </c>
     </row>
     <row r="413" hidden="1">
       <c r="A413" s="5" t="n">
@@ -19406,6 +21361,15 @@
         <f>IF(K413&lt;-5,"CRÍTICO",IF(K413&lt;0,"ATENÇÃO",IF(K413&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M413" t="n">
+        <v>23</v>
+      </c>
+      <c r="N413" t="n">
+        <v>100</v>
+      </c>
+      <c r="O413" t="n">
+        <v>13.04347826086956</v>
+      </c>
     </row>
     <row r="414" hidden="1">
       <c r="A414" s="5" t="n">
@@ -19449,6 +21413,15 @@
         <f>IF(K414&lt;-5,"CRÍTICO",IF(K414&lt;0,"ATENÇÃO",IF(K414&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M414" t="n">
+        <v>39</v>
+      </c>
+      <c r="N414" t="n">
+        <v>100</v>
+      </c>
+      <c r="O414" t="n">
+        <v>20.51282051282051</v>
+      </c>
     </row>
     <row r="415" hidden="1">
       <c r="A415" s="5" t="n">
@@ -19492,6 +21465,15 @@
         <f>IF(K415&lt;-5,"CRÍTICO",IF(K415&lt;0,"ATENÇÃO",IF(K415&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M415" t="n">
+        <v>23</v>
+      </c>
+      <c r="N415" t="n">
+        <v>100</v>
+      </c>
+      <c r="O415" t="n">
+        <v>21.73913043478261</v>
+      </c>
     </row>
     <row r="416" hidden="1">
       <c r="A416" s="5" t="n">
@@ -19535,6 +21517,15 @@
         <f>IF(K416&lt;-5,"CRÍTICO",IF(K416&lt;0,"ATENÇÃO",IF(K416&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M416" t="n">
+        <v>14</v>
+      </c>
+      <c r="N416" t="n">
+        <v>100</v>
+      </c>
+      <c r="O416" t="n">
+        <v>28.57142857142857</v>
+      </c>
     </row>
     <row r="417" hidden="1">
       <c r="A417" s="5" t="n">
@@ -19578,6 +21569,15 @@
         <f>IF(K417&lt;-5,"CRÍTICO",IF(K417&lt;0,"ATENÇÃO",IF(K417&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M417" t="n">
+        <v>0</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="418" hidden="1">
       <c r="A418" s="5" t="n">
@@ -19621,6 +21621,15 @@
         <f>IF(K418&lt;-5,"CRÍTICO",IF(K418&lt;0,"ATENÇÃO",IF(K418&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M418" t="n">
+        <v>23</v>
+      </c>
+      <c r="N418" t="n">
+        <v>100</v>
+      </c>
+      <c r="O418" t="n">
+        <v>13.04347826086956</v>
+      </c>
     </row>
     <row r="419" hidden="1">
       <c r="A419" s="5" t="n">
@@ -19664,6 +21673,15 @@
         <f>IF(K419&lt;-5,"CRÍTICO",IF(K419&lt;0,"ATENÇÃO",IF(K419&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M419" t="n">
+        <v>11</v>
+      </c>
+      <c r="N419" t="n">
+        <v>100</v>
+      </c>
+      <c r="O419" t="n">
+        <v>9.090909090909092</v>
+      </c>
     </row>
     <row r="420" hidden="1">
       <c r="A420" s="5" t="n">
@@ -19707,6 +21725,15 @@
         <f>IF(K420&lt;-5,"CRÍTICO",IF(K420&lt;0,"ATENÇÃO",IF(K420&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M420" t="n">
+        <v>19</v>
+      </c>
+      <c r="N420" t="n">
+        <v>100</v>
+      </c>
+      <c r="O420" t="n">
+        <v>36.84210526315789</v>
+      </c>
     </row>
     <row r="421" hidden="1">
       <c r="A421" s="5" t="n">
@@ -19750,6 +21777,15 @@
         <f>IF(K421&lt;-5,"CRÍTICO",IF(K421&lt;0,"ATENÇÃO",IF(K421&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M421" t="n">
+        <v>13</v>
+      </c>
+      <c r="N421" t="n">
+        <v>100</v>
+      </c>
+      <c r="O421" t="n">
+        <v>15.38461538461539</v>
+      </c>
     </row>
     <row r="422" hidden="1">
       <c r="A422" s="5" t="n">
@@ -19793,6 +21829,15 @@
         <f>IF(K422&lt;-5,"CRÍTICO",IF(K422&lt;0,"ATENÇÃO",IF(K422&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M422" t="n">
+        <v>24</v>
+      </c>
+      <c r="N422" t="n">
+        <v>100</v>
+      </c>
+      <c r="O422" t="n">
+        <v>16.66666666666666</v>
+      </c>
     </row>
     <row r="423" hidden="1">
       <c r="A423" s="5" t="n">
@@ -19836,6 +21881,15 @@
         <f>IF(K423&lt;-5,"CRÍTICO",IF(K423&lt;0,"ATENÇÃO",IF(K423&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M423" t="n">
+        <v>0</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="424" hidden="1">
       <c r="A424" s="5" t="n">
@@ -19879,6 +21933,15 @@
         <f>IF(K424&lt;-5,"CRÍTICO",IF(K424&lt;0,"ATENÇÃO",IF(K424&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M424" t="n">
+        <v>24</v>
+      </c>
+      <c r="N424" t="n">
+        <v>100</v>
+      </c>
+      <c r="O424" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="425" hidden="1">
       <c r="A425" s="5" t="n">
@@ -19922,6 +21985,15 @@
         <f>IF(K425&lt;-5,"CRÍTICO",IF(K425&lt;0,"ATENÇÃO",IF(K425&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M425" t="n">
+        <v>19</v>
+      </c>
+      <c r="N425" t="n">
+        <v>100</v>
+      </c>
+      <c r="O425" t="n">
+        <v>10.52631578947368</v>
+      </c>
     </row>
     <row r="426" hidden="1">
       <c r="A426" s="5" t="n">
@@ -19965,6 +22037,15 @@
         <f>IF(K426&lt;-5,"CRÍTICO",IF(K426&lt;0,"ATENÇÃO",IF(K426&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M426" t="n">
+        <v>22</v>
+      </c>
+      <c r="N426" t="n">
+        <v>100</v>
+      </c>
+      <c r="O426" t="n">
+        <v>36.36363636363637</v>
+      </c>
     </row>
     <row r="427" hidden="1">
       <c r="A427" s="5" t="n">
@@ -20008,6 +22089,15 @@
         <f>IF(K427&lt;-5,"CRÍTICO",IF(K427&lt;0,"ATENÇÃO",IF(K427&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M427" t="n">
+        <v>34</v>
+      </c>
+      <c r="N427" t="n">
+        <v>100</v>
+      </c>
+      <c r="O427" t="n">
+        <v>11.76470588235294</v>
+      </c>
     </row>
     <row r="428" hidden="1">
       <c r="A428" s="5" t="n">
@@ -20051,6 +22141,15 @@
         <f>IF(K428&lt;-5,"CRÍTICO",IF(K428&lt;0,"ATENÇÃO",IF(K428&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M428" t="n">
+        <v>8</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="429" hidden="1">
       <c r="A429" s="5" t="n">
@@ -20094,6 +22193,15 @@
         <f>IF(K429&lt;-5,"CRÍTICO",IF(K429&lt;0,"ATENÇÃO",IF(K429&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M429" t="n">
+        <v>0</v>
+      </c>
+      <c r="N429" t="n">
+        <v>100</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="430" hidden="1">
       <c r="A430" s="5" t="n">
@@ -20137,6 +22245,15 @@
         <f>IF(K430&lt;-5,"CRÍTICO",IF(K430&lt;0,"ATENÇÃO",IF(K430&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M430" t="n">
+        <v>0</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="431" hidden="1">
       <c r="A431" s="5" t="n">
@@ -20180,6 +22297,15 @@
         <f>IF(K431&lt;-5,"CRÍTICO",IF(K431&lt;0,"ATENÇÃO",IF(K431&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M431" t="n">
+        <v>1</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="432" hidden="1">
       <c r="A432" s="5" t="n">
@@ -20223,6 +22349,15 @@
         <f>IF(K432&lt;-5,"CRÍTICO",IF(K432&lt;0,"ATENÇÃO",IF(K432&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M432" t="n">
+        <v>0</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="433" hidden="1">
       <c r="A433" s="5" t="n">
@@ -20266,6 +22401,15 @@
         <f>IF(K433&lt;-5,"CRÍTICO",IF(K433&lt;0,"ATENÇÃO",IF(K433&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M433" t="n">
+        <v>14</v>
+      </c>
+      <c r="N433" t="n">
+        <v>100</v>
+      </c>
+      <c r="O433" t="n">
+        <v>21.42857142857143</v>
+      </c>
     </row>
     <row r="434" hidden="1">
       <c r="A434" s="5" t="n">
@@ -20309,6 +22453,15 @@
         <f>IF(K434&lt;-5,"CRÍTICO",IF(K434&lt;0,"ATENÇÃO",IF(K434&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M434" t="n">
+        <v>0</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="435" hidden="1">
       <c r="A435" s="5" t="n">
@@ -20352,6 +22505,15 @@
         <f>IF(K435&lt;-5,"CRÍTICO",IF(K435&lt;0,"ATENÇÃO",IF(K435&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M435" t="n">
+        <v>12</v>
+      </c>
+      <c r="N435" t="n">
+        <v>100</v>
+      </c>
+      <c r="O435" t="n">
+        <v>16.66666666666666</v>
+      </c>
     </row>
     <row r="436" hidden="1">
       <c r="A436" s="5" t="n">
@@ -20395,6 +22557,15 @@
         <f>IF(K436&lt;-5,"CRÍTICO",IF(K436&lt;0,"ATENÇÃO",IF(K436&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M436" t="n">
+        <v>0</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="437" hidden="1">
       <c r="A437" s="5" t="n">
@@ -20438,6 +22609,15 @@
         <f>IF(K437&lt;-5,"CRÍTICO",IF(K437&lt;0,"ATENÇÃO",IF(K437&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M437" t="n">
+        <v>15</v>
+      </c>
+      <c r="N437" t="n">
+        <v>100</v>
+      </c>
+      <c r="O437" t="n">
+        <v>6.666666666666667</v>
+      </c>
     </row>
     <row r="438" hidden="1">
       <c r="A438" s="5" t="n">
@@ -20481,6 +22661,15 @@
         <f>IF(K438&lt;-5,"CRÍTICO",IF(K438&lt;0,"ATENÇÃO",IF(K438&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M438" t="n">
+        <v>0</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="439" hidden="1">
       <c r="A439" s="5" t="n">
@@ -20524,6 +22713,15 @@
         <f>IF(K439&lt;-5,"CRÍTICO",IF(K439&lt;0,"ATENÇÃO",IF(K439&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M439" t="n">
+        <v>29</v>
+      </c>
+      <c r="N439" t="n">
+        <v>100</v>
+      </c>
+      <c r="O439" t="n">
+        <v>31.03448275862069</v>
+      </c>
     </row>
     <row r="440" hidden="1">
       <c r="A440" s="5" t="n">
@@ -20567,6 +22765,15 @@
         <f>IF(K440&lt;-5,"CRÍTICO",IF(K440&lt;0,"ATENÇÃO",IF(K440&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M440" t="n">
+        <v>14</v>
+      </c>
+      <c r="N440" t="n">
+        <v>100</v>
+      </c>
+      <c r="O440" t="n">
+        <v>7.142857142857142</v>
+      </c>
     </row>
     <row r="441" hidden="1">
       <c r="A441" s="5" t="n">
@@ -20610,6 +22817,15 @@
         <f>IF(K441&lt;-5,"CRÍTICO",IF(K441&lt;0,"ATENÇÃO",IF(K441&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M441" t="n">
+        <v>17</v>
+      </c>
+      <c r="N441" t="n">
+        <v>100</v>
+      </c>
+      <c r="O441" t="n">
+        <v>5.88235294117647</v>
+      </c>
     </row>
     <row r="442" hidden="1">
       <c r="A442" s="5" t="n">
@@ -20660,7 +22876,7 @@
         <v>100</v>
       </c>
       <c r="O442" s="3" t="n">
-        <v>10.53</v>
+        <v>42.10526315789473</v>
       </c>
     </row>
     <row r="443" hidden="1">
@@ -20709,7 +22925,7 @@
         <v>0</v>
       </c>
       <c r="N443" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O443" s="9" t="n">
         <v>0</v>
@@ -20758,13 +22974,13 @@
         <v/>
       </c>
       <c r="M444" s="3" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N444" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O444" s="3" t="n">
-        <v>17.24</v>
+        <v>83.33333333333334</v>
       </c>
     </row>
     <row r="445" hidden="1">
@@ -20809,6 +23025,15 @@
         <f>IF(K445&lt;-5,"CRÍTICO",IF(K445&lt;0,"ATENÇÃO",IF(K445&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M445" t="n">
+        <v>0</v>
+      </c>
+      <c r="N445" t="n">
+        <v>100</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="446" hidden="1">
       <c r="A446" s="5" t="n">
@@ -20852,6 +23077,15 @@
         <f>IF(K446&lt;-5,"CRÍTICO",IF(K446&lt;0,"ATENÇÃO",IF(K446&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M446" t="n">
+        <v>28</v>
+      </c>
+      <c r="N446" t="n">
+        <v>100</v>
+      </c>
+      <c r="O446" t="n">
+        <v>21.42857142857143</v>
+      </c>
     </row>
     <row r="447" hidden="1">
       <c r="A447" s="5" t="n">
@@ -20895,6 +23129,15 @@
         <f>IF(K447&lt;-5,"CRÍTICO",IF(K447&lt;0,"ATENÇÃO",IF(K447&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M447" t="n">
+        <v>0</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="448" hidden="1">
       <c r="A448" s="5" t="n">
@@ -20938,6 +23181,15 @@
         <f>IF(K448&lt;-5,"CRÍTICO",IF(K448&lt;0,"ATENÇÃO",IF(K448&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M448" t="n">
+        <v>26</v>
+      </c>
+      <c r="N448" t="n">
+        <v>100</v>
+      </c>
+      <c r="O448" t="n">
+        <v>15.38461538461539</v>
+      </c>
     </row>
     <row r="449" hidden="1">
       <c r="A449" s="5" t="n">
@@ -20981,6 +23233,15 @@
         <f>IF(K449&lt;-5,"CRÍTICO",IF(K449&lt;0,"ATENÇÃO",IF(K449&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M449" t="n">
+        <v>22</v>
+      </c>
+      <c r="N449" t="n">
+        <v>100</v>
+      </c>
+      <c r="O449" t="n">
+        <v>31.81818181818182</v>
+      </c>
     </row>
     <row r="450" hidden="1">
       <c r="A450" s="5" t="n">
@@ -21024,6 +23285,15 @@
         <f>IF(K450&lt;-5,"CRÍTICO",IF(K450&lt;0,"ATENÇÃO",IF(K450&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M450" t="n">
+        <v>25</v>
+      </c>
+      <c r="N450" t="n">
+        <v>75</v>
+      </c>
+      <c r="O450" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="451" hidden="1">
       <c r="A451" s="5" t="n">
@@ -21067,6 +23337,15 @@
         <f>IF(K451&lt;-5,"CRÍTICO",IF(K451&lt;0,"ATENÇÃO",IF(K451&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M451" t="n">
+        <v>0</v>
+      </c>
+      <c r="N451" t="n">
+        <v>100</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="452" hidden="1">
       <c r="A452" s="5" t="n">
@@ -21110,6 +23389,15 @@
         <f>IF(K452&lt;-5,"CRÍTICO",IF(K452&lt;0,"ATENÇÃO",IF(K452&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M452" t="n">
+        <v>18</v>
+      </c>
+      <c r="N452" t="n">
+        <v>100</v>
+      </c>
+      <c r="O452" t="n">
+        <v>11.11111111111111</v>
+      </c>
     </row>
     <row r="453" hidden="1">
       <c r="A453" s="5" t="n">
@@ -21153,6 +23441,15 @@
         <f>IF(K453&lt;-5,"CRÍTICO",IF(K453&lt;0,"ATENÇÃO",IF(K453&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M453" t="n">
+        <v>0</v>
+      </c>
+      <c r="N453" t="n">
+        <v>100</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="454" hidden="1">
       <c r="A454" s="5" t="n">
@@ -21196,6 +23493,15 @@
         <f>IF(K454&lt;-5,"CRÍTICO",IF(K454&lt;0,"ATENÇÃO",IF(K454&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M454" t="n">
+        <v>0</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="455" hidden="1">
       <c r="A455" s="5" t="n">
@@ -21239,6 +23545,15 @@
         <f>IF(K455&lt;-5,"CRÍTICO",IF(K455&lt;0,"ATENÇÃO",IF(K455&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M455" t="n">
+        <v>0</v>
+      </c>
+      <c r="N455" t="n">
+        <v>100</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="456" hidden="1">
       <c r="A456" s="5" t="n">
@@ -21282,6 +23597,15 @@
         <f>IF(K456&lt;-5,"CRÍTICO",IF(K456&lt;0,"ATENÇÃO",IF(K456&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M456" t="n">
+        <v>18</v>
+      </c>
+      <c r="N456" t="n">
+        <v>100</v>
+      </c>
+      <c r="O456" t="n">
+        <v>27.77777777777778</v>
+      </c>
     </row>
     <row r="457" hidden="1">
       <c r="A457" s="5" t="n">
@@ -21325,6 +23649,15 @@
         <f>IF(K457&lt;-5,"CRÍTICO",IF(K457&lt;0,"ATENÇÃO",IF(K457&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M457" t="n">
+        <v>21</v>
+      </c>
+      <c r="N457" t="n">
+        <v>100</v>
+      </c>
+      <c r="O457" t="n">
+        <v>23.80952380952381</v>
+      </c>
     </row>
     <row r="458" hidden="1">
       <c r="A458" s="5" t="n">
@@ -21368,6 +23701,15 @@
         <f>IF(K458&lt;-5,"CRÍTICO",IF(K458&lt;0,"ATENÇÃO",IF(K458&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M458" t="n">
+        <v>34</v>
+      </c>
+      <c r="N458" t="n">
+        <v>100</v>
+      </c>
+      <c r="O458" t="n">
+        <v>23.52941176470588</v>
+      </c>
     </row>
     <row r="459" hidden="1">
       <c r="A459" s="5" t="n">
@@ -21411,6 +23753,15 @@
         <f>IF(K459&lt;-5,"CRÍTICO",IF(K459&lt;0,"ATENÇÃO",IF(K459&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M459" t="n">
+        <v>23</v>
+      </c>
+      <c r="N459" t="n">
+        <v>100</v>
+      </c>
+      <c r="O459" t="n">
+        <v>21.73913043478261</v>
+      </c>
     </row>
     <row r="460" hidden="1">
       <c r="A460" s="5" t="n">
@@ -21454,6 +23805,15 @@
         <f>IF(K460&lt;-5,"CRÍTICO",IF(K460&lt;0,"ATENÇÃO",IF(K460&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M460" t="n">
+        <v>19</v>
+      </c>
+      <c r="N460" t="n">
+        <v>100</v>
+      </c>
+      <c r="O460" t="n">
+        <v>21.05263157894737</v>
+      </c>
     </row>
     <row r="461" hidden="1">
       <c r="A461" s="5" t="n">
@@ -21497,6 +23857,15 @@
         <f>IF(K461&lt;-5,"CRÍTICO",IF(K461&lt;0,"ATENÇÃO",IF(K461&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M461" t="n">
+        <v>0</v>
+      </c>
+      <c r="N461" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="462" hidden="1">
       <c r="A462" s="5" t="n">
@@ -21540,6 +23909,15 @@
         <f>IF(K462&lt;-5,"CRÍTICO",IF(K462&lt;0,"ATENÇÃO",IF(K462&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M462" t="n">
+        <v>21</v>
+      </c>
+      <c r="N462" t="n">
+        <v>100</v>
+      </c>
+      <c r="O462" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="463" hidden="1">
       <c r="A463" s="5" t="n">
@@ -21583,6 +23961,15 @@
         <f>IF(K463&lt;-5,"CRÍTICO",IF(K463&lt;0,"ATENÇÃO",IF(K463&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M463" t="n">
+        <v>21</v>
+      </c>
+      <c r="N463" t="n">
+        <v>100</v>
+      </c>
+      <c r="O463" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="464" hidden="1">
       <c r="A464" s="5" t="n">
@@ -21626,6 +24013,15 @@
         <f>IF(K464&lt;-5,"CRÍTICO",IF(K464&lt;0,"ATENÇÃO",IF(K464&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M464" t="n">
+        <v>14</v>
+      </c>
+      <c r="N464" t="n">
+        <v>100</v>
+      </c>
+      <c r="O464" t="n">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="465" hidden="1">
       <c r="A465" s="5" t="n">
@@ -21669,6 +24065,15 @@
         <f>IF(K465&lt;-5,"CRÍTICO",IF(K465&lt;0,"ATENÇÃO",IF(K465&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M465" t="n">
+        <v>25</v>
+      </c>
+      <c r="N465" t="n">
+        <v>100</v>
+      </c>
+      <c r="O465" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="466" hidden="1">
       <c r="A466" s="5" t="n">
@@ -21712,6 +24117,15 @@
         <f>IF(K466&lt;-5,"CRÍTICO",IF(K466&lt;0,"ATENÇÃO",IF(K466&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M466" t="n">
+        <v>20</v>
+      </c>
+      <c r="N466" t="n">
+        <v>100</v>
+      </c>
+      <c r="O466" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="467" hidden="1">
       <c r="A467" s="5" t="n">
@@ -21755,6 +24169,15 @@
         <f>IF(K467&lt;-5,"CRÍTICO",IF(K467&lt;0,"ATENÇÃO",IF(K467&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M467" t="n">
+        <v>23</v>
+      </c>
+      <c r="N467" t="n">
+        <v>100</v>
+      </c>
+      <c r="O467" t="n">
+        <v>21.73913043478261</v>
+      </c>
     </row>
     <row r="468" hidden="1">
       <c r="A468" s="5" t="n">
@@ -21798,6 +24221,15 @@
         <f>IF(K468&lt;-5,"CRÍTICO",IF(K468&lt;0,"ATENÇÃO",IF(K468&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M468" t="n">
+        <v>0</v>
+      </c>
+      <c r="N468" t="n">
+        <v>0</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="469" hidden="1">
       <c r="A469" s="5" t="n">
@@ -21841,6 +24273,15 @@
         <f>IF(K469&lt;-5,"CRÍTICO",IF(K469&lt;0,"ATENÇÃO",IF(K469&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M469" t="n">
+        <v>20</v>
+      </c>
+      <c r="N469" t="n">
+        <v>100</v>
+      </c>
+      <c r="O469" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="470" hidden="1">
       <c r="A470" s="5" t="n">
@@ -21884,6 +24325,15 @@
         <f>IF(K470&lt;-5,"CRÍTICO",IF(K470&lt;0,"ATENÇÃO",IF(K470&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M470" t="n">
+        <v>16</v>
+      </c>
+      <c r="N470" t="n">
+        <v>100</v>
+      </c>
+      <c r="O470" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="471" hidden="1">
       <c r="A471" s="5" t="n">
@@ -21927,6 +24377,15 @@
         <f>IF(K471&lt;-5,"CRÍTICO",IF(K471&lt;0,"ATENÇÃO",IF(K471&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M471" t="n">
+        <v>27</v>
+      </c>
+      <c r="N471" t="n">
+        <v>100</v>
+      </c>
+      <c r="O471" t="n">
+        <v>29.62962962962963</v>
+      </c>
     </row>
     <row r="472" hidden="1">
       <c r="A472" s="5" t="n">
@@ -21970,6 +24429,15 @@
         <f>IF(K472&lt;-5,"CRÍTICO",IF(K472&lt;0,"ATENÇÃO",IF(K472&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M472" t="n">
+        <v>0</v>
+      </c>
+      <c r="N472" t="n">
+        <v>0</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="473" hidden="1">
       <c r="A473" s="5" t="n">
@@ -22013,6 +24481,15 @@
         <f>IF(K473&lt;-5,"CRÍTICO",IF(K473&lt;0,"ATENÇÃO",IF(K473&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M473" t="n">
+        <v>13</v>
+      </c>
+      <c r="N473" t="n">
+        <v>100</v>
+      </c>
+      <c r="O473" t="n">
+        <v>38.46153846153847</v>
+      </c>
     </row>
     <row r="474" hidden="1">
       <c r="A474" s="5" t="n">
@@ -22056,6 +24533,15 @@
         <f>IF(K474&lt;-5,"CRÍTICO",IF(K474&lt;0,"ATENÇÃO",IF(K474&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M474" t="n">
+        <v>0</v>
+      </c>
+      <c r="N474" t="n">
+        <v>0</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="475" hidden="1">
       <c r="A475" s="5" t="n">
@@ -22099,6 +24585,15 @@
         <f>IF(K475&lt;-5,"CRÍTICO",IF(K475&lt;0,"ATENÇÃO",IF(K475&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M475" t="n">
+        <v>14</v>
+      </c>
+      <c r="N475" t="n">
+        <v>100</v>
+      </c>
+      <c r="O475" t="n">
+        <v>21.42857142857143</v>
+      </c>
     </row>
     <row r="476" hidden="1">
       <c r="A476" s="5" t="n">
@@ -22142,6 +24637,15 @@
         <f>IF(K476&lt;-5,"CRÍTICO",IF(K476&lt;0,"ATENÇÃO",IF(K476&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M476" t="n">
+        <v>6</v>
+      </c>
+      <c r="N476" t="n">
+        <v>100</v>
+      </c>
+      <c r="O476" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="477" hidden="1">
       <c r="A477" s="5" t="n">
@@ -22185,6 +24689,15 @@
         <f>IF(K477&lt;-5,"CRÍTICO",IF(K477&lt;0,"ATENÇÃO",IF(K477&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M477" t="n">
+        <v>0</v>
+      </c>
+      <c r="N477" t="n">
+        <v>0</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="478" hidden="1">
       <c r="A478" s="5" t="n">
@@ -22228,6 +24741,15 @@
         <f>IF(K478&lt;-5,"CRÍTICO",IF(K478&lt;0,"ATENÇÃO",IF(K478&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M478" t="n">
+        <v>0</v>
+      </c>
+      <c r="N478" t="n">
+        <v>0</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="479" hidden="1">
       <c r="A479" s="5" t="n">
@@ -22271,6 +24793,15 @@
         <f>IF(K479&lt;-5,"CRÍTICO",IF(K479&lt;0,"ATENÇÃO",IF(K479&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M479" t="n">
+        <v>11</v>
+      </c>
+      <c r="N479" t="n">
+        <v>0</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="480" hidden="1">
       <c r="A480" s="5" t="n">
@@ -22314,6 +24845,15 @@
         <f>IF(K480&lt;-5,"CRÍTICO",IF(K480&lt;0,"ATENÇÃO",IF(K480&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M480" t="n">
+        <v>0</v>
+      </c>
+      <c r="N480" t="n">
+        <v>0</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="481" hidden="1">
       <c r="A481" s="5" t="n">
@@ -22357,6 +24897,15 @@
         <f>IF(K481&lt;-5,"CRÍTICO",IF(K481&lt;0,"ATENÇÃO",IF(K481&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M481" t="n">
+        <v>9</v>
+      </c>
+      <c r="N481" t="n">
+        <v>100</v>
+      </c>
+      <c r="O481" t="n">
+        <v>22.22222222222222</v>
+      </c>
     </row>
     <row r="482" hidden="1">
       <c r="A482" s="5" t="n">
@@ -22400,6 +24949,15 @@
         <f>IF(K482&lt;-5,"CRÍTICO",IF(K482&lt;0,"ATENÇÃO",IF(K482&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M482" t="n">
+        <v>0</v>
+      </c>
+      <c r="N482" t="n">
+        <v>0</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="483" hidden="1">
       <c r="A483" s="5" t="n">
@@ -22443,6 +25001,15 @@
         <f>IF(K483&lt;-5,"CRÍTICO",IF(K483&lt;0,"ATENÇÃO",IF(K483&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M483" t="n">
+        <v>26</v>
+      </c>
+      <c r="N483" t="n">
+        <v>100</v>
+      </c>
+      <c r="O483" t="n">
+        <v>19.23076923076923</v>
+      </c>
     </row>
     <row r="484" hidden="1">
       <c r="A484" s="5" t="n">
@@ -22486,6 +25053,15 @@
         <f>IF(K484&lt;-5,"CRÍTICO",IF(K484&lt;0,"ATENÇÃO",IF(K484&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M484" t="n">
+        <v>18</v>
+      </c>
+      <c r="N484" t="n">
+        <v>100</v>
+      </c>
+      <c r="O484" t="n">
+        <v>5.555555555555555</v>
+      </c>
     </row>
     <row r="485" hidden="1">
       <c r="A485" s="5" t="n">
@@ -22529,6 +25105,15 @@
         <f>IF(K485&lt;-5,"CRÍTICO",IF(K485&lt;0,"ATENÇÃO",IF(K485&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M485" t="n">
+        <v>21</v>
+      </c>
+      <c r="N485" t="n">
+        <v>100</v>
+      </c>
+      <c r="O485" t="n">
+        <v>28.57142857142857</v>
+      </c>
     </row>
     <row r="486" hidden="1">
       <c r="A486" s="7" t="n">
@@ -22579,7 +25164,7 @@
         <v>91.67</v>
       </c>
       <c r="O486" s="3" t="n">
-        <v>29.41</v>
+        <v>70.58823529411765</v>
       </c>
     </row>
     <row r="487" hidden="1">
@@ -22677,13 +25262,13 @@
         <v/>
       </c>
       <c r="M488" s="3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N488" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O488" s="3" t="n">
-        <v>22.86</v>
+        <v>41.37931034482759</v>
       </c>
     </row>
     <row r="489" hidden="1">
@@ -22729,13 +25314,13 @@
         <v/>
       </c>
       <c r="M489" s="3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="N489" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="O489" s="3" t="n">
-        <v>3.85</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="490" hidden="1">
@@ -22780,6 +25365,15 @@
         <f>IF(K490&lt;-5,"CRÍTICO",IF(K490&lt;0,"ATENÇÃO",IF(K490&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M490" t="n">
+        <v>28</v>
+      </c>
+      <c r="N490" t="n">
+        <v>100</v>
+      </c>
+      <c r="O490" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="491" hidden="1">
       <c r="A491" s="7" t="n">
@@ -22823,6 +25417,15 @@
         <f>IF(K491&lt;-5,"CRÍTICO",IF(K491&lt;0,"ATENÇÃO",IF(K491&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M491" t="n">
+        <v>0</v>
+      </c>
+      <c r="N491" t="n">
+        <v>0</v>
+      </c>
+      <c r="O491" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="492" hidden="1">
       <c r="A492" s="7" t="n">
@@ -22866,6 +25469,15 @@
         <f>IF(K492&lt;-5,"CRÍTICO",IF(K492&lt;0,"ATENÇÃO",IF(K492&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M492" t="n">
+        <v>29</v>
+      </c>
+      <c r="N492" t="n">
+        <v>50</v>
+      </c>
+      <c r="O492" t="n">
+        <v>6.896551724137931</v>
+      </c>
     </row>
     <row r="493" hidden="1">
       <c r="A493" s="7" t="n">
@@ -22909,6 +25521,15 @@
         <f>IF(K493&lt;-5,"CRÍTICO",IF(K493&lt;0,"ATENÇÃO",IF(K493&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M493" t="n">
+        <v>7</v>
+      </c>
+      <c r="N493" t="n">
+        <v>100</v>
+      </c>
+      <c r="O493" t="n">
+        <v>57.14285714285714</v>
+      </c>
     </row>
     <row r="494" hidden="1">
       <c r="A494" s="7" t="n">
@@ -22952,6 +25573,15 @@
         <f>IF(K494&lt;-5,"CRÍTICO",IF(K494&lt;0,"ATENÇÃO",IF(K494&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M494" t="n">
+        <v>19</v>
+      </c>
+      <c r="N494" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="O494" t="n">
+        <v>31.57894736842105</v>
+      </c>
     </row>
     <row r="495" hidden="1">
       <c r="A495" s="7" t="n">
@@ -22995,6 +25625,15 @@
         <f>IF(K495&lt;-5,"CRÍTICO",IF(K495&lt;0,"ATENÇÃO",IF(K495&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M495" t="n">
+        <v>30</v>
+      </c>
+      <c r="N495" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="O495" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="496" hidden="1">
       <c r="A496" s="7" t="n">
@@ -23038,6 +25677,15 @@
         <f>IF(K496&lt;-5,"CRÍTICO",IF(K496&lt;0,"ATENÇÃO",IF(K496&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M496" t="n">
+        <v>0</v>
+      </c>
+      <c r="N496" t="n">
+        <v>100</v>
+      </c>
+      <c r="O496" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="497" hidden="1">
       <c r="A497" s="7" t="n">
@@ -23081,6 +25729,15 @@
         <f>IF(K497&lt;-5,"CRÍTICO",IF(K497&lt;0,"ATENÇÃO",IF(K497&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M497" t="n">
+        <v>15</v>
+      </c>
+      <c r="N497" t="n">
+        <v>100</v>
+      </c>
+      <c r="O497" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="498" hidden="1">
       <c r="A498" s="7" t="n">
@@ -23124,6 +25781,15 @@
         <f>IF(K498&lt;-5,"CRÍTICO",IF(K498&lt;0,"ATENÇÃO",IF(K498&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M498" t="n">
+        <v>0</v>
+      </c>
+      <c r="N498" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="O498" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="499" hidden="1">
       <c r="A499" s="7" t="n">
@@ -23167,6 +25833,15 @@
         <f>IF(K499&lt;-5,"CRÍTICO",IF(K499&lt;0,"ATENÇÃO",IF(K499&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M499" t="n">
+        <v>0</v>
+      </c>
+      <c r="N499" t="n">
+        <v>0</v>
+      </c>
+      <c r="O499" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="500" hidden="1">
       <c r="A500" s="7" t="n">
@@ -23210,6 +25885,15 @@
         <f>IF(K500&lt;-5,"CRÍTICO",IF(K500&lt;0,"ATENÇÃO",IF(K500&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M500" t="n">
+        <v>0</v>
+      </c>
+      <c r="N500" t="n">
+        <v>0</v>
+      </c>
+      <c r="O500" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="501" hidden="1">
       <c r="A501" s="7" t="n">
@@ -23253,6 +25937,15 @@
         <f>IF(K501&lt;-5,"CRÍTICO",IF(K501&lt;0,"ATENÇÃO",IF(K501&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M501" t="n">
+        <v>11</v>
+      </c>
+      <c r="N501" t="n">
+        <v>100</v>
+      </c>
+      <c r="O501" t="n">
+        <v>18.18181818181818</v>
+      </c>
     </row>
     <row r="502" hidden="1">
       <c r="A502" s="7" t="n">
@@ -23296,6 +25989,15 @@
         <f>IF(K502&lt;-5,"CRÍTICO",IF(K502&lt;0,"ATENÇÃO",IF(K502&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M502" t="n">
+        <v>0</v>
+      </c>
+      <c r="N502" t="n">
+        <v>0</v>
+      </c>
+      <c r="O502" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="503" hidden="1">
       <c r="A503" s="7" t="n">
@@ -23339,6 +26041,15 @@
         <f>IF(K503&lt;-5,"CRÍTICO",IF(K503&lt;0,"ATENÇÃO",IF(K503&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M503" t="n">
+        <v>0</v>
+      </c>
+      <c r="N503" t="n">
+        <v>0</v>
+      </c>
+      <c r="O503" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="504" hidden="1">
       <c r="A504" s="7" t="n">
@@ -23382,6 +26093,15 @@
         <f>IF(K504&lt;-5,"CRÍTICO",IF(K504&lt;0,"ATENÇÃO",IF(K504&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M504" t="n">
+        <v>20</v>
+      </c>
+      <c r="N504" t="n">
+        <v>100</v>
+      </c>
+      <c r="O504" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="505" hidden="1">
       <c r="A505" s="7" t="n">
@@ -23425,6 +26145,15 @@
         <f>IF(K505&lt;-5,"CRÍTICO",IF(K505&lt;0,"ATENÇÃO",IF(K505&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M505" t="n">
+        <v>22</v>
+      </c>
+      <c r="N505" t="n">
+        <v>75</v>
+      </c>
+      <c r="O505" t="n">
+        <v>18.18181818181818</v>
+      </c>
     </row>
     <row r="506" hidden="1">
       <c r="A506" s="7" t="n">
@@ -23468,6 +26197,15 @@
         <f>IF(K506&lt;-5,"CRÍTICO",IF(K506&lt;0,"ATENÇÃO",IF(K506&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M506" t="n">
+        <v>40</v>
+      </c>
+      <c r="N506" t="n">
+        <v>100</v>
+      </c>
+      <c r="O506" t="n">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="507" hidden="1">
       <c r="A507" s="7" t="n">
@@ -23511,6 +26249,15 @@
         <f>IF(K507&lt;-5,"CRÍTICO",IF(K507&lt;0,"ATENÇÃO",IF(K507&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M507" t="n">
+        <v>12</v>
+      </c>
+      <c r="N507" t="n">
+        <v>50</v>
+      </c>
+      <c r="O507" t="n">
+        <v>33.33333333333333</v>
+      </c>
     </row>
     <row r="508" hidden="1">
       <c r="A508" s="7" t="n">
@@ -23554,6 +26301,15 @@
         <f>IF(K508&lt;-5,"CRÍTICO",IF(K508&lt;0,"ATENÇÃO",IF(K508&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M508" t="n">
+        <v>16</v>
+      </c>
+      <c r="N508" t="n">
+        <v>100</v>
+      </c>
+      <c r="O508" t="n">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="509" hidden="1">
       <c r="A509" s="7" t="n">
@@ -23597,6 +26353,15 @@
         <f>IF(K509&lt;-5,"CRÍTICO",IF(K509&lt;0,"ATENÇÃO",IF(K509&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M509" t="n">
+        <v>0</v>
+      </c>
+      <c r="N509" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510" hidden="1">
       <c r="A510" s="7" t="n">
@@ -23640,6 +26405,15 @@
         <f>IF(K510&lt;-5,"CRÍTICO",IF(K510&lt;0,"ATENÇÃO",IF(K510&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M510" t="n">
+        <v>20</v>
+      </c>
+      <c r="N510" t="n">
+        <v>75</v>
+      </c>
+      <c r="O510" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="511" hidden="1">
       <c r="A511" s="7" t="n">
@@ -23683,6 +26457,15 @@
         <f>IF(K511&lt;-5,"CRÍTICO",IF(K511&lt;0,"ATENÇÃO",IF(K511&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M511" t="n">
+        <v>28</v>
+      </c>
+      <c r="N511" t="n">
+        <v>100</v>
+      </c>
+      <c r="O511" t="n">
+        <v>32.14285714285715</v>
+      </c>
     </row>
     <row r="512" hidden="1">
       <c r="A512" s="7" t="n">
@@ -23726,6 +26509,15 @@
         <f>IF(K512&lt;-5,"CRÍTICO",IF(K512&lt;0,"ATENÇÃO",IF(K512&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M512" t="n">
+        <v>15</v>
+      </c>
+      <c r="N512" t="n">
+        <v>100</v>
+      </c>
+      <c r="O512" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="513" hidden="1">
       <c r="A513" s="7" t="n">
@@ -23769,6 +26561,15 @@
         <f>IF(K513&lt;-5,"CRÍTICO",IF(K513&lt;0,"ATENÇÃO",IF(K513&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M513" t="n">
+        <v>24</v>
+      </c>
+      <c r="N513" t="n">
+        <v>100</v>
+      </c>
+      <c r="O513" t="n">
+        <v>12.5</v>
+      </c>
     </row>
     <row r="514" hidden="1">
       <c r="A514" s="7" t="n">
@@ -23812,6 +26613,15 @@
         <f>IF(K514&lt;-5,"CRÍTICO",IF(K514&lt;0,"ATENÇÃO",IF(K514&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M514" t="n">
+        <v>45</v>
+      </c>
+      <c r="N514" t="n">
+        <v>100</v>
+      </c>
+      <c r="O514" t="n">
+        <v>13.33333333333333</v>
+      </c>
     </row>
     <row r="515" hidden="1">
       <c r="A515" s="7" t="n">
@@ -23855,6 +26665,15 @@
         <f>IF(K515&lt;-5,"CRÍTICO",IF(K515&lt;0,"ATENÇÃO",IF(K515&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M515" t="n">
+        <v>19</v>
+      </c>
+      <c r="N515" t="n">
+        <v>100</v>
+      </c>
+      <c r="O515" t="n">
+        <v>21.05263157894737</v>
+      </c>
     </row>
     <row r="516" hidden="1">
       <c r="A516" s="7" t="n">
@@ -23898,6 +26717,15 @@
         <f>IF(K516&lt;-5,"CRÍTICO",IF(K516&lt;0,"ATENÇÃO",IF(K516&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M516" t="n">
+        <v>18</v>
+      </c>
+      <c r="N516" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="517" hidden="1">
       <c r="A517" s="7" t="n">
@@ -23941,6 +26769,15 @@
         <f>IF(K517&lt;-5,"CRÍTICO",IF(K517&lt;0,"ATENÇÃO",IF(K517&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M517" t="n">
+        <v>18</v>
+      </c>
+      <c r="N517" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="O517" t="n">
+        <v>38.88888888888889</v>
+      </c>
     </row>
     <row r="518" hidden="1">
       <c r="A518" s="7" t="n">
@@ -23984,6 +26821,15 @@
         <f>IF(K518&lt;-5,"CRÍTICO",IF(K518&lt;0,"ATENÇÃO",IF(K518&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M518" t="n">
+        <v>12</v>
+      </c>
+      <c r="N518" t="n">
+        <v>100</v>
+      </c>
+      <c r="O518" t="n">
+        <v>8.333333333333332</v>
+      </c>
     </row>
     <row r="519" hidden="1">
       <c r="A519" s="7" t="n">
@@ -24027,6 +26873,15 @@
         <f>IF(K519&lt;-5,"CRÍTICO",IF(K519&lt;0,"ATENÇÃO",IF(K519&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M519" t="n">
+        <v>14</v>
+      </c>
+      <c r="N519" t="n">
+        <v>100</v>
+      </c>
+      <c r="O519" t="n">
+        <v>7.142857142857142</v>
+      </c>
     </row>
     <row r="520" hidden="1">
       <c r="A520" s="7" t="n">
@@ -24070,6 +26925,15 @@
         <f>IF(K520&lt;-5,"CRÍTICO",IF(K520&lt;0,"ATENÇÃO",IF(K520&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M520" t="n">
+        <v>30</v>
+      </c>
+      <c r="N520" t="n">
+        <v>100</v>
+      </c>
+      <c r="O520" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="521" hidden="1">
       <c r="A521" s="7" t="n">
@@ -24113,6 +26977,15 @@
         <f>IF(K521&lt;-5,"CRÍTICO",IF(K521&lt;0,"ATENÇÃO",IF(K521&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M521" t="n">
+        <v>0</v>
+      </c>
+      <c r="N521" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="522" hidden="1">
       <c r="A522" s="7" t="n">
@@ -24156,6 +27029,15 @@
         <f>IF(K522&lt;-5,"CRÍTICO",IF(K522&lt;0,"ATENÇÃO",IF(K522&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M522" t="n">
+        <v>0</v>
+      </c>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="523" hidden="1">
       <c r="A523" s="7" t="n">
@@ -24199,6 +27081,15 @@
         <f>IF(K523&lt;-5,"CRÍTICO",IF(K523&lt;0,"ATENÇÃO",IF(K523&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M523" t="n">
+        <v>22</v>
+      </c>
+      <c r="N523" t="n">
+        <v>100</v>
+      </c>
+      <c r="O523" t="n">
+        <v>9.090909090909092</v>
+      </c>
     </row>
     <row r="524" hidden="1">
       <c r="A524" s="7" t="n">
@@ -24242,6 +27133,15 @@
         <f>IF(K524&lt;-5,"CRÍTICO",IF(K524&lt;0,"ATENÇÃO",IF(K524&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M524" t="n">
+        <v>0</v>
+      </c>
+      <c r="N524" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="525" hidden="1">
       <c r="A525" s="7" t="n">
@@ -24285,6 +27185,15 @@
         <f>IF(K525&lt;-5,"CRÍTICO",IF(K525&lt;0,"ATENÇÃO",IF(K525&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M525" t="n">
+        <v>15</v>
+      </c>
+      <c r="N525" t="n">
+        <v>100</v>
+      </c>
+      <c r="O525" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="526" hidden="1">
       <c r="A526" s="7" t="n">
@@ -24328,6 +27237,15 @@
         <f>IF(K526&lt;-5,"CRÍTICO",IF(K526&lt;0,"ATENÇÃO",IF(K526&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M526" t="n">
+        <v>16</v>
+      </c>
+      <c r="N526" t="n">
+        <v>100</v>
+      </c>
+      <c r="O526" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="527" hidden="1">
       <c r="A527" s="7" t="n">
@@ -24371,6 +27289,15 @@
         <f>IF(K527&lt;-5,"CRÍTICO",IF(K527&lt;0,"ATENÇÃO",IF(K527&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M527" t="n">
+        <v>0</v>
+      </c>
+      <c r="N527" t="n">
+        <v>0</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="528" hidden="1">
       <c r="A528" s="7" t="n">
@@ -24414,6 +27341,15 @@
         <f>IF(K528&lt;-5,"CRÍTICO",IF(K528&lt;0,"ATENÇÃO",IF(K528&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M528" t="n">
+        <v>34</v>
+      </c>
+      <c r="N528" t="n">
+        <v>100</v>
+      </c>
+      <c r="O528" t="n">
+        <v>47.05882352941176</v>
+      </c>
     </row>
     <row r="529" hidden="1">
       <c r="A529" s="7" t="n">
@@ -24457,6 +27393,15 @@
         <f>IF(K529&lt;-5,"CRÍTICO",IF(K529&lt;0,"ATENÇÃO",IF(K529&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M529" t="n">
+        <v>17</v>
+      </c>
+      <c r="N529" t="n">
+        <v>100</v>
+      </c>
+      <c r="O529" t="n">
+        <v>29.41176470588236</v>
+      </c>
     </row>
     <row r="530" hidden="1">
       <c r="A530" s="7" t="n">
@@ -24500,6 +27445,15 @@
         <f>IF(K530&lt;-5,"CRÍTICO",IF(K530&lt;0,"ATENÇÃO",IF(K530&lt;=5,"BOM","EXCELENTE")))</f>
         <v/>
       </c>
+      <c r="M530" t="n">
+        <v>21</v>
+      </c>
+      <c r="N530" t="n">
+        <v>80</v>
+      </c>
+      <c r="O530" t="n">
+        <v>23.80952380952381</v>
+      </c>
     </row>
     <row r="531" hidden="1">
       <c r="A531" s="7" t="n">
@@ -24553,7 +27507,7 @@
         <v>100</v>
       </c>
       <c r="O531" s="3" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="532" hidden="1">
@@ -24659,10 +27613,10 @@
         <v>26</v>
       </c>
       <c r="N533" s="9" t="n">
-        <v>88.70999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="O533" s="9" t="n">
-        <v>3.85</v>
+        <v>26.92307692307692</v>
       </c>
     </row>
     <row r="534" hidden="1">
@@ -24711,13 +27665,13 @@
         <v/>
       </c>
       <c r="M534" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N534" s="9" t="n">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="O534" s="9" t="n">
-        <v>15.38</v>
+        <v>27.77777777777778</v>
       </c>
     </row>
     <row r="535" hidden="1">
@@ -24769,10 +27723,10 @@
         <v>32</v>
       </c>
       <c r="N535" s="9" t="n">
-        <v>98.91</v>
+        <v>100</v>
       </c>
       <c r="O535" s="9" t="n">
-        <v>15.04</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="536" hidden="1">
@@ -24821,13 +27775,13 @@
         <v/>
       </c>
       <c r="M536" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="N536" s="9" t="n">
-        <v>98.97</v>
+        <v>0</v>
       </c>
       <c r="O536" s="9" t="n">
-        <v>12.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" hidden="1">
@@ -24879,10 +27833,10 @@
         <v>25</v>
       </c>
       <c r="N537" s="9" t="n">
-        <v>98.53</v>
+        <v>100</v>
       </c>
       <c r="O537" s="9" t="n">
-        <v>14.33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="538" hidden="1">
@@ -24934,10 +27888,10 @@
         <v>8</v>
       </c>
       <c r="N538" s="9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="O538" s="9" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="539" hidden="1">
@@ -24989,10 +27943,10 @@
         <v>22</v>
       </c>
       <c r="N539" s="9" t="n">
-        <v>96.25</v>
+        <v>100</v>
       </c>
       <c r="O539" s="9" t="n">
-        <v>16.45</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="540" hidden="1">
@@ -25044,10 +27998,10 @@
         <v>21</v>
       </c>
       <c r="N540" s="9" t="n">
-        <v>92.23999999999999</v>
+        <v>80</v>
       </c>
       <c r="O540" s="9" t="n">
-        <v>18.99</v>
+        <v>47.61904761904761</v>
       </c>
     </row>
     <row r="541" hidden="1">
@@ -25099,7 +28053,7 @@
         <v>0</v>
       </c>
       <c r="N541" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O541" s="9" t="n">
         <v>0</v>
@@ -25157,7 +28111,7 @@
         <v>100</v>
       </c>
       <c r="O542" s="9" t="n">
-        <v>18.06</v>
+        <v>38.46153846153847</v>
       </c>
     </row>
     <row r="543" hidden="1">
@@ -25209,10 +28163,10 @@
         <v>0</v>
       </c>
       <c r="N543" s="9" t="n">
-        <v>98.89</v>
+        <v>100</v>
       </c>
       <c r="O543" s="9" t="n">
-        <v>18.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544" hidden="1">
@@ -25264,10 +28218,10 @@
         <v>0</v>
       </c>
       <c r="N544" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O544" s="9" t="n">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545" hidden="1">
@@ -25316,13 +28270,13 @@
         <v/>
       </c>
       <c r="M545" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N545" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O545" s="9" t="n">
-        <v>13.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546" hidden="1">
@@ -25377,7 +28331,7 @@
         <v>100</v>
       </c>
       <c r="O546" s="9" t="n">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547" hidden="1">
@@ -25432,7 +28386,7 @@
         <v>100</v>
       </c>
       <c r="O547" s="9" t="n">
-        <v>17.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548" hidden="1">
@@ -25542,7 +28496,7 @@
         <v>100</v>
       </c>
       <c r="O549" s="9" t="n">
-        <v>14.78</v>
+        <v>38.09523809523809</v>
       </c>
     </row>
     <row r="550" hidden="1">
@@ -25594,10 +28548,10 @@
         <v>22</v>
       </c>
       <c r="N550" s="9" t="n">
-        <v>98.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="O550" s="9" t="n">
-        <v>12.04</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="551" hidden="1">
@@ -25649,10 +28603,10 @@
         <v>34</v>
       </c>
       <c r="N551" s="9" t="n">
-        <v>99.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="O551" s="9" t="n">
-        <v>14.47</v>
+        <v>29.41176470588236</v>
       </c>
     </row>
     <row r="552" hidden="1">
@@ -25704,10 +28658,10 @@
         <v>19</v>
       </c>
       <c r="N552" s="9" t="n">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="O552" s="9" t="n">
-        <v>17.09</v>
+        <v>42.10526315789473</v>
       </c>
     </row>
     <row r="553" hidden="1">
@@ -25762,7 +28716,7 @@
         <v>100</v>
       </c>
       <c r="O553" s="9" t="n">
-        <v>14</v>
+        <v>34.78260869565217</v>
       </c>
     </row>
     <row r="554" hidden="1">
@@ -25869,10 +28823,10 @@
         <v>20</v>
       </c>
       <c r="N555" s="9" t="n">
-        <v>96.48999999999999</v>
+        <v>100</v>
       </c>
       <c r="O555" s="9" t="n">
-        <v>12.82</v>
+        <v>35</v>
       </c>
     </row>
     <row r="556" hidden="1">
@@ -25924,10 +28878,10 @@
         <v>18</v>
       </c>
       <c r="N556" s="9" t="n">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="O556" s="9" t="n">
-        <v>10.34</v>
+        <v>27.77777777777778</v>
       </c>
     </row>
     <row r="557" hidden="1">
@@ -25982,7 +28936,7 @@
         <v>100</v>
       </c>
       <c r="O557" s="9" t="n">
-        <v>14.47</v>
+        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="558" hidden="1">
@@ -26037,7 +28991,7 @@
         <v>100</v>
       </c>
       <c r="O558" s="9" t="n">
-        <v>11.56</v>
+        <v>39.28571428571428</v>
       </c>
     </row>
     <row r="559" hidden="1">
@@ -26089,10 +29043,10 @@
         <v>19</v>
       </c>
       <c r="N559" s="9" t="n">
-        <v>98.28</v>
+        <v>100</v>
       </c>
       <c r="O559" s="9" t="n">
-        <v>14.43</v>
+        <v>42.10526315789473</v>
       </c>
     </row>
     <row r="560" hidden="1">
@@ -26147,7 +29101,7 @@
         <v>100</v>
       </c>
       <c r="O560" s="9" t="n">
-        <v>17.11</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="561" hidden="1">
@@ -26199,7 +29153,7 @@
         <v>18</v>
       </c>
       <c r="N561" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O561" s="9" t="n">
         <v>0</v>
@@ -26254,10 +29208,10 @@
         <v>16</v>
       </c>
       <c r="N562" s="9" t="n">
-        <v>92.95999999999999</v>
+        <v>75</v>
       </c>
       <c r="O562" s="9" t="n">
-        <v>16.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="563" hidden="1">
@@ -26312,7 +29266,7 @@
         <v>100</v>
       </c>
       <c r="O563" s="9" t="n">
-        <v>8.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="564" hidden="1">
@@ -26361,13 +29315,13 @@
         <v/>
       </c>
       <c r="M564" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N564" s="9" t="n">
         <v>100</v>
       </c>
       <c r="O564" s="9" t="n">
-        <v>29.17</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="565" hidden="1">
@@ -26419,10 +29373,10 @@
         <v>23</v>
       </c>
       <c r="N565" s="9" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="O565" s="9" t="n">
-        <v>16.62</v>
+        <v>34.78260869565217</v>
       </c>
     </row>
     <row r="566" hidden="1">
@@ -26471,13 +29425,13 @@
         <v/>
       </c>
       <c r="M566" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N566" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O566" s="9" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567" hidden="1">
@@ -26526,13 +29480,13 @@
         <v/>
       </c>
       <c r="M567" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N567" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O567" s="9" t="n">
-        <v>13.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568" hidden="1">
@@ -26587,7 +29541,7 @@
         <v>100</v>
       </c>
       <c r="O568" s="9" t="n">
-        <v>14.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569" hidden="1">
@@ -26636,13 +29590,13 @@
         <v/>
       </c>
       <c r="M569" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N569" s="9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O569" s="9" t="n">
-        <v>17.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570" hidden="1">
@@ -26697,7 +29651,7 @@
         <v>100</v>
       </c>
       <c r="O570" s="9" t="n">
-        <v>13.04</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="571" hidden="1">
@@ -26749,10 +29703,10 @@
         <v>13</v>
       </c>
       <c r="N571" s="9" t="n">
-        <v>97.87</v>
+        <v>100</v>
       </c>
       <c r="O571" s="9" t="n">
-        <v>19.32</v>
+        <v>30.76923076923077</v>
       </c>
     </row>
     <row r="572" hidden="1">
@@ -26801,13 +29755,13 @@
         <v/>
       </c>
       <c r="M572" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N572" s="9" t="n">
-        <v>96.88</v>
+        <v>0</v>
       </c>
       <c r="O572" s="9" t="n">
-        <v>15.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="573" hidden="1">
@@ -26859,10 +29813,10 @@
         <v>28</v>
       </c>
       <c r="N573" s="9" t="n">
-        <v>99.09999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="O573" s="9" t="n">
-        <v>19.32</v>
+        <v>42.85714285714285</v>
       </c>
     </row>
     <row r="574" hidden="1">
@@ -26917,7 +29871,7 @@
         <v>100</v>
       </c>
       <c r="O574" s="9" t="n">
-        <v>13.02</v>
+        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="575" hidden="1">
@@ -26969,10 +29923,10 @@
         <v>21</v>
       </c>
       <c r="N575" s="9" t="n">
-        <v>96.83</v>
+        <v>100</v>
       </c>
       <c r="O575" s="9" t="n">
-        <v>14.33</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="576">
@@ -27027,7 +29981,7 @@
         <v>100</v>
       </c>
       <c r="O576" s="3" t="n">
-        <v>5.88</v>
+        <v>47.05882352941176</v>
       </c>
     </row>
     <row r="577">
@@ -27137,7 +30091,7 @@
         <v>100</v>
       </c>
       <c r="O578" s="3" t="n">
-        <v>4.76</v>
+        <v>47.61904761904761</v>
       </c>
     </row>
     <row r="579">
@@ -27192,7 +30146,7 @@
         <v>87.5</v>
       </c>
       <c r="O579" s="3" t="n">
-        <v>0</v>
+        <v>61.53846153846154</v>
       </c>
     </row>
     <row r="580">
@@ -27247,7 +30201,7 @@
         <v>100</v>
       </c>
       <c r="O580" s="3" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="581">
@@ -27296,10 +30250,10 @@
         <v/>
       </c>
       <c r="M581" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N581" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O581" s="3" t="n">
         <v>0</v>
@@ -27357,7 +30311,7 @@
         <v>100</v>
       </c>
       <c r="O582" s="3" t="n">
-        <v>9.52</v>
+        <v>52.38095238095239</v>
       </c>
     </row>
     <row r="583">
@@ -27412,7 +30366,7 @@
         <v>100</v>
       </c>
       <c r="O583" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="584">
@@ -27467,7 +30421,7 @@
         <v>100</v>
       </c>
       <c r="O584" s="3" t="n">
-        <v>0</v>
+        <v>35.29411764705883</v>
       </c>
     </row>
     <row r="585">
@@ -27522,7 +30476,7 @@
         <v>100</v>
       </c>
       <c r="O585" s="3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="586">
@@ -27632,7 +30586,7 @@
         <v>100</v>
       </c>
       <c r="O587" s="3" t="n">
-        <v>0</v>
+        <v>21.42857142857143</v>
       </c>
     </row>
     <row r="588">
@@ -27742,7 +30696,7 @@
         <v>100</v>
       </c>
       <c r="O589" s="3" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
     </row>
     <row r="590">
@@ -27791,10 +30745,10 @@
         <v/>
       </c>
       <c r="M590" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N590" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O590" s="3" t="n">
         <v>0</v>
@@ -27959,7 +30913,7 @@
         <v>0</v>
       </c>
       <c r="N593" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O593" s="3" t="n">
         <v>0</v>
@@ -28017,7 +30971,7 @@
         <v>87.5</v>
       </c>
       <c r="O594" s="3" t="n">
-        <v>0</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="595">
@@ -28072,7 +31026,7 @@
         <v>100</v>
       </c>
       <c r="O595" s="3" t="n">
-        <v>0</v>
+        <v>42.10526315789473</v>
       </c>
     </row>
     <row r="596">
@@ -28127,7 +31081,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="O596" s="3" t="n">
-        <v>3.57</v>
+        <v>67.85714285714286</v>
       </c>
     </row>
     <row r="597">
@@ -28182,7 +31136,7 @@
         <v>100</v>
       </c>
       <c r="O597" s="3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="598">
@@ -28237,7 +31191,7 @@
         <v>87.5</v>
       </c>
       <c r="O598" s="3" t="n">
-        <v>0</v>
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="599">
@@ -28289,7 +31243,7 @@
         <v>0</v>
       </c>
       <c r="N599" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O599" s="3" t="n">
         <v>0</v>
@@ -28347,7 +31301,7 @@
         <v>100</v>
       </c>
       <c r="O600" s="3" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="601">
@@ -28402,7 +31356,7 @@
         <v>100</v>
       </c>
       <c r="O601" s="3" t="n">
-        <v>4.76</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="602">
@@ -28457,7 +31411,7 @@
         <v>100</v>
       </c>
       <c r="O602" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="603">
@@ -28512,7 +31466,7 @@
         <v>100</v>
       </c>
       <c r="O603" s="3" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="604">
@@ -28567,7 +31521,7 @@
         <v>100</v>
       </c>
       <c r="O604" s="3" t="n">
-        <v>0</v>
+        <v>47.05882352941176</v>
       </c>
     </row>
     <row r="605">
@@ -28622,7 +31576,7 @@
         <v>100</v>
       </c>
       <c r="O605" s="3" t="n">
-        <v>18.75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="606">
@@ -28732,7 +31686,7 @@
         <v>100</v>
       </c>
       <c r="O607" s="3" t="n">
-        <v>9.52</v>
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="608">
@@ -28787,7 +31741,7 @@
         <v>100</v>
       </c>
       <c r="O608" s="3" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="609">
@@ -28836,13 +31790,13 @@
         <v/>
       </c>
       <c r="M609" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N609" s="3" t="n">
         <v>100</v>
       </c>
       <c r="O609" s="3" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
     </row>
     <row r="610">
@@ -28897,7 +31851,7 @@
         <v>83.33</v>
       </c>
       <c r="O610" s="3" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="611">
@@ -28946,10 +31900,10 @@
         <v/>
       </c>
       <c r="M611" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N611" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O611" s="3" t="n">
         <v>0</v>
@@ -29001,10 +31955,10 @@
         <v/>
       </c>
       <c r="M612" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N612" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O612" s="3" t="n">
         <v>0</v>
@@ -29111,13 +32065,13 @@
         <v/>
       </c>
       <c r="M614" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N614" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O614" s="3" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -29172,7 +32126,7 @@
         <v>100</v>
       </c>
       <c r="O615" s="3" t="n">
-        <v>0</v>
+        <v>58.33333333333334</v>
       </c>
     </row>
     <row r="616">
@@ -29227,7 +32181,7 @@
         <v>100</v>
       </c>
       <c r="O616" s="3" t="n">
-        <v>0</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="617">
@@ -29276,10 +32230,10 @@
         <v/>
       </c>
       <c r="M617" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N617" s="3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O617" s="3" t="n">
         <v>0</v>
@@ -29337,7 +32291,7 @@
         <v>100</v>
       </c>
       <c r="O618" s="3" t="n">
-        <v>9.09</v>
+        <v>40.90909090909091</v>
       </c>
     </row>
     <row r="619">
@@ -29392,7 +32346,7 @@
         <v>100</v>
       </c>
       <c r="O619" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="620">
@@ -29447,7 +32401,7 @@
         <v>100</v>
       </c>
       <c r="O620" s="3" t="n">
-        <v>4.76</v>
+        <v>23.80952380952381</v>
       </c>
     </row>
   </sheetData>
@@ -29521,7 +32475,6 @@
           <t>Ana Karollyne Souza Faria</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29541,7 +32494,6 @@
           <t>Anna Luiza Rezende Tavares</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29549,7 +32501,6 @@
           <t>Brenda de Menezes Silva</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29557,7 +32508,6 @@
           <t>Carlos Mateus Cassimiro Nunes</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29565,7 +32515,6 @@
           <t>Claudio de Sousa Velasco Filho</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29585,7 +32534,6 @@
           <t>Cristiane Ramos da Silva Rocha</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29593,7 +32541,6 @@
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29613,7 +32560,6 @@
           <t>Davylla Rodrigues Freitas Silva</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29633,7 +32579,6 @@
           <t>Emilly Kamilly Medeiros Miranda</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29641,7 +32586,6 @@
           <t>Francielson de Oliveira</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29649,7 +32593,6 @@
           <t>Francilene Ferreira de Jesus</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29657,7 +32600,6 @@
           <t>Gabriel Alves</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -29725,7 +32667,6 @@
           <t>Jéssica Fé Moura</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -29745,7 +32686,6 @@
           <t>Kerollen Cristielly de Jesus Siqueira</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -29789,7 +32729,6 @@
           <t>Lorena Dias de Araujo</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -29809,7 +32748,6 @@
           <t>Luiz Fernando de Carvalho Junior</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -29817,7 +32755,6 @@
           <t>Maria Eduarda Sousa Costa</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -29825,7 +32762,6 @@
           <t>Matheus Farias De Souza</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -29833,7 +32769,6 @@
           <t>Maysa Victoria Dias Moura</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -29841,7 +32776,6 @@
           <t>Michelle G Santos</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -29861,7 +32795,6 @@
           <t>Patrícia Karla de Sousa Araújo</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -29893,7 +32826,6 @@
           <t>Quirino Diogo Leite Torres</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -29925,7 +32857,6 @@
           <t>Sara Maria Monteiro Lopes</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -29933,7 +32864,6 @@
           <t>Sarah Steffanie de Lima Borges</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -620,10 +620,10 @@
         <v>36</v>
       </c>
       <c r="N2" s="9" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O2" s="9" t="n">
-        <v>22.22222222222222</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="3" hidden="1">
@@ -721,10 +721,10 @@
         <v>35</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>25.71428571428571</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="5" hidden="1">
@@ -773,10 +773,10 @@
         <v>31</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>38.70967741935484</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="6" hidden="1">
@@ -828,10 +828,10 @@
         <v>29</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>10.3448275862069</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="7" hidden="1">
@@ -932,10 +932,10 @@
         <v>28</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>7.142857142857142</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="9" hidden="1">
@@ -984,10 +984,10 @@
         <v>7</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>14.28571428571428</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="10" hidden="1">
@@ -1036,10 +1036,10 @@
         <v>29</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>20.68965517241379</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="11" hidden="1">
@@ -1088,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="N11" s="9" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>34.375</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="12" hidden="1">
@@ -1140,10 +1140,10 @@
         <v>25</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>36</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="13" hidden="1">
@@ -1195,7 +1195,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>43.75</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="14" hidden="1">
@@ -1244,10 +1244,10 @@
         <v>25</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>40</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="15" hidden="1">
@@ -1299,7 +1299,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>37.5</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="16" hidden="1">
@@ -1403,7 +1403,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="18" hidden="1">
@@ -1455,7 +1455,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>20.68965517241379</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="19" hidden="1">
@@ -1504,10 +1504,10 @@
         <v>22</v>
       </c>
       <c r="N19" s="9" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>36.36363636363637</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="20" hidden="1">
@@ -1556,10 +1556,10 @@
         <v>33</v>
       </c>
       <c r="N20" s="9" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>12.12121212121212</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="21" hidden="1">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>4.347826086956522</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="22" hidden="1">
@@ -1660,10 +1660,10 @@
         <v>18</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>11.11111111111111</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="23" hidden="1">
@@ -1712,10 +1712,10 @@
         <v>31</v>
       </c>
       <c r="N23" s="9" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>9.67741935483871</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="24" hidden="1">
@@ -1816,10 +1816,10 @@
         <v>22</v>
       </c>
       <c r="N25" s="9" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>18.18181818181818</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="26" hidden="1">
@@ -1868,10 +1868,10 @@
         <v>20</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>85.70999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>35</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="27" hidden="1">
@@ -1923,7 +1923,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>46.66666666666666</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="28" hidden="1">
@@ -1975,7 +1975,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>14.81481481481481</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="29" hidden="1">
@@ -2024,10 +2024,10 @@
         <v>15</v>
       </c>
       <c r="N29" s="9" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>6.666666666666667</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="30" hidden="1">
@@ -2079,7 +2079,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>6.451612903225806</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="31" hidden="1">
@@ -2128,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="32" hidden="1">
@@ -2180,10 +2180,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="9" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>23.07692307692308</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="33" hidden="1">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="34" hidden="1">
@@ -2290,10 +2290,10 @@
         <v>36</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>22.22222222222222</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="35" hidden="1">
@@ -2342,10 +2342,10 @@
         <v>33</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>91.67</v>
+        <v>96.91</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>36.36363636363637</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="36" hidden="1">
@@ -2501,7 +2501,7 @@
         <v>100</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>14.28571428571428</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="39" hidden="1">
@@ -2605,7 +2605,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>4.761904761904762</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="41" hidden="1">
@@ -2657,10 +2657,10 @@
         <v>12</v>
       </c>
       <c r="N41" s="9" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>41.66666666666667</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="42" hidden="1">
@@ -2761,10 +2761,10 @@
         <v>32</v>
       </c>
       <c r="N43" s="9" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>34.375</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="44" hidden="1">
@@ -2816,7 +2816,7 @@
         <v>100</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>20</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="45" hidden="1">
@@ -2868,10 +2868,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>19.23076923076923</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="46" hidden="1">
@@ -2920,10 +2920,10 @@
         <v>32</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>3.125</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="47" hidden="1">
@@ -3024,10 +3024,10 @@
         <v>36</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="49" hidden="1">
@@ -3076,10 +3076,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>7.692307692307693</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="50" hidden="1">
@@ -3131,10 +3131,10 @@
         <v>33</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>42.42424242424242</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="51" hidden="1">
@@ -3183,10 +3183,10 @@
         <v>9</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>33.33333333333333</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="52" hidden="1">
@@ -3241,7 +3241,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="54" hidden="1">
@@ -3394,10 +3394,10 @@
         <v>27</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>7.407407407407407</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="56" hidden="1">
@@ -3504,10 +3504,10 @@
         <v>18</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>5.555555555555555</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="58" hidden="1">
@@ -3556,10 +3556,10 @@
         <v>16</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>12.5</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="59" hidden="1">
@@ -3608,10 +3608,10 @@
         <v>46</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>87.5</v>
+        <v>92.8</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>17.39130434782609</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="60" hidden="1">
@@ -3660,10 +3660,10 @@
         <v>26</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>19.23076923076923</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="61" hidden="1">
@@ -3715,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>22.22222222222222</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="62" hidden="1">
@@ -3764,10 +3764,10 @@
         <v>28</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>21.42857142857143</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="63" hidden="1">
@@ -3871,7 +3871,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="65" hidden="1">
@@ -3923,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="66" hidden="1">
@@ -3972,10 +3972,10 @@
         <v>12</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>58.33333333333334</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="67" hidden="1">
@@ -4024,10 +4024,10 @@
         <v>31</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>98.39</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="68" hidden="1">
@@ -4076,10 +4076,10 @@
         <v>40</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>27.5</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="69" hidden="1">
@@ -4128,10 +4128,10 @@
         <v>41</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>50</v>
+        <v>94.67</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>4.878048780487805</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="70" hidden="1">
@@ -4180,10 +4180,10 @@
         <v>30</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>10</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="71" hidden="1">
@@ -4284,10 +4284,10 @@
         <v>27</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>14.81481481481481</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="73" hidden="1">
@@ -4336,10 +4336,10 @@
         <v>22</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>31.81818181818182</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="74" hidden="1">
@@ -4391,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>31.25</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="75" hidden="1">
@@ -4443,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>3.125</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="76" hidden="1">
@@ -4492,10 +4492,10 @@
         <v>25</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>12</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="77" hidden="1">
@@ -4547,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>5.405405405405405</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="78" hidden="1">
@@ -4599,7 +4599,7 @@
         <v>100</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="79" hidden="1">
@@ -4648,10 +4648,10 @@
         <v>30</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>10</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="80" hidden="1">
@@ -4703,10 +4703,10 @@
         <v>28</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>7.142857142857142</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="81" hidden="1">
@@ -4755,10 +4755,10 @@
         <v>37</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>2.702702702702703</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="82" hidden="1">
@@ -4862,7 +4862,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>9.523809523809524</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="84" hidden="1">
@@ -4966,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>10.52631578947368</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="86" hidden="1">
@@ -5067,10 +5067,10 @@
         <v>49</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>16.3265306122449</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="88" hidden="1">
@@ -5122,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>40</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="89" hidden="1">
@@ -5174,10 +5174,10 @@
         <v>28</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>83.33</v>
+        <v>97.06</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>21.42857142857143</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="90" hidden="1">
@@ -5223,10 +5223,10 @@
         <v>32</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>21.875</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="91" hidden="1">
@@ -5324,10 +5324,10 @@
         <v>43</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>16.27906976744186</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="93" hidden="1">
@@ -5373,10 +5373,10 @@
         <v>30</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>6.666666666666667</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="94" hidden="1">
@@ -5471,10 +5471,10 @@
         <v>31</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>19.35483870967742</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="96" hidden="1">
@@ -5523,10 +5523,10 @@
         <v>25</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>24</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="97" hidden="1">
@@ -5572,10 +5572,10 @@
         <v>9</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>0</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="98" hidden="1">
@@ -5624,10 +5624,10 @@
         <v>2</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O98" s="3" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="99" hidden="1">
@@ -5676,7 +5676,7 @@
         <v>100</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>33.33333333333333</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="100" hidden="1">
@@ -5771,10 +5771,10 @@
         <v>14</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>28.57142857142857</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="102" hidden="1">
@@ -5820,10 +5820,10 @@
         <v>30</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="103" hidden="1">
@@ -5869,10 +5869,10 @@
         <v>41</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>90</v>
+        <v>92.8</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>24.39024390243902</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="104" hidden="1">
@@ -5918,10 +5918,10 @@
         <v>29</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>66.67</v>
+        <v>98.61</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>10.3448275862069</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="105" hidden="1">
@@ -5970,7 +5970,7 @@
         <v>100</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>15.38461538461539</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="106" hidden="1">
@@ -6016,10 +6016,10 @@
         <v>32</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>15.625</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="107" hidden="1">
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="109" hidden="1">
@@ -6172,7 +6172,7 @@
         <v>100</v>
       </c>
       <c r="O109" s="3" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="110" hidden="1">
@@ -6218,10 +6218,10 @@
         <v>24</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="111" hidden="1">
@@ -6267,10 +6267,10 @@
         <v>30</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="112" hidden="1">
@@ -6316,10 +6316,10 @@
         <v>55</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>12.72727272727273</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="113" hidden="1">
@@ -6365,10 +6365,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O113" s="3" t="n">
-        <v>11.53846153846154</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="114" hidden="1">
@@ -6414,10 +6414,10 @@
         <v>34</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>5.88235294117647</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="115" hidden="1">
@@ -6515,10 +6515,10 @@
         <v>22</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>22.72727272727273</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="117" hidden="1">
@@ -6564,10 +6564,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O117" s="3" t="n">
-        <v>23.07692307692308</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="118" hidden="1">
@@ -6616,7 +6616,7 @@
         <v>100</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>5.88235294117647</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="119" hidden="1">
@@ -6665,7 +6665,7 @@
         <v>100</v>
       </c>
       <c r="O119" s="3" t="n">
-        <v>19.44444444444445</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="120" hidden="1">
@@ -6711,10 +6711,10 @@
         <v>16</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>0</v>
+        <v>98.48</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>0</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="121" hidden="1">
@@ -6763,7 +6763,7 @@
         <v>100</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>7.142857142857142</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="122" hidden="1">
@@ -6815,7 +6815,7 @@
         <v>100</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="123" hidden="1">
@@ -6861,10 +6861,10 @@
         <v>36</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="124" hidden="1">
@@ -6913,10 +6913,10 @@
         <v>31</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>88.89</v>
+        <v>98.25</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>29.03225806451613</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="125" hidden="1">
@@ -6962,10 +6962,10 @@
         <v>31</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>25.80645161290322</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="126" hidden="1">
@@ -7066,7 +7066,7 @@
         <v>100</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="128" hidden="1">
@@ -7164,7 +7164,7 @@
         <v>100</v>
       </c>
       <c r="O129" s="3" t="n">
-        <v>33.33333333333333</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="130" hidden="1">
@@ -7259,10 +7259,10 @@
         <v>37</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O131" s="3" t="n">
-        <v>27.02702702702703</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="132" hidden="1">
@@ -7311,7 +7311,7 @@
         <v>100</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>5.555555555555555</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="133" hidden="1">
@@ -7357,10 +7357,10 @@
         <v>25</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>24</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="134" hidden="1">
@@ -7406,10 +7406,10 @@
         <v>19</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>26.31578947368421</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="135" hidden="1">
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="N135" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O135" s="9" t="n">
         <v>0</v>
@@ -7507,10 +7507,10 @@
         <v>36</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>91.67</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>33.33333333333333</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="137" hidden="1">
@@ -7556,10 +7556,10 @@
         <v>33</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>21.21212121212121</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="138" hidden="1">
@@ -7654,10 +7654,10 @@
         <v>27</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>25.92592592592592</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="140" hidden="1">
@@ -7706,10 +7706,10 @@
         <v>30</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>26.66666666666667</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="141" hidden="1">
@@ -7755,10 +7755,10 @@
         <v>9</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>50</v>
+        <v>96.3</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>22.22222222222222</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="142" hidden="1">
@@ -7804,10 +7804,10 @@
         <v>1</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O142" s="3" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="143" hidden="1">
@@ -7856,10 +7856,10 @@
         <v>4</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O143" s="3" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="144" hidden="1">
@@ -7905,10 +7905,10 @@
         <v>23</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O144" s="3" t="n">
-        <v>13.04347826086956</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="145" hidden="1">
@@ -7954,10 +7954,10 @@
         <v>38</v>
       </c>
       <c r="N145" s="3" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O145" s="3" t="n">
-        <v>26.31578947368421</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="146" hidden="1">
@@ -8003,10 +8003,10 @@
         <v>19</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>36.84210526315789</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="147" hidden="1">
@@ -8055,7 +8055,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>26.31578947368421</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="148" hidden="1">
@@ -8101,10 +8101,10 @@
         <v>29</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O148" s="3" t="n">
-        <v>20.68965517241379</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="149" hidden="1">
@@ -8202,10 +8202,10 @@
         <v>13</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O150" s="3" t="n">
-        <v>30.76923076923077</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="151" hidden="1">
@@ -8306,7 +8306,7 @@
         <v>100</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="153" hidden="1">
@@ -8358,7 +8358,7 @@
         <v>100</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="154" hidden="1">
@@ -8404,10 +8404,10 @@
         <v>24</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>33.33333333333333</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="155" hidden="1">
@@ -8453,10 +8453,10 @@
         <v>22</v>
       </c>
       <c r="N155" s="3" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>18.18181818181818</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="156" hidden="1">
@@ -8502,10 +8502,10 @@
         <v>49</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>14.28571428571428</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="157" hidden="1">
@@ -8551,10 +8551,10 @@
         <v>41</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>12.19512195121951</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="158" hidden="1">
@@ -8600,10 +8600,10 @@
         <v>26</v>
       </c>
       <c r="N158" s="3" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O158" s="3" t="n">
-        <v>34.61538461538461</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="159" hidden="1">
@@ -8701,10 +8701,10 @@
         <v>22</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>13.63636363636363</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="161" hidden="1">
@@ -8750,10 +8750,10 @@
         <v>23</v>
       </c>
       <c r="N161" s="3" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>17.39130434782609</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="162" hidden="1">
@@ -8802,7 +8802,7 @@
         <v>100</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>62.5</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="163" hidden="1">
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="O163" s="3" t="n">
-        <v>16</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="164" hidden="1">
@@ -8897,10 +8897,10 @@
         <v>51</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O164" s="3" t="n">
-        <v>15.68627450980392</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="165" hidden="1">
@@ -8949,7 +8949,7 @@
         <v>100</v>
       </c>
       <c r="O165" s="3" t="n">
-        <v>26.92307692307692</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="166" hidden="1">
@@ -9001,7 +9001,7 @@
         <v>100</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="167" hidden="1">
@@ -9047,10 +9047,10 @@
         <v>25</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>4</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="168" hidden="1">
@@ -9099,10 +9099,10 @@
         <v>35</v>
       </c>
       <c r="N168" s="3" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O168" s="3" t="n">
-        <v>8.571428571428571</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="169" hidden="1">
@@ -9148,10 +9148,10 @@
         <v>26</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O169" s="3" t="n">
-        <v>19.23076923076923</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="170" hidden="1">
@@ -9252,7 +9252,7 @@
         <v>100</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>100</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="172" hidden="1">
@@ -9350,7 +9350,7 @@
         <v>100</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>20</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="174" hidden="1">
@@ -9445,10 +9445,10 @@
         <v>37</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>18.91891891891892</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="176" hidden="1">
@@ -9497,7 +9497,7 @@
         <v>100</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>30</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="177" hidden="1">
@@ -9546,10 +9546,10 @@
         <v>28</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O177" s="3" t="n">
-        <v>14.28571428571428</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="178" hidden="1">
@@ -9598,10 +9598,10 @@
         <v>21</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>4.761904761904762</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="179" hidden="1">
@@ -9702,10 +9702,10 @@
         <v>24</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>75</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="181" hidden="1">
@@ -9754,10 +9754,10 @@
         <v>20</v>
       </c>
       <c r="N181" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O181" t="n">
-        <v>5</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="182" hidden="1">
@@ -9858,10 +9858,10 @@
         <v>12</v>
       </c>
       <c r="N183" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O183" t="n">
-        <v>33.33333333333333</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="184" hidden="1">
@@ -9910,10 +9910,10 @@
         <v>27</v>
       </c>
       <c r="N184" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O184" t="n">
-        <v>25.92592592592592</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="185" hidden="1">
@@ -9962,10 +9962,10 @@
         <v>25</v>
       </c>
       <c r="N185" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O185" t="n">
-        <v>16</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="186" hidden="1">
@@ -10014,10 +10014,10 @@
         <v>16</v>
       </c>
       <c r="N186" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O186" t="n">
-        <v>6.25</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="187" hidden="1">
@@ -10069,7 +10069,7 @@
         <v>100</v>
       </c>
       <c r="O187" t="n">
-        <v>9.090909090909092</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="188" hidden="1">
@@ -10118,10 +10118,10 @@
         <v>22</v>
       </c>
       <c r="N188" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O188" t="n">
-        <v>40.90909090909091</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="189" hidden="1">
@@ -10170,10 +10170,10 @@
         <v>29</v>
       </c>
       <c r="N189" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O189" t="n">
-        <v>10.3448275862069</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="190" hidden="1">
@@ -10222,10 +10222,10 @@
         <v>7</v>
       </c>
       <c r="N190" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O190" t="n">
-        <v>28.57142857142857</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="191" hidden="1">
@@ -10277,7 +10277,7 @@
         <v>100</v>
       </c>
       <c r="O191" t="n">
-        <v>66.66666666666666</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="192" hidden="1">
@@ -10378,10 +10378,10 @@
         <v>1</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="194" hidden="1">
@@ -10482,10 +10482,10 @@
         <v>11</v>
       </c>
       <c r="N195" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O195" t="n">
-        <v>18.18181818181818</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="196" hidden="1">
@@ -10589,7 +10589,7 @@
         <v>100</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="198" hidden="1">
@@ -10641,7 +10641,7 @@
         <v>100</v>
       </c>
       <c r="O198" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="199" hidden="1">
@@ -10690,10 +10690,10 @@
         <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="200" hidden="1">
@@ -10742,10 +10742,10 @@
         <v>22</v>
       </c>
       <c r="N200" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O200" t="n">
-        <v>22.72727272727273</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="201" hidden="1">
@@ -10794,10 +10794,10 @@
         <v>41</v>
       </c>
       <c r="N201" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O201" t="n">
-        <v>29.26829268292683</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="202" hidden="1">
@@ -10846,10 +10846,10 @@
         <v>21</v>
       </c>
       <c r="N202" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O202" t="n">
-        <v>4.761904761904762</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="203" hidden="1">
@@ -10898,10 +10898,10 @@
         <v>24</v>
       </c>
       <c r="N203" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O203" t="n">
-        <v>8.333333333333332</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="204" hidden="1">
@@ -11002,10 +11002,10 @@
         <v>16</v>
       </c>
       <c r="N205" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O205" t="n">
-        <v>25</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="206" hidden="1">
@@ -11054,10 +11054,10 @@
         <v>4</v>
       </c>
       <c r="N206" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O206" t="n">
-        <v>75</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="207" hidden="1">
@@ -11109,7 +11109,7 @@
         <v>100</v>
       </c>
       <c r="O207" t="n">
-        <v>7.142857142857142</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="208" hidden="1">
@@ -11161,7 +11161,7 @@
         <v>100</v>
       </c>
       <c r="O208" t="n">
-        <v>25</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="209" hidden="1">
@@ -11210,10 +11210,10 @@
         <v>18</v>
       </c>
       <c r="N209" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O209" t="n">
-        <v>22.22222222222222</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="210" hidden="1">
@@ -11265,7 +11265,7 @@
         <v>100</v>
       </c>
       <c r="O210" t="n">
-        <v>19.04761904761905</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="211" hidden="1">
@@ -11314,10 +11314,10 @@
         <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="212" hidden="1">
@@ -11366,10 +11366,10 @@
         <v>23</v>
       </c>
       <c r="N212" t="n">
-        <v>75</v>
+        <v>93.98</v>
       </c>
       <c r="O212" t="n">
-        <v>34.78260869565217</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="213" hidden="1">
@@ -11418,10 +11418,10 @@
         <v>21</v>
       </c>
       <c r="N213" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O213" t="n">
-        <v>9.523809523809524</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="214" hidden="1">
@@ -11470,10 +11470,10 @@
         <v>23</v>
       </c>
       <c r="N214" t="n">
-        <v>87.5</v>
+        <v>96.91</v>
       </c>
       <c r="O214" t="n">
-        <v>34.78260869565217</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="215" hidden="1">
@@ -11577,7 +11577,7 @@
         <v>100</v>
       </c>
       <c r="O216" t="n">
-        <v>11.76470588235294</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="217" hidden="1">
@@ -11681,7 +11681,7 @@
         <v>100</v>
       </c>
       <c r="O218" t="n">
-        <v>6.25</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="219" hidden="1">
@@ -11782,10 +11782,10 @@
         <v>26</v>
       </c>
       <c r="N220" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O220" t="n">
-        <v>23.07692307692308</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="221" hidden="1">
@@ -11837,7 +11837,7 @@
         <v>100</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="222" hidden="1">
@@ -11886,10 +11886,10 @@
         <v>25</v>
       </c>
       <c r="N222" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O222" t="n">
-        <v>20</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="223" hidden="1">
@@ -11935,10 +11935,10 @@
         <v>18</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O223" s="3" t="n">
-        <v>27.77777777777778</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="224" hidden="1">
@@ -12036,10 +12036,10 @@
         <v>38</v>
       </c>
       <c r="N225" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O225" s="3" t="n">
-        <v>18.42105263157895</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="226" hidden="1">
@@ -12082,10 +12082,10 @@
         <v>13</v>
       </c>
       <c r="N226" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O226" t="n">
-        <v>30.76923076923077</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="227" hidden="1">
@@ -12180,10 +12180,10 @@
         <v>26</v>
       </c>
       <c r="N228" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O228" t="n">
-        <v>11.53846153846154</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="229" hidden="1">
@@ -12229,10 +12229,10 @@
         <v>21</v>
       </c>
       <c r="N229" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O229" t="n">
-        <v>28.57142857142857</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="230" hidden="1">
@@ -12275,10 +12275,10 @@
         <v>31</v>
       </c>
       <c r="N230" t="n">
-        <v>90</v>
+        <v>92.8</v>
       </c>
       <c r="O230" t="n">
-        <v>32.25806451612903</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="231" hidden="1">
@@ -12324,10 +12324,10 @@
         <v>22</v>
       </c>
       <c r="N231" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O231" t="n">
-        <v>31.81818181818182</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="232" hidden="1">
@@ -12376,7 +12376,7 @@
         <v>100</v>
       </c>
       <c r="O232" t="n">
-        <v>15.78947368421053</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="233" hidden="1">
@@ -12419,10 +12419,10 @@
         <v>25</v>
       </c>
       <c r="N233" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O233" t="n">
-        <v>8</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="234" hidden="1">
@@ -12471,10 +12471,10 @@
         <v>29</v>
       </c>
       <c r="N234" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O234" t="n">
-        <v>13.79310344827586</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="235" hidden="1">
@@ -12517,10 +12517,10 @@
         <v>1</v>
       </c>
       <c r="N235" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O235" t="n">
-        <v>200</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="236" hidden="1">
@@ -12566,7 +12566,7 @@
         <v>100</v>
       </c>
       <c r="O236" t="n">
-        <v>100</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="237" hidden="1">
@@ -12667,7 +12667,7 @@
         <v>100</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="239" hidden="1">
@@ -12719,7 +12719,7 @@
         <v>100</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="240" hidden="1">
@@ -12771,7 +12771,7 @@
         <v>100</v>
       </c>
       <c r="O240" t="n">
-        <v>50</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="241" hidden="1">
@@ -12860,10 +12860,10 @@
         <v>15</v>
       </c>
       <c r="N242" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O242" t="n">
-        <v>6.666666666666667</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="243" hidden="1">
@@ -12909,10 +12909,10 @@
         <v>23</v>
       </c>
       <c r="N243" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O243" t="n">
-        <v>17.39130434782609</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="244" hidden="1">
@@ -12955,10 +12955,10 @@
         <v>23</v>
       </c>
       <c r="N244" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O244" t="n">
-        <v>17.39130434782609</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="245" hidden="1">
@@ -13004,10 +13004,10 @@
         <v>44</v>
       </c>
       <c r="N245" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O245" t="n">
-        <v>22.72727272727273</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="246" hidden="1">
@@ -13053,10 +13053,10 @@
         <v>17</v>
       </c>
       <c r="N246" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O246" t="n">
-        <v>17.64705882352941</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="247" hidden="1">
@@ -13102,10 +13102,10 @@
         <v>25</v>
       </c>
       <c r="N247" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O247" t="n">
-        <v>20</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="248" hidden="1">
@@ -13203,10 +13203,10 @@
         <v>18</v>
       </c>
       <c r="N249" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O249" t="n">
-        <v>16.66666666666666</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="250" hidden="1">
@@ -13252,10 +13252,10 @@
         <v>23</v>
       </c>
       <c r="N250" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O250" t="n">
-        <v>13.04347826086956</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="251" hidden="1">
@@ -13304,7 +13304,7 @@
         <v>100</v>
       </c>
       <c r="O251" t="n">
-        <v>27.27272727272727</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="252" hidden="1">
@@ -13353,7 +13353,7 @@
         <v>100</v>
       </c>
       <c r="O252" t="n">
-        <v>20.68965517241379</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="253" hidden="1">
@@ -13399,10 +13399,10 @@
         <v>21</v>
       </c>
       <c r="N253" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O253" t="n">
-        <v>23.80952380952381</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="254" hidden="1">
@@ -13448,7 +13448,7 @@
         <v>100</v>
       </c>
       <c r="O254" t="n">
-        <v>8</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="255" hidden="1">
@@ -13497,10 +13497,10 @@
         <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O255" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="256" hidden="1">
@@ -13546,10 +13546,10 @@
         <v>25</v>
       </c>
       <c r="N256" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O256" t="n">
-        <v>16</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="257" hidden="1">
@@ -13595,10 +13595,10 @@
         <v>27</v>
       </c>
       <c r="N257" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O257" t="n">
-        <v>18.51851851851852</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="258" hidden="1">
@@ -13644,10 +13644,10 @@
         <v>26</v>
       </c>
       <c r="N258" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O258" t="n">
-        <v>19.23076923076923</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="259" hidden="1">
@@ -13739,7 +13739,7 @@
         <v>100</v>
       </c>
       <c r="O260" t="n">
-        <v>71.42857142857143</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="261" hidden="1">
@@ -13834,7 +13834,7 @@
         <v>100</v>
       </c>
       <c r="O262" t="n">
-        <v>11.76470588235294</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="263" hidden="1">
@@ -13929,10 +13929,10 @@
         <v>17</v>
       </c>
       <c r="N264" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O264" t="n">
-        <v>17.64705882352941</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="265" hidden="1">
@@ -13981,7 +13981,7 @@
         <v>100</v>
       </c>
       <c r="O265" t="n">
-        <v>26.66666666666667</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="266" hidden="1">
@@ -14024,10 +14024,10 @@
         <v>16</v>
       </c>
       <c r="N266" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O266" t="n">
-        <v>12.5</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="267" hidden="1">
@@ -14073,10 +14073,10 @@
         <v>17</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O267" s="3" t="n">
-        <v>35.29411764705883</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="268" hidden="1">
@@ -14174,10 +14174,10 @@
         <v>27</v>
       </c>
       <c r="N269" s="3" t="n">
-        <v>87.5</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O269" s="3" t="n">
-        <v>29.62962962962963</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="270" hidden="1">
@@ -14223,10 +14223,10 @@
         <v>25</v>
       </c>
       <c r="N270" t="n">
-        <v>87.5</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O270" t="n">
-        <v>32</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="271" hidden="1">
@@ -14318,10 +14318,10 @@
         <v>24</v>
       </c>
       <c r="N272" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O272" t="n">
-        <v>45.83333333333333</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="273" hidden="1">
@@ -14367,10 +14367,10 @@
         <v>25</v>
       </c>
       <c r="N273" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O273" t="n">
-        <v>40</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="274" hidden="1">
@@ -14413,10 +14413,10 @@
         <v>33</v>
       </c>
       <c r="N274" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O274" t="n">
-        <v>36.36363636363637</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="275" hidden="1">
@@ -14459,10 +14459,10 @@
         <v>27</v>
       </c>
       <c r="N275" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O275" t="n">
-        <v>18.51851851851852</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="276" hidden="1">
@@ -14508,7 +14508,7 @@
         <v>100</v>
       </c>
       <c r="O276" t="n">
-        <v>64.70588235294117</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="277" hidden="1">
@@ -14554,10 +14554,10 @@
         <v>27</v>
       </c>
       <c r="N277" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O277" t="n">
-        <v>29.62962962962963</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="278" hidden="1">
@@ -14658,7 +14658,7 @@
         <v>100</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="280" hidden="1">
@@ -14710,7 +14710,7 @@
         <v>100</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="281" hidden="1">
@@ -14753,10 +14753,10 @@
         <v>18</v>
       </c>
       <c r="N281" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O281" t="n">
-        <v>61.11111111111111</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="282" hidden="1">
@@ -14802,10 +14802,10 @@
         <v>24</v>
       </c>
       <c r="N282" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O282" t="n">
-        <v>25</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="283" hidden="1">
@@ -14848,10 +14848,10 @@
         <v>18</v>
       </c>
       <c r="N283" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O283" t="n">
-        <v>38.88888888888889</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="284" hidden="1">
@@ -14897,10 +14897,10 @@
         <v>45</v>
       </c>
       <c r="N284" t="n">
-        <v>87.5</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O284" t="n">
-        <v>17.77777777777778</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="285" hidden="1">
@@ -14946,10 +14946,10 @@
         <v>37</v>
       </c>
       <c r="N285" t="n">
-        <v>87.5</v>
+        <v>94.67</v>
       </c>
       <c r="O285" t="n">
-        <v>21.62162162162162</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="286" hidden="1">
@@ -14995,10 +14995,10 @@
         <v>26</v>
       </c>
       <c r="N286" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O286" t="n">
-        <v>19.23076923076923</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="287" hidden="1">
@@ -15093,10 +15093,10 @@
         <v>22</v>
       </c>
       <c r="N288" t="n">
-        <v>87.5</v>
+        <v>96.72</v>
       </c>
       <c r="O288" t="n">
-        <v>36.36363636363637</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="289" hidden="1">
@@ -15142,10 +15142,10 @@
         <v>18</v>
       </c>
       <c r="N289" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O289" t="n">
-        <v>33.33333333333333</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="290" hidden="1">
@@ -15194,7 +15194,7 @@
         <v>100</v>
       </c>
       <c r="O290" t="n">
-        <v>36.36363636363637</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="291" hidden="1">
@@ -15243,7 +15243,7 @@
         <v>100</v>
       </c>
       <c r="O291" t="n">
-        <v>14.28571428571428</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="292" hidden="1">
@@ -15289,10 +15289,10 @@
         <v>22</v>
       </c>
       <c r="N292" t="n">
-        <v>85.70999999999999</v>
+        <v>98.48</v>
       </c>
       <c r="O292" t="n">
-        <v>31.81818181818182</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="293" hidden="1">
@@ -15338,7 +15338,7 @@
         <v>100</v>
       </c>
       <c r="O293" t="n">
-        <v>35</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="294" hidden="1">
@@ -15387,10 +15387,10 @@
         <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O294" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="295" hidden="1">
@@ -15436,10 +15436,10 @@
         <v>22</v>
       </c>
       <c r="N295" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O295" t="n">
-        <v>36.36363636363637</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="296" hidden="1">
@@ -15482,10 +15482,10 @@
         <v>6</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="O296" t="n">
-        <v>0</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="297" hidden="1">
@@ -15531,7 +15531,7 @@
         <v>100</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="298" hidden="1">
@@ -15574,10 +15574,10 @@
         <v>1</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O298" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="299" hidden="1">
@@ -15672,10 +15672,10 @@
         <v>13</v>
       </c>
       <c r="N300" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O300" t="n">
-        <v>38.46153846153847</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="301" hidden="1">
@@ -15721,10 +15721,10 @@
         <v>25</v>
       </c>
       <c r="N301" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O301" t="n">
-        <v>24</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="302" hidden="1">
@@ -15770,10 +15770,10 @@
         <v>28</v>
       </c>
       <c r="N302" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O302" t="n">
-        <v>25</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="303" hidden="1">
@@ -15865,7 +15865,7 @@
         <v>100</v>
       </c>
       <c r="O304" t="n">
-        <v>36.36363636363637</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="305" hidden="1">
@@ -15957,7 +15957,7 @@
         <v>100</v>
       </c>
       <c r="O306" t="n">
-        <v>33.33333333333333</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="307" hidden="1">
@@ -16052,10 +16052,10 @@
         <v>22</v>
       </c>
       <c r="N308" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O308" t="n">
-        <v>50</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="309" hidden="1">
@@ -16101,7 +16101,7 @@
         <v>100</v>
       </c>
       <c r="O309" t="n">
-        <v>15.78947368421053</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="310" hidden="1">
@@ -16147,10 +16147,10 @@
         <v>25</v>
       </c>
       <c r="N310" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O310" t="n">
-        <v>24</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="311" hidden="1">
@@ -16196,10 +16196,10 @@
         <v>17</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O311" s="3" t="n">
-        <v>11.76470588235294</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="312" hidden="1">
@@ -16297,10 +16297,10 @@
         <v>26</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O313" s="3" t="n">
-        <v>23.07692307692308</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="314" hidden="1">
@@ -16343,10 +16343,10 @@
         <v>21</v>
       </c>
       <c r="N314" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O314" t="n">
-        <v>14.28571428571428</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="315" hidden="1">
@@ -16441,10 +16441,10 @@
         <v>19</v>
       </c>
       <c r="N316" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O316" t="n">
-        <v>36.84210526315789</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="317" hidden="1">
@@ -16490,10 +16490,10 @@
         <v>26</v>
       </c>
       <c r="N317" t="n">
-        <v>85.70999999999999</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O317" t="n">
-        <v>26.92307692307692</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="318" hidden="1">
@@ -16536,10 +16536,10 @@
         <v>31</v>
       </c>
       <c r="N318" t="n">
-        <v>75</v>
+        <v>92.8</v>
       </c>
       <c r="O318" t="n">
-        <v>12.90322580645161</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="319" hidden="1">
@@ -16585,10 +16585,10 @@
         <v>13</v>
       </c>
       <c r="N319" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O319" t="n">
-        <v>23.07692307692308</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="320" hidden="1">
@@ -16637,7 +16637,7 @@
         <v>100</v>
       </c>
       <c r="O320" t="n">
-        <v>15.78947368421053</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="321" hidden="1">
@@ -16680,10 +16680,10 @@
         <v>21</v>
       </c>
       <c r="N321" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O321" t="n">
-        <v>76.19047619047619</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="322" hidden="1">
@@ -16781,10 +16781,10 @@
         <v>0</v>
       </c>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O323" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="324" hidden="1">
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="N324" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O324" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="325" hidden="1">
@@ -16885,10 +16885,10 @@
         <v>18</v>
       </c>
       <c r="N325" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O325" t="n">
-        <v>33.33333333333333</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="326" hidden="1">
@@ -16934,10 +16934,10 @@
         <v>22</v>
       </c>
       <c r="N326" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O326" t="n">
-        <v>4.545454545454546</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="327" hidden="1">
@@ -16983,10 +16983,10 @@
         <v>37</v>
       </c>
       <c r="N327" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O327" t="n">
-        <v>27.02702702702703</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="328" hidden="1">
@@ -17032,10 +17032,10 @@
         <v>31</v>
       </c>
       <c r="N328" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O328" t="n">
-        <v>25.80645161290322</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="329" hidden="1">
@@ -17078,10 +17078,10 @@
         <v>23</v>
       </c>
       <c r="N329" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O329" t="n">
-        <v>17.39130434782609</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="330" hidden="1">
@@ -17179,10 +17179,10 @@
         <v>18</v>
       </c>
       <c r="N331" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O331" t="n">
-        <v>16.66666666666666</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="332" hidden="1">
@@ -17225,10 +17225,10 @@
         <v>20</v>
       </c>
       <c r="N332" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O332" t="n">
-        <v>15</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="333" hidden="1">
@@ -17277,10 +17277,10 @@
         <v>0</v>
       </c>
       <c r="N333" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O333" t="n">
-        <v>0</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="334" hidden="1">
@@ -17329,7 +17329,7 @@
         <v>100</v>
       </c>
       <c r="O334" t="n">
-        <v>23.07692307692308</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="335" hidden="1">
@@ -17375,10 +17375,10 @@
         <v>22</v>
       </c>
       <c r="N335" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O335" t="n">
-        <v>9.090909090909092</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="336" hidden="1">
@@ -17427,7 +17427,7 @@
         <v>100</v>
       </c>
       <c r="O336" t="n">
-        <v>7.692307692307693</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="337" hidden="1">
@@ -17476,10 +17476,10 @@
         <v>0</v>
       </c>
       <c r="N337" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O337" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="338" hidden="1">
@@ -17525,10 +17525,10 @@
         <v>22</v>
       </c>
       <c r="N338" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O338" t="n">
-        <v>9.090909090909092</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="339" hidden="1">
@@ -17577,10 +17577,10 @@
         <v>18</v>
       </c>
       <c r="N339" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O339" t="n">
-        <v>27.77777777777778</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="340" hidden="1">
@@ -17623,10 +17623,10 @@
         <v>5</v>
       </c>
       <c r="N340" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O340" t="n">
-        <v>60</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="341" hidden="1">
@@ -17669,10 +17669,10 @@
         <v>0</v>
       </c>
       <c r="N341" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O341" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="342" hidden="1">
@@ -17721,10 +17721,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O342" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="343" hidden="1">
@@ -17813,10 +17813,10 @@
         <v>13</v>
       </c>
       <c r="N344" t="n">
-        <v>80</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O344" t="n">
-        <v>38.46153846153847</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="345" hidden="1">
@@ -17865,10 +17865,10 @@
         <v>28</v>
       </c>
       <c r="N345" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O345" t="n">
-        <v>14.28571428571428</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="346" hidden="1">
@@ -17914,10 +17914,10 @@
         <v>29</v>
       </c>
       <c r="N346" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O346" t="n">
-        <v>24.13793103448276</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="347" hidden="1">
@@ -18012,7 +18012,7 @@
         <v>100</v>
       </c>
       <c r="O348" t="n">
-        <v>11.11111111111111</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="349" hidden="1">
@@ -18107,7 +18107,7 @@
         <v>100</v>
       </c>
       <c r="O350" t="n">
-        <v>27.77777777777778</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="351" hidden="1">
@@ -18202,10 +18202,10 @@
         <v>32</v>
       </c>
       <c r="N352" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O352" t="n">
-        <v>12.5</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="353" hidden="1">
@@ -18254,7 +18254,7 @@
         <v>100</v>
       </c>
       <c r="O353" t="n">
-        <v>25</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="354" hidden="1">
@@ -18297,10 +18297,10 @@
         <v>21</v>
       </c>
       <c r="N354" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O354" t="n">
-        <v>28.57142857142857</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="355" hidden="1">
@@ -18349,10 +18349,10 @@
         <v>23</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O355" s="3" t="n">
-        <v>52.17391304347826</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="356" hidden="1">
@@ -18453,10 +18453,10 @@
         <v>23</v>
       </c>
       <c r="N357" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O357" s="3" t="n">
-        <v>43.47826086956522</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="358" hidden="1">
@@ -18505,10 +18505,10 @@
         <v>27</v>
       </c>
       <c r="N358" t="n">
-        <v>88.89</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O358" t="n">
-        <v>33.33333333333333</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="359" hidden="1">
@@ -18609,10 +18609,10 @@
         <v>25</v>
       </c>
       <c r="N360" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O360" t="n">
-        <v>36</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="361" hidden="1">
@@ -18661,10 +18661,10 @@
         <v>30</v>
       </c>
       <c r="N361" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O361" t="n">
-        <v>16.66666666666666</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="362" hidden="1">
@@ -18713,10 +18713,10 @@
         <v>14</v>
       </c>
       <c r="N362" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O362" t="n">
-        <v>107.1428571428571</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="363" hidden="1">
@@ -18765,10 +18765,10 @@
         <v>17</v>
       </c>
       <c r="N363" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O363" t="n">
-        <v>70.58823529411765</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="364" hidden="1">
@@ -18820,7 +18820,7 @@
         <v>100</v>
       </c>
       <c r="O364" t="n">
-        <v>50</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="365" hidden="1">
@@ -18869,10 +18869,10 @@
         <v>26</v>
       </c>
       <c r="N365" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O365" t="n">
-        <v>26.92307692307692</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="366" hidden="1">
@@ -18976,7 +18976,7 @@
         <v>100</v>
       </c>
       <c r="O367" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="368" hidden="1">
@@ -19028,7 +19028,7 @@
         <v>100</v>
       </c>
       <c r="O368" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="369" hidden="1">
@@ -19077,10 +19077,10 @@
         <v>23</v>
       </c>
       <c r="N369" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O369" t="n">
-        <v>34.78260869565217</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="370" hidden="1">
@@ -19129,10 +19129,10 @@
         <v>13</v>
       </c>
       <c r="N370" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O370" t="n">
-        <v>30.76923076923077</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="371" hidden="1">
@@ -19181,10 +19181,10 @@
         <v>38</v>
       </c>
       <c r="N371" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O371" t="n">
-        <v>31.57894736842105</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="372" hidden="1">
@@ -19233,10 +19233,10 @@
         <v>44</v>
       </c>
       <c r="N372" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O372" t="n">
-        <v>27.27272727272727</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="373" hidden="1">
@@ -19285,10 +19285,10 @@
         <v>9</v>
       </c>
       <c r="N373" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O373" t="n">
-        <v>66.66666666666666</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="374" hidden="1">
@@ -19389,10 +19389,10 @@
         <v>22</v>
       </c>
       <c r="N375" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O375" t="n">
-        <v>27.27272727272727</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="376" hidden="1">
@@ -19441,10 +19441,10 @@
         <v>28</v>
       </c>
       <c r="N376" t="n">
-        <v>75</v>
+        <v>95.31</v>
       </c>
       <c r="O376" t="n">
-        <v>14.28571428571428</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="377" hidden="1">
@@ -19496,7 +19496,7 @@
         <v>100</v>
       </c>
       <c r="O377" t="n">
-        <v>33.33333333333333</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="378" hidden="1">
@@ -19548,7 +19548,7 @@
         <v>100</v>
       </c>
       <c r="O378" t="n">
-        <v>43.47826086956522</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="379" hidden="1">
@@ -19597,10 +19597,10 @@
         <v>12</v>
       </c>
       <c r="N379" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O379" t="n">
-        <v>91.66666666666666</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="380" hidden="1">
@@ -19652,7 +19652,7 @@
         <v>100</v>
       </c>
       <c r="O380" t="n">
-        <v>50</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="381" hidden="1">
@@ -19704,7 +19704,7 @@
         <v>100</v>
       </c>
       <c r="O381" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="382" hidden="1">
@@ -19753,10 +19753,10 @@
         <v>16</v>
       </c>
       <c r="N382" t="n">
-        <v>91.67</v>
+        <v>93.98</v>
       </c>
       <c r="O382" t="n">
-        <v>75</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="383" hidden="1">
@@ -19805,10 +19805,10 @@
         <v>26</v>
       </c>
       <c r="N383" t="n">
-        <v>90</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O383" t="n">
-        <v>38.46153846153847</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="384" hidden="1">
@@ -19857,10 +19857,10 @@
         <v>30</v>
       </c>
       <c r="N384" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O384" t="n">
-        <v>20</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="385" hidden="1">
@@ -19909,10 +19909,10 @@
         <v>29</v>
       </c>
       <c r="N385" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O385" t="n">
-        <v>37.93103448275862</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="386" hidden="1">
@@ -19961,10 +19961,10 @@
         <v>6</v>
       </c>
       <c r="N386" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O386" t="n">
-        <v>50</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="387" hidden="1">
@@ -20013,10 +20013,10 @@
         <v>0</v>
       </c>
       <c r="N387" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O387" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="388" hidden="1">
@@ -20068,7 +20068,7 @@
         <v>100</v>
       </c>
       <c r="O388" t="n">
-        <v>50</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="389" hidden="1">
@@ -20169,10 +20169,10 @@
         <v>15</v>
       </c>
       <c r="N390" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O390" t="n">
-        <v>46.66666666666666</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="391" hidden="1">
@@ -20276,7 +20276,7 @@
         <v>100</v>
       </c>
       <c r="O392" t="n">
-        <v>17.39130434782609</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="393" hidden="1">
@@ -20380,7 +20380,7 @@
         <v>100</v>
       </c>
       <c r="O394" t="n">
-        <v>160</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="395" hidden="1">
@@ -20481,10 +20481,10 @@
         <v>40</v>
       </c>
       <c r="N396" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O396" t="n">
-        <v>20</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="397" hidden="1">
@@ -20536,7 +20536,7 @@
         <v>100</v>
       </c>
       <c r="O397" t="n">
-        <v>17.64705882352941</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="398" hidden="1">
@@ -20585,10 +20585,10 @@
         <v>21</v>
       </c>
       <c r="N398" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O398" t="n">
-        <v>33.33333333333333</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="399" hidden="1">
@@ -20637,10 +20637,10 @@
         <v>12</v>
       </c>
       <c r="N399" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O399" s="3" t="n">
-        <v>8.333333333333332</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="400" hidden="1">
@@ -20741,10 +20741,10 @@
         <v>36</v>
       </c>
       <c r="N401" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O401" s="3" t="n">
-        <v>16.66666666666666</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="402" hidden="1">
@@ -20793,10 +20793,10 @@
         <v>25</v>
       </c>
       <c r="N402" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O402" t="n">
-        <v>16</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="403" hidden="1">
@@ -20897,10 +20897,10 @@
         <v>29</v>
       </c>
       <c r="N404" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O404" t="n">
-        <v>13.79310344827586</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="405" hidden="1">
@@ -20949,10 +20949,10 @@
         <v>20</v>
       </c>
       <c r="N405" t="n">
-        <v>87.5</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O405" t="n">
-        <v>40</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="406" hidden="1">
@@ -21001,10 +21001,10 @@
         <v>29</v>
       </c>
       <c r="N406" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O406" t="n">
-        <v>6.896551724137931</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="407" hidden="1">
@@ -21053,10 +21053,10 @@
         <v>30</v>
       </c>
       <c r="N407" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O407" t="n">
-        <v>3.333333333333333</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="408" hidden="1">
@@ -21108,7 +21108,7 @@
         <v>100</v>
       </c>
       <c r="O408" t="n">
-        <v>15.78947368421053</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="409" hidden="1">
@@ -21157,10 +21157,10 @@
         <v>23</v>
       </c>
       <c r="N409" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O409" t="n">
-        <v>13.04347826086956</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="410" hidden="1">
@@ -21261,10 +21261,10 @@
         <v>0</v>
       </c>
       <c r="N411" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O411" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="412" hidden="1">
@@ -21313,10 +21313,10 @@
         <v>15</v>
       </c>
       <c r="N412" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O412" t="n">
-        <v>13.33333333333333</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="413" hidden="1">
@@ -21365,10 +21365,10 @@
         <v>23</v>
       </c>
       <c r="N413" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O413" t="n">
-        <v>13.04347826086956</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="414" hidden="1">
@@ -21417,10 +21417,10 @@
         <v>39</v>
       </c>
       <c r="N414" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O414" t="n">
-        <v>20.51282051282051</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="415" hidden="1">
@@ -21469,10 +21469,10 @@
         <v>23</v>
       </c>
       <c r="N415" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O415" t="n">
-        <v>21.73913043478261</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="416" hidden="1">
@@ -21521,10 +21521,10 @@
         <v>14</v>
       </c>
       <c r="N416" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O416" t="n">
-        <v>28.57142857142857</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="417" hidden="1">
@@ -21625,10 +21625,10 @@
         <v>23</v>
       </c>
       <c r="N418" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O418" t="n">
-        <v>13.04347826086956</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="419" hidden="1">
@@ -21680,7 +21680,7 @@
         <v>100</v>
       </c>
       <c r="O419" t="n">
-        <v>9.090909090909092</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="420" hidden="1">
@@ -21732,7 +21732,7 @@
         <v>100</v>
       </c>
       <c r="O420" t="n">
-        <v>36.84210526315789</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="421" hidden="1">
@@ -21781,10 +21781,10 @@
         <v>13</v>
       </c>
       <c r="N421" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O421" t="n">
-        <v>15.38461538461539</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="422" hidden="1">
@@ -21836,7 +21836,7 @@
         <v>100</v>
       </c>
       <c r="O422" t="n">
-        <v>16.66666666666666</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="423" hidden="1">
@@ -21885,10 +21885,10 @@
         <v>0</v>
       </c>
       <c r="N423" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O423" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="424" hidden="1">
@@ -21937,10 +21937,10 @@
         <v>24</v>
       </c>
       <c r="N424" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O424" t="n">
-        <v>12.5</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="425" hidden="1">
@@ -21989,10 +21989,10 @@
         <v>19</v>
       </c>
       <c r="N425" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O425" t="n">
-        <v>10.52631578947368</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="426" hidden="1">
@@ -22041,10 +22041,10 @@
         <v>22</v>
       </c>
       <c r="N426" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O426" t="n">
-        <v>36.36363636363637</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="427" hidden="1">
@@ -22093,10 +22093,10 @@
         <v>34</v>
       </c>
       <c r="N427" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O427" t="n">
-        <v>11.76470588235294</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="428" hidden="1">
@@ -22145,10 +22145,10 @@
         <v>8</v>
       </c>
       <c r="N428" t="n">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="O428" t="n">
-        <v>0</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="429" hidden="1">
@@ -22200,7 +22200,7 @@
         <v>100</v>
       </c>
       <c r="O429" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="430" hidden="1">
@@ -22301,10 +22301,10 @@
         <v>1</v>
       </c>
       <c r="N431" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O431" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="432" hidden="1">
@@ -22405,10 +22405,10 @@
         <v>14</v>
       </c>
       <c r="N433" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O433" t="n">
-        <v>21.42857142857143</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="434" hidden="1">
@@ -22512,7 +22512,7 @@
         <v>100</v>
       </c>
       <c r="O435" t="n">
-        <v>16.66666666666666</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="436" hidden="1">
@@ -22616,7 +22616,7 @@
         <v>100</v>
       </c>
       <c r="O437" t="n">
-        <v>6.666666666666667</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="438" hidden="1">
@@ -22717,10 +22717,10 @@
         <v>29</v>
       </c>
       <c r="N439" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O439" t="n">
-        <v>31.03448275862069</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="440" hidden="1">
@@ -22772,7 +22772,7 @@
         <v>100</v>
       </c>
       <c r="O440" t="n">
-        <v>7.142857142857142</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="441" hidden="1">
@@ -22821,10 +22821,10 @@
         <v>17</v>
       </c>
       <c r="N441" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O441" t="n">
-        <v>5.88235294117647</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="442" hidden="1">
@@ -22873,10 +22873,10 @@
         <v>19</v>
       </c>
       <c r="N442" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O442" s="3" t="n">
-        <v>42.10526315789473</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="443" hidden="1">
@@ -22977,10 +22977,10 @@
         <v>18</v>
       </c>
       <c r="N444" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O444" s="3" t="n">
-        <v>83.33333333333334</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="445" hidden="1">
@@ -23029,10 +23029,10 @@
         <v>0</v>
       </c>
       <c r="N445" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="446" hidden="1">
@@ -23081,10 +23081,10 @@
         <v>28</v>
       </c>
       <c r="N446" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O446" t="n">
-        <v>21.42857142857143</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="447" hidden="1">
@@ -23185,10 +23185,10 @@
         <v>26</v>
       </c>
       <c r="N448" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O448" t="n">
-        <v>15.38461538461539</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="449" hidden="1">
@@ -23237,10 +23237,10 @@
         <v>22</v>
       </c>
       <c r="N449" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O449" t="n">
-        <v>31.81818181818182</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="450" hidden="1">
@@ -23289,10 +23289,10 @@
         <v>25</v>
       </c>
       <c r="N450" t="n">
-        <v>75</v>
+        <v>92.8</v>
       </c>
       <c r="O450" t="n">
-        <v>32</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="451" hidden="1">
@@ -23341,10 +23341,10 @@
         <v>0</v>
       </c>
       <c r="N451" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O451" t="n">
-        <v>0</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="452" hidden="1">
@@ -23396,7 +23396,7 @@
         <v>100</v>
       </c>
       <c r="O452" t="n">
-        <v>11.11111111111111</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="453" hidden="1">
@@ -23445,10 +23445,10 @@
         <v>0</v>
       </c>
       <c r="N453" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O453" t="n">
-        <v>0</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="454" hidden="1">
@@ -23552,7 +23552,7 @@
         <v>100</v>
       </c>
       <c r="O455" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="456" hidden="1">
@@ -23601,10 +23601,10 @@
         <v>18</v>
       </c>
       <c r="N456" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O456" t="n">
-        <v>27.77777777777778</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="457" hidden="1">
@@ -23653,10 +23653,10 @@
         <v>21</v>
       </c>
       <c r="N457" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O457" t="n">
-        <v>23.80952380952381</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="458" hidden="1">
@@ -23705,10 +23705,10 @@
         <v>34</v>
       </c>
       <c r="N458" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O458" t="n">
-        <v>23.52941176470588</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="459" hidden="1">
@@ -23757,10 +23757,10 @@
         <v>23</v>
       </c>
       <c r="N459" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O459" t="n">
-        <v>21.73913043478261</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="460" hidden="1">
@@ -23809,10 +23809,10 @@
         <v>19</v>
       </c>
       <c r="N460" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O460" t="n">
-        <v>21.05263157894737</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="461" hidden="1">
@@ -23913,10 +23913,10 @@
         <v>21</v>
       </c>
       <c r="N462" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O462" t="n">
-        <v>14.28571428571428</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="463" hidden="1">
@@ -23965,10 +23965,10 @@
         <v>21</v>
       </c>
       <c r="N463" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O463" t="n">
-        <v>14.28571428571428</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="464" hidden="1">
@@ -24020,7 +24020,7 @@
         <v>100</v>
       </c>
       <c r="O464" t="n">
-        <v>14.28571428571428</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="465" hidden="1">
@@ -24072,7 +24072,7 @@
         <v>100</v>
       </c>
       <c r="O465" t="n">
-        <v>32</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="466" hidden="1">
@@ -24121,10 +24121,10 @@
         <v>20</v>
       </c>
       <c r="N466" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O466" t="n">
-        <v>5</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="467" hidden="1">
@@ -24176,7 +24176,7 @@
         <v>100</v>
       </c>
       <c r="O467" t="n">
-        <v>21.73913043478261</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="468" hidden="1">
@@ -24225,10 +24225,10 @@
         <v>0</v>
       </c>
       <c r="N468" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O468" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="469" hidden="1">
@@ -24277,10 +24277,10 @@
         <v>20</v>
       </c>
       <c r="N469" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O469" t="n">
-        <v>30</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="470" hidden="1">
@@ -24329,10 +24329,10 @@
         <v>16</v>
       </c>
       <c r="N470" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O470" t="n">
-        <v>25</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="471" hidden="1">
@@ -24381,10 +24381,10 @@
         <v>27</v>
       </c>
       <c r="N471" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O471" t="n">
-        <v>29.62962962962963</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="472" hidden="1">
@@ -24488,7 +24488,7 @@
         <v>100</v>
       </c>
       <c r="O473" t="n">
-        <v>38.46153846153847</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="474" hidden="1">
@@ -24592,7 +24592,7 @@
         <v>100</v>
       </c>
       <c r="O475" t="n">
-        <v>21.42857142857143</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="476" hidden="1">
@@ -24641,10 +24641,10 @@
         <v>6</v>
       </c>
       <c r="N476" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O476" t="n">
-        <v>50</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="477" hidden="1">
@@ -24693,10 +24693,10 @@
         <v>0</v>
       </c>
       <c r="N477" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O477" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="478" hidden="1">
@@ -24797,10 +24797,10 @@
         <v>11</v>
       </c>
       <c r="N479" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O479" t="n">
-        <v>0</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="480" hidden="1">
@@ -24901,10 +24901,10 @@
         <v>9</v>
       </c>
       <c r="N481" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O481" t="n">
-        <v>22.22222222222222</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="482" hidden="1">
@@ -25005,10 +25005,10 @@
         <v>26</v>
       </c>
       <c r="N483" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O483" t="n">
-        <v>19.23076923076923</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="484" hidden="1">
@@ -25060,7 +25060,7 @@
         <v>100</v>
       </c>
       <c r="O484" t="n">
-        <v>5.555555555555555</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="485" hidden="1">
@@ -25109,10 +25109,10 @@
         <v>21</v>
       </c>
       <c r="N485" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O485" t="n">
-        <v>28.57142857142857</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="486" hidden="1">
@@ -25161,10 +25161,10 @@
         <v>17</v>
       </c>
       <c r="N486" s="3" t="n">
-        <v>91.67</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O486" s="3" t="n">
-        <v>70.58823529411765</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="487" hidden="1">
@@ -25213,7 +25213,7 @@
         <v>0</v>
       </c>
       <c r="N487" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O487" s="9" t="n">
         <v>0</v>
@@ -25265,10 +25265,10 @@
         <v>29</v>
       </c>
       <c r="N488" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O488" s="3" t="n">
-        <v>41.37931034482759</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="489" hidden="1">
@@ -25317,10 +25317,10 @@
         <v>16</v>
       </c>
       <c r="N489" s="3" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O489" s="3" t="n">
-        <v>31.25</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="490" hidden="1">
@@ -25369,10 +25369,10 @@
         <v>28</v>
       </c>
       <c r="N490" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O490" t="n">
-        <v>25</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="491" hidden="1">
@@ -25473,10 +25473,10 @@
         <v>29</v>
       </c>
       <c r="N492" t="n">
-        <v>50</v>
+        <v>98.73</v>
       </c>
       <c r="O492" t="n">
-        <v>6.896551724137931</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="493" hidden="1">
@@ -25525,10 +25525,10 @@
         <v>7</v>
       </c>
       <c r="N493" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O493" t="n">
-        <v>57.14285714285714</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="494" hidden="1">
@@ -25577,10 +25577,10 @@
         <v>19</v>
       </c>
       <c r="N494" t="n">
-        <v>83.33</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O494" t="n">
-        <v>31.57894736842105</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="495" hidden="1">
@@ -25629,10 +25629,10 @@
         <v>30</v>
       </c>
       <c r="N495" t="n">
-        <v>91.67</v>
+        <v>92.8</v>
       </c>
       <c r="O495" t="n">
-        <v>40</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="496" hidden="1">
@@ -25681,10 +25681,10 @@
         <v>0</v>
       </c>
       <c r="N496" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O496" t="n">
-        <v>0</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="497" hidden="1">
@@ -25736,7 +25736,7 @@
         <v>100</v>
       </c>
       <c r="O497" t="n">
-        <v>20</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="498" hidden="1">
@@ -25785,10 +25785,10 @@
         <v>0</v>
       </c>
       <c r="N498" t="n">
-        <v>85.70999999999999</v>
+        <v>99</v>
       </c>
       <c r="O498" t="n">
-        <v>0</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="499" hidden="1">
@@ -25837,10 +25837,10 @@
         <v>0</v>
       </c>
       <c r="N499" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O499" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="500" hidden="1">
@@ -25944,7 +25944,7 @@
         <v>100</v>
       </c>
       <c r="O501" t="n">
-        <v>18.18181818181818</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="502" hidden="1">
@@ -25993,10 +25993,10 @@
         <v>0</v>
       </c>
       <c r="N502" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O502" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="503" hidden="1">
@@ -26097,10 +26097,10 @@
         <v>20</v>
       </c>
       <c r="N504" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O504" t="n">
-        <v>20</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="505" hidden="1">
@@ -26149,10 +26149,10 @@
         <v>22</v>
       </c>
       <c r="N505" t="n">
-        <v>75</v>
+        <v>98.39</v>
       </c>
       <c r="O505" t="n">
-        <v>18.18181818181818</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="506" hidden="1">
@@ -26201,10 +26201,10 @@
         <v>40</v>
       </c>
       <c r="N506" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O506" t="n">
-        <v>27.5</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="507" hidden="1">
@@ -26253,10 +26253,10 @@
         <v>12</v>
       </c>
       <c r="N507" t="n">
-        <v>50</v>
+        <v>94.67</v>
       </c>
       <c r="O507" t="n">
-        <v>33.33333333333333</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="508" hidden="1">
@@ -26305,10 +26305,10 @@
         <v>16</v>
       </c>
       <c r="N508" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O508" t="n">
-        <v>18.75</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="509" hidden="1">
@@ -26409,10 +26409,10 @@
         <v>20</v>
       </c>
       <c r="N510" t="n">
-        <v>75</v>
+        <v>96.72</v>
       </c>
       <c r="O510" t="n">
-        <v>20</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="511" hidden="1">
@@ -26461,10 +26461,10 @@
         <v>28</v>
       </c>
       <c r="N511" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O511" t="n">
-        <v>32.14285714285715</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="512" hidden="1">
@@ -26516,7 +26516,7 @@
         <v>100</v>
       </c>
       <c r="O512" t="n">
-        <v>20</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="513" hidden="1">
@@ -26568,7 +26568,7 @@
         <v>100</v>
       </c>
       <c r="O513" t="n">
-        <v>12.5</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="514" hidden="1">
@@ -26617,10 +26617,10 @@
         <v>45</v>
       </c>
       <c r="N514" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O514" t="n">
-        <v>13.33333333333333</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="515" hidden="1">
@@ -26672,7 +26672,7 @@
         <v>100</v>
       </c>
       <c r="O515" t="n">
-        <v>21.05263157894737</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="516" hidden="1">
@@ -26721,10 +26721,10 @@
         <v>18</v>
       </c>
       <c r="N516" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O516" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="517" hidden="1">
@@ -26773,10 +26773,10 @@
         <v>18</v>
       </c>
       <c r="N517" t="n">
-        <v>85.70999999999999</v>
+        <v>93.98</v>
       </c>
       <c r="O517" t="n">
-        <v>38.88888888888889</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="518" hidden="1">
@@ -26828,7 +26828,7 @@
         <v>100</v>
       </c>
       <c r="O518" t="n">
-        <v>8.333333333333332</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="519" hidden="1">
@@ -26877,10 +26877,10 @@
         <v>14</v>
       </c>
       <c r="N519" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O519" t="n">
-        <v>7.142857142857142</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="520" hidden="1">
@@ -26929,10 +26929,10 @@
         <v>30</v>
       </c>
       <c r="N520" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O520" t="n">
-        <v>10</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="521" hidden="1">
@@ -27088,7 +27088,7 @@
         <v>100</v>
       </c>
       <c r="O523" t="n">
-        <v>9.090909090909092</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="524" hidden="1">
@@ -27192,7 +27192,7 @@
         <v>100</v>
       </c>
       <c r="O525" t="n">
-        <v>20</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="526" hidden="1">
@@ -27241,10 +27241,10 @@
         <v>16</v>
       </c>
       <c r="N526" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O526" t="n">
-        <v>25</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="527" hidden="1">
@@ -27345,10 +27345,10 @@
         <v>34</v>
       </c>
       <c r="N528" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O528" t="n">
-        <v>47.05882352941176</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="529" hidden="1">
@@ -27400,7 +27400,7 @@
         <v>100</v>
       </c>
       <c r="O529" t="n">
-        <v>29.41176470588236</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="530" hidden="1">
@@ -27449,10 +27449,10 @@
         <v>21</v>
       </c>
       <c r="N530" t="n">
-        <v>80</v>
+        <v>97.06</v>
       </c>
       <c r="O530" t="n">
-        <v>23.80952380952381</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="531" hidden="1">
@@ -27504,10 +27504,10 @@
         <v>20</v>
       </c>
       <c r="N531" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O531" s="3" t="n">
-        <v>40</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="532" hidden="1">
@@ -27558,7 +27558,7 @@
         <v>0</v>
       </c>
       <c r="N532" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O532" s="9" t="n">
         <v>0</v>
@@ -27613,10 +27613,10 @@
         <v>26</v>
       </c>
       <c r="N533" s="9" t="n">
-        <v>85.70999999999999</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O533" s="9" t="n">
-        <v>26.92307692307692</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="534" hidden="1">
@@ -27668,10 +27668,10 @@
         <v>18</v>
       </c>
       <c r="N534" s="9" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O534" s="9" t="n">
-        <v>27.77777777777778</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="535" hidden="1">
@@ -27723,10 +27723,10 @@
         <v>32</v>
       </c>
       <c r="N535" s="9" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O535" s="9" t="n">
-        <v>34.375</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="536" hidden="1">
@@ -27833,10 +27833,10 @@
         <v>25</v>
       </c>
       <c r="N537" s="9" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O537" s="9" t="n">
-        <v>24</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="538" hidden="1">
@@ -27888,10 +27888,10 @@
         <v>8</v>
       </c>
       <c r="N538" s="9" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O538" s="9" t="n">
-        <v>25</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="539" hidden="1">
@@ -27943,10 +27943,10 @@
         <v>22</v>
       </c>
       <c r="N539" s="9" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O539" s="9" t="n">
-        <v>36.36363636363637</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="540" hidden="1">
@@ -27998,10 +27998,10 @@
         <v>21</v>
       </c>
       <c r="N540" s="9" t="n">
-        <v>80</v>
+        <v>92.8</v>
       </c>
       <c r="O540" s="9" t="n">
-        <v>47.61904761904761</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="541" hidden="1">
@@ -28053,10 +28053,10 @@
         <v>0</v>
       </c>
       <c r="N541" s="9" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O541" s="9" t="n">
-        <v>0</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="542" hidden="1">
@@ -28111,7 +28111,7 @@
         <v>100</v>
       </c>
       <c r="O542" s="9" t="n">
-        <v>38.46153846153847</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="543" hidden="1">
@@ -28163,10 +28163,10 @@
         <v>0</v>
       </c>
       <c r="N543" s="9" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O543" s="9" t="n">
-        <v>0</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="544" hidden="1">
@@ -28218,10 +28218,10 @@
         <v>0</v>
       </c>
       <c r="N544" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O544" s="9" t="n">
-        <v>0</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="545" hidden="1">
@@ -28331,7 +28331,7 @@
         <v>100</v>
       </c>
       <c r="O546" s="9" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="547" hidden="1">
@@ -28386,7 +28386,7 @@
         <v>100</v>
       </c>
       <c r="O547" s="9" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="548" hidden="1">
@@ -28493,10 +28493,10 @@
         <v>21</v>
       </c>
       <c r="N549" s="9" t="n">
-        <v>100</v>
+        <v>98.75</v>
       </c>
       <c r="O549" s="9" t="n">
-        <v>38.09523809523809</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="550" hidden="1">
@@ -28548,10 +28548,10 @@
         <v>22</v>
       </c>
       <c r="N550" s="9" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O550" s="9" t="n">
-        <v>36.36363636363637</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="551" hidden="1">
@@ -28603,10 +28603,10 @@
         <v>34</v>
       </c>
       <c r="N551" s="9" t="n">
-        <v>100</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O551" s="9" t="n">
-        <v>29.41176470588236</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="552" hidden="1">
@@ -28658,10 +28658,10 @@
         <v>19</v>
       </c>
       <c r="N552" s="9" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O552" s="9" t="n">
-        <v>42.10526315789473</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="553" hidden="1">
@@ -28713,10 +28713,10 @@
         <v>23</v>
       </c>
       <c r="N553" s="9" t="n">
-        <v>100</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O553" s="9" t="n">
-        <v>34.78260869565217</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="554" hidden="1">
@@ -28823,10 +28823,10 @@
         <v>20</v>
       </c>
       <c r="N555" s="9" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O555" s="9" t="n">
-        <v>35</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="556" hidden="1">
@@ -28878,10 +28878,10 @@
         <v>18</v>
       </c>
       <c r="N556" s="9" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O556" s="9" t="n">
-        <v>27.77777777777778</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="557" hidden="1">
@@ -28936,7 +28936,7 @@
         <v>100</v>
       </c>
       <c r="O557" s="9" t="n">
-        <v>33.33333333333333</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="558" hidden="1">
@@ -28991,7 +28991,7 @@
         <v>100</v>
       </c>
       <c r="O558" s="9" t="n">
-        <v>39.28571428571428</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="559" hidden="1">
@@ -29043,10 +29043,10 @@
         <v>19</v>
       </c>
       <c r="N559" s="9" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O559" s="9" t="n">
-        <v>42.10526315789473</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="560" hidden="1">
@@ -29101,7 +29101,7 @@
         <v>100</v>
       </c>
       <c r="O560" s="9" t="n">
-        <v>62.5</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="561" hidden="1">
@@ -29153,10 +29153,10 @@
         <v>18</v>
       </c>
       <c r="N561" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O561" s="9" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="562" hidden="1">
@@ -29208,10 +29208,10 @@
         <v>16</v>
       </c>
       <c r="N562" s="9" t="n">
-        <v>75</v>
+        <v>93.98</v>
       </c>
       <c r="O562" s="9" t="n">
-        <v>25</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="563" hidden="1">
@@ -29266,7 +29266,7 @@
         <v>100</v>
       </c>
       <c r="O563" s="9" t="n">
-        <v>40</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="564" hidden="1">
@@ -29318,10 +29318,10 @@
         <v>16</v>
       </c>
       <c r="N564" s="9" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O564" s="9" t="n">
-        <v>6.25</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="565" hidden="1">
@@ -29373,10 +29373,10 @@
         <v>23</v>
       </c>
       <c r="N565" s="9" t="n">
-        <v>100</v>
+        <v>96.91</v>
       </c>
       <c r="O565" s="9" t="n">
-        <v>34.78260869565217</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="566" hidden="1">
@@ -29541,7 +29541,7 @@
         <v>100</v>
       </c>
       <c r="O568" s="9" t="n">
-        <v>0</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="569" hidden="1">
@@ -29651,7 +29651,7 @@
         <v>100</v>
       </c>
       <c r="O570" s="9" t="n">
-        <v>26.66666666666667</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="571" hidden="1">
@@ -29703,10 +29703,10 @@
         <v>13</v>
       </c>
       <c r="N571" s="9" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O571" s="9" t="n">
-        <v>30.76923076923077</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="572" hidden="1">
@@ -29813,10 +29813,10 @@
         <v>28</v>
       </c>
       <c r="N573" s="9" t="n">
-        <v>91.67</v>
+        <v>99.17</v>
       </c>
       <c r="O573" s="9" t="n">
-        <v>42.85714285714285</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="574" hidden="1">
@@ -29871,7 +29871,7 @@
         <v>100</v>
       </c>
       <c r="O574" s="9" t="n">
-        <v>28.57142857142857</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="575" hidden="1">
@@ -29923,10 +29923,10 @@
         <v>21</v>
       </c>
       <c r="N575" s="9" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O575" s="9" t="n">
-        <v>14.28571428571428</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
     <row r="576">
@@ -29978,10 +29978,10 @@
         <v>17</v>
       </c>
       <c r="N576" s="3" t="n">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="O576" s="3" t="n">
-        <v>47.05882352941176</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="577">
@@ -30088,10 +30088,10 @@
         <v>21</v>
       </c>
       <c r="N578" s="3" t="n">
-        <v>100</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O578" s="3" t="n">
-        <v>47.61904761904761</v>
+        <v>29.08653846153846</v>
       </c>
     </row>
     <row r="579">
@@ -30143,10 +30143,10 @@
         <v>13</v>
       </c>
       <c r="N579" s="3" t="n">
-        <v>87.5</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="O579" s="3" t="n">
-        <v>61.53846153846154</v>
+        <v>26.1744966442953</v>
       </c>
     </row>
     <row r="580">
@@ -30198,10 +30198,10 @@
         <v>20</v>
       </c>
       <c r="N580" s="3" t="n">
-        <v>100</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="O580" s="3" t="n">
-        <v>60</v>
+        <v>27.51322751322751</v>
       </c>
     </row>
     <row r="581">
@@ -30308,10 +30308,10 @@
         <v>21</v>
       </c>
       <c r="N582" s="3" t="n">
-        <v>100</v>
+        <v>98.73</v>
       </c>
       <c r="O582" s="3" t="n">
-        <v>52.38095238095239</v>
+        <v>22.63610315186246</v>
       </c>
     </row>
     <row r="583">
@@ -30363,10 +30363,10 @@
         <v>4</v>
       </c>
       <c r="N583" s="3" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="O583" s="3" t="n">
-        <v>50</v>
+        <v>29.34782608695652</v>
       </c>
     </row>
     <row r="584">
@@ -30418,10 +30418,10 @@
         <v>17</v>
       </c>
       <c r="N584" s="3" t="n">
-        <v>100</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="O584" s="3" t="n">
-        <v>35.29411764705883</v>
+        <v>26.29969418960244</v>
       </c>
     </row>
     <row r="585">
@@ -30473,10 +30473,10 @@
         <v>20</v>
       </c>
       <c r="N585" s="3" t="n">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="O585" s="3" t="n">
-        <v>45</v>
+        <v>30.12048192771084</v>
       </c>
     </row>
     <row r="586">
@@ -30528,10 +30528,10 @@
         <v>0</v>
       </c>
       <c r="N586" s="3" t="n">
-        <v>100</v>
+        <v>98.61</v>
       </c>
       <c r="O586" s="3" t="n">
-        <v>0</v>
+        <v>32.14285714285715</v>
       </c>
     </row>
     <row r="587">
@@ -30586,7 +30586,7 @@
         <v>100</v>
       </c>
       <c r="O587" s="3" t="n">
-        <v>21.42857142857143</v>
+        <v>27.82608695652174</v>
       </c>
     </row>
     <row r="588">
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="N588" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O588" s="3" t="n">
-        <v>0</v>
+        <v>38.91050583657588</v>
       </c>
     </row>
     <row r="589">
@@ -30696,7 +30696,7 @@
         <v>100</v>
       </c>
       <c r="O589" s="3" t="n">
-        <v>28.57142857142857</v>
+        <v>65.38461538461539</v>
       </c>
     </row>
     <row r="590">
@@ -30806,7 +30806,7 @@
         <v>100</v>
       </c>
       <c r="O591" s="3" t="n">
-        <v>0</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="592">
@@ -30861,7 +30861,7 @@
         <v>100</v>
       </c>
       <c r="O592" s="3" t="n">
-        <v>0</v>
+        <v>131.0344827586207</v>
       </c>
     </row>
     <row r="593">
@@ -30968,10 +30968,10 @@
         <v>15</v>
       </c>
       <c r="N594" s="3" t="n">
-        <v>87.5</v>
+        <v>98.75</v>
       </c>
       <c r="O594" s="3" t="n">
-        <v>53.33333333333334</v>
+        <v>30.88803088803089</v>
       </c>
     </row>
     <row r="595">
@@ -31023,10 +31023,10 @@
         <v>19</v>
       </c>
       <c r="N595" s="3" t="n">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="O595" s="3" t="n">
-        <v>42.10526315789473</v>
+        <v>19.5583596214511</v>
       </c>
     </row>
     <row r="596">
@@ -31078,10 +31078,10 @@
         <v>28</v>
       </c>
       <c r="N596" s="3" t="n">
-        <v>94.73999999999999</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="O596" s="3" t="n">
-        <v>67.85714285714286</v>
+        <v>24.16225749559083</v>
       </c>
     </row>
     <row r="597">
@@ -31133,10 +31133,10 @@
         <v>10</v>
       </c>
       <c r="N597" s="3" t="n">
-        <v>100</v>
+        <v>94.67</v>
       </c>
       <c r="O597" s="3" t="n">
-        <v>90</v>
+        <v>20.77562326869806</v>
       </c>
     </row>
     <row r="598">
@@ -31188,10 +31188,10 @@
         <v>14</v>
       </c>
       <c r="N598" s="3" t="n">
-        <v>87.5</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="O598" s="3" t="n">
-        <v>57.14285714285714</v>
+        <v>21.3375796178344</v>
       </c>
     </row>
     <row r="599">
@@ -31298,10 +31298,10 @@
         <v>15</v>
       </c>
       <c r="N600" s="3" t="n">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="O600" s="3" t="n">
-        <v>26.66666666666667</v>
+        <v>21.18055555555555</v>
       </c>
     </row>
     <row r="601">
@@ -31353,10 +31353,10 @@
         <v>21</v>
       </c>
       <c r="N601" s="3" t="n">
-        <v>100</v>
+        <v>95.31</v>
       </c>
       <c r="O601" s="3" t="n">
-        <v>14.28571428571428</v>
+        <v>22.69503546099291</v>
       </c>
     </row>
     <row r="602">
@@ -31411,7 +31411,7 @@
         <v>100</v>
       </c>
       <c r="O602" s="3" t="n">
-        <v>40</v>
+        <v>26.54320987654321</v>
       </c>
     </row>
     <row r="603">
@@ -31466,7 +31466,7 @@
         <v>100</v>
       </c>
       <c r="O603" s="3" t="n">
-        <v>70</v>
+        <v>25.40983606557377</v>
       </c>
     </row>
     <row r="604">
@@ -31518,10 +31518,10 @@
         <v>17</v>
       </c>
       <c r="N604" s="3" t="n">
-        <v>100</v>
+        <v>98.48</v>
       </c>
       <c r="O604" s="3" t="n">
-        <v>47.05882352941176</v>
+        <v>20.95238095238095</v>
       </c>
     </row>
     <row r="605">
@@ -31576,7 +31576,7 @@
         <v>100</v>
       </c>
       <c r="O605" s="3" t="n">
-        <v>50</v>
+        <v>19.43573667711599</v>
       </c>
     </row>
     <row r="606">
@@ -31628,10 +31628,10 @@
         <v>18</v>
       </c>
       <c r="N606" s="3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O606" s="3" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="607">
@@ -31683,10 +31683,10 @@
         <v>21</v>
       </c>
       <c r="N607" s="3" t="n">
-        <v>100</v>
+        <v>93.98</v>
       </c>
       <c r="O607" s="3" t="n">
-        <v>57.14285714285714</v>
+        <v>25.69659442724458</v>
       </c>
     </row>
     <row r="608">
@@ -31741,7 +31741,7 @@
         <v>100</v>
       </c>
       <c r="O608" s="3" t="n">
-        <v>25</v>
+        <v>16.9811320754717</v>
       </c>
     </row>
     <row r="609">
@@ -31793,10 +31793,10 @@
         <v>15</v>
       </c>
       <c r="N609" s="3" t="n">
-        <v>100</v>
+        <v>98.25</v>
       </c>
       <c r="O609" s="3" t="n">
-        <v>13.33333333333333</v>
+        <v>16.76470588235294</v>
       </c>
     </row>
     <row r="610">
@@ -31848,10 +31848,10 @@
         <v>20</v>
       </c>
       <c r="N610" s="3" t="n">
-        <v>83.33</v>
+        <v>96.91</v>
       </c>
       <c r="O610" s="3" t="n">
-        <v>30</v>
+        <v>25.45931758530184</v>
       </c>
     </row>
     <row r="611">
@@ -32016,7 +32016,7 @@
         <v>100</v>
       </c>
       <c r="O613" s="3" t="n">
-        <v>0</v>
+        <v>27.53623188405797</v>
       </c>
     </row>
     <row r="614">
@@ -32126,7 +32126,7 @@
         <v>100</v>
       </c>
       <c r="O615" s="3" t="n">
-        <v>58.33333333333334</v>
+        <v>23.39449541284404</v>
       </c>
     </row>
     <row r="616">
@@ -32178,10 +32178,10 @@
         <v>13</v>
       </c>
       <c r="N616" s="3" t="n">
-        <v>100</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="O616" s="3" t="n">
-        <v>15.38461538461539</v>
+        <v>25.92592592592592</v>
       </c>
     </row>
     <row r="617">
@@ -32288,10 +32288,10 @@
         <v>22</v>
       </c>
       <c r="N618" s="3" t="n">
-        <v>100</v>
+        <v>99.17</v>
       </c>
       <c r="O618" s="3" t="n">
-        <v>40.90909090909091</v>
+        <v>27.84222737819026</v>
       </c>
     </row>
     <row r="619">
@@ -32346,7 +32346,7 @@
         <v>100</v>
       </c>
       <c r="O619" s="3" t="n">
-        <v>50</v>
+        <v>23.26732673267327</v>
       </c>
     </row>
     <row r="620">
@@ -32398,10 +32398,10 @@
         <v>21</v>
       </c>
       <c r="N620" s="3" t="n">
-        <v>100</v>
+        <v>97.06</v>
       </c>
       <c r="O620" s="3" t="n">
-        <v>23.80952380952381</v>
+        <v>21.7948717948718</v>
       </c>
     </row>
   </sheetData>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -623,7 +623,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O2" s="9" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="3" hidden="1">
@@ -724,7 +724,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="5" hidden="1">
@@ -776,7 +776,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="6" hidden="1">
@@ -831,7 +831,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="7" hidden="1">
@@ -935,7 +935,7 @@
         <v>98.73</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="9" hidden="1">
@@ -987,7 +987,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="10" hidden="1">
@@ -1039,7 +1039,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="11" hidden="1">
@@ -1091,7 +1091,7 @@
         <v>92.8</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="12" hidden="1">
@@ -1143,7 +1143,7 @@
         <v>98.61</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="13" hidden="1">
@@ -1195,7 +1195,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="14" hidden="1">
@@ -1247,7 +1247,7 @@
         <v>99</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="15" hidden="1">
@@ -1299,7 +1299,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="16" hidden="1">
@@ -1403,7 +1403,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="18" hidden="1">
@@ -1455,7 +1455,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="19" hidden="1">
@@ -1507,7 +1507,7 @@
         <v>98.75</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="20" hidden="1">
@@ -1559,7 +1559,7 @@
         <v>98.39</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="21" hidden="1">
@@ -1611,7 +1611,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="22" hidden="1">
@@ -1663,7 +1663,7 @@
         <v>94.67</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="23" hidden="1">
@@ -1715,7 +1715,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="24" hidden="1">
@@ -1819,7 +1819,7 @@
         <v>96.72</v>
       </c>
       <c r="O25" s="9" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="26" hidden="1">
@@ -1871,7 +1871,7 @@
         <v>95.31</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="27" hidden="1">
@@ -1923,7 +1923,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="9" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="28" hidden="1">
@@ -1975,7 +1975,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="29" hidden="1">
@@ -2027,7 +2027,7 @@
         <v>98.48</v>
       </c>
       <c r="O29" s="9" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="30" hidden="1">
@@ -2079,7 +2079,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="31" hidden="1">
@@ -2131,7 +2131,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="9" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" hidden="1">
@@ -2183,7 +2183,7 @@
         <v>93.98</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="33" hidden="1">
@@ -2238,7 +2238,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="34" hidden="1">
@@ -2293,7 +2293,7 @@
         <v>98.25</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="35" hidden="1">
@@ -2345,7 +2345,7 @@
         <v>96.91</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="36" hidden="1">
@@ -2501,7 +2501,7 @@
         <v>100</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="39" hidden="1">
@@ -2605,7 +2605,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="41" hidden="1">
@@ -2660,7 +2660,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="42" hidden="1">
@@ -2764,7 +2764,7 @@
         <v>99.17</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="44" hidden="1">
@@ -2816,7 +2816,7 @@
         <v>100</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="45" hidden="1">
@@ -2871,7 +2871,7 @@
         <v>97.06</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="46" hidden="1">
@@ -2923,7 +2923,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="47" hidden="1">
@@ -3027,7 +3027,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="49" hidden="1">
@@ -3079,7 +3079,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="50" hidden="1">
@@ -3134,7 +3134,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="51" hidden="1">
@@ -3186,7 +3186,7 @@
         <v>96.3</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="52" hidden="1">
@@ -3241,7 +3241,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="53" hidden="1">
@@ -3293,7 +3293,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="54" hidden="1">
@@ -3397,7 +3397,7 @@
         <v>98.73</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="56" hidden="1">
@@ -3507,7 +3507,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="58" hidden="1">
@@ -3559,7 +3559,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="59" hidden="1">
@@ -3611,7 +3611,7 @@
         <v>92.8</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="60" hidden="1">
@@ -3663,7 +3663,7 @@
         <v>98.61</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="61" hidden="1">
@@ -3715,7 +3715,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="62" hidden="1">
@@ -3767,7 +3767,7 @@
         <v>99</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="63" hidden="1">
@@ -3871,7 +3871,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="65" hidden="1">
@@ -3923,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="66" hidden="1">
@@ -3975,7 +3975,7 @@
         <v>98.75</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="67" hidden="1">
@@ -4027,7 +4027,7 @@
         <v>98.39</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="68" hidden="1">
@@ -4079,7 +4079,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="69" hidden="1">
@@ -4131,7 +4131,7 @@
         <v>94.67</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="70" hidden="1">
@@ -4183,7 +4183,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="71" hidden="1">
@@ -4287,7 +4287,7 @@
         <v>96.72</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="73" hidden="1">
@@ -4339,7 +4339,7 @@
         <v>95.31</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="74" hidden="1">
@@ -4391,7 +4391,7 @@
         <v>100</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="75" hidden="1">
@@ -4443,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="76" hidden="1">
@@ -4495,7 +4495,7 @@
         <v>98.48</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="77" hidden="1">
@@ -4547,7 +4547,7 @@
         <v>100</v>
       </c>
       <c r="O77" s="3" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="78" hidden="1">
@@ -4599,7 +4599,7 @@
         <v>100</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" hidden="1">
@@ -4651,7 +4651,7 @@
         <v>93.98</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="80" hidden="1">
@@ -4706,7 +4706,7 @@
         <v>98.25</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="81" hidden="1">
@@ -4758,7 +4758,7 @@
         <v>96.91</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="82" hidden="1">
@@ -4862,7 +4862,7 @@
         <v>100</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="84" hidden="1">
@@ -4966,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="86" hidden="1">
@@ -5070,7 +5070,7 @@
         <v>99.17</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="88" hidden="1">
@@ -5122,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="89" hidden="1">
@@ -5177,7 +5177,7 @@
         <v>97.06</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="90" hidden="1">
@@ -5226,7 +5226,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="91" hidden="1">
@@ -5327,7 +5327,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="93" hidden="1">
@@ -5376,7 +5376,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="94" hidden="1">
@@ -5474,7 +5474,7 @@
         <v>98.73</v>
       </c>
       <c r="O95" s="3" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="96" hidden="1">
@@ -5526,7 +5526,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O96" s="3" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="97" hidden="1">
@@ -5575,7 +5575,7 @@
         <v>96.3</v>
       </c>
       <c r="O97" s="3" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="98" hidden="1">
@@ -5627,7 +5627,7 @@
         <v>100</v>
       </c>
       <c r="O98" s="3" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="99" hidden="1">
@@ -5676,7 +5676,7 @@
         <v>100</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="100" hidden="1">
@@ -5774,7 +5774,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="102" hidden="1">
@@ -5823,7 +5823,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="103" hidden="1">
@@ -5872,7 +5872,7 @@
         <v>92.8</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="104" hidden="1">
@@ -5921,7 +5921,7 @@
         <v>98.61</v>
       </c>
       <c r="O104" s="3" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="105" hidden="1">
@@ -5970,7 +5970,7 @@
         <v>100</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="106" hidden="1">
@@ -6019,7 +6019,7 @@
         <v>99</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="107" hidden="1">
@@ -6120,7 +6120,7 @@
         <v>100</v>
       </c>
       <c r="O108" s="3" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="109" hidden="1">
@@ -6172,7 +6172,7 @@
         <v>100</v>
       </c>
       <c r="O109" s="3" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="110" hidden="1">
@@ -6221,7 +6221,7 @@
         <v>98.75</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="111" hidden="1">
@@ -6270,7 +6270,7 @@
         <v>98.39</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="112" hidden="1">
@@ -6319,7 +6319,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="113" hidden="1">
@@ -6368,7 +6368,7 @@
         <v>94.67</v>
       </c>
       <c r="O113" s="3" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="114" hidden="1">
@@ -6417,7 +6417,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="115" hidden="1">
@@ -6518,7 +6518,7 @@
         <v>96.72</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="117" hidden="1">
@@ -6567,7 +6567,7 @@
         <v>95.31</v>
       </c>
       <c r="O117" s="3" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="118" hidden="1">
@@ -6616,7 +6616,7 @@
         <v>100</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="119" hidden="1">
@@ -6665,7 +6665,7 @@
         <v>100</v>
       </c>
       <c r="O119" s="3" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="120" hidden="1">
@@ -6714,7 +6714,7 @@
         <v>98.48</v>
       </c>
       <c r="O120" s="3" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="121" hidden="1">
@@ -6763,7 +6763,7 @@
         <v>100</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="122" hidden="1">
@@ -6815,7 +6815,7 @@
         <v>100</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" hidden="1">
@@ -6864,7 +6864,7 @@
         <v>93.98</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="124" hidden="1">
@@ -6916,7 +6916,7 @@
         <v>98.25</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="125" hidden="1">
@@ -6965,7 +6965,7 @@
         <v>96.91</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="126" hidden="1">
@@ -7066,7 +7066,7 @@
         <v>100</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="128" hidden="1">
@@ -7164,7 +7164,7 @@
         <v>100</v>
       </c>
       <c r="O129" s="3" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="130" hidden="1">
@@ -7262,7 +7262,7 @@
         <v>99.17</v>
       </c>
       <c r="O131" s="3" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="132" hidden="1">
@@ -7311,7 +7311,7 @@
         <v>100</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="133" hidden="1">
@@ -7360,7 +7360,7 @@
         <v>97.06</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="134" hidden="1">
@@ -7409,7 +7409,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="135" hidden="1">
@@ -7510,7 +7510,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="137" hidden="1">
@@ -7559,7 +7559,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="138" hidden="1">
@@ -7657,7 +7657,7 @@
         <v>98.73</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="140" hidden="1">
@@ -7709,7 +7709,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="141" hidden="1">
@@ -7758,7 +7758,7 @@
         <v>96.3</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="142" hidden="1">
@@ -7807,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="O142" s="3" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="143" hidden="1">
@@ -7859,7 +7859,7 @@
         <v>100</v>
       </c>
       <c r="O143" s="3" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="144" hidden="1">
@@ -7908,7 +7908,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O144" s="3" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="145" hidden="1">
@@ -7957,7 +7957,7 @@
         <v>92.8</v>
       </c>
       <c r="O145" s="3" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="146" hidden="1">
@@ -8006,7 +8006,7 @@
         <v>98.61</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="147" hidden="1">
@@ -8055,7 +8055,7 @@
         <v>100</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="148" hidden="1">
@@ -8104,7 +8104,7 @@
         <v>99</v>
       </c>
       <c r="O148" s="3" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="149" hidden="1">
@@ -8205,7 +8205,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O150" s="3" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="151" hidden="1">
@@ -8306,7 +8306,7 @@
         <v>100</v>
       </c>
       <c r="O152" s="3" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="153" hidden="1">
@@ -8358,7 +8358,7 @@
         <v>100</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="154" hidden="1">
@@ -8407,7 +8407,7 @@
         <v>98.75</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="155" hidden="1">
@@ -8456,7 +8456,7 @@
         <v>98.39</v>
       </c>
       <c r="O155" s="3" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="156" hidden="1">
@@ -8505,7 +8505,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O156" s="3" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="157" hidden="1">
@@ -8554,7 +8554,7 @@
         <v>94.67</v>
       </c>
       <c r="O157" s="3" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="158" hidden="1">
@@ -8603,7 +8603,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O158" s="3" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="159" hidden="1">
@@ -8704,7 +8704,7 @@
         <v>96.72</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="161" hidden="1">
@@ -8753,7 +8753,7 @@
         <v>95.31</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="162" hidden="1">
@@ -8802,7 +8802,7 @@
         <v>100</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="163" hidden="1">
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="O163" s="3" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="164" hidden="1">
@@ -8900,7 +8900,7 @@
         <v>98.48</v>
       </c>
       <c r="O164" s="3" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="165" hidden="1">
@@ -8949,7 +8949,7 @@
         <v>100</v>
       </c>
       <c r="O165" s="3" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="166" hidden="1">
@@ -9001,7 +9001,7 @@
         <v>100</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" hidden="1">
@@ -9050,7 +9050,7 @@
         <v>93.98</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="168" hidden="1">
@@ -9102,7 +9102,7 @@
         <v>98.25</v>
       </c>
       <c r="O168" s="3" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="169" hidden="1">
@@ -9151,7 +9151,7 @@
         <v>96.91</v>
       </c>
       <c r="O169" s="3" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="170" hidden="1">
@@ -9252,7 +9252,7 @@
         <v>100</v>
       </c>
       <c r="O171" s="3" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="172" hidden="1">
@@ -9350,7 +9350,7 @@
         <v>100</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="174" hidden="1">
@@ -9448,7 +9448,7 @@
         <v>99.17</v>
       </c>
       <c r="O175" s="3" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="176" hidden="1">
@@ -9497,7 +9497,7 @@
         <v>100</v>
       </c>
       <c r="O176" s="3" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="177" hidden="1">
@@ -9549,7 +9549,7 @@
         <v>97.06</v>
       </c>
       <c r="O177" s="3" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="178" hidden="1">
@@ -9601,7 +9601,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O178" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="179" hidden="1">
@@ -9705,7 +9705,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O180" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="181" hidden="1">
@@ -9757,7 +9757,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O181" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="182" hidden="1">
@@ -9861,7 +9861,7 @@
         <v>98.73</v>
       </c>
       <c r="O183" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="184" hidden="1">
@@ -9913,7 +9913,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O184" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="185" hidden="1">
@@ -9965,7 +9965,7 @@
         <v>92.8</v>
       </c>
       <c r="O185" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="186" hidden="1">
@@ -10017,7 +10017,7 @@
         <v>98.61</v>
       </c>
       <c r="O186" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="187" hidden="1">
@@ -10069,7 +10069,7 @@
         <v>100</v>
       </c>
       <c r="O187" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="188" hidden="1">
@@ -10121,7 +10121,7 @@
         <v>99</v>
       </c>
       <c r="O188" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="189" hidden="1">
@@ -10173,7 +10173,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O189" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="190" hidden="1">
@@ -10225,7 +10225,7 @@
         <v>96.3</v>
       </c>
       <c r="O190" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="191" hidden="1">
@@ -10277,7 +10277,7 @@
         <v>100</v>
       </c>
       <c r="O191" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="192" hidden="1">
@@ -10381,7 +10381,7 @@
         <v>100</v>
       </c>
       <c r="O193" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="194" hidden="1">
@@ -10485,7 +10485,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O195" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="196" hidden="1">
@@ -10589,7 +10589,7 @@
         <v>100</v>
       </c>
       <c r="O197" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="198" hidden="1">
@@ -10641,7 +10641,7 @@
         <v>100</v>
       </c>
       <c r="O198" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="199" hidden="1">
@@ -10693,7 +10693,7 @@
         <v>98.75</v>
       </c>
       <c r="O199" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="200" hidden="1">
@@ -10745,7 +10745,7 @@
         <v>98.39</v>
       </c>
       <c r="O200" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="201" hidden="1">
@@ -10797,7 +10797,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O201" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="202" hidden="1">
@@ -10849,7 +10849,7 @@
         <v>94.67</v>
       </c>
       <c r="O202" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="203" hidden="1">
@@ -10901,7 +10901,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O203" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="204" hidden="1">
@@ -11005,7 +11005,7 @@
         <v>96.72</v>
       </c>
       <c r="O205" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="206" hidden="1">
@@ -11057,7 +11057,7 @@
         <v>95.31</v>
       </c>
       <c r="O206" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="207" hidden="1">
@@ -11109,7 +11109,7 @@
         <v>100</v>
       </c>
       <c r="O207" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="208" hidden="1">
@@ -11161,7 +11161,7 @@
         <v>100</v>
       </c>
       <c r="O208" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="209" hidden="1">
@@ -11213,7 +11213,7 @@
         <v>98.48</v>
       </c>
       <c r="O209" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="210" hidden="1">
@@ -11265,7 +11265,7 @@
         <v>100</v>
       </c>
       <c r="O210" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="211" hidden="1">
@@ -11317,7 +11317,7 @@
         <v>100</v>
       </c>
       <c r="O211" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" hidden="1">
@@ -11369,7 +11369,7 @@
         <v>93.98</v>
       </c>
       <c r="O212" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="213" hidden="1">
@@ -11421,7 +11421,7 @@
         <v>98.25</v>
       </c>
       <c r="O213" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="214" hidden="1">
@@ -11473,7 +11473,7 @@
         <v>96.91</v>
       </c>
       <c r="O214" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="215" hidden="1">
@@ -11577,7 +11577,7 @@
         <v>100</v>
       </c>
       <c r="O216" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="217" hidden="1">
@@ -11681,7 +11681,7 @@
         <v>100</v>
       </c>
       <c r="O218" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="219" hidden="1">
@@ -11785,7 +11785,7 @@
         <v>99.17</v>
       </c>
       <c r="O220" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="221" hidden="1">
@@ -11837,7 +11837,7 @@
         <v>100</v>
       </c>
       <c r="O221" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="222" hidden="1">
@@ -11889,7 +11889,7 @@
         <v>97.06</v>
       </c>
       <c r="O222" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="223" hidden="1">
@@ -11938,7 +11938,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O223" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="224" hidden="1">
@@ -12039,7 +12039,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O225" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="226" hidden="1">
@@ -12085,7 +12085,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O226" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="227" hidden="1">
@@ -12183,7 +12183,7 @@
         <v>98.73</v>
       </c>
       <c r="O228" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="229" hidden="1">
@@ -12232,7 +12232,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O229" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="230" hidden="1">
@@ -12278,7 +12278,7 @@
         <v>92.8</v>
       </c>
       <c r="O230" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="231" hidden="1">
@@ -12327,7 +12327,7 @@
         <v>98.61</v>
       </c>
       <c r="O231" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="232" hidden="1">
@@ -12376,7 +12376,7 @@
         <v>100</v>
       </c>
       <c r="O232" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="233" hidden="1">
@@ -12422,7 +12422,7 @@
         <v>99</v>
       </c>
       <c r="O233" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="234" hidden="1">
@@ -12474,7 +12474,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O234" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="235" hidden="1">
@@ -12520,7 +12520,7 @@
         <v>96.3</v>
       </c>
       <c r="O235" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="236" hidden="1">
@@ -12566,7 +12566,7 @@
         <v>100</v>
       </c>
       <c r="O236" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="237" hidden="1">
@@ -12667,7 +12667,7 @@
         <v>100</v>
       </c>
       <c r="O238" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="239" hidden="1">
@@ -12719,7 +12719,7 @@
         <v>100</v>
       </c>
       <c r="O239" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="240" hidden="1">
@@ -12771,7 +12771,7 @@
         <v>100</v>
       </c>
       <c r="O240" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="241" hidden="1">
@@ -12863,7 +12863,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O242" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="243" hidden="1">
@@ -12912,7 +12912,7 @@
         <v>98.75</v>
       </c>
       <c r="O243" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="244" hidden="1">
@@ -12958,7 +12958,7 @@
         <v>98.39</v>
       </c>
       <c r="O244" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="245" hidden="1">
@@ -13007,7 +13007,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O245" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="246" hidden="1">
@@ -13056,7 +13056,7 @@
         <v>94.67</v>
       </c>
       <c r="O246" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="247" hidden="1">
@@ -13105,7 +13105,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O247" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="248" hidden="1">
@@ -13206,7 +13206,7 @@
         <v>96.72</v>
       </c>
       <c r="O249" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="250" hidden="1">
@@ -13255,7 +13255,7 @@
         <v>95.31</v>
       </c>
       <c r="O250" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="251" hidden="1">
@@ -13304,7 +13304,7 @@
         <v>100</v>
       </c>
       <c r="O251" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="252" hidden="1">
@@ -13353,7 +13353,7 @@
         <v>100</v>
       </c>
       <c r="O252" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="253" hidden="1">
@@ -13402,7 +13402,7 @@
         <v>98.48</v>
       </c>
       <c r="O253" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="254" hidden="1">
@@ -13448,7 +13448,7 @@
         <v>100</v>
       </c>
       <c r="O254" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="255" hidden="1">
@@ -13500,7 +13500,7 @@
         <v>100</v>
       </c>
       <c r="O255" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" hidden="1">
@@ -13549,7 +13549,7 @@
         <v>93.98</v>
       </c>
       <c r="O256" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="257" hidden="1">
@@ -13598,7 +13598,7 @@
         <v>98.25</v>
       </c>
       <c r="O257" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="258" hidden="1">
@@ -13647,7 +13647,7 @@
         <v>96.91</v>
       </c>
       <c r="O258" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="259" hidden="1">
@@ -13739,7 +13739,7 @@
         <v>100</v>
       </c>
       <c r="O260" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="261" hidden="1">
@@ -13834,7 +13834,7 @@
         <v>100</v>
       </c>
       <c r="O262" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="263" hidden="1">
@@ -13932,7 +13932,7 @@
         <v>99.17</v>
       </c>
       <c r="O264" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="265" hidden="1">
@@ -13981,7 +13981,7 @@
         <v>100</v>
       </c>
       <c r="O265" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="266" hidden="1">
@@ -14027,7 +14027,7 @@
         <v>97.06</v>
       </c>
       <c r="O266" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="267" hidden="1">
@@ -14076,7 +14076,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O267" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="268" hidden="1">
@@ -14177,7 +14177,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O269" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="270" hidden="1">
@@ -14226,7 +14226,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O270" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="271" hidden="1">
@@ -14321,7 +14321,7 @@
         <v>98.73</v>
       </c>
       <c r="O272" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="273" hidden="1">
@@ -14370,7 +14370,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O273" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="274" hidden="1">
@@ -14416,7 +14416,7 @@
         <v>92.8</v>
       </c>
       <c r="O274" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="275" hidden="1">
@@ -14462,7 +14462,7 @@
         <v>98.61</v>
       </c>
       <c r="O275" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="276" hidden="1">
@@ -14508,7 +14508,7 @@
         <v>100</v>
       </c>
       <c r="O276" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="277" hidden="1">
@@ -14557,7 +14557,7 @@
         <v>99</v>
       </c>
       <c r="O277" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="278" hidden="1">
@@ -14658,7 +14658,7 @@
         <v>100</v>
       </c>
       <c r="O279" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="280" hidden="1">
@@ -14710,7 +14710,7 @@
         <v>100</v>
       </c>
       <c r="O280" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="281" hidden="1">
@@ -14756,7 +14756,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O281" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="282" hidden="1">
@@ -14805,7 +14805,7 @@
         <v>98.75</v>
       </c>
       <c r="O282" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="283" hidden="1">
@@ -14851,7 +14851,7 @@
         <v>98.39</v>
       </c>
       <c r="O283" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="284" hidden="1">
@@ -14900,7 +14900,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O284" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="285" hidden="1">
@@ -14949,7 +14949,7 @@
         <v>94.67</v>
       </c>
       <c r="O285" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="286" hidden="1">
@@ -14998,7 +14998,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O286" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="287" hidden="1">
@@ -15096,7 +15096,7 @@
         <v>96.72</v>
       </c>
       <c r="O288" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="289" hidden="1">
@@ -15145,7 +15145,7 @@
         <v>95.31</v>
       </c>
       <c r="O289" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="290" hidden="1">
@@ -15194,7 +15194,7 @@
         <v>100</v>
       </c>
       <c r="O290" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="291" hidden="1">
@@ -15243,7 +15243,7 @@
         <v>100</v>
       </c>
       <c r="O291" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="292" hidden="1">
@@ -15292,7 +15292,7 @@
         <v>98.48</v>
       </c>
       <c r="O292" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="293" hidden="1">
@@ -15338,7 +15338,7 @@
         <v>100</v>
       </c>
       <c r="O293" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="294" hidden="1">
@@ -15390,7 +15390,7 @@
         <v>100</v>
       </c>
       <c r="O294" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" hidden="1">
@@ -15439,7 +15439,7 @@
         <v>93.98</v>
       </c>
       <c r="O295" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="296" hidden="1">
@@ -15485,7 +15485,7 @@
         <v>96.3</v>
       </c>
       <c r="O296" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="297" hidden="1">
@@ -15531,7 +15531,7 @@
         <v>100</v>
       </c>
       <c r="O297" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="298" hidden="1">
@@ -15577,7 +15577,7 @@
         <v>100</v>
       </c>
       <c r="O298" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="299" hidden="1">
@@ -15675,7 +15675,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O300" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="301" hidden="1">
@@ -15724,7 +15724,7 @@
         <v>98.25</v>
       </c>
       <c r="O301" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="302" hidden="1">
@@ -15773,7 +15773,7 @@
         <v>96.91</v>
       </c>
       <c r="O302" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="303" hidden="1">
@@ -15865,7 +15865,7 @@
         <v>100</v>
       </c>
       <c r="O304" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="305" hidden="1">
@@ -15957,7 +15957,7 @@
         <v>100</v>
       </c>
       <c r="O306" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="307" hidden="1">
@@ -16055,7 +16055,7 @@
         <v>99.17</v>
       </c>
       <c r="O308" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="309" hidden="1">
@@ -16101,7 +16101,7 @@
         <v>100</v>
       </c>
       <c r="O309" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="310" hidden="1">
@@ -16150,7 +16150,7 @@
         <v>97.06</v>
       </c>
       <c r="O310" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="311" hidden="1">
@@ -16199,7 +16199,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O311" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="312" hidden="1">
@@ -16300,7 +16300,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O313" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="314" hidden="1">
@@ -16346,7 +16346,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O314" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="315" hidden="1">
@@ -16444,7 +16444,7 @@
         <v>98.73</v>
       </c>
       <c r="O316" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="317" hidden="1">
@@ -16493,7 +16493,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O317" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="318" hidden="1">
@@ -16539,7 +16539,7 @@
         <v>92.8</v>
       </c>
       <c r="O318" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="319" hidden="1">
@@ -16588,7 +16588,7 @@
         <v>98.61</v>
       </c>
       <c r="O319" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="320" hidden="1">
@@ -16637,7 +16637,7 @@
         <v>100</v>
       </c>
       <c r="O320" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="321" hidden="1">
@@ -16683,7 +16683,7 @@
         <v>99</v>
       </c>
       <c r="O321" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="322" hidden="1">
@@ -16784,7 +16784,7 @@
         <v>100</v>
       </c>
       <c r="O323" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="324" hidden="1">
@@ -16836,7 +16836,7 @@
         <v>100</v>
       </c>
       <c r="O324" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="325" hidden="1">
@@ -16888,7 +16888,7 @@
         <v>98.75</v>
       </c>
       <c r="O325" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="326" hidden="1">
@@ -16937,7 +16937,7 @@
         <v>98.39</v>
       </c>
       <c r="O326" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="327" hidden="1">
@@ -16986,7 +16986,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O327" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="328" hidden="1">
@@ -17035,7 +17035,7 @@
         <v>94.67</v>
       </c>
       <c r="O328" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="329" hidden="1">
@@ -17081,7 +17081,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O329" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="330" hidden="1">
@@ -17182,7 +17182,7 @@
         <v>96.72</v>
       </c>
       <c r="O331" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="332" hidden="1">
@@ -17228,7 +17228,7 @@
         <v>95.31</v>
       </c>
       <c r="O332" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="333" hidden="1">
@@ -17280,7 +17280,7 @@
         <v>100</v>
       </c>
       <c r="O333" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="334" hidden="1">
@@ -17329,7 +17329,7 @@
         <v>100</v>
       </c>
       <c r="O334" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="335" hidden="1">
@@ -17378,7 +17378,7 @@
         <v>98.48</v>
       </c>
       <c r="O335" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="336" hidden="1">
@@ -17427,7 +17427,7 @@
         <v>100</v>
       </c>
       <c r="O336" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="337" hidden="1">
@@ -17479,7 +17479,7 @@
         <v>100</v>
       </c>
       <c r="O337" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" hidden="1">
@@ -17528,7 +17528,7 @@
         <v>93.98</v>
       </c>
       <c r="O338" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="339" hidden="1">
@@ -17580,7 +17580,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O339" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="340" hidden="1">
@@ -17626,7 +17626,7 @@
         <v>96.3</v>
       </c>
       <c r="O340" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="341" hidden="1">
@@ -17672,7 +17672,7 @@
         <v>100</v>
       </c>
       <c r="O341" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="342" hidden="1">
@@ -17724,7 +17724,7 @@
         <v>100</v>
       </c>
       <c r="O342" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="343" hidden="1">
@@ -17816,7 +17816,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O344" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="345" hidden="1">
@@ -17868,7 +17868,7 @@
         <v>98.25</v>
       </c>
       <c r="O345" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="346" hidden="1">
@@ -17917,7 +17917,7 @@
         <v>96.91</v>
       </c>
       <c r="O346" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="347" hidden="1">
@@ -18012,7 +18012,7 @@
         <v>100</v>
       </c>
       <c r="O348" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="349" hidden="1">
@@ -18107,7 +18107,7 @@
         <v>100</v>
       </c>
       <c r="O350" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="351" hidden="1">
@@ -18205,7 +18205,7 @@
         <v>99.17</v>
       </c>
       <c r="O352" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="353" hidden="1">
@@ -18254,7 +18254,7 @@
         <v>100</v>
       </c>
       <c r="O353" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="354" hidden="1">
@@ -18300,7 +18300,7 @@
         <v>97.06</v>
       </c>
       <c r="O354" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="355" hidden="1">
@@ -18352,7 +18352,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O355" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="356" hidden="1">
@@ -18456,7 +18456,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O357" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="358" hidden="1">
@@ -18508,7 +18508,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O358" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="359" hidden="1">
@@ -18612,7 +18612,7 @@
         <v>98.73</v>
       </c>
       <c r="O360" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="361" hidden="1">
@@ -18664,7 +18664,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O361" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="362" hidden="1">
@@ -18716,7 +18716,7 @@
         <v>92.8</v>
       </c>
       <c r="O362" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="363" hidden="1">
@@ -18768,7 +18768,7 @@
         <v>98.61</v>
       </c>
       <c r="O363" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="364" hidden="1">
@@ -18820,7 +18820,7 @@
         <v>100</v>
       </c>
       <c r="O364" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="365" hidden="1">
@@ -18872,7 +18872,7 @@
         <v>99</v>
       </c>
       <c r="O365" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="366" hidden="1">
@@ -18976,7 +18976,7 @@
         <v>100</v>
       </c>
       <c r="O367" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="368" hidden="1">
@@ -19028,7 +19028,7 @@
         <v>100</v>
       </c>
       <c r="O368" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="369" hidden="1">
@@ -19080,7 +19080,7 @@
         <v>98.75</v>
       </c>
       <c r="O369" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="370" hidden="1">
@@ -19132,7 +19132,7 @@
         <v>98.39</v>
       </c>
       <c r="O370" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="371" hidden="1">
@@ -19184,7 +19184,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O371" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="372" hidden="1">
@@ -19236,7 +19236,7 @@
         <v>94.67</v>
       </c>
       <c r="O372" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="373" hidden="1">
@@ -19288,7 +19288,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O373" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="374" hidden="1">
@@ -19392,7 +19392,7 @@
         <v>96.72</v>
       </c>
       <c r="O375" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="376" hidden="1">
@@ -19444,7 +19444,7 @@
         <v>95.31</v>
       </c>
       <c r="O376" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="377" hidden="1">
@@ -19496,7 +19496,7 @@
         <v>100</v>
       </c>
       <c r="O377" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="378" hidden="1">
@@ -19548,7 +19548,7 @@
         <v>100</v>
       </c>
       <c r="O378" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="379" hidden="1">
@@ -19600,7 +19600,7 @@
         <v>98.48</v>
       </c>
       <c r="O379" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="380" hidden="1">
@@ -19652,7 +19652,7 @@
         <v>100</v>
       </c>
       <c r="O380" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="381" hidden="1">
@@ -19704,7 +19704,7 @@
         <v>100</v>
       </c>
       <c r="O381" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" hidden="1">
@@ -19756,7 +19756,7 @@
         <v>93.98</v>
       </c>
       <c r="O382" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="383" hidden="1">
@@ -19808,7 +19808,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O383" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="384" hidden="1">
@@ -19860,7 +19860,7 @@
         <v>98.25</v>
       </c>
       <c r="O384" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="385" hidden="1">
@@ -19912,7 +19912,7 @@
         <v>96.91</v>
       </c>
       <c r="O385" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="386" hidden="1">
@@ -19964,7 +19964,7 @@
         <v>96.3</v>
       </c>
       <c r="O386" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="387" hidden="1">
@@ -20016,7 +20016,7 @@
         <v>100</v>
       </c>
       <c r="O387" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="388" hidden="1">
@@ -20068,7 +20068,7 @@
         <v>100</v>
       </c>
       <c r="O388" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="389" hidden="1">
@@ -20172,7 +20172,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O390" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="391" hidden="1">
@@ -20276,7 +20276,7 @@
         <v>100</v>
       </c>
       <c r="O392" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="393" hidden="1">
@@ -20380,7 +20380,7 @@
         <v>100</v>
       </c>
       <c r="O394" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="395" hidden="1">
@@ -20484,7 +20484,7 @@
         <v>99.17</v>
       </c>
       <c r="O396" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="397" hidden="1">
@@ -20536,7 +20536,7 @@
         <v>100</v>
       </c>
       <c r="O397" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="398" hidden="1">
@@ -20588,7 +20588,7 @@
         <v>97.06</v>
       </c>
       <c r="O398" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="399" hidden="1">
@@ -20640,7 +20640,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O399" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="400" hidden="1">
@@ -20744,7 +20744,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O401" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="402" hidden="1">
@@ -20796,7 +20796,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O402" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="403" hidden="1">
@@ -20900,7 +20900,7 @@
         <v>98.73</v>
       </c>
       <c r="O404" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="405" hidden="1">
@@ -20952,7 +20952,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O405" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="406" hidden="1">
@@ -21004,7 +21004,7 @@
         <v>92.8</v>
       </c>
       <c r="O406" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="407" hidden="1">
@@ -21056,7 +21056,7 @@
         <v>98.61</v>
       </c>
       <c r="O407" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="408" hidden="1">
@@ -21108,7 +21108,7 @@
         <v>100</v>
       </c>
       <c r="O408" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="409" hidden="1">
@@ -21160,7 +21160,7 @@
         <v>99</v>
       </c>
       <c r="O409" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="410" hidden="1">
@@ -21264,7 +21264,7 @@
         <v>100</v>
       </c>
       <c r="O411" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="412" hidden="1">
@@ -21316,7 +21316,7 @@
         <v>98.75</v>
       </c>
       <c r="O412" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="413" hidden="1">
@@ -21368,7 +21368,7 @@
         <v>98.39</v>
       </c>
       <c r="O413" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="414" hidden="1">
@@ -21420,7 +21420,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O414" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="415" hidden="1">
@@ -21472,7 +21472,7 @@
         <v>94.67</v>
       </c>
       <c r="O415" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="416" hidden="1">
@@ -21524,7 +21524,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O416" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="417" hidden="1">
@@ -21628,7 +21628,7 @@
         <v>96.72</v>
       </c>
       <c r="O418" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="419" hidden="1">
@@ -21680,7 +21680,7 @@
         <v>100</v>
       </c>
       <c r="O419" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="420" hidden="1">
@@ -21732,7 +21732,7 @@
         <v>100</v>
       </c>
       <c r="O420" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="421" hidden="1">
@@ -21784,7 +21784,7 @@
         <v>98.48</v>
       </c>
       <c r="O421" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="422" hidden="1">
@@ -21836,7 +21836,7 @@
         <v>100</v>
       </c>
       <c r="O422" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="423" hidden="1">
@@ -21888,7 +21888,7 @@
         <v>100</v>
       </c>
       <c r="O423" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424" hidden="1">
@@ -21940,7 +21940,7 @@
         <v>93.98</v>
       </c>
       <c r="O424" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="425" hidden="1">
@@ -21992,7 +21992,7 @@
         <v>98.25</v>
       </c>
       <c r="O425" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="426" hidden="1">
@@ -22044,7 +22044,7 @@
         <v>96.91</v>
       </c>
       <c r="O426" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="427" hidden="1">
@@ -22096,7 +22096,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O427" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="428" hidden="1">
@@ -22148,7 +22148,7 @@
         <v>96.3</v>
       </c>
       <c r="O428" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="429" hidden="1">
@@ -22200,7 +22200,7 @@
         <v>100</v>
       </c>
       <c r="O429" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="430" hidden="1">
@@ -22304,7 +22304,7 @@
         <v>100</v>
       </c>
       <c r="O431" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="432" hidden="1">
@@ -22408,7 +22408,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O433" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="434" hidden="1">
@@ -22512,7 +22512,7 @@
         <v>100</v>
       </c>
       <c r="O435" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="436" hidden="1">
@@ -22616,7 +22616,7 @@
         <v>100</v>
       </c>
       <c r="O437" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="438" hidden="1">
@@ -22720,7 +22720,7 @@
         <v>99.17</v>
       </c>
       <c r="O439" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="440" hidden="1">
@@ -22772,7 +22772,7 @@
         <v>100</v>
       </c>
       <c r="O440" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="441" hidden="1">
@@ -22824,7 +22824,7 @@
         <v>97.06</v>
       </c>
       <c r="O441" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="442" hidden="1">
@@ -22876,7 +22876,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O442" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="443" hidden="1">
@@ -22980,7 +22980,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O444" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="445" hidden="1">
@@ -23032,7 +23032,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O445" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="446" hidden="1">
@@ -23084,7 +23084,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O446" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="447" hidden="1">
@@ -23188,7 +23188,7 @@
         <v>98.73</v>
       </c>
       <c r="O448" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="449" hidden="1">
@@ -23240,7 +23240,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O449" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="450" hidden="1">
@@ -23292,7 +23292,7 @@
         <v>92.8</v>
       </c>
       <c r="O450" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="451" hidden="1">
@@ -23344,7 +23344,7 @@
         <v>98.61</v>
       </c>
       <c r="O451" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="452" hidden="1">
@@ -23396,7 +23396,7 @@
         <v>100</v>
       </c>
       <c r="O452" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="453" hidden="1">
@@ -23448,7 +23448,7 @@
         <v>99</v>
       </c>
       <c r="O453" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="454" hidden="1">
@@ -23552,7 +23552,7 @@
         <v>100</v>
       </c>
       <c r="O455" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="456" hidden="1">
@@ -23604,7 +23604,7 @@
         <v>98.75</v>
       </c>
       <c r="O456" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="457" hidden="1">
@@ -23656,7 +23656,7 @@
         <v>98.39</v>
       </c>
       <c r="O457" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="458" hidden="1">
@@ -23708,7 +23708,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O458" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="459" hidden="1">
@@ -23760,7 +23760,7 @@
         <v>94.67</v>
       </c>
       <c r="O459" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="460" hidden="1">
@@ -23812,7 +23812,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O460" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="461" hidden="1">
@@ -23916,7 +23916,7 @@
         <v>96.72</v>
       </c>
       <c r="O462" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="463" hidden="1">
@@ -23968,7 +23968,7 @@
         <v>95.31</v>
       </c>
       <c r="O463" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="464" hidden="1">
@@ -24020,7 +24020,7 @@
         <v>100</v>
       </c>
       <c r="O464" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="465" hidden="1">
@@ -24072,7 +24072,7 @@
         <v>100</v>
       </c>
       <c r="O465" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="466" hidden="1">
@@ -24124,7 +24124,7 @@
         <v>98.48</v>
       </c>
       <c r="O466" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="467" hidden="1">
@@ -24176,7 +24176,7 @@
         <v>100</v>
       </c>
       <c r="O467" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="468" hidden="1">
@@ -24228,7 +24228,7 @@
         <v>100</v>
       </c>
       <c r="O468" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469" hidden="1">
@@ -24280,7 +24280,7 @@
         <v>93.98</v>
       </c>
       <c r="O469" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="470" hidden="1">
@@ -24332,7 +24332,7 @@
         <v>98.25</v>
       </c>
       <c r="O470" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="471" hidden="1">
@@ -24384,7 +24384,7 @@
         <v>96.91</v>
       </c>
       <c r="O471" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="472" hidden="1">
@@ -24488,7 +24488,7 @@
         <v>100</v>
       </c>
       <c r="O473" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="474" hidden="1">
@@ -24592,7 +24592,7 @@
         <v>100</v>
       </c>
       <c r="O475" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="476" hidden="1">
@@ -24644,7 +24644,7 @@
         <v>96.3</v>
       </c>
       <c r="O476" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="477" hidden="1">
@@ -24696,7 +24696,7 @@
         <v>100</v>
       </c>
       <c r="O477" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="478" hidden="1">
@@ -24800,7 +24800,7 @@
         <v>100</v>
       </c>
       <c r="O479" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="480" hidden="1">
@@ -24904,7 +24904,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O481" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="482" hidden="1">
@@ -25008,7 +25008,7 @@
         <v>99.17</v>
       </c>
       <c r="O483" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="484" hidden="1">
@@ -25060,7 +25060,7 @@
         <v>100</v>
       </c>
       <c r="O484" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="485" hidden="1">
@@ -25112,7 +25112,7 @@
         <v>97.06</v>
       </c>
       <c r="O485" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="486" hidden="1">
@@ -25164,7 +25164,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O486" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="487" hidden="1">
@@ -25268,7 +25268,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O488" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="489" hidden="1">
@@ -25320,7 +25320,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O489" s="3" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="490" hidden="1">
@@ -25372,7 +25372,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O490" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="491" hidden="1">
@@ -25476,7 +25476,7 @@
         <v>98.73</v>
       </c>
       <c r="O492" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="493" hidden="1">
@@ -25528,7 +25528,7 @@
         <v>96.3</v>
       </c>
       <c r="O493" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="494" hidden="1">
@@ -25580,7 +25580,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O494" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="495" hidden="1">
@@ -25632,7 +25632,7 @@
         <v>92.8</v>
       </c>
       <c r="O495" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="496" hidden="1">
@@ -25684,7 +25684,7 @@
         <v>98.61</v>
       </c>
       <c r="O496" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="497" hidden="1">
@@ -25736,7 +25736,7 @@
         <v>100</v>
       </c>
       <c r="O497" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="498" hidden="1">
@@ -25788,7 +25788,7 @@
         <v>99</v>
       </c>
       <c r="O498" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="499" hidden="1">
@@ -25840,7 +25840,7 @@
         <v>100</v>
       </c>
       <c r="O499" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="500" hidden="1">
@@ -25944,7 +25944,7 @@
         <v>100</v>
       </c>
       <c r="O501" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="502" hidden="1">
@@ -25996,7 +25996,7 @@
         <v>100</v>
       </c>
       <c r="O502" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="503" hidden="1">
@@ -26100,7 +26100,7 @@
         <v>98.75</v>
       </c>
       <c r="O504" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="505" hidden="1">
@@ -26152,7 +26152,7 @@
         <v>98.39</v>
       </c>
       <c r="O505" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="506" hidden="1">
@@ -26204,7 +26204,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O506" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="507" hidden="1">
@@ -26256,7 +26256,7 @@
         <v>94.67</v>
       </c>
       <c r="O507" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="508" hidden="1">
@@ -26308,7 +26308,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O508" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="509" hidden="1">
@@ -26412,7 +26412,7 @@
         <v>96.72</v>
       </c>
       <c r="O510" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="511" hidden="1">
@@ -26464,7 +26464,7 @@
         <v>95.31</v>
       </c>
       <c r="O511" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="512" hidden="1">
@@ -26516,7 +26516,7 @@
         <v>100</v>
       </c>
       <c r="O512" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="513" hidden="1">
@@ -26568,7 +26568,7 @@
         <v>100</v>
       </c>
       <c r="O513" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="514" hidden="1">
@@ -26620,7 +26620,7 @@
         <v>98.48</v>
       </c>
       <c r="O514" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="515" hidden="1">
@@ -26672,7 +26672,7 @@
         <v>100</v>
       </c>
       <c r="O515" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="516" hidden="1">
@@ -26724,7 +26724,7 @@
         <v>100</v>
       </c>
       <c r="O516" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517" hidden="1">
@@ -26776,7 +26776,7 @@
         <v>93.98</v>
       </c>
       <c r="O517" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="518" hidden="1">
@@ -26828,7 +26828,7 @@
         <v>100</v>
       </c>
       <c r="O518" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="519" hidden="1">
@@ -26880,7 +26880,7 @@
         <v>98.25</v>
       </c>
       <c r="O519" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="520" hidden="1">
@@ -26932,7 +26932,7 @@
         <v>96.91</v>
       </c>
       <c r="O520" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="521" hidden="1">
@@ -27088,7 +27088,7 @@
         <v>100</v>
       </c>
       <c r="O523" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="524" hidden="1">
@@ -27192,7 +27192,7 @@
         <v>100</v>
       </c>
       <c r="O525" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="526" hidden="1">
@@ -27244,7 +27244,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O526" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="527" hidden="1">
@@ -27348,7 +27348,7 @@
         <v>99.17</v>
       </c>
       <c r="O528" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="529" hidden="1">
@@ -27400,7 +27400,7 @@
         <v>100</v>
       </c>
       <c r="O529" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="530" hidden="1">
@@ -27452,7 +27452,7 @@
         <v>97.06</v>
       </c>
       <c r="O530" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="531" hidden="1">
@@ -27507,7 +27507,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O531" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="532" hidden="1">
@@ -27616,7 +27616,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O533" s="9" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="534" hidden="1">
@@ -27671,7 +27671,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O534" s="9" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="535" hidden="1">
@@ -27726,7 +27726,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O535" s="9" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="536" hidden="1">
@@ -27836,7 +27836,7 @@
         <v>98.73</v>
       </c>
       <c r="O537" s="9" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="538" hidden="1">
@@ -27891,7 +27891,7 @@
         <v>96.3</v>
       </c>
       <c r="O538" s="9" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="539" hidden="1">
@@ -27946,7 +27946,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O539" s="9" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="540" hidden="1">
@@ -28001,7 +28001,7 @@
         <v>92.8</v>
       </c>
       <c r="O540" s="9" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="541" hidden="1">
@@ -28056,7 +28056,7 @@
         <v>98.61</v>
       </c>
       <c r="O541" s="9" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="542" hidden="1">
@@ -28111,7 +28111,7 @@
         <v>100</v>
       </c>
       <c r="O542" s="9" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="543" hidden="1">
@@ -28166,7 +28166,7 @@
         <v>99</v>
       </c>
       <c r="O543" s="9" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="544" hidden="1">
@@ -28221,7 +28221,7 @@
         <v>100</v>
       </c>
       <c r="O544" s="9" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="545" hidden="1">
@@ -28331,7 +28331,7 @@
         <v>100</v>
       </c>
       <c r="O546" s="9" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="547" hidden="1">
@@ -28386,7 +28386,7 @@
         <v>100</v>
       </c>
       <c r="O547" s="9" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="548" hidden="1">
@@ -28496,7 +28496,7 @@
         <v>98.75</v>
       </c>
       <c r="O549" s="9" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="550" hidden="1">
@@ -28551,7 +28551,7 @@
         <v>98.39</v>
       </c>
       <c r="O550" s="9" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="551" hidden="1">
@@ -28606,7 +28606,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O551" s="9" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="552" hidden="1">
@@ -28661,7 +28661,7 @@
         <v>94.67</v>
       </c>
       <c r="O552" s="9" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="553" hidden="1">
@@ -28716,7 +28716,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O553" s="9" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="554" hidden="1">
@@ -28826,7 +28826,7 @@
         <v>96.72</v>
       </c>
       <c r="O555" s="9" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="556" hidden="1">
@@ -28881,7 +28881,7 @@
         <v>95.31</v>
       </c>
       <c r="O556" s="9" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="557" hidden="1">
@@ -28936,7 +28936,7 @@
         <v>100</v>
       </c>
       <c r="O557" s="9" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="558" hidden="1">
@@ -28991,7 +28991,7 @@
         <v>100</v>
       </c>
       <c r="O558" s="9" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="559" hidden="1">
@@ -29046,7 +29046,7 @@
         <v>98.48</v>
       </c>
       <c r="O559" s="9" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="560" hidden="1">
@@ -29101,7 +29101,7 @@
         <v>100</v>
       </c>
       <c r="O560" s="9" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="561" hidden="1">
@@ -29156,7 +29156,7 @@
         <v>100</v>
       </c>
       <c r="O561" s="9" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562" hidden="1">
@@ -29211,7 +29211,7 @@
         <v>93.98</v>
       </c>
       <c r="O562" s="9" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="563" hidden="1">
@@ -29266,7 +29266,7 @@
         <v>100</v>
       </c>
       <c r="O563" s="9" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="564" hidden="1">
@@ -29321,7 +29321,7 @@
         <v>98.25</v>
       </c>
       <c r="O564" s="9" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="565" hidden="1">
@@ -29376,7 +29376,7 @@
         <v>96.91</v>
       </c>
       <c r="O565" s="9" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="566" hidden="1">
@@ -29541,7 +29541,7 @@
         <v>100</v>
       </c>
       <c r="O568" s="9" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="569" hidden="1">
@@ -29651,7 +29651,7 @@
         <v>100</v>
       </c>
       <c r="O570" s="9" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="571" hidden="1">
@@ -29706,7 +29706,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O571" s="9" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="572" hidden="1">
@@ -29816,7 +29816,7 @@
         <v>99.17</v>
       </c>
       <c r="O573" s="9" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="574" hidden="1">
@@ -29871,7 +29871,7 @@
         <v>100</v>
       </c>
       <c r="O574" s="9" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="575" hidden="1">
@@ -29926,7 +29926,7 @@
         <v>97.06</v>
       </c>
       <c r="O575" s="9" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
     <row r="576">
@@ -29981,7 +29981,7 @@
         <v>98.81999999999999</v>
       </c>
       <c r="O576" s="3" t="n">
-        <v>28.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="577">
@@ -30091,7 +30091,7 @@
         <v>95.04000000000001</v>
       </c>
       <c r="O578" s="3" t="n">
-        <v>29.08653846153846</v>
+        <v>19.95192307692308</v>
       </c>
     </row>
     <row r="579">
@@ -30146,7 +30146,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="O579" s="3" t="n">
-        <v>26.1744966442953</v>
+        <v>17.4496644295302</v>
       </c>
     </row>
     <row r="580">
@@ -30201,7 +30201,7 @@
         <v>99.04000000000001</v>
       </c>
       <c r="O580" s="3" t="n">
-        <v>27.51322751322751</v>
+        <v>16.93121693121693</v>
       </c>
     </row>
     <row r="581">
@@ -30311,7 +30311,7 @@
         <v>98.73</v>
       </c>
       <c r="O582" s="3" t="n">
-        <v>22.63610315186246</v>
+        <v>16.3323782234957</v>
       </c>
     </row>
     <row r="583">
@@ -30366,7 +30366,7 @@
         <v>96.3</v>
       </c>
       <c r="O583" s="3" t="n">
-        <v>29.34782608695652</v>
+        <v>19.56521739130435</v>
       </c>
     </row>
     <row r="584">
@@ -30421,7 +30421,7 @@
         <v>96.51000000000001</v>
       </c>
       <c r="O584" s="3" t="n">
-        <v>26.29969418960244</v>
+        <v>17.43119266055046</v>
       </c>
     </row>
     <row r="585">
@@ -30476,7 +30476,7 @@
         <v>92.8</v>
       </c>
       <c r="O585" s="3" t="n">
-        <v>30.12048192771084</v>
+        <v>19.51807228915663</v>
       </c>
     </row>
     <row r="586">
@@ -30531,7 +30531,7 @@
         <v>98.61</v>
       </c>
       <c r="O586" s="3" t="n">
-        <v>32.14285714285715</v>
+        <v>18.30357142857143</v>
       </c>
     </row>
     <row r="587">
@@ -30586,7 +30586,7 @@
         <v>100</v>
       </c>
       <c r="O587" s="3" t="n">
-        <v>27.82608695652174</v>
+        <v>17.82608695652174</v>
       </c>
     </row>
     <row r="588">
@@ -30641,7 +30641,7 @@
         <v>99</v>
       </c>
       <c r="O588" s="3" t="n">
-        <v>38.91050583657588</v>
+        <v>22.17898832684825</v>
       </c>
     </row>
     <row r="589">
@@ -30696,7 +30696,7 @@
         <v>100</v>
       </c>
       <c r="O589" s="3" t="n">
-        <v>65.38461538461539</v>
+        <v>34.61538461538461</v>
       </c>
     </row>
     <row r="590">
@@ -30806,7 +30806,7 @@
         <v>100</v>
       </c>
       <c r="O591" s="3" t="n">
-        <v>309.0909090909091</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="592">
@@ -30861,7 +30861,7 @@
         <v>100</v>
       </c>
       <c r="O592" s="3" t="n">
-        <v>131.0344827586207</v>
+        <v>17.24137931034483</v>
       </c>
     </row>
     <row r="593">
@@ -30971,7 +30971,7 @@
         <v>98.75</v>
       </c>
       <c r="O594" s="3" t="n">
-        <v>30.88803088803089</v>
+        <v>15.05791505791506</v>
       </c>
     </row>
     <row r="595">
@@ -31026,7 +31026,7 @@
         <v>98.39</v>
       </c>
       <c r="O595" s="3" t="n">
-        <v>19.5583596214511</v>
+        <v>13.24921135646688</v>
       </c>
     </row>
     <row r="596">
@@ -31081,7 +31081,7 @@
         <v>98.54000000000001</v>
       </c>
       <c r="O596" s="3" t="n">
-        <v>24.16225749559083</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="597">
@@ -31136,7 +31136,7 @@
         <v>94.67</v>
       </c>
       <c r="O597" s="3" t="n">
-        <v>20.77562326869806</v>
+        <v>18.28254847645429</v>
       </c>
     </row>
     <row r="598">
@@ -31191,7 +31191,7 @@
         <v>98.51000000000001</v>
       </c>
       <c r="O598" s="3" t="n">
-        <v>21.3375796178344</v>
+        <v>15.92356687898089</v>
       </c>
     </row>
     <row r="599">
@@ -31301,7 +31301,7 @@
         <v>96.72</v>
       </c>
       <c r="O600" s="3" t="n">
-        <v>21.18055555555555</v>
+        <v>13.19444444444444</v>
       </c>
     </row>
     <row r="601">
@@ -31356,7 +31356,7 @@
         <v>95.31</v>
       </c>
       <c r="O601" s="3" t="n">
-        <v>22.69503546099291</v>
+        <v>10.28368794326241</v>
       </c>
     </row>
     <row r="602">
@@ -31411,7 +31411,7 @@
         <v>100</v>
       </c>
       <c r="O602" s="3" t="n">
-        <v>26.54320987654321</v>
+        <v>15.4320987654321</v>
       </c>
     </row>
     <row r="603">
@@ -31466,7 +31466,7 @@
         <v>100</v>
       </c>
       <c r="O603" s="3" t="n">
-        <v>25.40983606557377</v>
+        <v>14.20765027322404</v>
       </c>
     </row>
     <row r="604">
@@ -31521,7 +31521,7 @@
         <v>98.48</v>
       </c>
       <c r="O604" s="3" t="n">
-        <v>20.95238095238095</v>
+        <v>15.87301587301587</v>
       </c>
     </row>
     <row r="605">
@@ -31576,7 +31576,7 @@
         <v>100</v>
       </c>
       <c r="O605" s="3" t="n">
-        <v>19.43573667711599</v>
+        <v>18.80877742946709</v>
       </c>
     </row>
     <row r="606">
@@ -31631,7 +31631,7 @@
         <v>100</v>
       </c>
       <c r="O606" s="3" t="n">
-        <v>11.11111111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607">
@@ -31686,7 +31686,7 @@
         <v>93.98</v>
       </c>
       <c r="O607" s="3" t="n">
-        <v>25.69659442724458</v>
+        <v>19.19504643962848</v>
       </c>
     </row>
     <row r="608">
@@ -31741,7 +31741,7 @@
         <v>100</v>
       </c>
       <c r="O608" s="3" t="n">
-        <v>16.9811320754717</v>
+        <v>9.433962264150944</v>
       </c>
     </row>
     <row r="609">
@@ -31796,7 +31796,7 @@
         <v>98.25</v>
       </c>
       <c r="O609" s="3" t="n">
-        <v>16.76470588235294</v>
+        <v>9.117647058823529</v>
       </c>
     </row>
     <row r="610">
@@ -31851,7 +31851,7 @@
         <v>96.91</v>
       </c>
       <c r="O610" s="3" t="n">
-        <v>25.45931758530184</v>
+        <v>17.32283464566929</v>
       </c>
     </row>
     <row r="611">
@@ -32016,7 +32016,7 @@
         <v>100</v>
       </c>
       <c r="O613" s="3" t="n">
-        <v>27.53623188405797</v>
+        <v>15.94202898550724</v>
       </c>
     </row>
     <row r="614">
@@ -32126,7 +32126,7 @@
         <v>100</v>
       </c>
       <c r="O615" s="3" t="n">
-        <v>23.39449541284404</v>
+        <v>15.13761467889908</v>
       </c>
     </row>
     <row r="616">
@@ -32181,7 +32181,7 @@
         <v>97.95999999999999</v>
       </c>
       <c r="O616" s="3" t="n">
-        <v>25.92592592592592</v>
+        <v>19.04761904761905</v>
       </c>
     </row>
     <row r="617">
@@ -32291,7 +32291,7 @@
         <v>99.17</v>
       </c>
       <c r="O618" s="3" t="n">
-        <v>27.84222737819026</v>
+        <v>19.7215777262181</v>
       </c>
     </row>
     <row r="619">
@@ -32346,7 +32346,7 @@
         <v>100</v>
       </c>
       <c r="O619" s="3" t="n">
-        <v>23.26732673267327</v>
+        <v>14.35643564356435</v>
       </c>
     </row>
     <row r="620">
@@ -32401,7 +32401,7 @@
         <v>97.06</v>
       </c>
       <c r="O620" s="3" t="n">
-        <v>21.7948717948718</v>
+        <v>14.42307692307692</v>
       </c>
     </row>
   </sheetData>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -32475,6 +32475,7 @@
           <t>Ana Karollyne Souza Faria</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32494,6 +32495,7 @@
           <t>Anna Luiza Rezende Tavares</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32501,6 +32503,7 @@
           <t>Brenda de Menezes Silva</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32508,6 +32511,7 @@
           <t>Carlos Mateus Cassimiro Nunes</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32515,6 +32519,7 @@
           <t>Claudio de Sousa Velasco Filho</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32534,6 +32539,7 @@
           <t>Cristiane Ramos da Silva Rocha</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -32541,6 +32547,7 @@
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32560,6 +32567,7 @@
           <t>Davylla Rodrigues Freitas Silva</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32579,6 +32587,7 @@
           <t>Emilly Kamilly Medeiros Miranda</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -32586,6 +32595,7 @@
           <t>Francielson de Oliveira</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -32593,6 +32603,7 @@
           <t>Francilene Ferreira de Jesus</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -32600,6 +32611,7 @@
           <t>Gabriel Alves</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32667,6 +32679,7 @@
           <t>Jéssica Fé Moura</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -32686,6 +32699,7 @@
           <t>Kerollen Cristielly de Jesus Siqueira</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -32729,6 +32743,7 @@
           <t>Lorena Dias de Araujo</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -32748,6 +32763,7 @@
           <t>Luiz Fernando de Carvalho Junior</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -32755,6 +32771,7 @@
           <t>Maria Eduarda Sousa Costa</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -32762,6 +32779,7 @@
           <t>Matheus Farias De Souza</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -32769,6 +32787,7 @@
           <t>Maysa Victoria Dias Moura</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -32776,6 +32795,7 @@
           <t>Michelle G Santos</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -32795,6 +32815,7 @@
           <t>Patrícia Karla de Sousa Araújo</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -32826,6 +32847,7 @@
           <t>Quirino Diogo Leite Torres</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -32857,6 +32879,7 @@
           <t>Sara Maria Monteiro Lopes</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -32864,6 +32887,7 @@
           <t>Sarah Steffanie de Lima Borges</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -32527,6 +32527,15 @@
           <t>Técnico I</t>
         </is>
       </c>
+      <c r="D623" t="n">
+        <v>11</v>
+      </c>
+      <c r="E623" t="n">
+        <v>9</v>
+      </c>
+      <c r="F623" t="n">
+        <v>15.17</v>
+      </c>
       <c r="G623" s="3" t="n">
         <v>3</v>
       </c>
@@ -32622,6 +32631,15 @@
           <t>JR</t>
         </is>
       </c>
+      <c r="D625" t="n">
+        <v>20</v>
+      </c>
+      <c r="E625" t="n">
+        <v>19</v>
+      </c>
+      <c r="F625" t="n">
+        <v>22.07</v>
+      </c>
       <c r="G625" s="3" t="n">
         <v>0</v>
       </c>
@@ -32665,6 +32683,15 @@
           <t>Técnico II</t>
         </is>
       </c>
+      <c r="D626" t="n">
+        <v>30</v>
+      </c>
+      <c r="E626" t="n">
+        <v>27</v>
+      </c>
+      <c r="F626" t="n">
+        <v>9.15</v>
+      </c>
       <c r="G626" s="3" t="n">
         <v>6</v>
       </c>
@@ -32708,6 +32735,15 @@
           <t>Técnico II</t>
         </is>
       </c>
+      <c r="D627" t="n">
+        <v>13</v>
+      </c>
+      <c r="E627" t="n">
+        <v>12</v>
+      </c>
+      <c r="F627" t="n">
+        <v>16.53</v>
+      </c>
       <c r="G627" s="3" t="n">
         <v>0</v>
       </c>
@@ -32751,6 +32787,15 @@
           <t>Estágio</t>
         </is>
       </c>
+      <c r="D628" t="n">
+        <v>7</v>
+      </c>
+      <c r="E628" t="n">
+        <v>7</v>
+      </c>
+      <c r="F628" t="n">
+        <v>22.38</v>
+      </c>
       <c r="G628" s="3" t="n">
         <v>0</v>
       </c>
@@ -32846,6 +32891,15 @@
           <t>Técnico III</t>
         </is>
       </c>
+      <c r="D630" t="n">
+        <v>25</v>
+      </c>
+      <c r="E630" t="n">
+        <v>24</v>
+      </c>
+      <c r="F630" t="n">
+        <v>15.42</v>
+      </c>
       <c r="G630" s="3" t="n">
         <v>0</v>
       </c>
@@ -33079,6 +33133,15 @@
           <t>Técnico II</t>
         </is>
       </c>
+      <c r="D635" t="n">
+        <v>17</v>
+      </c>
+      <c r="E635" t="n">
+        <v>14</v>
+      </c>
+      <c r="F635" t="n">
+        <v>13.23</v>
+      </c>
       <c r="G635" s="3" t="n">
         <v>1</v>
       </c>
@@ -33122,6 +33185,15 @@
           <t>Técnico III</t>
         </is>
       </c>
+      <c r="D636" t="n">
+        <v>12</v>
+      </c>
+      <c r="E636" t="n">
+        <v>11</v>
+      </c>
+      <c r="F636" t="n">
+        <v>12.15</v>
+      </c>
       <c r="G636" s="3" t="n">
         <v>1</v>
       </c>
@@ -33208,6 +33280,15 @@
           <t>Estágio</t>
         </is>
       </c>
+      <c r="D638" t="n">
+        <v>8</v>
+      </c>
+      <c r="E638" t="n">
+        <v>7</v>
+      </c>
+      <c r="F638" t="n">
+        <v>18.34</v>
+      </c>
       <c r="G638" s="3" t="n">
         <v>0</v>
       </c>
@@ -33606,6 +33687,15 @@
           <t>Técnico III</t>
         </is>
       </c>
+      <c r="D646" t="n">
+        <v>19</v>
+      </c>
+      <c r="E646" t="n">
+        <v>19</v>
+      </c>
+      <c r="F646" t="n">
+        <v>16.57</v>
+      </c>
       <c r="G646" s="3" t="n">
         <v>0</v>
       </c>
@@ -33900,6 +33990,15 @@
           <t>Técnico I</t>
         </is>
       </c>
+      <c r="D652" t="n">
+        <v>8</v>
+      </c>
+      <c r="E652" t="n">
+        <v>8</v>
+      </c>
+      <c r="F652" t="n">
+        <v>32.37</v>
+      </c>
       <c r="G652" s="3" t="n">
         <v>0</v>
       </c>
@@ -33943,6 +34042,15 @@
           <t>Estágio</t>
         </is>
       </c>
+      <c r="D653" t="n">
+        <v>8</v>
+      </c>
+      <c r="E653" t="n">
+        <v>8</v>
+      </c>
+      <c r="F653" t="n">
+        <v>20.01</v>
+      </c>
       <c r="G653" s="3" t="n">
         <v>0</v>
       </c>
@@ -34029,6 +34137,15 @@
           <t>Técnico III</t>
         </is>
       </c>
+      <c r="D655" t="n">
+        <v>23</v>
+      </c>
+      <c r="E655" t="n">
+        <v>20</v>
+      </c>
+      <c r="F655" t="n">
+        <v>13.5</v>
+      </c>
       <c r="G655" s="3" t="n">
         <v>5</v>
       </c>
@@ -34072,6 +34189,15 @@
           <t>Estágio</t>
         </is>
       </c>
+      <c r="D656" t="n">
+        <v>15</v>
+      </c>
+      <c r="E656" t="n">
+        <v>14</v>
+      </c>
+      <c r="F656" t="n">
+        <v>31.4</v>
+      </c>
       <c r="G656" s="3" t="n">
         <v>0</v>
       </c>
@@ -34314,6 +34440,15 @@
           <t>Estágio</t>
         </is>
       </c>
+      <c r="D661" t="n">
+        <v>17</v>
+      </c>
+      <c r="E661" t="n">
+        <v>15</v>
+      </c>
+      <c r="F661" t="n">
+        <v>25.36</v>
+      </c>
       <c r="G661" s="3" t="n">
         <v>0</v>
       </c>
@@ -34461,6 +34596,15 @@
           <t>Técnico I</t>
         </is>
       </c>
+      <c r="D664" t="n">
+        <v>17</v>
+      </c>
+      <c r="E664" t="n">
+        <v>16</v>
+      </c>
+      <c r="F664" t="n">
+        <v>20.55</v>
+      </c>
       <c r="G664" s="3" t="n">
         <v>1</v>
       </c>
@@ -34503,6 +34647,15 @@
         <is>
           <t>Técnico III</t>
         </is>
+      </c>
+      <c r="D665" t="n">
+        <v>26</v>
+      </c>
+      <c r="E665" t="n">
+        <v>22</v>
+      </c>
+      <c r="F665" t="n">
+        <v>13.4</v>
       </c>
       <c r="G665" s="3" t="n">
         <v>0</v>
@@ -34957,6 +35110,11 @@
           <t>Jéssica Fé Moura</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -35175,6 +35333,11 @@
           <t>Patrícia Karla de Sousa Araújo</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>Patrícia Karla de Sousa Araújo</t>
@@ -35311,7 +35474,6 @@
           <t>Jessica</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -35324,7 +35486,6 @@
           <t>Patricia</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -33592,6 +33592,15 @@
           <t>Técnico III</t>
         </is>
       </c>
+      <c r="D644" t="n">
+        <v>38</v>
+      </c>
+      <c r="E644" t="n">
+        <v>36</v>
+      </c>
+      <c r="F644" t="n">
+        <v>20.2</v>
+      </c>
       <c r="G644" s="3" t="n">
         <v>0</v>
       </c>
@@ -34292,6 +34301,15 @@
         <is>
           <t>Técnico II</t>
         </is>
+      </c>
+      <c r="D658" t="n">
+        <v>17</v>
+      </c>
+      <c r="E658" t="n">
+        <v>17</v>
+      </c>
+      <c r="F658" t="n">
+        <v>22.2</v>
       </c>
       <c r="G658" s="3" t="n">
         <v>0</v>
@@ -34904,6 +34922,7 @@
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
@@ -34933,6 +34952,7 @@
           <t>Davylla Rodrigues Freitas Silva</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Davylla Rodrigues Freitas Silva</t>
@@ -34996,6 +35016,7 @@
           <t>Francilene Ferreira de Jesus</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Francilene Ferreira de Jesus</t>
@@ -35207,6 +35228,7 @@
           <t>Lorena Dias de Araujo</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Lorena Dias de Araujo</t>
@@ -35270,6 +35292,7 @@
           <t>Matheus Farias De Souza</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Matheus Farias De Souza</t>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE36F9A-D02D-4D13-A357-B74DF0596F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9B1D75-0544-4988-A4D5-09A463398F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -913,7 +913,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46146</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>46146</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46147</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>46147</v>
       </c>
@@ -5167,7 +5167,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>46148</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>46148</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>46149</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>46149</v>
       </c>
@@ -9190,7 +9190,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>46150</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>46150</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>46153</v>
       </c>
@@ -11968,7 +11968,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>46153</v>
       </c>
@@ -13309,7 +13309,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5">
         <v>46154</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>46154</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5">
         <v>46155</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
         <v>46155</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="5">
         <v>46156</v>
       </c>
@@ -17761,7 +17761,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
         <v>46156</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="5">
         <v>46157</v>
       </c>
@@ -21409,7 +21409,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="5">
         <v>46160</v>
       </c>
@@ -23521,7 +23521,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7">
         <v>46161</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A501" s="7">
         <v>46161</v>
       </c>
@@ -24208,6 +24208,9 @@
       </c>
       <c r="E501" s="3">
         <v>12</v>
+      </c>
+      <c r="F501" s="3">
+        <v>0</v>
       </c>
       <c r="G501" s="3">
         <v>0</v>
@@ -25684,7 +25687,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="7">
         <v>46162</v>
       </c>
@@ -26389,7 +26392,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A546" s="7">
         <v>46162</v>
       </c>
@@ -27958,7 +27961,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="5">
         <v>46163</v>
       </c>
@@ -28665,7 +28668,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="591" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A591" s="5">
         <v>46163</v>
       </c>
@@ -30228,7 +30231,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="10">
         <v>46164</v>
       </c>
@@ -30899,7 +30902,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A636" s="10">
         <v>46164</v>
       </c>
@@ -30920,6 +30923,9 @@
       </c>
       <c r="G636" s="3">
         <v>1</v>
+      </c>
+      <c r="H636" s="3">
+        <v>0</v>
       </c>
       <c r="I636" s="3">
         <f>E636+G636+H636</f>
@@ -34012,7 +34018,7 @@
   <autoFilter ref="A1:O729" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Amanda Moura Ferreira"/>
+        <filter val="Francielson de Oliveira"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A590:O590">

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9B1D75-0544-4988-A4D5-09A463398F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41F172E-68BE-4231-A4EE-26A87D2D695B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -865,7 +865,7 @@
       </c>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46146</v>
       </c>
@@ -886,6 +886,9 @@
       </c>
       <c r="G2" s="3">
         <v>4</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
       </c>
       <c r="I2" s="3">
         <f>E2+G2+H2</f>
@@ -929,7 +932,7 @@
       <c r="E3" s="3">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
       <c r="G3" s="3">
@@ -961,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46146</v>
       </c>
@@ -982,6 +985,9 @@
       </c>
       <c r="G4" s="3">
         <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" ref="I4:I16" si="1">E4+G4+H4</f>
@@ -1009,7 +1015,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46146</v>
       </c>
@@ -1029,6 +1035,9 @@
         <v>10.4</v>
       </c>
       <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
         <v>0</v>
       </c>
       <c r="I5" s="3">
@@ -1108,7 +1117,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46146</v>
       </c>
@@ -1129,6 +1138,9 @@
       </c>
       <c r="G7" s="3">
         <v>5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="1"/>
@@ -1156,7 +1168,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46146</v>
       </c>
@@ -1176,6 +1188,9 @@
         <v>12.3</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3">
@@ -1204,7 +1219,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46146</v>
       </c>
@@ -1224,6 +1239,9 @@
         <v>15.3</v>
       </c>
       <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>0</v>
       </c>
       <c r="I9" s="3">
@@ -1252,7 +1270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>46146</v>
       </c>
@@ -1273,6 +1291,9 @@
       </c>
       <c r="G10" s="3">
         <v>6</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="1"/>
@@ -1300,7 +1321,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>46146</v>
       </c>
@@ -1321,6 +1342,9 @@
       </c>
       <c r="G11" s="3">
         <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="1"/>
@@ -1348,7 +1372,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46146</v>
       </c>
@@ -1369,6 +1393,9 @@
       </c>
       <c r="G12" s="3">
         <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="1"/>
@@ -1396,7 +1423,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46146</v>
       </c>
@@ -1416,6 +1443,9 @@
         <v>10.34</v>
       </c>
       <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
         <v>0</v>
       </c>
       <c r="I13" s="3">
@@ -1444,7 +1474,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>46146</v>
       </c>
@@ -1465,6 +1495,9 @@
       </c>
       <c r="G14" s="3">
         <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="1"/>
@@ -1492,7 +1525,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>46146</v>
       </c>
@@ -1512,6 +1545,9 @@
         <v>23.25</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
@@ -1540,7 +1576,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>46146</v>
       </c>
@@ -1561,6 +1597,9 @@
       </c>
       <c r="G16" s="3">
         <v>7</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="1"/>
@@ -1588,7 +1627,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>46146</v>
       </c>
@@ -1636,7 +1675,7 @@
         <v>9.5238095238095237</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>46146</v>
       </c>
@@ -1656,6 +1695,9 @@
         <v>11.17</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>0</v>
       </c>
       <c r="I18" s="3">
@@ -1684,7 +1726,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46146</v>
       </c>
@@ -1705,6 +1747,9 @@
       </c>
       <c r="G19" s="3">
         <v>7</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="4"/>
@@ -1732,7 +1777,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46146</v>
       </c>
@@ -1752,6 +1797,9 @@
         <v>8.51</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
@@ -1780,7 +1828,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>46146</v>
       </c>
@@ -1801,6 +1849,9 @@
       </c>
       <c r="G21" s="3">
         <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="4"/>
@@ -1828,7 +1879,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>46146</v>
       </c>
@@ -1849,6 +1900,9 @@
       </c>
       <c r="G22" s="3">
         <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <f t="shared" si="4"/>
@@ -1876,7 +1930,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>46146</v>
       </c>
@@ -1897,6 +1951,9 @@
       </c>
       <c r="G23" s="3">
         <v>4</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <f t="shared" si="4"/>
@@ -1972,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>46146</v>
       </c>
@@ -1992,6 +2049,9 @@
         <v>11.31</v>
       </c>
       <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
         <v>0</v>
       </c>
       <c r="I25" s="3">
@@ -2020,7 +2080,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>46146</v>
       </c>
@@ -2040,6 +2100,9 @@
         <v>12.48</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>0</v>
       </c>
       <c r="I26" s="3">
@@ -2068,7 +2131,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>46146</v>
       </c>
@@ -2089,6 +2152,9 @@
       </c>
       <c r="G27" s="3">
         <v>4</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <f t="shared" si="7"/>
@@ -2116,7 +2182,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>46146</v>
       </c>
@@ -2136,6 +2202,9 @@
         <v>9.44</v>
       </c>
       <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
         <v>0</v>
       </c>
       <c r="I28" s="3">
@@ -2164,7 +2233,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>46146</v>
       </c>
@@ -2184,6 +2253,9 @@
         <v>9.4700000000000006</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
@@ -2212,7 +2284,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>46146</v>
       </c>
@@ -2232,6 +2304,9 @@
         <v>9.1</v>
       </c>
       <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
         <v>0</v>
       </c>
       <c r="I30" s="3">
@@ -2308,7 +2383,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>46146</v>
       </c>
@@ -2329,6 +2404,9 @@
       </c>
       <c r="G32" s="3">
         <v>4</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <f t="shared" ref="I32:I46" si="10">E32+G32+H32</f>
@@ -2458,7 +2536,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>46146</v>
       </c>
@@ -2479,6 +2557,9 @@
       </c>
       <c r="G35" s="3">
         <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
       </c>
       <c r="I35" s="3">
         <f t="shared" si="10"/>
@@ -2506,7 +2587,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>46146</v>
       </c>
@@ -2526,6 +2607,9 @@
         <v>14.1</v>
       </c>
       <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
         <v>0</v>
       </c>
       <c r="I36" s="3">
@@ -2554,7 +2638,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>46146</v>
       </c>
@@ -2574,6 +2658,9 @@
         <v>5.14</v>
       </c>
       <c r="G37" s="3">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3">
         <v>0</v>
       </c>
       <c r="I37" s="3">
@@ -2602,7 +2689,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>46146</v>
       </c>
@@ -2622,6 +2709,9 @@
         <v>10.11</v>
       </c>
       <c r="G38" s="3">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3">
         <v>0</v>
       </c>
       <c r="I38" s="3">
@@ -2650,7 +2740,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>46146</v>
       </c>
@@ -2670,6 +2760,9 @@
         <v>10.55</v>
       </c>
       <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
         <v>0</v>
       </c>
       <c r="I39" s="3">
@@ -2698,7 +2791,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>46146</v>
       </c>
@@ -2718,6 +2811,9 @@
         <v>10.31</v>
       </c>
       <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
         <v>0</v>
       </c>
       <c r="I40" s="3">
@@ -2797,7 +2893,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>46146</v>
       </c>
@@ -2818,6 +2914,9 @@
       </c>
       <c r="G42" s="3">
         <v>4</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <f t="shared" si="10"/>
@@ -2845,7 +2944,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>46146</v>
       </c>
@@ -2866,6 +2965,9 @@
       </c>
       <c r="G43" s="3">
         <v>1</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <f t="shared" si="10"/>
@@ -2893,7 +2995,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>46146</v>
       </c>
@@ -2913,6 +3015,9 @@
         <v>15.29</v>
       </c>
       <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
         <v>0</v>
       </c>
       <c r="I44" s="3">
@@ -2992,7 +3097,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>46147</v>
       </c>
@@ -3013,6 +3118,9 @@
       </c>
       <c r="G46" s="3">
         <v>4</v>
+      </c>
+      <c r="H46" s="3">
+        <v>0</v>
       </c>
       <c r="I46" s="3">
         <f t="shared" si="10"/>
@@ -3088,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>46147</v>
       </c>
@@ -3109,6 +3217,9 @@
       </c>
       <c r="G48" s="3">
         <v>7</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <f>E48+G48+H48</f>
@@ -3136,7 +3247,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46147</v>
       </c>
@@ -3156,6 +3267,9 @@
         <v>11.21</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>0</v>
       </c>
       <c r="I49" s="3">
@@ -3235,7 +3349,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46147</v>
       </c>
@@ -3255,6 +3369,9 @@
         <v>8.32</v>
       </c>
       <c r="G51" s="3">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3">
         <v>0</v>
       </c>
       <c r="I51" s="3">
@@ -3382,7 +3499,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>46147</v>
       </c>
@@ -3403,6 +3520,9 @@
       </c>
       <c r="G54" s="3">
         <v>6</v>
+      </c>
+      <c r="H54" s="3">
+        <v>0</v>
       </c>
       <c r="I54" s="3">
         <f t="shared" ref="I54:I63" si="13">E54+G54+H54</f>
@@ -3430,7 +3550,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>46147</v>
       </c>
@@ -3451,6 +3571,9 @@
       </c>
       <c r="G55" s="3">
         <v>9</v>
+      </c>
+      <c r="H55" s="3">
+        <v>0</v>
       </c>
       <c r="I55" s="3">
         <f t="shared" si="13"/>
@@ -3580,7 +3703,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>46147</v>
       </c>
@@ -3601,6 +3724,9 @@
       </c>
       <c r="G58" s="3">
         <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <f t="shared" si="13"/>
@@ -3628,7 +3754,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>46147</v>
       </c>
@@ -3649,6 +3775,9 @@
       </c>
       <c r="G59" s="3">
         <v>8</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3">
         <f t="shared" si="13"/>
@@ -3676,7 +3805,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>46147</v>
       </c>
@@ -3697,6 +3826,9 @@
       </c>
       <c r="G60" s="3">
         <v>9</v>
+      </c>
+      <c r="H60" s="3">
+        <v>0</v>
       </c>
       <c r="I60" s="3">
         <f t="shared" si="13"/>
@@ -3724,7 +3856,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>46147</v>
       </c>
@@ -3745,6 +3877,9 @@
       </c>
       <c r="G61" s="3">
         <v>10</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <f t="shared" si="13"/>
@@ -3772,7 +3907,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>46147</v>
       </c>
@@ -3792,6 +3927,9 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>0</v>
       </c>
       <c r="I62" s="3">
@@ -3820,7 +3958,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>46147</v>
       </c>
@@ -3841,6 +3979,9 @@
       </c>
       <c r="G63" s="3">
         <v>3</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0</v>
       </c>
       <c r="I63" s="3">
         <f t="shared" si="13"/>
@@ -3868,7 +4009,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>46147</v>
       </c>
@@ -3964,7 +4105,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>46147</v>
       </c>
@@ -3985,6 +4126,9 @@
       </c>
       <c r="G66" s="3">
         <v>9</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0</v>
       </c>
       <c r="I66" s="3">
         <f>E66+G66+H66</f>
@@ -4012,7 +4156,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>46147</v>
       </c>
@@ -4033,6 +4177,9 @@
       </c>
       <c r="G67" s="3">
         <v>1</v>
+      </c>
+      <c r="H67" s="3">
+        <v>0</v>
       </c>
       <c r="I67" s="3">
         <f>E67+G67+H67</f>
@@ -4060,7 +4207,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>46147</v>
       </c>
@@ -4081,6 +4228,9 @@
       </c>
       <c r="G68" s="3">
         <v>2</v>
+      </c>
+      <c r="H68" s="3">
+        <v>0</v>
       </c>
       <c r="I68" s="3">
         <f>E68+G68+H68</f>
@@ -4108,7 +4258,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>46147</v>
       </c>
@@ -4129,6 +4279,9 @@
       </c>
       <c r="G69" s="3">
         <v>2</v>
+      </c>
+      <c r="H69" s="3">
+        <v>0</v>
       </c>
       <c r="I69" s="3">
         <f>E69+G69+H69</f>
@@ -4156,7 +4309,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>46147</v>
       </c>
@@ -4176,6 +4329,9 @@
         <v>11.22</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>0</v>
       </c>
       <c r="I70" s="3">
@@ -4252,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>46147</v>
       </c>
@@ -4273,6 +4429,9 @@
       </c>
       <c r="G72" s="3">
         <v>10</v>
+      </c>
+      <c r="H72" s="3">
+        <v>0</v>
       </c>
       <c r="I72" s="3">
         <f t="shared" ref="I72:I77" si="17">E72+G72+H72</f>
@@ -4300,7 +4459,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>46147</v>
       </c>
@@ -4321,6 +4480,9 @@
       </c>
       <c r="G73" s="3">
         <v>1</v>
+      </c>
+      <c r="H73" s="3">
+        <v>0</v>
       </c>
       <c r="I73" s="3">
         <f t="shared" si="17"/>
@@ -4348,7 +4510,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>46147</v>
       </c>
@@ -4369,6 +4531,9 @@
       </c>
       <c r="G74" s="3">
         <v>5</v>
+      </c>
+      <c r="H74" s="3">
+        <v>0</v>
       </c>
       <c r="I74" s="3">
         <f t="shared" si="17"/>
@@ -4396,7 +4561,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>46147</v>
       </c>
@@ -4416,6 +4581,9 @@
         <v>0</v>
       </c>
       <c r="G75" s="3">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3">
         <v>0</v>
       </c>
       <c r="I75" s="3">
@@ -4444,7 +4612,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>46147</v>
       </c>
@@ -4465,6 +4633,9 @@
       </c>
       <c r="G76" s="3">
         <v>4</v>
+      </c>
+      <c r="H76" s="3">
+        <v>0</v>
       </c>
       <c r="I76" s="3">
         <f t="shared" si="17"/>
@@ -4492,7 +4663,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>46147</v>
       </c>
@@ -4512,6 +4683,9 @@
         <v>0</v>
       </c>
       <c r="G77" s="3">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3">
         <v>0</v>
       </c>
       <c r="I77" s="3">
@@ -4588,7 +4762,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>46147</v>
       </c>
@@ -4609,6 +4783,9 @@
       </c>
       <c r="G79" s="3">
         <v>1</v>
+      </c>
+      <c r="H79" s="3">
+        <v>0</v>
       </c>
       <c r="I79" s="3">
         <f t="shared" ref="I79:I90" si="20">E79+G79+H79</f>
@@ -4687,7 +4864,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>46147</v>
       </c>
@@ -4708,6 +4885,9 @@
       </c>
       <c r="G81" s="3">
         <v>10</v>
+      </c>
+      <c r="H81" s="3">
+        <v>0</v>
       </c>
       <c r="I81" s="3">
         <f t="shared" si="20"/>
@@ -4735,7 +4915,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>46147</v>
       </c>
@@ -4755,6 +4935,9 @@
         <v>10.59</v>
       </c>
       <c r="G82" s="3">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
         <v>0</v>
       </c>
       <c r="I82" s="3">
@@ -4783,7 +4966,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>46147</v>
       </c>
@@ -4803,6 +4986,9 @@
         <v>12.04</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
@@ -4831,7 +5017,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>46147</v>
       </c>
@@ -4851,6 +5037,9 @@
         <v>11.03</v>
       </c>
       <c r="G84" s="3">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3">
         <v>0</v>
       </c>
       <c r="I84" s="3">
@@ -4879,7 +5068,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>46147</v>
       </c>
@@ -4900,6 +5089,9 @@
       </c>
       <c r="G85" s="3">
         <v>9</v>
+      </c>
+      <c r="H85" s="3">
+        <v>0</v>
       </c>
       <c r="I85" s="3">
         <f t="shared" si="20"/>
@@ -4927,7 +5119,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>46147</v>
       </c>
@@ -4948,6 +5140,9 @@
       </c>
       <c r="G86" s="3">
         <v>10</v>
+      </c>
+      <c r="H86" s="3">
+        <v>0</v>
       </c>
       <c r="I86" s="3">
         <f t="shared" si="20"/>
@@ -4975,7 +5170,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>46147</v>
       </c>
@@ -4996,6 +5191,9 @@
       </c>
       <c r="G87" s="3">
         <v>9</v>
+      </c>
+      <c r="H87" s="3">
+        <v>0</v>
       </c>
       <c r="I87" s="3">
         <f t="shared" si="20"/>
@@ -5023,7 +5221,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>46147</v>
       </c>
@@ -5044,6 +5242,9 @@
       </c>
       <c r="G88" s="3">
         <v>3</v>
+      </c>
+      <c r="H88" s="3">
+        <v>0</v>
       </c>
       <c r="I88" s="3">
         <f t="shared" si="20"/>
@@ -5122,7 +5323,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>46148</v>
       </c>
@@ -5140,6 +5341,9 @@
       </c>
       <c r="G90" s="3">
         <v>11</v>
+      </c>
+      <c r="H90" s="3">
+        <v>0</v>
       </c>
       <c r="I90" s="3">
         <f t="shared" si="20"/>
@@ -5215,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>46148</v>
       </c>
@@ -5233,6 +5437,9 @@
       </c>
       <c r="G92" s="3">
         <v>6</v>
+      </c>
+      <c r="H92" s="3">
+        <v>0</v>
       </c>
       <c r="I92" s="3">
         <f t="shared" ref="I92:I107" si="23">E92+G92+H92</f>
@@ -5260,7 +5467,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>46148</v>
       </c>
@@ -5278,6 +5485,9 @@
       </c>
       <c r="G93" s="3">
         <v>12</v>
+      </c>
+      <c r="H93" s="3">
+        <v>0</v>
       </c>
       <c r="I93" s="3">
         <f t="shared" si="23"/>
@@ -5305,7 +5515,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>46148</v>
       </c>
@@ -5323,6 +5533,9 @@
       </c>
       <c r="G94" s="3">
         <v>9</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3">
         <f t="shared" si="23"/>
@@ -5350,7 +5563,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>46148</v>
       </c>
@@ -5368,6 +5581,9 @@
       </c>
       <c r="G95" s="3">
         <v>1</v>
+      </c>
+      <c r="H95" s="3">
+        <v>0</v>
       </c>
       <c r="I95" s="3">
         <f t="shared" si="23"/>
@@ -5443,7 +5659,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>46148</v>
       </c>
@@ -5460,6 +5676,9 @@
         <v>12</v>
       </c>
       <c r="G97" s="3">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3">
         <v>0</v>
       </c>
       <c r="I97" s="3">
@@ -5536,7 +5755,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>46148</v>
       </c>
@@ -5553,6 +5772,9 @@
         <v>38</v>
       </c>
       <c r="G99" s="3">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3">
         <v>0</v>
       </c>
       <c r="I99" s="3">
@@ -5581,7 +5803,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>46148</v>
       </c>
@@ -5598,6 +5820,9 @@
         <v>8</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
@@ -5626,7 +5851,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>46148</v>
       </c>
@@ -5643,6 +5868,9 @@
         <v>15</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
@@ -5671,7 +5899,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>46148</v>
       </c>
@@ -5689,6 +5917,9 @@
       </c>
       <c r="G102" s="3">
         <v>9</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
       </c>
       <c r="I102" s="3">
         <f t="shared" si="23"/>
@@ -5716,7 +5947,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>46148</v>
       </c>
@@ -5733,6 +5964,9 @@
         <v>44</v>
       </c>
       <c r="G103" s="3">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3">
         <v>0</v>
       </c>
       <c r="I103" s="3">
@@ -5761,7 +5995,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>46148</v>
       </c>
@@ -5779,6 +6013,9 @@
       </c>
       <c r="G104" s="3">
         <v>1</v>
+      </c>
+      <c r="H104" s="3">
+        <v>0</v>
       </c>
       <c r="I104" s="3">
         <f t="shared" si="23"/>
@@ -5806,7 +6043,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>46148</v>
       </c>
@@ -5823,6 +6060,9 @@
         <v>16</v>
       </c>
       <c r="G105" s="3">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3">
         <v>0</v>
       </c>
       <c r="I105" s="3">
@@ -5851,7 +6091,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>46148</v>
       </c>
@@ -5869,6 +6109,9 @@
       </c>
       <c r="G106" s="3">
         <v>9</v>
+      </c>
+      <c r="H106" s="3">
+        <v>0</v>
       </c>
       <c r="I106" s="3">
         <f t="shared" si="23"/>
@@ -5896,7 +6139,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>46148</v>
       </c>
@@ -5914,6 +6157,9 @@
       </c>
       <c r="G107" s="3">
         <v>9</v>
+      </c>
+      <c r="H107" s="3">
+        <v>0</v>
       </c>
       <c r="I107" s="3">
         <f t="shared" si="23"/>
@@ -5941,7 +6187,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>46148</v>
       </c>
@@ -6037,7 +6283,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>46148</v>
       </c>
@@ -6055,6 +6301,9 @@
       </c>
       <c r="G110" s="3">
         <v>9</v>
+      </c>
+      <c r="H110" s="3">
+        <v>0</v>
       </c>
       <c r="I110" s="3">
         <f>E110+G110+H110</f>
@@ -6082,7 +6331,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>46148</v>
       </c>
@@ -6100,6 +6349,9 @@
       </c>
       <c r="G111" s="3">
         <v>9</v>
+      </c>
+      <c r="H111" s="3">
+        <v>0</v>
       </c>
       <c r="I111" s="3">
         <f>E111+G111+H111</f>
@@ -6127,7 +6379,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>46148</v>
       </c>
@@ -6145,6 +6397,9 @@
       </c>
       <c r="G112" s="3">
         <v>23</v>
+      </c>
+      <c r="H112" s="3">
+        <v>0</v>
       </c>
       <c r="I112" s="3">
         <f>E112+G112+H112</f>
@@ -6172,7 +6427,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>46148</v>
       </c>
@@ -6190,6 +6445,9 @@
       </c>
       <c r="G113" s="3">
         <v>7</v>
+      </c>
+      <c r="H113" s="3">
+        <v>0</v>
       </c>
       <c r="I113" s="3">
         <f>E113+G113+H113</f>
@@ -6217,7 +6475,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>46148</v>
       </c>
@@ -6235,6 +6493,9 @@
       </c>
       <c r="G114" s="3">
         <v>7</v>
+      </c>
+      <c r="H114" s="3">
+        <v>0</v>
       </c>
       <c r="I114" s="3">
         <f>E114+G114+H114</f>
@@ -6310,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>46148</v>
       </c>
@@ -6328,6 +6589,9 @@
       </c>
       <c r="G116" s="3">
         <v>1</v>
+      </c>
+      <c r="H116" s="3">
+        <v>0</v>
       </c>
       <c r="I116" s="3">
         <f t="shared" ref="I116:I121" si="26">E116+G116+H116</f>
@@ -6355,7 +6619,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>46148</v>
       </c>
@@ -6373,6 +6637,9 @@
       </c>
       <c r="G117" s="3">
         <v>1</v>
+      </c>
+      <c r="H117" s="3">
+        <v>0</v>
       </c>
       <c r="I117" s="3">
         <f t="shared" si="26"/>
@@ -6400,7 +6667,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>46148</v>
       </c>
@@ -6418,6 +6685,9 @@
       </c>
       <c r="G118" s="3">
         <v>12</v>
+      </c>
+      <c r="H118" s="3">
+        <v>0</v>
       </c>
       <c r="I118" s="3">
         <f t="shared" si="26"/>
@@ -6445,7 +6715,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>46148</v>
       </c>
@@ -6462,6 +6732,9 @@
         <v>38</v>
       </c>
       <c r="G119" s="3">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3">
         <v>0</v>
       </c>
       <c r="I119" s="3">
@@ -6490,7 +6763,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>46148</v>
       </c>
@@ -6508,6 +6781,9 @@
       </c>
       <c r="G120" s="3">
         <v>2</v>
+      </c>
+      <c r="H120" s="3">
+        <v>0</v>
       </c>
       <c r="I120" s="3">
         <f t="shared" si="26"/>
@@ -6535,7 +6811,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>46148</v>
       </c>
@@ -6552,6 +6828,9 @@
         <v>31</v>
       </c>
       <c r="G121" s="3">
+        <v>0</v>
+      </c>
+      <c r="H121" s="3">
         <v>0</v>
       </c>
       <c r="I121" s="3">
@@ -6628,7 +6907,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>46148</v>
       </c>
@@ -6646,6 +6925,9 @@
       </c>
       <c r="G123" s="3">
         <v>8</v>
+      </c>
+      <c r="H123" s="3">
+        <v>0</v>
       </c>
       <c r="I123" s="3">
         <f>E123+G123+H123</f>
@@ -6721,7 +7003,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>46148</v>
       </c>
@@ -6739,6 +7021,9 @@
       </c>
       <c r="G125" s="3">
         <v>1</v>
+      </c>
+      <c r="H125" s="3">
+        <v>0</v>
       </c>
       <c r="I125" s="3">
         <f>E125+G125+H125</f>
@@ -6814,7 +7099,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>46148</v>
       </c>
@@ -6831,6 +7116,9 @@
         <v>33</v>
       </c>
       <c r="G127" s="3">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3">
         <v>0</v>
       </c>
       <c r="I127" s="3">
@@ -6859,7 +7147,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>46148</v>
       </c>
@@ -6876,6 +7164,9 @@
         <v>17</v>
       </c>
       <c r="G128" s="3">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3">
         <v>0</v>
       </c>
       <c r="I128" s="3">
@@ -6904,7 +7195,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>46148</v>
       </c>
@@ -6922,6 +7213,9 @@
       </c>
       <c r="G129" s="3">
         <v>3</v>
+      </c>
+      <c r="H129" s="3">
+        <v>0</v>
       </c>
       <c r="I129" s="3">
         <f t="shared" si="29"/>
@@ -6949,7 +7243,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>46148</v>
       </c>
@@ -6967,6 +7261,9 @@
       </c>
       <c r="G130" s="3">
         <v>5</v>
+      </c>
+      <c r="H130" s="3">
+        <v>0</v>
       </c>
       <c r="I130" s="3">
         <f t="shared" si="29"/>
@@ -6994,7 +7291,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>46148</v>
       </c>
@@ -7012,6 +7309,9 @@
       </c>
       <c r="G131" s="3">
         <v>1</v>
+      </c>
+      <c r="H131" s="3">
+        <v>0</v>
       </c>
       <c r="I131" s="3">
         <f t="shared" si="29"/>
@@ -7039,7 +7339,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>46148</v>
       </c>
@@ -7057,6 +7357,9 @@
       </c>
       <c r="G132" s="3">
         <v>1</v>
+      </c>
+      <c r="H132" s="3">
+        <v>0</v>
       </c>
       <c r="I132" s="3">
         <f t="shared" si="29"/>
@@ -7084,7 +7387,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>46148</v>
       </c>
@@ -7102,6 +7405,9 @@
       </c>
       <c r="G133" s="3">
         <v>8</v>
+      </c>
+      <c r="H133" s="3">
+        <v>0</v>
       </c>
       <c r="I133" s="3">
         <f t="shared" si="29"/>
@@ -7129,7 +7435,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>46149</v>
       </c>
@@ -7146,6 +7452,9 @@
         <v>34</v>
       </c>
       <c r="G134" s="3">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3">
         <v>0</v>
       </c>
       <c r="I134" s="3">
@@ -7222,7 +7531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>46149</v>
       </c>
@@ -7240,6 +7549,9 @@
       </c>
       <c r="G136" s="3">
         <v>10</v>
+      </c>
+      <c r="H136" s="3">
+        <v>0</v>
       </c>
       <c r="I136" s="3">
         <f t="shared" ref="I136:I151" si="33">E136+G136+H136</f>
@@ -7267,7 +7579,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>46149</v>
       </c>
@@ -7284,6 +7596,9 @@
         <v>32</v>
       </c>
       <c r="G137" s="3">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3">
         <v>0</v>
       </c>
       <c r="I137" s="3">
@@ -7312,7 +7627,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>46149</v>
       </c>
@@ -7330,6 +7645,9 @@
       </c>
       <c r="G138" s="3">
         <v>5</v>
+      </c>
+      <c r="H138" s="3">
+        <v>0</v>
       </c>
       <c r="I138" s="3">
         <f t="shared" si="33"/>
@@ -7357,7 +7675,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>46149</v>
       </c>
@@ -7375,6 +7693,9 @@
       </c>
       <c r="G139" s="3">
         <v>5</v>
+      </c>
+      <c r="H139" s="3">
+        <v>0</v>
       </c>
       <c r="I139" s="3">
         <f t="shared" si="33"/>
@@ -7450,7 +7771,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>46149</v>
       </c>
@@ -7467,6 +7788,9 @@
         <v>12</v>
       </c>
       <c r="G141" s="3">
+        <v>0</v>
+      </c>
+      <c r="H141" s="3">
         <v>0</v>
       </c>
       <c r="I141" s="3">
@@ -7495,7 +7819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>46149</v>
       </c>
@@ -7512,6 +7836,9 @@
         <v>32</v>
       </c>
       <c r="G142" s="3">
+        <v>0</v>
+      </c>
+      <c r="H142" s="3">
         <v>0</v>
       </c>
       <c r="I142" s="3">
@@ -7588,7 +7915,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>46149</v>
       </c>
@@ -7606,6 +7933,9 @@
       </c>
       <c r="G144" s="3">
         <v>1</v>
+      </c>
+      <c r="H144" s="3">
+        <v>0</v>
       </c>
       <c r="I144" s="3">
         <f t="shared" si="33"/>
@@ -7633,7 +7963,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>46149</v>
       </c>
@@ -7650,6 +7980,9 @@
         <v>44</v>
       </c>
       <c r="G145" s="3">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3">
         <v>0</v>
       </c>
       <c r="I145" s="3">
@@ -7678,7 +8011,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>46149</v>
       </c>
@@ -7696,6 +8029,9 @@
       </c>
       <c r="G146" s="3">
         <v>4</v>
+      </c>
+      <c r="H146" s="3">
+        <v>0</v>
       </c>
       <c r="I146" s="3">
         <f t="shared" si="33"/>
@@ -7723,7 +8059,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>46149</v>
       </c>
@@ -7741,6 +8077,9 @@
       </c>
       <c r="G147" s="3">
         <v>7</v>
+      </c>
+      <c r="H147" s="3">
+        <v>0</v>
       </c>
       <c r="I147" s="3">
         <f t="shared" si="33"/>
@@ -7768,7 +8107,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>46149</v>
       </c>
@@ -7785,6 +8124,9 @@
         <v>30</v>
       </c>
       <c r="G148" s="3">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3">
         <v>0</v>
       </c>
       <c r="I148" s="3">
@@ -7813,7 +8155,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>46149</v>
       </c>
@@ -7830,6 +8172,9 @@
         <v>15</v>
       </c>
       <c r="G149" s="3">
+        <v>0</v>
+      </c>
+      <c r="H149" s="3">
         <v>0</v>
       </c>
       <c r="I149" s="3">
@@ -7906,7 +8251,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>46149</v>
       </c>
@@ -7924,6 +8269,9 @@
       </c>
       <c r="G151" s="3">
         <v>2</v>
+      </c>
+      <c r="H151" s="3">
+        <v>0</v>
       </c>
       <c r="I151" s="3">
         <f t="shared" si="33"/>
@@ -7951,7 +8299,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>46149</v>
       </c>
@@ -8047,7 +8395,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>46149</v>
       </c>
@@ -8065,6 +8413,9 @@
       </c>
       <c r="G154" s="3">
         <v>2</v>
+      </c>
+      <c r="H154" s="3">
+        <v>0</v>
       </c>
       <c r="I154" s="3">
         <f>E154+G154+H154</f>
@@ -8092,7 +8443,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>46149</v>
       </c>
@@ -8109,6 +8460,9 @@
         <v>24</v>
       </c>
       <c r="G155" s="3">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3">
         <v>0</v>
       </c>
       <c r="I155" s="3">
@@ -8137,7 +8491,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>46149</v>
       </c>
@@ -8155,6 +8509,9 @@
       </c>
       <c r="G156" s="3">
         <v>9</v>
+      </c>
+      <c r="H156" s="3">
+        <v>0</v>
       </c>
       <c r="I156" s="3">
         <f>E156+G156+H156</f>
@@ -8182,7 +8539,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>46149</v>
       </c>
@@ -8200,6 +8557,9 @@
       </c>
       <c r="G157" s="3">
         <v>6</v>
+      </c>
+      <c r="H157" s="3">
+        <v>0</v>
       </c>
       <c r="I157" s="3">
         <f>E157+G157+H157</f>
@@ -8227,7 +8587,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>46149</v>
       </c>
@@ -8244,6 +8604,9 @@
         <v>28</v>
       </c>
       <c r="G158" s="3">
+        <v>0</v>
+      </c>
+      <c r="H158" s="3">
         <v>0</v>
       </c>
       <c r="I158" s="3">
@@ -8320,7 +8683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>46149</v>
       </c>
@@ -8338,6 +8701,9 @@
       </c>
       <c r="G160" s="3">
         <v>9</v>
+      </c>
+      <c r="H160" s="3">
+        <v>0</v>
       </c>
       <c r="I160" s="3">
         <f t="shared" ref="I160:I165" si="36">E160+G160+H160</f>
@@ -8365,7 +8731,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>46149</v>
       </c>
@@ -8383,6 +8749,9 @@
       </c>
       <c r="G161" s="3">
         <v>4</v>
+      </c>
+      <c r="H161" s="3">
+        <v>0</v>
       </c>
       <c r="I161" s="3">
         <f t="shared" si="36"/>
@@ -8410,7 +8779,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>46149</v>
       </c>
@@ -8428,6 +8797,9 @@
       </c>
       <c r="G162" s="3">
         <v>4</v>
+      </c>
+      <c r="H162" s="3">
+        <v>0</v>
       </c>
       <c r="I162" s="3">
         <f t="shared" si="36"/>
@@ -8455,7 +8827,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>46149</v>
       </c>
@@ -8472,6 +8844,9 @@
         <v>23</v>
       </c>
       <c r="G163" s="3">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3">
         <v>0</v>
       </c>
       <c r="I163" s="3">
@@ -8500,7 +8875,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>46149</v>
       </c>
@@ -8518,6 +8893,9 @@
       </c>
       <c r="G164" s="3">
         <v>6</v>
+      </c>
+      <c r="H164" s="3">
+        <v>0</v>
       </c>
       <c r="I164" s="3">
         <f t="shared" si="36"/>
@@ -8545,7 +8923,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>46149</v>
       </c>
@@ -8563,6 +8941,9 @@
       </c>
       <c r="G165" s="3">
         <v>3</v>
+      </c>
+      <c r="H165" s="3">
+        <v>0</v>
       </c>
       <c r="I165" s="3">
         <f t="shared" si="36"/>
@@ -8638,7 +9019,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>46149</v>
       </c>
@@ -8656,6 +9037,9 @@
       </c>
       <c r="G167" s="3">
         <v>1</v>
+      </c>
+      <c r="H167" s="3">
+        <v>0</v>
       </c>
       <c r="I167" s="3">
         <f>E167+G167+H167</f>
@@ -8731,7 +9115,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>46149</v>
       </c>
@@ -8749,6 +9133,9 @@
       </c>
       <c r="G169" s="3">
         <v>6</v>
+      </c>
+      <c r="H169" s="3">
+        <v>0</v>
       </c>
       <c r="I169" s="3">
         <f>E169+G169+H169</f>
@@ -8824,7 +9211,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>46149</v>
       </c>
@@ -8841,6 +9228,9 @@
         <v>10</v>
       </c>
       <c r="G171" s="3">
+        <v>0</v>
+      </c>
+      <c r="H171" s="3">
         <v>0</v>
       </c>
       <c r="I171" s="3">
@@ -8869,7 +9259,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>46149</v>
       </c>
@@ -8887,6 +9277,9 @@
       </c>
       <c r="G172" s="3">
         <v>8</v>
+      </c>
+      <c r="H172" s="3">
+        <v>0</v>
       </c>
       <c r="I172" s="3">
         <f t="shared" si="39"/>
@@ -8914,7 +9307,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>46149</v>
       </c>
@@ -8932,6 +9325,9 @@
       </c>
       <c r="G173" s="3">
         <v>5</v>
+      </c>
+      <c r="H173" s="3">
+        <v>0</v>
       </c>
       <c r="I173" s="3">
         <f t="shared" si="39"/>
@@ -8959,7 +9355,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>46149</v>
       </c>
@@ -8977,6 +9373,9 @@
       </c>
       <c r="G174" s="3">
         <v>14</v>
+      </c>
+      <c r="H174" s="3">
+        <v>0</v>
       </c>
       <c r="I174" s="3">
         <f t="shared" si="39"/>
@@ -9004,7 +9403,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>46149</v>
       </c>
@@ -9022,6 +9421,9 @@
       </c>
       <c r="G175" s="3">
         <v>8</v>
+      </c>
+      <c r="H175" s="3">
+        <v>0</v>
       </c>
       <c r="I175" s="3">
         <f t="shared" si="39"/>
@@ -9049,7 +9451,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>46149</v>
       </c>
@@ -9067,6 +9469,9 @@
       </c>
       <c r="G176" s="3">
         <v>6</v>
+      </c>
+      <c r="H176" s="3">
+        <v>0</v>
       </c>
       <c r="I176" s="3">
         <f t="shared" si="39"/>
@@ -10054,7 +10459,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>46150</v>
       </c>
@@ -10092,13 +10497,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M197">
-        <v>0</v>
-      </c>
-      <c r="N197">
+      <c r="M197" s="9">
+        <v>0</v>
+      </c>
+      <c r="N197" s="9">
         <v>100</v>
       </c>
-      <c r="O197">
+      <c r="O197" s="9">
         <v>9.5238095238095237</v>
       </c>
     </row>
@@ -10140,13 +10545,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M198">
-        <v>0</v>
-      </c>
-      <c r="N198">
+      <c r="M198" s="9">
+        <v>0</v>
+      </c>
+      <c r="N198" s="9">
         <v>100</v>
       </c>
-      <c r="O198">
+      <c r="O198" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -10188,13 +10593,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M199">
-        <v>0</v>
-      </c>
-      <c r="N199">
+      <c r="M199" s="9">
+        <v>0</v>
+      </c>
+      <c r="N199" s="9">
         <v>98.8</v>
       </c>
-      <c r="O199">
+      <c r="O199" s="9">
         <v>15.41353383458646</v>
       </c>
     </row>
@@ -10428,13 +10833,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M204">
-        <v>0</v>
-      </c>
-      <c r="N204">
-        <v>0</v>
-      </c>
-      <c r="O204">
+      <c r="M204" s="9">
+        <v>0</v>
+      </c>
+      <c r="N204" s="9">
+        <v>0</v>
+      </c>
+      <c r="O204" s="9">
         <v>0</v>
       </c>
     </row>
@@ -10764,13 +11169,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M211">
-        <v>0</v>
-      </c>
-      <c r="N211">
+      <c r="M211" s="9">
+        <v>0</v>
+      </c>
+      <c r="N211" s="9">
         <v>100</v>
       </c>
-      <c r="O211">
+      <c r="O211" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
@@ -11244,13 +11649,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M221">
-        <v>0</v>
-      </c>
-      <c r="N221">
+      <c r="M221" s="9">
+        <v>0</v>
+      </c>
+      <c r="N221" s="9">
         <v>100</v>
       </c>
-      <c r="O221">
+      <c r="O221" s="9">
         <v>16.97247706422019</v>
       </c>
     </row>
@@ -11302,7 +11707,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>46153</v>
       </c>
@@ -11320,6 +11725,9 @@
       </c>
       <c r="G223" s="3">
         <v>5</v>
+      </c>
+      <c r="H223" s="3">
+        <v>0</v>
       </c>
       <c r="I223" s="3">
         <f>E223+G223+H223</f>
@@ -11395,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>46153</v>
       </c>
@@ -11413,6 +11821,9 @@
       </c>
       <c r="G225" s="3">
         <v>8</v>
+      </c>
+      <c r="H225" s="3">
+        <v>0</v>
       </c>
       <c r="I225" s="3">
         <f t="shared" ref="I225:I237" si="52">E225+G225+H225</f>
@@ -11440,7 +11851,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>46153</v>
       </c>
@@ -11455,6 +11866,9 @@
       </c>
       <c r="E226" s="3">
         <v>16</v>
+      </c>
+      <c r="H226" s="3">
+        <v>0</v>
       </c>
       <c r="I226" s="3">
         <f t="shared" si="52"/>
@@ -11482,7 +11896,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>46153</v>
       </c>
@@ -11500,6 +11914,9 @@
       </c>
       <c r="G227" s="3">
         <v>1</v>
+      </c>
+      <c r="H227" s="3">
+        <v>0</v>
       </c>
       <c r="I227" s="3">
         <f t="shared" si="52"/>
@@ -11527,7 +11944,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>46153</v>
       </c>
@@ -11545,6 +11962,9 @@
       </c>
       <c r="G228" s="3">
         <v>4</v>
+      </c>
+      <c r="H228" s="3">
+        <v>0</v>
       </c>
       <c r="I228" s="3">
         <f t="shared" si="52"/>
@@ -11572,7 +11992,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>46153</v>
       </c>
@@ -11590,6 +12010,9 @@
       </c>
       <c r="G229" s="3">
         <v>2</v>
+      </c>
+      <c r="H229" s="3">
+        <v>0</v>
       </c>
       <c r="I229" s="3">
         <f t="shared" si="52"/>
@@ -11617,7 +12040,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>46153</v>
       </c>
@@ -11632,6 +12055,9 @@
       </c>
       <c r="E230" s="3">
         <v>35</v>
+      </c>
+      <c r="H230" s="3">
+        <v>0</v>
       </c>
       <c r="I230" s="3">
         <f t="shared" si="52"/>
@@ -11659,7 +12085,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>46153</v>
       </c>
@@ -11677,6 +12103,9 @@
       </c>
       <c r="G231" s="3">
         <v>4</v>
+      </c>
+      <c r="H231" s="3">
+        <v>0</v>
       </c>
       <c r="I231" s="3">
         <f t="shared" si="52"/>
@@ -11704,7 +12133,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>46153</v>
       </c>
@@ -11722,6 +12151,9 @@
       </c>
       <c r="G232" s="3">
         <v>2</v>
+      </c>
+      <c r="H232" s="3">
+        <v>0</v>
       </c>
       <c r="I232" s="3">
         <f t="shared" si="52"/>
@@ -11749,7 +12181,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>46153</v>
       </c>
@@ -11764,6 +12196,9 @@
       </c>
       <c r="E233" s="3">
         <v>25</v>
+      </c>
+      <c r="H233" s="3">
+        <v>0</v>
       </c>
       <c r="I233" s="3">
         <f t="shared" si="52"/>
@@ -11839,7 +12274,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>46153</v>
       </c>
@@ -11854,6 +12289,9 @@
       </c>
       <c r="E235" s="3">
         <v>1</v>
+      </c>
+      <c r="H235" s="3">
+        <v>0</v>
       </c>
       <c r="I235" s="3">
         <f t="shared" si="52"/>
@@ -11881,7 +12319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>46153</v>
       </c>
@@ -11896,6 +12334,9 @@
       </c>
       <c r="E236" s="3">
         <v>5</v>
+      </c>
+      <c r="H236" s="3">
+        <v>0</v>
       </c>
       <c r="I236" s="3">
         <f t="shared" si="52"/>
@@ -11923,7 +12364,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>46153</v>
       </c>
@@ -11941,6 +12382,9 @@
       </c>
       <c r="G237" s="3">
         <v>4</v>
+      </c>
+      <c r="H237" s="3">
+        <v>0</v>
       </c>
       <c r="I237" s="3">
         <f t="shared" si="52"/>
@@ -11968,7 +12412,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>46153</v>
       </c>
@@ -12006,13 +12450,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M238">
-        <v>0</v>
-      </c>
-      <c r="N238">
+      <c r="M238" s="9">
+        <v>0</v>
+      </c>
+      <c r="N238" s="9">
         <v>100</v>
       </c>
-      <c r="O238">
+      <c r="O238" s="9">
         <v>9.5238095238095237</v>
       </c>
     </row>
@@ -12054,13 +12498,13 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M239">
-        <v>0</v>
-      </c>
-      <c r="N239">
+      <c r="M239" s="9">
+        <v>0</v>
+      </c>
+      <c r="N239" s="9">
         <v>100</v>
       </c>
-      <c r="O239">
+      <c r="O239" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -12112,7 +12556,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>46153</v>
       </c>
@@ -12127,6 +12571,9 @@
       </c>
       <c r="E241" s="3">
         <v>7</v>
+      </c>
+      <c r="H241" s="3">
+        <v>0</v>
       </c>
       <c r="I241" s="3">
         <f t="shared" si="55"/>
@@ -12154,7 +12601,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>46153</v>
       </c>
@@ -12169,6 +12616,9 @@
       </c>
       <c r="E242" s="3">
         <v>16</v>
+      </c>
+      <c r="H242" s="3">
+        <v>0</v>
       </c>
       <c r="I242" s="3">
         <f t="shared" si="55"/>
@@ -12196,7 +12646,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>46153</v>
       </c>
@@ -12214,6 +12664,9 @@
       </c>
       <c r="G243" s="3">
         <v>5</v>
+      </c>
+      <c r="H243" s="3">
+        <v>0</v>
       </c>
       <c r="I243" s="3">
         <f t="shared" si="55"/>
@@ -12241,7 +12694,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>46153</v>
       </c>
@@ -12256,6 +12709,9 @@
       </c>
       <c r="E244" s="3">
         <v>24</v>
+      </c>
+      <c r="H244" s="3">
+        <v>0</v>
       </c>
       <c r="I244" s="3">
         <f t="shared" si="55"/>
@@ -12283,7 +12739,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>46153</v>
       </c>
@@ -12301,6 +12757,9 @@
       </c>
       <c r="G245" s="3">
         <v>3</v>
+      </c>
+      <c r="H245" s="3">
+        <v>0</v>
       </c>
       <c r="I245" s="3">
         <f t="shared" si="55"/>
@@ -12328,7 +12787,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>46153</v>
       </c>
@@ -12346,6 +12805,9 @@
       </c>
       <c r="G246" s="3">
         <v>4</v>
+      </c>
+      <c r="H246" s="3">
+        <v>0</v>
       </c>
       <c r="I246" s="3">
         <f t="shared" si="55"/>
@@ -12373,7 +12835,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
         <v>46153</v>
       </c>
@@ -12391,6 +12853,9 @@
       </c>
       <c r="G247" s="3">
         <v>1</v>
+      </c>
+      <c r="H247" s="3">
+        <v>0</v>
       </c>
       <c r="I247" s="3">
         <f t="shared" si="55"/>
@@ -12456,17 +12921,17 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M248">
-        <v>0</v>
-      </c>
-      <c r="N248">
-        <v>0</v>
-      </c>
-      <c r="O248">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M248" s="9">
+        <v>0</v>
+      </c>
+      <c r="N248" s="9">
+        <v>0</v>
+      </c>
+      <c r="O248" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>46153</v>
       </c>
@@ -12484,6 +12949,9 @@
       </c>
       <c r="G249" s="3">
         <v>2</v>
+      </c>
+      <c r="H249" s="3">
+        <v>0</v>
       </c>
       <c r="I249" s="3">
         <f t="shared" ref="I249:I254" si="58">E249+G249+H249</f>
@@ -12511,7 +12979,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>46153</v>
       </c>
@@ -12529,6 +12997,9 @@
       </c>
       <c r="G250" s="3">
         <v>1</v>
+      </c>
+      <c r="H250" s="3">
+        <v>0</v>
       </c>
       <c r="I250" s="3">
         <f t="shared" si="58"/>
@@ -12556,7 +13027,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>46153</v>
       </c>
@@ -12574,6 +13045,9 @@
       </c>
       <c r="G251" s="3">
         <v>1</v>
+      </c>
+      <c r="H251" s="3">
+        <v>0</v>
       </c>
       <c r="I251" s="3">
         <f t="shared" si="58"/>
@@ -12601,7 +13075,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>46153</v>
       </c>
@@ -12618,6 +13092,9 @@
         <v>29</v>
       </c>
       <c r="G252" s="3">
+        <v>0</v>
+      </c>
+      <c r="H252" s="3">
         <v>0</v>
       </c>
       <c r="I252" s="3">
@@ -12646,7 +13123,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>46153</v>
       </c>
@@ -12664,6 +13141,9 @@
       </c>
       <c r="G253" s="3">
         <v>2</v>
+      </c>
+      <c r="H253" s="3">
+        <v>0</v>
       </c>
       <c r="I253" s="3">
         <f t="shared" si="58"/>
@@ -12691,7 +13171,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>46153</v>
       </c>
@@ -12706,6 +13186,9 @@
       </c>
       <c r="E254" s="3">
         <v>30</v>
+      </c>
+      <c r="H254" s="3">
+        <v>0</v>
       </c>
       <c r="I254" s="3">
         <f t="shared" si="58"/>
@@ -12771,17 +13254,17 @@
         <f t="shared" si="45"/>
         <v>BOM</v>
       </c>
-      <c r="M255">
-        <v>0</v>
-      </c>
-      <c r="N255">
+      <c r="M255" s="9">
+        <v>0</v>
+      </c>
+      <c r="N255" s="9">
         <v>100</v>
       </c>
-      <c r="O255">
+      <c r="O255" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>46153</v>
       </c>
@@ -12799,6 +13282,9 @@
       </c>
       <c r="G256" s="3">
         <v>1</v>
+      </c>
+      <c r="H256" s="3">
+        <v>0</v>
       </c>
       <c r="I256" s="3">
         <f t="shared" ref="I256:I267" si="61">E256+G256+H256</f>
@@ -12871,7 +13357,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>46153</v>
       </c>
@@ -12889,6 +13375,9 @@
       </c>
       <c r="G258" s="3">
         <v>5</v>
+      </c>
+      <c r="H258" s="3">
+        <v>0</v>
       </c>
       <c r="I258" s="3">
         <f t="shared" si="61"/>
@@ -12916,7 +13405,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>46153</v>
       </c>
@@ -12931,6 +13420,9 @@
       </c>
       <c r="E259" s="3">
         <v>23</v>
+      </c>
+      <c r="H259" s="3">
+        <v>0</v>
       </c>
       <c r="I259" s="3">
         <f t="shared" si="61"/>
@@ -12958,7 +13450,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>46153</v>
       </c>
@@ -12973,6 +13465,9 @@
       </c>
       <c r="E260" s="3">
         <v>8</v>
+      </c>
+      <c r="H260" s="3">
+        <v>0</v>
       </c>
       <c r="I260" s="3">
         <f t="shared" si="61"/>
@@ -13000,7 +13495,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>46153</v>
       </c>
@@ -13015,6 +13510,9 @@
       </c>
       <c r="E261" s="3">
         <v>11</v>
+      </c>
+      <c r="H261" s="3">
+        <v>0</v>
       </c>
       <c r="I261" s="3">
         <f t="shared" si="61"/>
@@ -13042,7 +13540,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>46153</v>
       </c>
@@ -13060,6 +13558,9 @@
       </c>
       <c r="G262" s="3">
         <v>3</v>
+      </c>
+      <c r="H262" s="3">
+        <v>0</v>
       </c>
       <c r="I262" s="3">
         <f t="shared" si="61"/>
@@ -13087,7 +13588,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>46153</v>
       </c>
@@ -13105,6 +13606,9 @@
       </c>
       <c r="G263" s="3">
         <v>6</v>
+      </c>
+      <c r="H263" s="3">
+        <v>0</v>
       </c>
       <c r="I263" s="3">
         <f t="shared" si="61"/>
@@ -13132,7 +13636,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>46153</v>
       </c>
@@ -13150,6 +13654,9 @@
       </c>
       <c r="G264" s="3">
         <v>2</v>
+      </c>
+      <c r="H264" s="3">
+        <v>0</v>
       </c>
       <c r="I264" s="3">
         <f t="shared" si="61"/>
@@ -13177,7 +13684,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>46153</v>
       </c>
@@ -13195,6 +13702,9 @@
       </c>
       <c r="G265" s="3">
         <v>1</v>
+      </c>
+      <c r="H265" s="3">
+        <v>0</v>
       </c>
       <c r="I265" s="3">
         <f t="shared" si="61"/>
@@ -13222,7 +13732,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>46153</v>
       </c>
@@ -13237,6 +13747,9 @@
       </c>
       <c r="E266" s="3">
         <v>21</v>
+      </c>
+      <c r="H266" s="3">
+        <v>0</v>
       </c>
       <c r="I266" s="3">
         <f t="shared" si="61"/>
@@ -13264,7 +13777,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>46154</v>
       </c>
@@ -13282,6 +13795,9 @@
       </c>
       <c r="G267" s="3">
         <v>8</v>
+      </c>
+      <c r="H267" s="3">
+        <v>0</v>
       </c>
       <c r="I267" s="3">
         <f t="shared" si="61"/>
@@ -13357,7 +13873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>46154</v>
       </c>
@@ -13375,6 +13891,9 @@
       </c>
       <c r="G269" s="3">
         <v>2</v>
+      </c>
+      <c r="H269" s="3">
+        <v>0</v>
       </c>
       <c r="I269" s="3">
         <f t="shared" ref="I269:I278" si="65">E269+G269+H269</f>
@@ -13402,7 +13921,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>46154</v>
       </c>
@@ -13420,6 +13939,9 @@
       </c>
       <c r="G270" s="3">
         <v>4</v>
+      </c>
+      <c r="H270" s="3">
+        <v>0</v>
       </c>
       <c r="I270" s="3">
         <f t="shared" si="65"/>
@@ -13447,7 +13969,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>46154</v>
       </c>
@@ -13465,6 +13987,9 @@
       </c>
       <c r="G271" s="3">
         <v>3</v>
+      </c>
+      <c r="H271" s="3">
+        <v>0</v>
       </c>
       <c r="I271" s="3">
         <f t="shared" si="65"/>
@@ -13492,7 +14017,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>46154</v>
       </c>
@@ -13507,6 +14032,9 @@
       </c>
       <c r="E272" s="3">
         <v>26</v>
+      </c>
+      <c r="H272" s="3">
+        <v>0</v>
       </c>
       <c r="I272" s="3">
         <f t="shared" si="65"/>
@@ -13534,7 +14062,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>46154</v>
       </c>
@@ -13552,6 +14080,9 @@
       </c>
       <c r="G273" s="3">
         <v>5</v>
+      </c>
+      <c r="H273" s="3">
+        <v>0</v>
       </c>
       <c r="I273" s="3">
         <f t="shared" si="65"/>
@@ -13579,7 +14110,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>46154</v>
       </c>
@@ -13594,6 +14125,9 @@
       </c>
       <c r="E274" s="3">
         <v>39</v>
+      </c>
+      <c r="H274" s="3">
+        <v>0</v>
       </c>
       <c r="I274" s="3">
         <f t="shared" si="65"/>
@@ -13621,7 +14155,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>46154</v>
       </c>
@@ -13636,6 +14170,9 @@
       </c>
       <c r="E275" s="3">
         <v>30</v>
+      </c>
+      <c r="H275" s="3">
+        <v>0</v>
       </c>
       <c r="I275" s="3">
         <f t="shared" si="65"/>
@@ -13663,7 +14200,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>46154</v>
       </c>
@@ -13678,6 +14215,9 @@
       </c>
       <c r="E276" s="3">
         <v>26</v>
+      </c>
+      <c r="H276" s="3">
+        <v>0</v>
       </c>
       <c r="I276" s="3">
         <f t="shared" si="65"/>
@@ -13705,7 +14245,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>46154</v>
       </c>
@@ -13723,6 +14263,9 @@
       </c>
       <c r="G277" s="3">
         <v>2</v>
+      </c>
+      <c r="H277" s="3">
+        <v>0</v>
       </c>
       <c r="I277" s="3">
         <f t="shared" si="65"/>
@@ -13750,7 +14293,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>46154</v>
       </c>
@@ -13768,6 +14311,9 @@
       </c>
       <c r="G278" s="3">
         <v>5</v>
+      </c>
+      <c r="H278" s="3">
+        <v>0</v>
       </c>
       <c r="I278" s="3">
         <f t="shared" si="65"/>
@@ -13795,7 +14341,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>46154</v>
       </c>
@@ -13833,13 +14379,13 @@
         <f t="shared" si="64"/>
         <v>BOM</v>
       </c>
-      <c r="M279">
-        <v>0</v>
-      </c>
-      <c r="N279">
+      <c r="M279" s="9">
+        <v>0</v>
+      </c>
+      <c r="N279" s="9">
         <v>100</v>
       </c>
-      <c r="O279">
+      <c r="O279" s="9">
         <v>9.5238095238095237</v>
       </c>
     </row>
@@ -13881,17 +14427,17 @@
         <f t="shared" si="64"/>
         <v>BOM</v>
       </c>
-      <c r="M280">
-        <v>0</v>
-      </c>
-      <c r="N280">
+      <c r="M280" s="9">
+        <v>0</v>
+      </c>
+      <c r="N280" s="9">
         <v>100</v>
       </c>
-      <c r="O280">
+      <c r="O280" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>46154</v>
       </c>
@@ -13906,6 +14452,9 @@
       </c>
       <c r="E281" s="3">
         <v>25</v>
+      </c>
+      <c r="H281" s="3">
+        <v>0</v>
       </c>
       <c r="I281" s="3">
         <f t="shared" ref="I281:I286" si="68">E281+G281+H281</f>
@@ -13978,7 +14527,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>46154</v>
       </c>
@@ -13993,6 +14542,9 @@
       </c>
       <c r="E283" s="3">
         <v>24</v>
+      </c>
+      <c r="H283" s="3">
+        <v>0</v>
       </c>
       <c r="I283" s="3">
         <f t="shared" si="68"/>
@@ -14020,7 +14572,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>46154</v>
       </c>
@@ -14038,6 +14590,9 @@
       </c>
       <c r="G284" s="3">
         <v>8</v>
+      </c>
+      <c r="H284" s="3">
+        <v>0</v>
       </c>
       <c r="I284" s="3">
         <f t="shared" si="68"/>
@@ -14065,7 +14620,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>46154</v>
       </c>
@@ -14083,6 +14638,9 @@
       </c>
       <c r="G285" s="3">
         <v>9</v>
+      </c>
+      <c r="H285" s="3">
+        <v>0</v>
       </c>
       <c r="I285" s="3">
         <f t="shared" si="68"/>
@@ -14110,7 +14668,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>46154</v>
       </c>
@@ -14128,6 +14686,9 @@
       </c>
       <c r="G286" s="3">
         <v>5</v>
+      </c>
+      <c r="H286" s="3">
+        <v>0</v>
       </c>
       <c r="I286" s="3">
         <f t="shared" si="68"/>
@@ -14193,17 +14754,17 @@
         <f t="shared" si="64"/>
         <v>BOM</v>
       </c>
-      <c r="M287">
-        <v>0</v>
-      </c>
-      <c r="N287">
-        <v>0</v>
-      </c>
-      <c r="O287">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M287" s="9">
+        <v>0</v>
+      </c>
+      <c r="N287" s="9">
+        <v>0</v>
+      </c>
+      <c r="O287" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>46154</v>
       </c>
@@ -14218,6 +14779,9 @@
       </c>
       <c r="E288" s="3">
         <v>22</v>
+      </c>
+      <c r="H288" s="3">
+        <v>0</v>
       </c>
       <c r="I288" s="3">
         <f t="shared" ref="I288:I293" si="71">E288+G288+H288</f>
@@ -14245,7 +14809,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>46154</v>
       </c>
@@ -14263,6 +14827,9 @@
       </c>
       <c r="G289" s="3">
         <v>1</v>
+      </c>
+      <c r="H289" s="3">
+        <v>0</v>
       </c>
       <c r="I289" s="3">
         <f t="shared" si="71"/>
@@ -14290,7 +14857,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>46154</v>
       </c>
@@ -14308,6 +14875,9 @@
       </c>
       <c r="G290" s="3">
         <v>7</v>
+      </c>
+      <c r="H290" s="3">
+        <v>0</v>
       </c>
       <c r="I290" s="3">
         <f t="shared" si="71"/>
@@ -14335,7 +14905,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>46154</v>
       </c>
@@ -14352,6 +14922,9 @@
         <v>25</v>
       </c>
       <c r="G291" s="3">
+        <v>0</v>
+      </c>
+      <c r="H291" s="3">
         <v>0</v>
       </c>
       <c r="I291" s="3">
@@ -14380,7 +14953,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>46154</v>
       </c>
@@ -14398,6 +14971,9 @@
       </c>
       <c r="G292" s="3">
         <v>2</v>
+      </c>
+      <c r="H292" s="3">
+        <v>0</v>
       </c>
       <c r="I292" s="3">
         <f t="shared" si="71"/>
@@ -14425,7 +15001,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="5">
         <v>46154</v>
       </c>
@@ -14440,6 +15016,9 @@
       </c>
       <c r="E293" s="3">
         <v>24</v>
+      </c>
+      <c r="H293" s="3">
+        <v>0</v>
       </c>
       <c r="I293" s="3">
         <f t="shared" si="71"/>
@@ -14505,17 +15084,17 @@
         <f t="shared" si="64"/>
         <v>BOM</v>
       </c>
-      <c r="M294">
-        <v>0</v>
-      </c>
-      <c r="N294">
+      <c r="M294" s="9">
+        <v>0</v>
+      </c>
+      <c r="N294" s="9">
         <v>100</v>
       </c>
-      <c r="O294">
+      <c r="O294" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="5">
         <v>46154</v>
       </c>
@@ -14533,6 +15112,9 @@
       </c>
       <c r="G295" s="3">
         <v>4</v>
+      </c>
+      <c r="H295" s="3">
+        <v>0</v>
       </c>
       <c r="I295" s="3">
         <f t="shared" ref="I295:I311" si="74">E295+G295+H295</f>
@@ -14560,7 +15142,7 @@
         <v>19.93957703927493</v>
       </c>
     </row>
-    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="5">
         <v>46154</v>
       </c>
@@ -14575,6 +15157,9 @@
       </c>
       <c r="E296" s="3">
         <v>7</v>
+      </c>
+      <c r="H296" s="3">
+        <v>0</v>
       </c>
       <c r="I296" s="3">
         <f t="shared" si="74"/>
@@ -14602,7 +15187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="5">
         <v>46154</v>
       </c>
@@ -14617,6 +15202,9 @@
       </c>
       <c r="E297" s="3">
         <v>16</v>
+      </c>
+      <c r="H297" s="3">
+        <v>0</v>
       </c>
       <c r="I297" s="3">
         <f t="shared" si="74"/>
@@ -14644,7 +15232,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="5">
         <v>46154</v>
       </c>
@@ -14659,6 +15247,9 @@
       </c>
       <c r="E298" s="3">
         <v>27</v>
+      </c>
+      <c r="H298" s="3">
+        <v>0</v>
       </c>
       <c r="I298" s="3">
         <f t="shared" si="74"/>
@@ -14686,7 +15277,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="5">
         <v>46154</v>
       </c>
@@ -14701,6 +15292,9 @@
       </c>
       <c r="E299" s="3">
         <v>7</v>
+      </c>
+      <c r="H299" s="3">
+        <v>0</v>
       </c>
       <c r="I299" s="3">
         <f t="shared" si="74"/>
@@ -14821,7 +15415,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>46154</v>
       </c>
@@ -14839,6 +15433,9 @@
       </c>
       <c r="G302" s="3">
         <v>2</v>
+      </c>
+      <c r="H302" s="3">
+        <v>0</v>
       </c>
       <c r="I302" s="3">
         <f t="shared" si="74"/>
@@ -14866,7 +15463,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>46154</v>
       </c>
@@ -14881,6 +15478,9 @@
       </c>
       <c r="E303" s="3">
         <v>23</v>
+      </c>
+      <c r="H303" s="3">
+        <v>0</v>
       </c>
       <c r="I303" s="3">
         <f t="shared" si="74"/>
@@ -14908,7 +15508,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>46154</v>
       </c>
@@ -14923,6 +15523,9 @@
       </c>
       <c r="E304" s="3">
         <v>26</v>
+      </c>
+      <c r="H304" s="3">
+        <v>0</v>
       </c>
       <c r="I304" s="3">
         <f t="shared" si="74"/>
@@ -14950,7 +15553,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>46154</v>
       </c>
@@ -14965,6 +15568,9 @@
       </c>
       <c r="E305" s="3">
         <v>21</v>
+      </c>
+      <c r="H305" s="3">
+        <v>0</v>
       </c>
       <c r="I305" s="3">
         <f t="shared" si="74"/>
@@ -14992,7 +15598,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>46154</v>
       </c>
@@ -15007,6 +15613,9 @@
       </c>
       <c r="E306" s="3">
         <v>12</v>
+      </c>
+      <c r="H306" s="3">
+        <v>0</v>
       </c>
       <c r="I306" s="3">
         <f t="shared" si="74"/>
@@ -15034,7 +15643,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>46154</v>
       </c>
@@ -15052,6 +15661,9 @@
       </c>
       <c r="G307" s="3">
         <v>1</v>
+      </c>
+      <c r="H307" s="3">
+        <v>0</v>
       </c>
       <c r="I307" s="3">
         <f t="shared" si="74"/>
@@ -15079,7 +15691,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>46154</v>
       </c>
@@ -15097,6 +15709,9 @@
       </c>
       <c r="G308" s="3">
         <v>1</v>
+      </c>
+      <c r="H308" s="3">
+        <v>0</v>
       </c>
       <c r="I308" s="3">
         <f t="shared" si="74"/>
@@ -15124,7 +15739,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>46154</v>
       </c>
@@ -15139,6 +15754,9 @@
       </c>
       <c r="E309" s="3">
         <v>19</v>
+      </c>
+      <c r="H309" s="3">
+        <v>0</v>
       </c>
       <c r="I309" s="3">
         <f t="shared" si="74"/>
@@ -15166,7 +15784,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>46154</v>
       </c>
@@ -15184,6 +15802,9 @@
       </c>
       <c r="G310" s="3">
         <v>4</v>
+      </c>
+      <c r="H310" s="3">
+        <v>0</v>
       </c>
       <c r="I310" s="3">
         <f t="shared" si="74"/>
@@ -15211,7 +15832,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A311" s="5">
         <v>46155</v>
       </c>
@@ -15229,6 +15850,9 @@
       </c>
       <c r="G311" s="3">
         <v>2</v>
+      </c>
+      <c r="H311" s="3">
+        <v>0</v>
       </c>
       <c r="I311" s="3">
         <f t="shared" si="74"/>
@@ -15304,7 +15928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A313" s="5">
         <v>46155</v>
       </c>
@@ -15322,6 +15946,9 @@
       </c>
       <c r="G313" s="3">
         <v>7</v>
+      </c>
+      <c r="H313" s="3">
+        <v>0</v>
       </c>
       <c r="I313" s="3">
         <f t="shared" ref="I313:I322" si="77">E313+G313+H313</f>
@@ -15349,7 +15976,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A314" s="5">
         <v>46155</v>
       </c>
@@ -15364,6 +15991,9 @@
       </c>
       <c r="E314" s="3">
         <v>23</v>
+      </c>
+      <c r="H314" s="3">
+        <v>0</v>
       </c>
       <c r="I314" s="3">
         <f t="shared" si="77"/>
@@ -15391,7 +16021,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A315" s="5">
         <v>46155</v>
       </c>
@@ -15409,6 +16039,9 @@
       </c>
       <c r="G315" s="3">
         <v>1</v>
+      </c>
+      <c r="H315" s="3">
+        <v>0</v>
       </c>
       <c r="I315" s="3">
         <f t="shared" si="77"/>
@@ -15436,7 +16069,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A316" s="5">
         <v>46155</v>
       </c>
@@ -15454,6 +16087,9 @@
       </c>
       <c r="G316" s="3">
         <v>5</v>
+      </c>
+      <c r="H316" s="3">
+        <v>0</v>
       </c>
       <c r="I316" s="3">
         <f t="shared" si="77"/>
@@ -15481,7 +16117,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
         <v>46155</v>
       </c>
@@ -15499,6 +16135,9 @@
       </c>
       <c r="G317" s="3">
         <v>3</v>
+      </c>
+      <c r="H317" s="3">
+        <v>0</v>
       </c>
       <c r="I317" s="3">
         <f t="shared" si="77"/>
@@ -15526,7 +16165,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
         <v>46155</v>
       </c>
@@ -15541,6 +16180,9 @@
       </c>
       <c r="E318" s="3">
         <v>30</v>
+      </c>
+      <c r="H318" s="3">
+        <v>0</v>
       </c>
       <c r="I318" s="3">
         <f t="shared" si="77"/>
@@ -15568,7 +16210,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
         <v>46155</v>
       </c>
@@ -15586,6 +16228,9 @@
       </c>
       <c r="G319" s="3">
         <v>4</v>
+      </c>
+      <c r="H319" s="3">
+        <v>0</v>
       </c>
       <c r="I319" s="3">
         <f t="shared" si="77"/>
@@ -15613,7 +16258,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
         <v>46155</v>
       </c>
@@ -15631,6 +16276,9 @@
       </c>
       <c r="G320" s="3">
         <v>5</v>
+      </c>
+      <c r="H320" s="3">
+        <v>0</v>
       </c>
       <c r="I320" s="3">
         <f t="shared" si="77"/>
@@ -15658,7 +16306,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>46155</v>
       </c>
@@ -15673,6 +16321,9 @@
       </c>
       <c r="E321" s="3">
         <v>23</v>
+      </c>
+      <c r="H321" s="3">
+        <v>0</v>
       </c>
       <c r="I321" s="3">
         <f t="shared" si="77"/>
@@ -15700,7 +16351,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322" s="5">
         <v>46155</v>
       </c>
@@ -15718,6 +16369,9 @@
       </c>
       <c r="G322" s="3">
         <v>2</v>
+      </c>
+      <c r="H322" s="3">
+        <v>0</v>
       </c>
       <c r="I322" s="3">
         <f t="shared" si="77"/>
@@ -15745,7 +16399,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
         <v>46155</v>
       </c>
@@ -15783,13 +16437,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M323">
-        <v>0</v>
-      </c>
-      <c r="N323">
+      <c r="M323" s="9">
+        <v>0</v>
+      </c>
+      <c r="N323" s="9">
         <v>100</v>
       </c>
-      <c r="O323">
+      <c r="O323" s="9">
         <v>9.5238095238095237</v>
       </c>
     </row>
@@ -15831,13 +16485,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M324">
-        <v>0</v>
-      </c>
-      <c r="N324">
+      <c r="M324" s="9">
+        <v>0</v>
+      </c>
+      <c r="N324" s="9">
         <v>100</v>
       </c>
-      <c r="O324">
+      <c r="O324" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -15889,7 +16543,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
         <v>46155</v>
       </c>
@@ -15907,6 +16561,9 @@
       </c>
       <c r="G326" s="3">
         <v>1</v>
+      </c>
+      <c r="H326" s="3">
+        <v>0</v>
       </c>
       <c r="I326" s="3">
         <f>E326+G326+H326</f>
@@ -15934,7 +16591,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
         <v>46155</v>
       </c>
@@ -15952,6 +16609,9 @@
       </c>
       <c r="G327" s="3">
         <v>3</v>
+      </c>
+      <c r="H327" s="3">
+        <v>0</v>
       </c>
       <c r="I327" s="3">
         <f>E327+G327+H327</f>
@@ -15979,7 +16639,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
         <v>46155</v>
       </c>
@@ -15997,6 +16657,9 @@
       </c>
       <c r="G328" s="3">
         <v>5</v>
+      </c>
+      <c r="H328" s="3">
+        <v>0</v>
       </c>
       <c r="I328" s="3">
         <f>E328+G328+H328</f>
@@ -16024,7 +16687,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
         <v>46155</v>
       </c>
@@ -16039,6 +16702,9 @@
       </c>
       <c r="E329" s="3">
         <v>27</v>
+      </c>
+      <c r="H329" s="3">
+        <v>0</v>
       </c>
       <c r="I329" s="3">
         <f>E329+G329+H329</f>
@@ -16104,17 +16770,17 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M330">
-        <v>0</v>
-      </c>
-      <c r="N330">
-        <v>0</v>
-      </c>
-      <c r="O330">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="M330" s="9">
+        <v>0</v>
+      </c>
+      <c r="N330" s="9">
+        <v>0</v>
+      </c>
+      <c r="O330" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
         <v>46155</v>
       </c>
@@ -16132,6 +16798,9 @@
       </c>
       <c r="G331" s="3">
         <v>6</v>
+      </c>
+      <c r="H331" s="3">
+        <v>0</v>
       </c>
       <c r="I331" s="3">
         <f>E331+G331+H331</f>
@@ -16159,7 +16828,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>46155</v>
       </c>
@@ -16174,6 +16843,9 @@
       </c>
       <c r="E332" s="3">
         <v>26</v>
+      </c>
+      <c r="H332" s="3">
+        <v>0</v>
       </c>
       <c r="I332" s="3">
         <f>E332+G332+H332</f>
@@ -16239,17 +16911,17 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M333">
-        <v>0</v>
-      </c>
-      <c r="N333">
+      <c r="M333" s="9">
+        <v>0</v>
+      </c>
+      <c r="N333" s="9">
         <v>100</v>
       </c>
-      <c r="O333">
+      <c r="O333" s="9">
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
         <v>46155</v>
       </c>
@@ -16267,6 +16939,9 @@
       </c>
       <c r="G334" s="3">
         <v>1</v>
+      </c>
+      <c r="H334" s="3">
+        <v>0</v>
       </c>
       <c r="I334" s="3">
         <f>E334+G334+H334</f>
@@ -16294,7 +16969,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
         <v>46155</v>
       </c>
@@ -16312,6 +16987,9 @@
       </c>
       <c r="G335" s="3">
         <v>5</v>
+      </c>
+      <c r="H335" s="3">
+        <v>0</v>
       </c>
       <c r="I335" s="3">
         <f>E335+G335+H335</f>
@@ -16339,7 +17017,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
         <v>46155</v>
       </c>
@@ -16357,6 +17035,9 @@
       </c>
       <c r="G336" s="3">
         <v>1</v>
+      </c>
+      <c r="H336" s="3">
+        <v>0</v>
       </c>
       <c r="I336" s="3">
         <f>E336+G336+H336</f>
@@ -16422,17 +17103,17 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M337">
-        <v>0</v>
-      </c>
-      <c r="N337">
+      <c r="M337" s="9">
+        <v>0</v>
+      </c>
+      <c r="N337" s="9">
         <v>100</v>
       </c>
-      <c r="O337">
+      <c r="O337" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
         <v>46155</v>
       </c>
@@ -16450,6 +17131,9 @@
       </c>
       <c r="G338" s="3">
         <v>1</v>
+      </c>
+      <c r="H338" s="3">
+        <v>0</v>
       </c>
       <c r="I338" s="3">
         <f t="shared" ref="I338:I355" si="81">E338+G338+H338</f>
@@ -16525,7 +17209,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
         <v>46155</v>
       </c>
@@ -16540,6 +17224,9 @@
       </c>
       <c r="E340" s="3">
         <v>5</v>
+      </c>
+      <c r="H340" s="3">
+        <v>0</v>
       </c>
       <c r="I340" s="3">
         <f t="shared" si="81"/>
@@ -16567,7 +17254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
         <v>46155</v>
       </c>
@@ -16582,6 +17269,9 @@
       </c>
       <c r="E341" s="3">
         <v>19</v>
+      </c>
+      <c r="H341" s="3">
+        <v>0</v>
       </c>
       <c r="I341" s="3">
         <f t="shared" si="81"/>
@@ -16657,7 +17347,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>46155</v>
       </c>
@@ -16672,6 +17362,9 @@
       </c>
       <c r="E343" s="3">
         <v>6</v>
+      </c>
+      <c r="H343" s="3">
+        <v>0</v>
       </c>
       <c r="I343" s="3">
         <f t="shared" si="81"/>
@@ -16699,7 +17392,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>46155</v>
       </c>
@@ -16714,6 +17407,9 @@
       </c>
       <c r="E344" s="3">
         <v>18</v>
+      </c>
+      <c r="H344" s="3">
+        <v>0</v>
       </c>
       <c r="I344" s="3">
         <f t="shared" si="81"/>
@@ -16789,7 +17485,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
         <v>46155</v>
       </c>
@@ -16807,6 +17503,9 @@
       </c>
       <c r="G346" s="3">
         <v>4</v>
+      </c>
+      <c r="H346" s="3">
+        <v>0</v>
       </c>
       <c r="I346" s="3">
         <f t="shared" si="81"/>
@@ -16834,7 +17533,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
         <v>46155</v>
       </c>
@@ -16852,6 +17551,9 @@
       </c>
       <c r="G347" s="3">
         <v>1</v>
+      </c>
+      <c r="H347" s="3">
+        <v>0</v>
       </c>
       <c r="I347" s="3">
         <f t="shared" si="81"/>
@@ -16879,7 +17581,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
         <v>46155</v>
       </c>
@@ -16894,6 +17596,9 @@
       </c>
       <c r="E348" s="3">
         <v>22</v>
+      </c>
+      <c r="H348" s="3">
+        <v>0</v>
       </c>
       <c r="I348" s="3">
         <f t="shared" si="81"/>
@@ -16921,7 +17626,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
         <v>46155</v>
       </c>
@@ -16936,6 +17641,9 @@
       </c>
       <c r="E349" s="3">
         <v>11</v>
+      </c>
+      <c r="H349" s="3">
+        <v>0</v>
       </c>
       <c r="I349" s="3">
         <f t="shared" si="81"/>
@@ -16963,7 +17671,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
         <v>46155</v>
       </c>
@@ -16981,6 +17689,9 @@
       </c>
       <c r="G350" s="3">
         <v>4</v>
+      </c>
+      <c r="H350" s="3">
+        <v>0</v>
       </c>
       <c r="I350" s="3">
         <f t="shared" si="81"/>
@@ -17008,7 +17719,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>46155</v>
       </c>
@@ -17026,6 +17737,9 @@
       </c>
       <c r="G351" s="3">
         <v>7</v>
+      </c>
+      <c r="H351" s="3">
+        <v>0</v>
       </c>
       <c r="I351" s="3">
         <f t="shared" si="81"/>
@@ -17053,7 +17767,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
         <v>46155</v>
       </c>
@@ -17071,6 +17785,9 @@
       </c>
       <c r="G352" s="3">
         <v>5</v>
+      </c>
+      <c r="H352" s="3">
+        <v>0</v>
       </c>
       <c r="I352" s="3">
         <f t="shared" si="81"/>
@@ -17098,7 +17815,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
         <v>46155</v>
       </c>
@@ -17116,6 +17833,9 @@
       </c>
       <c r="G353" s="3">
         <v>5</v>
+      </c>
+      <c r="H353" s="3">
+        <v>0</v>
       </c>
       <c r="I353" s="3">
         <f t="shared" si="81"/>
@@ -17143,7 +17863,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354" s="5">
         <v>46155</v>
       </c>
@@ -17158,6 +17878,9 @@
       </c>
       <c r="E354" s="3">
         <v>23</v>
+      </c>
+      <c r="H354" s="3">
+        <v>0</v>
       </c>
       <c r="I354" s="3">
         <f t="shared" si="81"/>
@@ -17761,7 +18484,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
         <v>46156</v>
       </c>
@@ -17799,13 +18522,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M367">
-        <v>0</v>
-      </c>
-      <c r="N367">
+      <c r="M367" s="9">
+        <v>0</v>
+      </c>
+      <c r="N367" s="9">
         <v>100</v>
       </c>
-      <c r="O367">
+      <c r="O367" s="9">
         <v>9.5238095238095237</v>
       </c>
     </row>
@@ -17847,13 +18570,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M368">
-        <v>0</v>
-      </c>
-      <c r="N368">
+      <c r="M368" s="9">
+        <v>0</v>
+      </c>
+      <c r="N368" s="9">
         <v>100</v>
       </c>
-      <c r="O368">
+      <c r="O368" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -18135,13 +18858,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M374">
-        <v>0</v>
-      </c>
-      <c r="N374">
-        <v>0</v>
-      </c>
-      <c r="O374">
+      <c r="M374" s="9">
+        <v>0</v>
+      </c>
+      <c r="N374" s="9">
+        <v>0</v>
+      </c>
+      <c r="O374" s="9">
         <v>0</v>
       </c>
     </row>
@@ -18471,13 +19194,13 @@
         <f t="shared" si="80"/>
         <v>BOM</v>
       </c>
-      <c r="M381">
-        <v>0</v>
-      </c>
-      <c r="N381">
+      <c r="M381" s="9">
+        <v>0</v>
+      </c>
+      <c r="N381" s="9">
         <v>100</v>
       </c>
-      <c r="O381">
+      <c r="O381" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
@@ -19911,13 +20634,13 @@
         <f t="shared" si="93"/>
         <v>BOM</v>
       </c>
-      <c r="M411">
-        <v>0</v>
-      </c>
-      <c r="N411">
+      <c r="M411" s="9">
+        <v>0</v>
+      </c>
+      <c r="N411" s="9">
         <v>100</v>
       </c>
-      <c r="O411">
+      <c r="O411" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -20199,13 +20922,13 @@
         <f t="shared" si="93"/>
         <v>BOM</v>
       </c>
-      <c r="M417">
-        <v>0</v>
-      </c>
-      <c r="N417">
-        <v>0</v>
-      </c>
-      <c r="O417">
+      <c r="M417" s="9">
+        <v>0</v>
+      </c>
+      <c r="N417" s="9">
+        <v>0</v>
+      </c>
+      <c r="O417" s="9">
         <v>0</v>
       </c>
     </row>
@@ -20487,13 +21210,13 @@
         <f t="shared" si="93"/>
         <v>BOM</v>
       </c>
-      <c r="M423">
-        <v>0</v>
-      </c>
-      <c r="N423">
+      <c r="M423" s="9">
+        <v>0</v>
+      </c>
+      <c r="N423" s="9">
         <v>100</v>
       </c>
-      <c r="O423">
+      <c r="O423" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
@@ -21543,13 +22266,13 @@
         <f t="shared" si="93"/>
         <v>BOM</v>
       </c>
-      <c r="M445">
-        <v>0</v>
-      </c>
-      <c r="N445">
+      <c r="M445" s="9">
+        <v>0</v>
+      </c>
+      <c r="N445" s="9">
         <v>96.34</v>
       </c>
-      <c r="O445">
+      <c r="O445" s="9">
         <v>17.571884984025559</v>
       </c>
     </row>
@@ -21831,13 +22554,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M451">
-        <v>0</v>
-      </c>
-      <c r="N451">
+      <c r="M451" s="9">
+        <v>0</v>
+      </c>
+      <c r="N451" s="9">
         <v>98.63</v>
       </c>
-      <c r="O451">
+      <c r="O451" s="9">
         <v>18.75</v>
       </c>
     </row>
@@ -21927,13 +22650,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M453">
-        <v>0</v>
-      </c>
-      <c r="N453">
+      <c r="M453" s="9">
+        <v>0</v>
+      </c>
+      <c r="N453" s="9">
         <v>99.06</v>
       </c>
-      <c r="O453">
+      <c r="O453" s="9">
         <v>22.95719844357977</v>
       </c>
     </row>
@@ -22023,13 +22746,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M455">
-        <v>0</v>
-      </c>
-      <c r="N455">
+      <c r="M455" s="9">
+        <v>0</v>
+      </c>
+      <c r="N455" s="9">
         <v>100</v>
       </c>
-      <c r="O455">
+      <c r="O455" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -22311,13 +23034,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M461">
-        <v>0</v>
-      </c>
-      <c r="N461">
-        <v>0</v>
-      </c>
-      <c r="O461">
+      <c r="M461" s="9">
+        <v>0</v>
+      </c>
+      <c r="N461" s="9">
+        <v>0</v>
+      </c>
+      <c r="O461" s="9">
         <v>0</v>
       </c>
     </row>
@@ -22647,13 +23370,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M468">
-        <v>0</v>
-      </c>
-      <c r="N468">
+      <c r="M468" s="9">
+        <v>0</v>
+      </c>
+      <c r="N468" s="9">
         <v>100</v>
       </c>
-      <c r="O468">
+      <c r="O468" s="9">
         <v>4.3478260869565224</v>
       </c>
     </row>
@@ -23991,13 +24714,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M496">
-        <v>0</v>
-      </c>
-      <c r="N496">
+      <c r="M496" s="9">
+        <v>0</v>
+      </c>
+      <c r="N496" s="9">
         <v>98.63</v>
       </c>
-      <c r="O496">
+      <c r="O496" s="9">
         <v>18.75</v>
       </c>
     </row>
@@ -24087,13 +24810,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M498">
-        <v>0</v>
-      </c>
-      <c r="N498">
+      <c r="M498" s="9">
+        <v>0</v>
+      </c>
+      <c r="N498" s="9">
         <v>99.06</v>
       </c>
-      <c r="O498">
+      <c r="O498" s="9">
         <v>22.95719844357977</v>
       </c>
     </row>
@@ -24193,7 +24916,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="7">
         <v>46161</v>
       </c>
@@ -24282,13 +25005,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M502">
-        <v>0</v>
-      </c>
-      <c r="N502">
+      <c r="M502" s="9">
+        <v>0</v>
+      </c>
+      <c r="N502" s="9">
         <v>100</v>
       </c>
-      <c r="O502">
+      <c r="O502" s="9">
         <v>17.241379310344829</v>
       </c>
     </row>
@@ -24618,13 +25341,13 @@
         <f t="shared" si="100"/>
         <v>BOM</v>
       </c>
-      <c r="M509">
-        <v>0</v>
-      </c>
-      <c r="N509">
-        <v>0</v>
-      </c>
-      <c r="O509">
+      <c r="M509" s="9">
+        <v>0</v>
+      </c>
+      <c r="N509" s="9">
+        <v>0</v>
+      </c>
+      <c r="O509" s="9">
         <v>0</v>
       </c>
     </row>
@@ -24855,7 +25578,7 @@
         <v>5</v>
       </c>
       <c r="L514" s="3" t="str">
-        <f t="shared" ref="L514:L577" si="116">IF(K514&lt;-5,"CRÍTICO",IF(K514&lt;0,"ATENÇÃO",IF(K514&lt;=5,"BOM","EXCELENTE")))</f>
+        <f t="shared" ref="L514:L530" si="116">IF(K514&lt;-5,"CRÍTICO",IF(K514&lt;0,"ATENÇÃO",IF(K514&lt;=5,"BOM","EXCELENTE")))</f>
         <v>BOM</v>
       </c>
       <c r="M514">
@@ -26392,7 +27115,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="7">
         <v>46162</v>
       </c>
@@ -28668,7 +29391,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="5">
         <v>46163</v>
       </c>
@@ -30183,7 +30906,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="621" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A621" s="10">
         <v>46164</v>
       </c>
@@ -30204,6 +30927,9 @@
       </c>
       <c r="G621" s="3">
         <v>1</v>
+      </c>
+      <c r="H621" s="3">
+        <v>0</v>
       </c>
       <c r="I621" s="3">
         <f t="shared" si="135"/>
@@ -30231,7 +30957,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A622" s="10">
         <v>46164</v>
       </c>
@@ -30251,6 +30977,9 @@
         <v>0</v>
       </c>
       <c r="G622" s="3">
+        <v>0</v>
+      </c>
+      <c r="H622" s="3">
         <v>0</v>
       </c>
       <c r="I622" s="3">
@@ -30278,7 +31007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A623" s="10">
         <v>46164</v>
       </c>
@@ -30299,6 +31028,9 @@
       </c>
       <c r="G623" s="3">
         <v>3</v>
+      </c>
+      <c r="H623" s="3">
+        <v>0</v>
       </c>
       <c r="I623" s="3">
         <f t="shared" si="135"/>
@@ -30326,7 +31058,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="624" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A624" s="10">
         <v>46164</v>
       </c>
@@ -30347,6 +31079,9 @@
       </c>
       <c r="G624" s="3">
         <v>3</v>
+      </c>
+      <c r="H624" s="3">
+        <v>0</v>
       </c>
       <c r="I624" s="3">
         <f t="shared" si="135"/>
@@ -30374,7 +31109,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A625" s="10">
         <v>46164</v>
       </c>
@@ -30394,6 +31129,9 @@
         <v>22.07</v>
       </c>
       <c r="G625" s="3">
+        <v>0</v>
+      </c>
+      <c r="H625" s="3">
         <v>0</v>
       </c>
       <c r="I625" s="3">
@@ -30422,7 +31160,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A626" s="10">
         <v>46164</v>
       </c>
@@ -30443,6 +31181,9 @@
       </c>
       <c r="G626" s="3">
         <v>6</v>
+      </c>
+      <c r="H626" s="3">
+        <v>0</v>
       </c>
       <c r="I626" s="3">
         <f t="shared" si="135"/>
@@ -30470,7 +31211,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A627" s="10">
         <v>46164</v>
       </c>
@@ -30490,6 +31231,9 @@
         <v>16.53</v>
       </c>
       <c r="G627" s="3">
+        <v>0</v>
+      </c>
+      <c r="H627" s="3">
         <v>0</v>
       </c>
       <c r="I627" s="3">
@@ -30518,7 +31262,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A628" s="10">
         <v>46164</v>
       </c>
@@ -30538,6 +31282,9 @@
         <v>22.38</v>
       </c>
       <c r="G628" s="3">
+        <v>0</v>
+      </c>
+      <c r="H628" s="3">
         <v>0</v>
       </c>
       <c r="I628" s="3">
@@ -30566,7 +31313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A629" s="10">
         <v>46164</v>
       </c>
@@ -30586,6 +31333,9 @@
         <v>12.06</v>
       </c>
       <c r="G629" s="3">
+        <v>0</v>
+      </c>
+      <c r="H629" s="3">
         <v>0</v>
       </c>
       <c r="I629" s="3">
@@ -30614,7 +31364,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A630" s="10">
         <v>46164</v>
       </c>
@@ -30634,6 +31384,9 @@
         <v>15.42</v>
       </c>
       <c r="G630" s="3">
+        <v>0</v>
+      </c>
+      <c r="H630" s="3">
         <v>0</v>
       </c>
       <c r="I630" s="3">
@@ -30684,7 +31437,7 @@
       <c r="G631" s="3">
         <v>0</v>
       </c>
-      <c r="H631">
+      <c r="H631" s="3">
         <v>0</v>
       </c>
       <c r="I631" s="3">
@@ -30710,7 +31463,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A632" s="10">
         <v>46164</v>
       </c>
@@ -30730,6 +31483,9 @@
         <v>10.35</v>
       </c>
       <c r="G632" s="3">
+        <v>0</v>
+      </c>
+      <c r="H632" s="3">
         <v>0</v>
       </c>
       <c r="I632" s="3">
@@ -30780,7 +31536,7 @@
       <c r="G633" s="3">
         <v>0</v>
       </c>
-      <c r="H633">
+      <c r="H633" s="3">
         <v>0</v>
       </c>
       <c r="I633" s="3">
@@ -30806,7 +31562,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A634" s="10">
         <v>46164</v>
       </c>
@@ -30826,6 +31582,9 @@
         <v>36.58</v>
       </c>
       <c r="G634" s="3">
+        <v>0</v>
+      </c>
+      <c r="H634" s="3">
         <v>0</v>
       </c>
       <c r="I634" s="3">
@@ -30854,7 +31613,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A635" s="10">
         <v>46164</v>
       </c>
@@ -30875,6 +31634,9 @@
       </c>
       <c r="G635" s="3">
         <v>1</v>
+      </c>
+      <c r="H635" s="3">
+        <v>0</v>
       </c>
       <c r="I635" s="3">
         <f>E635+G635+H635</f>
@@ -30902,7 +31664,7 @@
         <v>13.8121546961326</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="10">
         <v>46164</v>
       </c>
@@ -30975,7 +31737,7 @@
       <c r="G637" s="3">
         <v>0</v>
       </c>
-      <c r="H637">
+      <c r="H637" s="3">
         <v>0</v>
       </c>
       <c r="I637" s="3">
@@ -31001,7 +31763,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A638" s="10">
         <v>46164</v>
       </c>
@@ -31021,6 +31783,9 @@
         <v>18.34</v>
       </c>
       <c r="G638" s="3">
+        <v>0</v>
+      </c>
+      <c r="H638" s="3">
         <v>0</v>
       </c>
       <c r="I638" s="3">
@@ -31049,7 +31814,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A639" s="10">
         <v>46164</v>
       </c>
@@ -31069,6 +31834,9 @@
         <v>18.34</v>
       </c>
       <c r="G639" s="3">
+        <v>0</v>
+      </c>
+      <c r="H639" s="3">
         <v>0</v>
       </c>
       <c r="I639" s="3">
@@ -31097,7 +31865,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A640" s="10">
         <v>46164</v>
       </c>
@@ -31117,6 +31885,9 @@
         <v>28.35</v>
       </c>
       <c r="G640" s="3">
+        <v>0</v>
+      </c>
+      <c r="H640" s="3">
         <v>0</v>
       </c>
       <c r="I640" s="3">
@@ -31145,7 +31916,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A641" s="10">
         <v>46164</v>
       </c>
@@ -31166,6 +31937,9 @@
       </c>
       <c r="G641" s="3">
         <v>5</v>
+      </c>
+      <c r="H641" s="3">
+        <v>0</v>
       </c>
       <c r="I641" s="3">
         <f t="shared" si="139"/>
@@ -31193,7 +31967,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A642" s="10">
         <v>46164</v>
       </c>
@@ -31213,6 +31987,9 @@
         <v>21.55</v>
       </c>
       <c r="G642" s="3">
+        <v>0</v>
+      </c>
+      <c r="H642" s="3">
         <v>0</v>
       </c>
       <c r="I642" s="3">
@@ -31241,7 +32018,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A643" s="10">
         <v>46164</v>
       </c>
@@ -31262,6 +32039,9 @@
       </c>
       <c r="G643" s="3">
         <v>1</v>
+      </c>
+      <c r="H643" s="3">
+        <v>0</v>
       </c>
       <c r="I643" s="3">
         <f t="shared" si="139"/>
@@ -31289,7 +32069,7 @@
         <v>16.97530864197531</v>
       </c>
     </row>
-    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A644" s="10">
         <v>46164</v>
       </c>
@@ -31309,6 +32089,9 @@
         <v>20.2</v>
       </c>
       <c r="G644" s="3">
+        <v>0</v>
+      </c>
+      <c r="H644" s="3">
         <v>0</v>
       </c>
       <c r="I644" s="3">
@@ -31337,7 +32120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A645" s="10">
         <v>46164</v>
       </c>
@@ -31357,6 +32140,9 @@
         <v>21.43</v>
       </c>
       <c r="G645" s="3">
+        <v>0</v>
+      </c>
+      <c r="H645" s="3">
         <v>0</v>
       </c>
       <c r="I645" s="3">
@@ -31385,7 +32171,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A646" s="10">
         <v>46164</v>
       </c>
@@ -31405,6 +32191,9 @@
         <v>16.57</v>
       </c>
       <c r="G646" s="3">
+        <v>0</v>
+      </c>
+      <c r="H646" s="3">
         <v>0</v>
       </c>
       <c r="I646" s="3">
@@ -31433,7 +32222,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A647" s="10">
         <v>46164</v>
       </c>
@@ -31454,6 +32243,9 @@
       </c>
       <c r="G647" s="3">
         <v>2</v>
+      </c>
+      <c r="H647" s="3">
+        <v>0</v>
       </c>
       <c r="I647" s="3">
         <f t="shared" si="139"/>
@@ -31481,7 +32273,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A648" s="10">
         <v>46164</v>
       </c>
@@ -31501,6 +32293,9 @@
         <v>16.59</v>
       </c>
       <c r="G648" s="3">
+        <v>0</v>
+      </c>
+      <c r="H648" s="3">
         <v>0</v>
       </c>
       <c r="I648" s="3">
@@ -31529,7 +32324,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A649" s="10">
         <v>46164</v>
       </c>
@@ -31550,6 +32345,9 @@
       </c>
       <c r="G649" s="3">
         <v>1</v>
+      </c>
+      <c r="H649" s="3">
+        <v>0</v>
       </c>
       <c r="I649" s="3">
         <f t="shared" si="139"/>
@@ -31599,7 +32397,7 @@
       <c r="G650" s="3">
         <v>0</v>
       </c>
-      <c r="H650">
+      <c r="H650" s="3">
         <v>0</v>
       </c>
       <c r="I650" s="3">
@@ -31625,7 +32423,7 @@
         <v>20.820189274447952</v>
       </c>
     </row>
-    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A651" s="10">
         <v>46164</v>
       </c>
@@ -31645,6 +32443,9 @@
         <v>12.11</v>
       </c>
       <c r="G651" s="3">
+        <v>0</v>
+      </c>
+      <c r="H651" s="3">
         <v>0</v>
       </c>
       <c r="I651" s="3">
@@ -31673,7 +32474,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A652" s="10">
         <v>46164</v>
       </c>
@@ -31693,6 +32494,9 @@
         <v>32.369999999999997</v>
       </c>
       <c r="G652" s="3">
+        <v>0</v>
+      </c>
+      <c r="H652" s="3">
         <v>0</v>
       </c>
       <c r="I652" s="3">
@@ -31721,7 +32525,7 @@
         <v>19.93957703927493</v>
       </c>
     </row>
-    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A653" s="10">
         <v>46164</v>
       </c>
@@ -31741,6 +32545,9 @@
         <v>20.010000000000002</v>
       </c>
       <c r="G653" s="3">
+        <v>0</v>
+      </c>
+      <c r="H653" s="3">
         <v>0</v>
       </c>
       <c r="I653" s="3">
@@ -31791,7 +32598,7 @@
       <c r="G654" s="3">
         <v>0</v>
       </c>
-      <c r="H654">
+      <c r="H654" s="3">
         <v>0</v>
       </c>
       <c r="I654" s="3">
@@ -31817,7 +32624,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A655" s="10">
         <v>46164</v>
       </c>
@@ -31838,6 +32645,9 @@
       </c>
       <c r="G655" s="3">
         <v>5</v>
+      </c>
+      <c r="H655" s="3">
+        <v>0</v>
       </c>
       <c r="I655" s="3">
         <f t="shared" ref="I655:I665" si="142">E655+G655+H655</f>
@@ -31865,7 +32675,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A656" s="10">
         <v>46164</v>
       </c>
@@ -31885,6 +32695,9 @@
         <v>31.4</v>
       </c>
       <c r="G656" s="3">
+        <v>0</v>
+      </c>
+      <c r="H656" s="3">
         <v>0</v>
       </c>
       <c r="I656" s="3">
@@ -31913,7 +32726,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A657" s="10">
         <v>46164</v>
       </c>
@@ -31933,6 +32746,9 @@
         <v>13.49</v>
       </c>
       <c r="G657" s="3">
+        <v>0</v>
+      </c>
+      <c r="H657" s="3">
         <v>0</v>
       </c>
       <c r="I657" s="3">
@@ -31961,7 +32777,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A658" s="10">
         <v>46164</v>
       </c>
@@ -31981,6 +32797,9 @@
         <v>22.2</v>
       </c>
       <c r="G658" s="3">
+        <v>0</v>
+      </c>
+      <c r="H658" s="3">
         <v>0</v>
       </c>
       <c r="I658" s="3">
@@ -32009,7 +32828,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A659" s="10">
         <v>46164</v>
       </c>
@@ -32030,6 +32849,9 @@
       </c>
       <c r="G659" s="3">
         <v>4</v>
+      </c>
+      <c r="H659" s="3">
+        <v>0</v>
       </c>
       <c r="I659" s="3">
         <f t="shared" si="142"/>
@@ -32044,7 +32866,7 @@
         <v>5</v>
       </c>
       <c r="L659" s="3" t="str">
-        <f t="shared" ref="L659:L690" si="145">IF(K659&lt;-5,"CRÍTICO",IF(K659&lt;0,"ATENÇÃO",IF(K659&lt;=5,"OPORTUNO","MUITO BOM")))</f>
+        <f t="shared" ref="L659:L665" si="145">IF(K659&lt;-5,"CRÍTICO",IF(K659&lt;0,"ATENÇÃO",IF(K659&lt;=5,"OPORTUNO","MUITO BOM")))</f>
         <v>OPORTUNO</v>
       </c>
       <c r="M659" s="3">
@@ -32057,7 +32879,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A660" s="10">
         <v>46164</v>
       </c>
@@ -32078,6 +32900,9 @@
       </c>
       <c r="G660" s="3">
         <v>2</v>
+      </c>
+      <c r="H660" s="3">
+        <v>0</v>
       </c>
       <c r="I660" s="3">
         <f t="shared" si="142"/>
@@ -32105,7 +32930,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A661" s="10">
         <v>46164</v>
       </c>
@@ -32125,6 +32950,9 @@
         <v>25.36</v>
       </c>
       <c r="G661" s="3">
+        <v>0</v>
+      </c>
+      <c r="H661" s="3">
         <v>0</v>
       </c>
       <c r="I661" s="3">
@@ -32153,7 +32981,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A662" s="10">
         <v>46164</v>
       </c>
@@ -32174,6 +33002,9 @@
       </c>
       <c r="G662" s="3">
         <v>2</v>
+      </c>
+      <c r="H662" s="3">
+        <v>0</v>
       </c>
       <c r="I662" s="3">
         <f t="shared" si="142"/>
@@ -32201,7 +33032,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A663" s="10">
         <v>46164</v>
       </c>
@@ -32221,6 +33052,9 @@
         <v>13.32</v>
       </c>
       <c r="G663" s="3">
+        <v>0</v>
+      </c>
+      <c r="H663" s="3">
         <v>0</v>
       </c>
       <c r="I663" s="3">
@@ -32249,7 +33083,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A664" s="10">
         <v>46164</v>
       </c>
@@ -32270,6 +33104,9 @@
       </c>
       <c r="G664" s="3">
         <v>1</v>
+      </c>
+      <c r="H664" s="3">
+        <v>0</v>
       </c>
       <c r="I664" s="3">
         <f t="shared" si="142"/>
@@ -32297,7 +33134,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A665" s="10">
         <v>46164</v>
       </c>
@@ -32317,6 +33154,9 @@
         <v>13.4</v>
       </c>
       <c r="G665" s="3">
+        <v>0</v>
+      </c>
+      <c r="H665" s="3">
         <v>0</v>
       </c>
       <c r="I665" s="3">
@@ -32346,1666 +33186,1666 @@
       </c>
     </row>
     <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D666">
-        <v>0</v>
-      </c>
-      <c r="E666">
-        <v>0</v>
-      </c>
-      <c r="F666">
-        <v>0</v>
-      </c>
-      <c r="G666">
-        <v>0</v>
-      </c>
-      <c r="H666">
-        <v>0</v>
-      </c>
-      <c r="I666">
+      <c r="D666" s="3">
+        <v>0</v>
+      </c>
+      <c r="E666" s="3">
+        <v>0</v>
+      </c>
+      <c r="F666" s="3">
+        <v>0</v>
+      </c>
+      <c r="G666" s="3">
+        <v>0</v>
+      </c>
+      <c r="H666" s="3">
+        <v>0</v>
+      </c>
+      <c r="I666" s="3">
         <v>0</v>
       </c>
       <c r="J666" s="3">
         <v>0</v>
       </c>
-      <c r="K666">
+      <c r="K666" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D667">
-        <v>0</v>
-      </c>
-      <c r="E667">
-        <v>0</v>
-      </c>
-      <c r="F667">
-        <v>0</v>
-      </c>
-      <c r="G667">
-        <v>0</v>
-      </c>
-      <c r="H667">
-        <v>0</v>
-      </c>
-      <c r="I667">
+      <c r="D667" s="3">
+        <v>0</v>
+      </c>
+      <c r="E667" s="3">
+        <v>0</v>
+      </c>
+      <c r="F667" s="3">
+        <v>0</v>
+      </c>
+      <c r="G667" s="3">
+        <v>0</v>
+      </c>
+      <c r="H667" s="3">
+        <v>0</v>
+      </c>
+      <c r="I667" s="3">
         <v>0</v>
       </c>
       <c r="J667" s="3">
         <v>0</v>
       </c>
-      <c r="K667">
+      <c r="K667" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D668">
-        <v>0</v>
-      </c>
-      <c r="E668">
-        <v>0</v>
-      </c>
-      <c r="F668">
-        <v>0</v>
-      </c>
-      <c r="G668">
-        <v>0</v>
-      </c>
-      <c r="H668">
-        <v>0</v>
-      </c>
-      <c r="I668">
+      <c r="D668" s="3">
+        <v>0</v>
+      </c>
+      <c r="E668" s="3">
+        <v>0</v>
+      </c>
+      <c r="F668" s="3">
+        <v>0</v>
+      </c>
+      <c r="G668" s="3">
+        <v>0</v>
+      </c>
+      <c r="H668" s="3">
+        <v>0</v>
+      </c>
+      <c r="I668" s="3">
         <v>0</v>
       </c>
       <c r="J668" s="3">
         <v>0</v>
       </c>
-      <c r="K668">
+      <c r="K668" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D669">
-        <v>0</v>
-      </c>
-      <c r="E669">
-        <v>0</v>
-      </c>
-      <c r="F669">
-        <v>0</v>
-      </c>
-      <c r="G669">
-        <v>0</v>
-      </c>
-      <c r="H669">
-        <v>0</v>
-      </c>
-      <c r="I669">
+      <c r="D669" s="3">
+        <v>0</v>
+      </c>
+      <c r="E669" s="3">
+        <v>0</v>
+      </c>
+      <c r="F669" s="3">
+        <v>0</v>
+      </c>
+      <c r="G669" s="3">
+        <v>0</v>
+      </c>
+      <c r="H669" s="3">
+        <v>0</v>
+      </c>
+      <c r="I669" s="3">
         <v>0</v>
       </c>
       <c r="J669" s="3">
         <v>0</v>
       </c>
-      <c r="K669">
+      <c r="K669" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D670">
-        <v>0</v>
-      </c>
-      <c r="E670">
-        <v>0</v>
-      </c>
-      <c r="F670">
-        <v>0</v>
-      </c>
-      <c r="G670">
-        <v>0</v>
-      </c>
-      <c r="H670">
-        <v>0</v>
-      </c>
-      <c r="I670">
+      <c r="D670" s="3">
+        <v>0</v>
+      </c>
+      <c r="E670" s="3">
+        <v>0</v>
+      </c>
+      <c r="F670" s="3">
+        <v>0</v>
+      </c>
+      <c r="G670" s="3">
+        <v>0</v>
+      </c>
+      <c r="H670" s="3">
+        <v>0</v>
+      </c>
+      <c r="I670" s="3">
         <v>0</v>
       </c>
       <c r="J670" s="3">
         <v>0</v>
       </c>
-      <c r="K670">
+      <c r="K670" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D671">
-        <v>0</v>
-      </c>
-      <c r="E671">
-        <v>0</v>
-      </c>
-      <c r="F671">
-        <v>0</v>
-      </c>
-      <c r="G671">
-        <v>0</v>
-      </c>
-      <c r="H671">
-        <v>0</v>
-      </c>
-      <c r="I671">
+      <c r="D671" s="3">
+        <v>0</v>
+      </c>
+      <c r="E671" s="3">
+        <v>0</v>
+      </c>
+      <c r="F671" s="3">
+        <v>0</v>
+      </c>
+      <c r="G671" s="3">
+        <v>0</v>
+      </c>
+      <c r="H671" s="3">
+        <v>0</v>
+      </c>
+      <c r="I671" s="3">
         <v>0</v>
       </c>
       <c r="J671" s="3">
         <v>0</v>
       </c>
-      <c r="K671">
+      <c r="K671" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D672">
-        <v>0</v>
-      </c>
-      <c r="E672">
-        <v>0</v>
-      </c>
-      <c r="F672">
-        <v>0</v>
-      </c>
-      <c r="G672">
-        <v>0</v>
-      </c>
-      <c r="H672">
-        <v>0</v>
-      </c>
-      <c r="I672">
+      <c r="D672" s="3">
+        <v>0</v>
+      </c>
+      <c r="E672" s="3">
+        <v>0</v>
+      </c>
+      <c r="F672" s="3">
+        <v>0</v>
+      </c>
+      <c r="G672" s="3">
+        <v>0</v>
+      </c>
+      <c r="H672" s="3">
+        <v>0</v>
+      </c>
+      <c r="I672" s="3">
         <v>0</v>
       </c>
       <c r="J672" s="3">
         <v>0</v>
       </c>
-      <c r="K672">
+      <c r="K672" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="673" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D673">
-        <v>0</v>
-      </c>
-      <c r="E673">
-        <v>0</v>
-      </c>
-      <c r="F673">
-        <v>0</v>
-      </c>
-      <c r="G673">
-        <v>0</v>
-      </c>
-      <c r="H673">
-        <v>0</v>
-      </c>
-      <c r="I673">
+      <c r="D673" s="3">
+        <v>0</v>
+      </c>
+      <c r="E673" s="3">
+        <v>0</v>
+      </c>
+      <c r="F673" s="3">
+        <v>0</v>
+      </c>
+      <c r="G673" s="3">
+        <v>0</v>
+      </c>
+      <c r="H673" s="3">
+        <v>0</v>
+      </c>
+      <c r="I673" s="3">
         <v>0</v>
       </c>
       <c r="J673" s="3">
         <v>0</v>
       </c>
-      <c r="K673">
+      <c r="K673" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="674" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D674">
-        <v>0</v>
-      </c>
-      <c r="E674">
-        <v>0</v>
-      </c>
-      <c r="F674">
-        <v>0</v>
-      </c>
-      <c r="G674">
-        <v>0</v>
-      </c>
-      <c r="H674">
-        <v>0</v>
-      </c>
-      <c r="I674">
+      <c r="D674" s="3">
+        <v>0</v>
+      </c>
+      <c r="E674" s="3">
+        <v>0</v>
+      </c>
+      <c r="F674" s="3">
+        <v>0</v>
+      </c>
+      <c r="G674" s="3">
+        <v>0</v>
+      </c>
+      <c r="H674" s="3">
+        <v>0</v>
+      </c>
+      <c r="I674" s="3">
         <v>0</v>
       </c>
       <c r="J674" s="3">
         <v>0</v>
       </c>
-      <c r="K674">
+      <c r="K674" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="675" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D675">
-        <v>0</v>
-      </c>
-      <c r="E675">
-        <v>0</v>
-      </c>
-      <c r="F675">
-        <v>0</v>
-      </c>
-      <c r="G675">
-        <v>0</v>
-      </c>
-      <c r="H675">
-        <v>0</v>
-      </c>
-      <c r="I675">
+      <c r="D675" s="3">
+        <v>0</v>
+      </c>
+      <c r="E675" s="3">
+        <v>0</v>
+      </c>
+      <c r="F675" s="3">
+        <v>0</v>
+      </c>
+      <c r="G675" s="3">
+        <v>0</v>
+      </c>
+      <c r="H675" s="3">
+        <v>0</v>
+      </c>
+      <c r="I675" s="3">
         <v>0</v>
       </c>
       <c r="J675" s="3">
         <v>0</v>
       </c>
-      <c r="K675">
+      <c r="K675" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="676" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D676">
-        <v>0</v>
-      </c>
-      <c r="E676">
-        <v>0</v>
-      </c>
-      <c r="F676">
-        <v>0</v>
-      </c>
-      <c r="G676">
-        <v>0</v>
-      </c>
-      <c r="H676">
-        <v>0</v>
-      </c>
-      <c r="I676">
+      <c r="D676" s="3">
+        <v>0</v>
+      </c>
+      <c r="E676" s="3">
+        <v>0</v>
+      </c>
+      <c r="F676" s="3">
+        <v>0</v>
+      </c>
+      <c r="G676" s="3">
+        <v>0</v>
+      </c>
+      <c r="H676" s="3">
+        <v>0</v>
+      </c>
+      <c r="I676" s="3">
         <v>0</v>
       </c>
       <c r="J676" s="3">
         <v>0</v>
       </c>
-      <c r="K676">
+      <c r="K676" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="677" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D677">
-        <v>0</v>
-      </c>
-      <c r="E677">
-        <v>0</v>
-      </c>
-      <c r="F677">
-        <v>0</v>
-      </c>
-      <c r="G677">
-        <v>0</v>
-      </c>
-      <c r="H677">
-        <v>0</v>
-      </c>
-      <c r="I677">
+      <c r="D677" s="3">
+        <v>0</v>
+      </c>
+      <c r="E677" s="3">
+        <v>0</v>
+      </c>
+      <c r="F677" s="3">
+        <v>0</v>
+      </c>
+      <c r="G677" s="3">
+        <v>0</v>
+      </c>
+      <c r="H677" s="3">
+        <v>0</v>
+      </c>
+      <c r="I677" s="3">
         <v>0</v>
       </c>
       <c r="J677" s="3">
         <v>0</v>
       </c>
-      <c r="K677">
+      <c r="K677" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="678" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D678">
-        <v>0</v>
-      </c>
-      <c r="E678">
-        <v>0</v>
-      </c>
-      <c r="F678">
-        <v>0</v>
-      </c>
-      <c r="G678">
-        <v>0</v>
-      </c>
-      <c r="H678">
-        <v>0</v>
-      </c>
-      <c r="I678">
+      <c r="D678" s="3">
+        <v>0</v>
+      </c>
+      <c r="E678" s="3">
+        <v>0</v>
+      </c>
+      <c r="F678" s="3">
+        <v>0</v>
+      </c>
+      <c r="G678" s="3">
+        <v>0</v>
+      </c>
+      <c r="H678" s="3">
+        <v>0</v>
+      </c>
+      <c r="I678" s="3">
         <v>0</v>
       </c>
       <c r="J678" s="3">
         <v>0</v>
       </c>
-      <c r="K678">
+      <c r="K678" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="679" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D679">
-        <v>0</v>
-      </c>
-      <c r="E679">
-        <v>0</v>
-      </c>
-      <c r="F679">
-        <v>0</v>
-      </c>
-      <c r="G679">
-        <v>0</v>
-      </c>
-      <c r="H679">
-        <v>0</v>
-      </c>
-      <c r="I679">
+      <c r="D679" s="3">
+        <v>0</v>
+      </c>
+      <c r="E679" s="3">
+        <v>0</v>
+      </c>
+      <c r="F679" s="3">
+        <v>0</v>
+      </c>
+      <c r="G679" s="3">
+        <v>0</v>
+      </c>
+      <c r="H679" s="3">
+        <v>0</v>
+      </c>
+      <c r="I679" s="3">
         <v>0</v>
       </c>
       <c r="J679" s="3">
         <v>0</v>
       </c>
-      <c r="K679">
+      <c r="K679" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="680" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D680">
-        <v>0</v>
-      </c>
-      <c r="E680">
-        <v>0</v>
-      </c>
-      <c r="F680">
-        <v>0</v>
-      </c>
-      <c r="G680">
-        <v>0</v>
-      </c>
-      <c r="H680">
-        <v>0</v>
-      </c>
-      <c r="I680">
+      <c r="D680" s="3">
+        <v>0</v>
+      </c>
+      <c r="E680" s="3">
+        <v>0</v>
+      </c>
+      <c r="F680" s="3">
+        <v>0</v>
+      </c>
+      <c r="G680" s="3">
+        <v>0</v>
+      </c>
+      <c r="H680" s="3">
+        <v>0</v>
+      </c>
+      <c r="I680" s="3">
         <v>0</v>
       </c>
       <c r="J680" s="3">
         <v>0</v>
       </c>
-      <c r="K680">
+      <c r="K680" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="681" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D681">
-        <v>0</v>
-      </c>
-      <c r="E681">
-        <v>0</v>
-      </c>
-      <c r="F681">
-        <v>0</v>
-      </c>
-      <c r="G681">
-        <v>0</v>
-      </c>
-      <c r="H681">
-        <v>0</v>
-      </c>
-      <c r="I681">
+      <c r="D681" s="3">
+        <v>0</v>
+      </c>
+      <c r="E681" s="3">
+        <v>0</v>
+      </c>
+      <c r="F681" s="3">
+        <v>0</v>
+      </c>
+      <c r="G681" s="3">
+        <v>0</v>
+      </c>
+      <c r="H681" s="3">
+        <v>0</v>
+      </c>
+      <c r="I681" s="3">
         <v>0</v>
       </c>
       <c r="J681" s="3">
         <v>0</v>
       </c>
-      <c r="K681">
+      <c r="K681" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="682" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D682">
-        <v>0</v>
-      </c>
-      <c r="E682">
-        <v>0</v>
-      </c>
-      <c r="F682">
-        <v>0</v>
-      </c>
-      <c r="G682">
-        <v>0</v>
-      </c>
-      <c r="H682">
-        <v>0</v>
-      </c>
-      <c r="I682">
+      <c r="D682" s="3">
+        <v>0</v>
+      </c>
+      <c r="E682" s="3">
+        <v>0</v>
+      </c>
+      <c r="F682" s="3">
+        <v>0</v>
+      </c>
+      <c r="G682" s="3">
+        <v>0</v>
+      </c>
+      <c r="H682" s="3">
+        <v>0</v>
+      </c>
+      <c r="I682" s="3">
         <v>0</v>
       </c>
       <c r="J682" s="3">
         <v>0</v>
       </c>
-      <c r="K682">
+      <c r="K682" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="683" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D683">
-        <v>0</v>
-      </c>
-      <c r="E683">
-        <v>0</v>
-      </c>
-      <c r="F683">
-        <v>0</v>
-      </c>
-      <c r="G683">
-        <v>0</v>
-      </c>
-      <c r="H683">
-        <v>0</v>
-      </c>
-      <c r="I683">
+      <c r="D683" s="3">
+        <v>0</v>
+      </c>
+      <c r="E683" s="3">
+        <v>0</v>
+      </c>
+      <c r="F683" s="3">
+        <v>0</v>
+      </c>
+      <c r="G683" s="3">
+        <v>0</v>
+      </c>
+      <c r="H683" s="3">
+        <v>0</v>
+      </c>
+      <c r="I683" s="3">
         <v>0</v>
       </c>
       <c r="J683" s="3">
         <v>0</v>
       </c>
-      <c r="K683">
+      <c r="K683" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="684" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D684">
-        <v>0</v>
-      </c>
-      <c r="E684">
-        <v>0</v>
-      </c>
-      <c r="F684">
-        <v>0</v>
-      </c>
-      <c r="G684">
-        <v>0</v>
-      </c>
-      <c r="H684">
-        <v>0</v>
-      </c>
-      <c r="I684">
+      <c r="D684" s="3">
+        <v>0</v>
+      </c>
+      <c r="E684" s="3">
+        <v>0</v>
+      </c>
+      <c r="F684" s="3">
+        <v>0</v>
+      </c>
+      <c r="G684" s="3">
+        <v>0</v>
+      </c>
+      <c r="H684" s="3">
+        <v>0</v>
+      </c>
+      <c r="I684" s="3">
         <v>0</v>
       </c>
       <c r="J684" s="3">
         <v>0</v>
       </c>
-      <c r="K684">
+      <c r="K684" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="685" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D685">
-        <v>0</v>
-      </c>
-      <c r="E685">
-        <v>0</v>
-      </c>
-      <c r="F685">
-        <v>0</v>
-      </c>
-      <c r="G685">
-        <v>0</v>
-      </c>
-      <c r="H685">
-        <v>0</v>
-      </c>
-      <c r="I685">
+      <c r="D685" s="3">
+        <v>0</v>
+      </c>
+      <c r="E685" s="3">
+        <v>0</v>
+      </c>
+      <c r="F685" s="3">
+        <v>0</v>
+      </c>
+      <c r="G685" s="3">
+        <v>0</v>
+      </c>
+      <c r="H685" s="3">
+        <v>0</v>
+      </c>
+      <c r="I685" s="3">
         <v>0</v>
       </c>
       <c r="J685" s="3">
         <v>0</v>
       </c>
-      <c r="K685">
+      <c r="K685" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="686" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D686">
-        <v>0</v>
-      </c>
-      <c r="E686">
-        <v>0</v>
-      </c>
-      <c r="F686">
-        <v>0</v>
-      </c>
-      <c r="G686">
-        <v>0</v>
-      </c>
-      <c r="H686">
-        <v>0</v>
-      </c>
-      <c r="I686">
+      <c r="D686" s="3">
+        <v>0</v>
+      </c>
+      <c r="E686" s="3">
+        <v>0</v>
+      </c>
+      <c r="F686" s="3">
+        <v>0</v>
+      </c>
+      <c r="G686" s="3">
+        <v>0</v>
+      </c>
+      <c r="H686" s="3">
+        <v>0</v>
+      </c>
+      <c r="I686" s="3">
         <v>0</v>
       </c>
       <c r="J686" s="3">
         <v>0</v>
       </c>
-      <c r="K686">
+      <c r="K686" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="687" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D687">
-        <v>0</v>
-      </c>
-      <c r="E687">
-        <v>0</v>
-      </c>
-      <c r="F687">
-        <v>0</v>
-      </c>
-      <c r="G687">
-        <v>0</v>
-      </c>
-      <c r="H687">
-        <v>0</v>
-      </c>
-      <c r="I687">
+      <c r="D687" s="3">
+        <v>0</v>
+      </c>
+      <c r="E687" s="3">
+        <v>0</v>
+      </c>
+      <c r="F687" s="3">
+        <v>0</v>
+      </c>
+      <c r="G687" s="3">
+        <v>0</v>
+      </c>
+      <c r="H687" s="3">
+        <v>0</v>
+      </c>
+      <c r="I687" s="3">
         <v>0</v>
       </c>
       <c r="J687" s="3">
         <v>0</v>
       </c>
-      <c r="K687">
+      <c r="K687" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="688" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D688">
-        <v>0</v>
-      </c>
-      <c r="E688">
-        <v>0</v>
-      </c>
-      <c r="F688">
-        <v>0</v>
-      </c>
-      <c r="G688">
-        <v>0</v>
-      </c>
-      <c r="H688">
-        <v>0</v>
-      </c>
-      <c r="I688">
+      <c r="D688" s="3">
+        <v>0</v>
+      </c>
+      <c r="E688" s="3">
+        <v>0</v>
+      </c>
+      <c r="F688" s="3">
+        <v>0</v>
+      </c>
+      <c r="G688" s="3">
+        <v>0</v>
+      </c>
+      <c r="H688" s="3">
+        <v>0</v>
+      </c>
+      <c r="I688" s="3">
         <v>0</v>
       </c>
       <c r="J688" s="3">
         <v>0</v>
       </c>
-      <c r="K688">
+      <c r="K688" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="689" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D689">
-        <v>0</v>
-      </c>
-      <c r="E689">
-        <v>0</v>
-      </c>
-      <c r="F689">
-        <v>0</v>
-      </c>
-      <c r="G689">
-        <v>0</v>
-      </c>
-      <c r="H689">
-        <v>0</v>
-      </c>
-      <c r="I689">
+      <c r="D689" s="3">
+        <v>0</v>
+      </c>
+      <c r="E689" s="3">
+        <v>0</v>
+      </c>
+      <c r="F689" s="3">
+        <v>0</v>
+      </c>
+      <c r="G689" s="3">
+        <v>0</v>
+      </c>
+      <c r="H689" s="3">
+        <v>0</v>
+      </c>
+      <c r="I689" s="3">
         <v>0</v>
       </c>
       <c r="J689" s="3">
         <v>0</v>
       </c>
-      <c r="K689">
+      <c r="K689" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="690" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D690">
-        <v>0</v>
-      </c>
-      <c r="E690">
-        <v>0</v>
-      </c>
-      <c r="F690">
-        <v>0</v>
-      </c>
-      <c r="G690">
-        <v>0</v>
-      </c>
-      <c r="H690">
-        <v>0</v>
-      </c>
-      <c r="I690">
+      <c r="D690" s="3">
+        <v>0</v>
+      </c>
+      <c r="E690" s="3">
+        <v>0</v>
+      </c>
+      <c r="F690" s="3">
+        <v>0</v>
+      </c>
+      <c r="G690" s="3">
+        <v>0</v>
+      </c>
+      <c r="H690" s="3">
+        <v>0</v>
+      </c>
+      <c r="I690" s="3">
         <v>0</v>
       </c>
       <c r="J690" s="3">
         <v>0</v>
       </c>
-      <c r="K690">
+      <c r="K690" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="691" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D691">
-        <v>0</v>
-      </c>
-      <c r="E691">
-        <v>0</v>
-      </c>
-      <c r="F691">
-        <v>0</v>
-      </c>
-      <c r="G691">
-        <v>0</v>
-      </c>
-      <c r="H691">
-        <v>0</v>
-      </c>
-      <c r="I691">
+      <c r="D691" s="3">
+        <v>0</v>
+      </c>
+      <c r="E691" s="3">
+        <v>0</v>
+      </c>
+      <c r="F691" s="3">
+        <v>0</v>
+      </c>
+      <c r="G691" s="3">
+        <v>0</v>
+      </c>
+      <c r="H691" s="3">
+        <v>0</v>
+      </c>
+      <c r="I691" s="3">
         <v>0</v>
       </c>
       <c r="J691" s="3">
         <v>0</v>
       </c>
-      <c r="K691">
+      <c r="K691" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="692" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D692">
-        <v>0</v>
-      </c>
-      <c r="E692">
-        <v>0</v>
-      </c>
-      <c r="F692">
-        <v>0</v>
-      </c>
-      <c r="G692">
-        <v>0</v>
-      </c>
-      <c r="H692">
-        <v>0</v>
-      </c>
-      <c r="I692">
+      <c r="D692" s="3">
+        <v>0</v>
+      </c>
+      <c r="E692" s="3">
+        <v>0</v>
+      </c>
+      <c r="F692" s="3">
+        <v>0</v>
+      </c>
+      <c r="G692" s="3">
+        <v>0</v>
+      </c>
+      <c r="H692" s="3">
+        <v>0</v>
+      </c>
+      <c r="I692" s="3">
         <v>0</v>
       </c>
       <c r="J692" s="3">
         <v>0</v>
       </c>
-      <c r="K692">
+      <c r="K692" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="693" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D693">
-        <v>0</v>
-      </c>
-      <c r="E693">
-        <v>0</v>
-      </c>
-      <c r="F693">
-        <v>0</v>
-      </c>
-      <c r="G693">
-        <v>0</v>
-      </c>
-      <c r="H693">
-        <v>0</v>
-      </c>
-      <c r="I693">
+      <c r="D693" s="3">
+        <v>0</v>
+      </c>
+      <c r="E693" s="3">
+        <v>0</v>
+      </c>
+      <c r="F693" s="3">
+        <v>0</v>
+      </c>
+      <c r="G693" s="3">
+        <v>0</v>
+      </c>
+      <c r="H693" s="3">
+        <v>0</v>
+      </c>
+      <c r="I693" s="3">
         <v>0</v>
       </c>
       <c r="J693" s="3">
         <v>0</v>
       </c>
-      <c r="K693">
+      <c r="K693" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="694" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D694">
-        <v>0</v>
-      </c>
-      <c r="E694">
-        <v>0</v>
-      </c>
-      <c r="F694">
-        <v>0</v>
-      </c>
-      <c r="G694">
-        <v>0</v>
-      </c>
-      <c r="H694">
-        <v>0</v>
-      </c>
-      <c r="I694">
+      <c r="D694" s="3">
+        <v>0</v>
+      </c>
+      <c r="E694" s="3">
+        <v>0</v>
+      </c>
+      <c r="F694" s="3">
+        <v>0</v>
+      </c>
+      <c r="G694" s="3">
+        <v>0</v>
+      </c>
+      <c r="H694" s="3">
+        <v>0</v>
+      </c>
+      <c r="I694" s="3">
         <v>0</v>
       </c>
       <c r="J694" s="3">
         <v>0</v>
       </c>
-      <c r="K694">
+      <c r="K694" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="695" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D695">
-        <v>0</v>
-      </c>
-      <c r="E695">
-        <v>0</v>
-      </c>
-      <c r="F695">
-        <v>0</v>
-      </c>
-      <c r="G695">
-        <v>0</v>
-      </c>
-      <c r="H695">
-        <v>0</v>
-      </c>
-      <c r="I695">
+      <c r="D695" s="3">
+        <v>0</v>
+      </c>
+      <c r="E695" s="3">
+        <v>0</v>
+      </c>
+      <c r="F695" s="3">
+        <v>0</v>
+      </c>
+      <c r="G695" s="3">
+        <v>0</v>
+      </c>
+      <c r="H695" s="3">
+        <v>0</v>
+      </c>
+      <c r="I695" s="3">
         <v>0</v>
       </c>
       <c r="J695" s="3">
         <v>0</v>
       </c>
-      <c r="K695">
+      <c r="K695" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="696" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D696">
-        <v>0</v>
-      </c>
-      <c r="E696">
-        <v>0</v>
-      </c>
-      <c r="F696">
-        <v>0</v>
-      </c>
-      <c r="G696">
-        <v>0</v>
-      </c>
-      <c r="H696">
-        <v>0</v>
-      </c>
-      <c r="I696">
+      <c r="D696" s="3">
+        <v>0</v>
+      </c>
+      <c r="E696" s="3">
+        <v>0</v>
+      </c>
+      <c r="F696" s="3">
+        <v>0</v>
+      </c>
+      <c r="G696" s="3">
+        <v>0</v>
+      </c>
+      <c r="H696" s="3">
+        <v>0</v>
+      </c>
+      <c r="I696" s="3">
         <v>0</v>
       </c>
       <c r="J696" s="3">
         <v>0</v>
       </c>
-      <c r="K696">
+      <c r="K696" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="697" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D697">
-        <v>0</v>
-      </c>
-      <c r="E697">
-        <v>0</v>
-      </c>
-      <c r="F697">
-        <v>0</v>
-      </c>
-      <c r="G697">
-        <v>0</v>
-      </c>
-      <c r="H697">
-        <v>0</v>
-      </c>
-      <c r="I697">
+      <c r="D697" s="3">
+        <v>0</v>
+      </c>
+      <c r="E697" s="3">
+        <v>0</v>
+      </c>
+      <c r="F697" s="3">
+        <v>0</v>
+      </c>
+      <c r="G697" s="3">
+        <v>0</v>
+      </c>
+      <c r="H697" s="3">
+        <v>0</v>
+      </c>
+      <c r="I697" s="3">
         <v>0</v>
       </c>
       <c r="J697" s="3">
         <v>0</v>
       </c>
-      <c r="K697">
+      <c r="K697" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="698" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D698">
-        <v>0</v>
-      </c>
-      <c r="E698">
-        <v>0</v>
-      </c>
-      <c r="F698">
-        <v>0</v>
-      </c>
-      <c r="G698">
-        <v>0</v>
-      </c>
-      <c r="H698">
-        <v>0</v>
-      </c>
-      <c r="I698">
+      <c r="D698" s="3">
+        <v>0</v>
+      </c>
+      <c r="E698" s="3">
+        <v>0</v>
+      </c>
+      <c r="F698" s="3">
+        <v>0</v>
+      </c>
+      <c r="G698" s="3">
+        <v>0</v>
+      </c>
+      <c r="H698" s="3">
+        <v>0</v>
+      </c>
+      <c r="I698" s="3">
         <v>0</v>
       </c>
       <c r="J698" s="3">
         <v>0</v>
       </c>
-      <c r="K698">
+      <c r="K698" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="699" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D699">
-        <v>0</v>
-      </c>
-      <c r="E699">
-        <v>0</v>
-      </c>
-      <c r="F699">
-        <v>0</v>
-      </c>
-      <c r="G699">
-        <v>0</v>
-      </c>
-      <c r="H699">
-        <v>0</v>
-      </c>
-      <c r="I699">
+      <c r="D699" s="3">
+        <v>0</v>
+      </c>
+      <c r="E699" s="3">
+        <v>0</v>
+      </c>
+      <c r="F699" s="3">
+        <v>0</v>
+      </c>
+      <c r="G699" s="3">
+        <v>0</v>
+      </c>
+      <c r="H699" s="3">
+        <v>0</v>
+      </c>
+      <c r="I699" s="3">
         <v>0</v>
       </c>
       <c r="J699" s="3">
         <v>0</v>
       </c>
-      <c r="K699">
+      <c r="K699" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="700" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D700">
-        <v>0</v>
-      </c>
-      <c r="E700">
-        <v>0</v>
-      </c>
-      <c r="F700">
-        <v>0</v>
-      </c>
-      <c r="G700">
-        <v>0</v>
-      </c>
-      <c r="H700">
-        <v>0</v>
-      </c>
-      <c r="I700">
+      <c r="D700" s="3">
+        <v>0</v>
+      </c>
+      <c r="E700" s="3">
+        <v>0</v>
+      </c>
+      <c r="F700" s="3">
+        <v>0</v>
+      </c>
+      <c r="G700" s="3">
+        <v>0</v>
+      </c>
+      <c r="H700" s="3">
+        <v>0</v>
+      </c>
+      <c r="I700" s="3">
         <v>0</v>
       </c>
       <c r="J700" s="3">
         <v>0</v>
       </c>
-      <c r="K700">
+      <c r="K700" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="701" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D701">
-        <v>0</v>
-      </c>
-      <c r="E701">
-        <v>0</v>
-      </c>
-      <c r="F701">
-        <v>0</v>
-      </c>
-      <c r="G701">
-        <v>0</v>
-      </c>
-      <c r="H701">
-        <v>0</v>
-      </c>
-      <c r="I701">
+      <c r="D701" s="3">
+        <v>0</v>
+      </c>
+      <c r="E701" s="3">
+        <v>0</v>
+      </c>
+      <c r="F701" s="3">
+        <v>0</v>
+      </c>
+      <c r="G701" s="3">
+        <v>0</v>
+      </c>
+      <c r="H701" s="3">
+        <v>0</v>
+      </c>
+      <c r="I701" s="3">
         <v>0</v>
       </c>
       <c r="J701" s="3">
         <v>0</v>
       </c>
-      <c r="K701">
+      <c r="K701" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="702" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D702">
-        <v>0</v>
-      </c>
-      <c r="E702">
-        <v>0</v>
-      </c>
-      <c r="F702">
-        <v>0</v>
-      </c>
-      <c r="G702">
-        <v>0</v>
-      </c>
-      <c r="H702">
-        <v>0</v>
-      </c>
-      <c r="I702">
+      <c r="D702" s="3">
+        <v>0</v>
+      </c>
+      <c r="E702" s="3">
+        <v>0</v>
+      </c>
+      <c r="F702" s="3">
+        <v>0</v>
+      </c>
+      <c r="G702" s="3">
+        <v>0</v>
+      </c>
+      <c r="H702" s="3">
+        <v>0</v>
+      </c>
+      <c r="I702" s="3">
         <v>0</v>
       </c>
       <c r="J702" s="3">
         <v>0</v>
       </c>
-      <c r="K702">
+      <c r="K702" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="703" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D703">
-        <v>0</v>
-      </c>
-      <c r="E703">
-        <v>0</v>
-      </c>
-      <c r="F703">
-        <v>0</v>
-      </c>
-      <c r="G703">
-        <v>0</v>
-      </c>
-      <c r="H703">
-        <v>0</v>
-      </c>
-      <c r="I703">
+      <c r="D703" s="3">
+        <v>0</v>
+      </c>
+      <c r="E703" s="3">
+        <v>0</v>
+      </c>
+      <c r="F703" s="3">
+        <v>0</v>
+      </c>
+      <c r="G703" s="3">
+        <v>0</v>
+      </c>
+      <c r="H703" s="3">
+        <v>0</v>
+      </c>
+      <c r="I703" s="3">
         <v>0</v>
       </c>
       <c r="J703" s="3">
         <v>0</v>
       </c>
-      <c r="K703">
+      <c r="K703" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="704" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D704">
-        <v>0</v>
-      </c>
-      <c r="E704">
-        <v>0</v>
-      </c>
-      <c r="F704">
-        <v>0</v>
-      </c>
-      <c r="G704">
-        <v>0</v>
-      </c>
-      <c r="H704">
-        <v>0</v>
-      </c>
-      <c r="I704">
+      <c r="D704" s="3">
+        <v>0</v>
+      </c>
+      <c r="E704" s="3">
+        <v>0</v>
+      </c>
+      <c r="F704" s="3">
+        <v>0</v>
+      </c>
+      <c r="G704" s="3">
+        <v>0</v>
+      </c>
+      <c r="H704" s="3">
+        <v>0</v>
+      </c>
+      <c r="I704" s="3">
         <v>0</v>
       </c>
       <c r="J704" s="3">
         <v>0</v>
       </c>
-      <c r="K704">
+      <c r="K704" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="705" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D705">
-        <v>0</v>
-      </c>
-      <c r="E705">
-        <v>0</v>
-      </c>
-      <c r="F705">
-        <v>0</v>
-      </c>
-      <c r="G705">
-        <v>0</v>
-      </c>
-      <c r="H705">
-        <v>0</v>
-      </c>
-      <c r="I705">
+      <c r="D705" s="3">
+        <v>0</v>
+      </c>
+      <c r="E705" s="3">
+        <v>0</v>
+      </c>
+      <c r="F705" s="3">
+        <v>0</v>
+      </c>
+      <c r="G705" s="3">
+        <v>0</v>
+      </c>
+      <c r="H705" s="3">
+        <v>0</v>
+      </c>
+      <c r="I705" s="3">
         <v>0</v>
       </c>
       <c r="J705" s="3">
         <v>0</v>
       </c>
-      <c r="K705">
+      <c r="K705" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="706" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D706">
-        <v>0</v>
-      </c>
-      <c r="E706">
-        <v>0</v>
-      </c>
-      <c r="F706">
-        <v>0</v>
-      </c>
-      <c r="G706">
-        <v>0</v>
-      </c>
-      <c r="H706">
-        <v>0</v>
-      </c>
-      <c r="I706">
+      <c r="D706" s="3">
+        <v>0</v>
+      </c>
+      <c r="E706" s="3">
+        <v>0</v>
+      </c>
+      <c r="F706" s="3">
+        <v>0</v>
+      </c>
+      <c r="G706" s="3">
+        <v>0</v>
+      </c>
+      <c r="H706" s="3">
+        <v>0</v>
+      </c>
+      <c r="I706" s="3">
         <v>0</v>
       </c>
       <c r="J706" s="3">
         <v>0</v>
       </c>
-      <c r="K706">
+      <c r="K706" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="707" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D707">
-        <v>0</v>
-      </c>
-      <c r="E707">
-        <v>0</v>
-      </c>
-      <c r="F707">
-        <v>0</v>
-      </c>
-      <c r="G707">
-        <v>0</v>
-      </c>
-      <c r="H707">
-        <v>0</v>
-      </c>
-      <c r="I707">
+      <c r="D707" s="3">
+        <v>0</v>
+      </c>
+      <c r="E707" s="3">
+        <v>0</v>
+      </c>
+      <c r="F707" s="3">
+        <v>0</v>
+      </c>
+      <c r="G707" s="3">
+        <v>0</v>
+      </c>
+      <c r="H707" s="3">
+        <v>0</v>
+      </c>
+      <c r="I707" s="3">
         <v>0</v>
       </c>
       <c r="J707" s="3">
         <v>0</v>
       </c>
-      <c r="K707">
+      <c r="K707" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="708" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D708">
-        <v>0</v>
-      </c>
-      <c r="E708">
-        <v>0</v>
-      </c>
-      <c r="F708">
-        <v>0</v>
-      </c>
-      <c r="G708">
-        <v>0</v>
-      </c>
-      <c r="H708">
-        <v>0</v>
-      </c>
-      <c r="I708">
+      <c r="D708" s="3">
+        <v>0</v>
+      </c>
+      <c r="E708" s="3">
+        <v>0</v>
+      </c>
+      <c r="F708" s="3">
+        <v>0</v>
+      </c>
+      <c r="G708" s="3">
+        <v>0</v>
+      </c>
+      <c r="H708" s="3">
+        <v>0</v>
+      </c>
+      <c r="I708" s="3">
         <v>0</v>
       </c>
       <c r="J708" s="3">
         <v>0</v>
       </c>
-      <c r="K708">
+      <c r="K708" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="709" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D709">
-        <v>0</v>
-      </c>
-      <c r="E709">
-        <v>0</v>
-      </c>
-      <c r="F709">
-        <v>0</v>
-      </c>
-      <c r="G709">
-        <v>0</v>
-      </c>
-      <c r="H709">
-        <v>0</v>
-      </c>
-      <c r="I709">
+      <c r="D709" s="3">
+        <v>0</v>
+      </c>
+      <c r="E709" s="3">
+        <v>0</v>
+      </c>
+      <c r="F709" s="3">
+        <v>0</v>
+      </c>
+      <c r="G709" s="3">
+        <v>0</v>
+      </c>
+      <c r="H709" s="3">
+        <v>0</v>
+      </c>
+      <c r="I709" s="3">
         <v>0</v>
       </c>
       <c r="J709" s="3">
         <v>0</v>
       </c>
-      <c r="K709">
+      <c r="K709" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="710" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D710">
-        <v>0</v>
-      </c>
-      <c r="E710">
-        <v>0</v>
-      </c>
-      <c r="F710">
-        <v>0</v>
-      </c>
-      <c r="G710">
-        <v>0</v>
-      </c>
-      <c r="H710">
-        <v>0</v>
-      </c>
-      <c r="I710">
+      <c r="D710" s="3">
+        <v>0</v>
+      </c>
+      <c r="E710" s="3">
+        <v>0</v>
+      </c>
+      <c r="F710" s="3">
+        <v>0</v>
+      </c>
+      <c r="G710" s="3">
+        <v>0</v>
+      </c>
+      <c r="H710" s="3">
+        <v>0</v>
+      </c>
+      <c r="I710" s="3">
         <v>0</v>
       </c>
       <c r="J710" s="3">
         <v>0</v>
       </c>
-      <c r="K710">
+      <c r="K710" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="711" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D711">
-        <v>0</v>
-      </c>
-      <c r="E711">
-        <v>0</v>
-      </c>
-      <c r="F711">
-        <v>0</v>
-      </c>
-      <c r="G711">
-        <v>0</v>
-      </c>
-      <c r="H711">
-        <v>0</v>
-      </c>
-      <c r="I711">
+      <c r="D711" s="3">
+        <v>0</v>
+      </c>
+      <c r="E711" s="3">
+        <v>0</v>
+      </c>
+      <c r="F711" s="3">
+        <v>0</v>
+      </c>
+      <c r="G711" s="3">
+        <v>0</v>
+      </c>
+      <c r="H711" s="3">
+        <v>0</v>
+      </c>
+      <c r="I711" s="3">
         <v>0</v>
       </c>
       <c r="J711" s="3">
         <v>0</v>
       </c>
-      <c r="K711">
+      <c r="K711" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="712" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D712">
-        <v>0</v>
-      </c>
-      <c r="E712">
-        <v>0</v>
-      </c>
-      <c r="F712">
-        <v>0</v>
-      </c>
-      <c r="G712">
-        <v>0</v>
-      </c>
-      <c r="H712">
-        <v>0</v>
-      </c>
-      <c r="I712">
+      <c r="D712" s="3">
+        <v>0</v>
+      </c>
+      <c r="E712" s="3">
+        <v>0</v>
+      </c>
+      <c r="F712" s="3">
+        <v>0</v>
+      </c>
+      <c r="G712" s="3">
+        <v>0</v>
+      </c>
+      <c r="H712" s="3">
+        <v>0</v>
+      </c>
+      <c r="I712" s="3">
         <v>0</v>
       </c>
       <c r="J712" s="3">
         <v>0</v>
       </c>
-      <c r="K712">
+      <c r="K712" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="713" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D713">
-        <v>0</v>
-      </c>
-      <c r="E713">
-        <v>0</v>
-      </c>
-      <c r="F713">
-        <v>0</v>
-      </c>
-      <c r="G713">
-        <v>0</v>
-      </c>
-      <c r="H713">
-        <v>0</v>
-      </c>
-      <c r="I713">
+      <c r="D713" s="3">
+        <v>0</v>
+      </c>
+      <c r="E713" s="3">
+        <v>0</v>
+      </c>
+      <c r="F713" s="3">
+        <v>0</v>
+      </c>
+      <c r="G713" s="3">
+        <v>0</v>
+      </c>
+      <c r="H713" s="3">
+        <v>0</v>
+      </c>
+      <c r="I713" s="3">
         <v>0</v>
       </c>
       <c r="J713" s="3">
         <v>0</v>
       </c>
-      <c r="K713">
+      <c r="K713" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="714" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D714">
-        <v>0</v>
-      </c>
-      <c r="E714">
-        <v>0</v>
-      </c>
-      <c r="F714">
-        <v>0</v>
-      </c>
-      <c r="G714">
-        <v>0</v>
-      </c>
-      <c r="H714">
-        <v>0</v>
-      </c>
-      <c r="I714">
+      <c r="D714" s="3">
+        <v>0</v>
+      </c>
+      <c r="E714" s="3">
+        <v>0</v>
+      </c>
+      <c r="F714" s="3">
+        <v>0</v>
+      </c>
+      <c r="G714" s="3">
+        <v>0</v>
+      </c>
+      <c r="H714" s="3">
+        <v>0</v>
+      </c>
+      <c r="I714" s="3">
         <v>0</v>
       </c>
       <c r="J714" s="3">
         <v>0</v>
       </c>
-      <c r="K714">
+      <c r="K714" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="715" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D715">
-        <v>0</v>
-      </c>
-      <c r="E715">
-        <v>0</v>
-      </c>
-      <c r="F715">
-        <v>0</v>
-      </c>
-      <c r="G715">
-        <v>0</v>
-      </c>
-      <c r="H715">
-        <v>0</v>
-      </c>
-      <c r="I715">
+      <c r="D715" s="3">
+        <v>0</v>
+      </c>
+      <c r="E715" s="3">
+        <v>0</v>
+      </c>
+      <c r="F715" s="3">
+        <v>0</v>
+      </c>
+      <c r="G715" s="3">
+        <v>0</v>
+      </c>
+      <c r="H715" s="3">
+        <v>0</v>
+      </c>
+      <c r="I715" s="3">
         <v>0</v>
       </c>
       <c r="J715" s="3">
         <v>0</v>
       </c>
-      <c r="K715">
+      <c r="K715" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="716" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D716">
-        <v>0</v>
-      </c>
-      <c r="E716">
-        <v>0</v>
-      </c>
-      <c r="F716">
-        <v>0</v>
-      </c>
-      <c r="G716">
-        <v>0</v>
-      </c>
-      <c r="H716">
-        <v>0</v>
-      </c>
-      <c r="I716">
+      <c r="D716" s="3">
+        <v>0</v>
+      </c>
+      <c r="E716" s="3">
+        <v>0</v>
+      </c>
+      <c r="F716" s="3">
+        <v>0</v>
+      </c>
+      <c r="G716" s="3">
+        <v>0</v>
+      </c>
+      <c r="H716" s="3">
+        <v>0</v>
+      </c>
+      <c r="I716" s="3">
         <v>0</v>
       </c>
       <c r="J716" s="3">
         <v>0</v>
       </c>
-      <c r="K716">
+      <c r="K716" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="717" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D717">
-        <v>0</v>
-      </c>
-      <c r="E717">
-        <v>0</v>
-      </c>
-      <c r="F717">
-        <v>0</v>
-      </c>
-      <c r="G717">
-        <v>0</v>
-      </c>
-      <c r="H717">
-        <v>0</v>
-      </c>
-      <c r="I717">
+      <c r="D717" s="3">
+        <v>0</v>
+      </c>
+      <c r="E717" s="3">
+        <v>0</v>
+      </c>
+      <c r="F717" s="3">
+        <v>0</v>
+      </c>
+      <c r="G717" s="3">
+        <v>0</v>
+      </c>
+      <c r="H717" s="3">
+        <v>0</v>
+      </c>
+      <c r="I717" s="3">
         <v>0</v>
       </c>
       <c r="J717" s="3">
         <v>0</v>
       </c>
-      <c r="K717">
+      <c r="K717" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="718" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D718">
-        <v>0</v>
-      </c>
-      <c r="E718">
-        <v>0</v>
-      </c>
-      <c r="F718">
-        <v>0</v>
-      </c>
-      <c r="G718">
-        <v>0</v>
-      </c>
-      <c r="H718">
-        <v>0</v>
-      </c>
-      <c r="I718">
+      <c r="D718" s="3">
+        <v>0</v>
+      </c>
+      <c r="E718" s="3">
+        <v>0</v>
+      </c>
+      <c r="F718" s="3">
+        <v>0</v>
+      </c>
+      <c r="G718" s="3">
+        <v>0</v>
+      </c>
+      <c r="H718" s="3">
+        <v>0</v>
+      </c>
+      <c r="I718" s="3">
         <v>0</v>
       </c>
       <c r="J718" s="3">
         <v>0</v>
       </c>
-      <c r="K718">
+      <c r="K718" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="719" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D719">
-        <v>0</v>
-      </c>
-      <c r="E719">
-        <v>0</v>
-      </c>
-      <c r="F719">
-        <v>0</v>
-      </c>
-      <c r="G719">
-        <v>0</v>
-      </c>
-      <c r="H719">
-        <v>0</v>
-      </c>
-      <c r="I719">
+      <c r="D719" s="3">
+        <v>0</v>
+      </c>
+      <c r="E719" s="3">
+        <v>0</v>
+      </c>
+      <c r="F719" s="3">
+        <v>0</v>
+      </c>
+      <c r="G719" s="3">
+        <v>0</v>
+      </c>
+      <c r="H719" s="3">
+        <v>0</v>
+      </c>
+      <c r="I719" s="3">
         <v>0</v>
       </c>
       <c r="J719" s="3">
         <v>0</v>
       </c>
-      <c r="K719">
+      <c r="K719" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="720" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D720">
-        <v>0</v>
-      </c>
-      <c r="E720">
-        <v>0</v>
-      </c>
-      <c r="F720">
-        <v>0</v>
-      </c>
-      <c r="G720">
-        <v>0</v>
-      </c>
-      <c r="H720">
-        <v>0</v>
-      </c>
-      <c r="I720">
+      <c r="D720" s="3">
+        <v>0</v>
+      </c>
+      <c r="E720" s="3">
+        <v>0</v>
+      </c>
+      <c r="F720" s="3">
+        <v>0</v>
+      </c>
+      <c r="G720" s="3">
+        <v>0</v>
+      </c>
+      <c r="H720" s="3">
+        <v>0</v>
+      </c>
+      <c r="I720" s="3">
         <v>0</v>
       </c>
       <c r="J720" s="3">
         <v>0</v>
       </c>
-      <c r="K720">
+      <c r="K720" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="721" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D721">
-        <v>0</v>
-      </c>
-      <c r="E721">
-        <v>0</v>
-      </c>
-      <c r="F721">
-        <v>0</v>
-      </c>
-      <c r="G721">
-        <v>0</v>
-      </c>
-      <c r="H721">
-        <v>0</v>
-      </c>
-      <c r="I721">
+      <c r="D721" s="3">
+        <v>0</v>
+      </c>
+      <c r="E721" s="3">
+        <v>0</v>
+      </c>
+      <c r="F721" s="3">
+        <v>0</v>
+      </c>
+      <c r="G721" s="3">
+        <v>0</v>
+      </c>
+      <c r="H721" s="3">
+        <v>0</v>
+      </c>
+      <c r="I721" s="3">
         <v>0</v>
       </c>
       <c r="J721" s="3">
         <v>0</v>
       </c>
-      <c r="K721">
+      <c r="K721" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="722" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D722">
-        <v>0</v>
-      </c>
-      <c r="E722">
-        <v>0</v>
-      </c>
-      <c r="F722">
-        <v>0</v>
-      </c>
-      <c r="G722">
-        <v>0</v>
-      </c>
-      <c r="H722">
-        <v>0</v>
-      </c>
-      <c r="I722">
+      <c r="D722" s="3">
+        <v>0</v>
+      </c>
+      <c r="E722" s="3">
+        <v>0</v>
+      </c>
+      <c r="F722" s="3">
+        <v>0</v>
+      </c>
+      <c r="G722" s="3">
+        <v>0</v>
+      </c>
+      <c r="H722" s="3">
+        <v>0</v>
+      </c>
+      <c r="I722" s="3">
         <v>0</v>
       </c>
       <c r="J722" s="3">
         <v>0</v>
       </c>
-      <c r="K722">
+      <c r="K722" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="723" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D723">
-        <v>0</v>
-      </c>
-      <c r="E723">
-        <v>0</v>
-      </c>
-      <c r="F723">
-        <v>0</v>
-      </c>
-      <c r="G723">
-        <v>0</v>
-      </c>
-      <c r="H723">
-        <v>0</v>
-      </c>
-      <c r="I723">
+      <c r="D723" s="3">
+        <v>0</v>
+      </c>
+      <c r="E723" s="3">
+        <v>0</v>
+      </c>
+      <c r="F723" s="3">
+        <v>0</v>
+      </c>
+      <c r="G723" s="3">
+        <v>0</v>
+      </c>
+      <c r="H723" s="3">
+        <v>0</v>
+      </c>
+      <c r="I723" s="3">
         <v>0</v>
       </c>
       <c r="J723" s="3">
         <v>0</v>
       </c>
-      <c r="K723">
+      <c r="K723" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="724" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D724">
-        <v>0</v>
-      </c>
-      <c r="E724">
-        <v>0</v>
-      </c>
-      <c r="F724">
-        <v>0</v>
-      </c>
-      <c r="G724">
-        <v>0</v>
-      </c>
-      <c r="H724">
-        <v>0</v>
-      </c>
-      <c r="I724">
+      <c r="D724" s="3">
+        <v>0</v>
+      </c>
+      <c r="E724" s="3">
+        <v>0</v>
+      </c>
+      <c r="F724" s="3">
+        <v>0</v>
+      </c>
+      <c r="G724" s="3">
+        <v>0</v>
+      </c>
+      <c r="H724" s="3">
+        <v>0</v>
+      </c>
+      <c r="I724" s="3">
         <v>0</v>
       </c>
       <c r="J724" s="3">
         <v>0</v>
       </c>
-      <c r="K724">
+      <c r="K724" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="725" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D725">
-        <v>0</v>
-      </c>
-      <c r="E725">
-        <v>0</v>
-      </c>
-      <c r="F725">
-        <v>0</v>
-      </c>
-      <c r="G725">
-        <v>0</v>
-      </c>
-      <c r="H725">
-        <v>0</v>
-      </c>
-      <c r="I725">
+      <c r="D725" s="3">
+        <v>0</v>
+      </c>
+      <c r="E725" s="3">
+        <v>0</v>
+      </c>
+      <c r="F725" s="3">
+        <v>0</v>
+      </c>
+      <c r="G725" s="3">
+        <v>0</v>
+      </c>
+      <c r="H725" s="3">
+        <v>0</v>
+      </c>
+      <c r="I725" s="3">
         <v>0</v>
       </c>
       <c r="J725" s="3">
         <v>0</v>
       </c>
-      <c r="K725">
+      <c r="K725" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="726" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D726">
-        <v>0</v>
-      </c>
-      <c r="E726">
-        <v>0</v>
-      </c>
-      <c r="F726">
-        <v>0</v>
-      </c>
-      <c r="G726">
-        <v>0</v>
-      </c>
-      <c r="H726">
-        <v>0</v>
-      </c>
-      <c r="I726">
+      <c r="D726" s="3">
+        <v>0</v>
+      </c>
+      <c r="E726" s="3">
+        <v>0</v>
+      </c>
+      <c r="F726" s="3">
+        <v>0</v>
+      </c>
+      <c r="G726" s="3">
+        <v>0</v>
+      </c>
+      <c r="H726" s="3">
+        <v>0</v>
+      </c>
+      <c r="I726" s="3">
         <v>0</v>
       </c>
       <c r="J726" s="3">
         <v>0</v>
       </c>
-      <c r="K726">
+      <c r="K726" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="727" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D727">
-        <v>0</v>
-      </c>
-      <c r="E727">
-        <v>0</v>
-      </c>
-      <c r="F727">
-        <v>0</v>
-      </c>
-      <c r="G727">
-        <v>0</v>
-      </c>
-      <c r="H727">
-        <v>0</v>
-      </c>
-      <c r="I727">
+      <c r="D727" s="3">
+        <v>0</v>
+      </c>
+      <c r="E727" s="3">
+        <v>0</v>
+      </c>
+      <c r="F727" s="3">
+        <v>0</v>
+      </c>
+      <c r="G727" s="3">
+        <v>0</v>
+      </c>
+      <c r="H727" s="3">
+        <v>0</v>
+      </c>
+      <c r="I727" s="3">
         <v>0</v>
       </c>
       <c r="J727" s="3">
         <v>0</v>
       </c>
-      <c r="K727">
+      <c r="K727" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="728" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D728">
-        <v>0</v>
-      </c>
-      <c r="E728">
-        <v>0</v>
-      </c>
-      <c r="F728">
-        <v>0</v>
-      </c>
-      <c r="G728">
-        <v>0</v>
-      </c>
-      <c r="H728">
-        <v>0</v>
-      </c>
-      <c r="I728">
+      <c r="D728" s="3">
+        <v>0</v>
+      </c>
+      <c r="E728" s="3">
+        <v>0</v>
+      </c>
+      <c r="F728" s="3">
+        <v>0</v>
+      </c>
+      <c r="G728" s="3">
+        <v>0</v>
+      </c>
+      <c r="H728" s="3">
+        <v>0</v>
+      </c>
+      <c r="I728" s="3">
         <v>0</v>
       </c>
       <c r="J728" s="3">
         <v>0</v>
       </c>
-      <c r="K728">
+      <c r="K728" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="729" spans="4:11" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D729">
-        <v>0</v>
-      </c>
-      <c r="E729">
-        <v>0</v>
-      </c>
-      <c r="F729">
-        <v>0</v>
-      </c>
-      <c r="G729">
-        <v>0</v>
-      </c>
-      <c r="H729">
-        <v>0</v>
-      </c>
-      <c r="I729">
+      <c r="D729" s="3">
+        <v>0</v>
+      </c>
+      <c r="E729" s="3">
+        <v>0</v>
+      </c>
+      <c r="F729" s="3">
+        <v>0</v>
+      </c>
+      <c r="G729" s="3">
+        <v>0</v>
+      </c>
+      <c r="H729" s="3">
+        <v>0</v>
+      </c>
+      <c r="I729" s="3">
         <v>0</v>
       </c>
       <c r="J729" s="3">
         <v>0</v>
       </c>
-      <c r="K729">
+      <c r="K729" s="3">
         <v>0</v>
       </c>
     </row>
@@ -34016,10 +34856,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O729" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Francielson de Oliveira"/>
-      </filters>
+    <filterColumn colId="7">
+      <filters blank="1"/>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A590:O590">
       <sortCondition ref="B1:B620"/>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41F172E-68BE-4231-A4EE-26A87D2D695B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D51CBA-2C38-4C69-9789-838F8F547CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -865,7 +865,7 @@
       </c>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46146</v>
       </c>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46146</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46146</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46146</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46146</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46146</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>46146</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>46146</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46146</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46146</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>46146</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>46146</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>46146</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>9.5238095238095237</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>46146</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46146</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46146</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>46146</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>46146</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>46146</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>46146</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>46146</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>46146</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>46146</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>46146</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>46146</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>46146</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>46146</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>46146</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>46146</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>46146</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>46146</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>46146</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>46146</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>46146</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>46146</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>46147</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>46147</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>46147</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>46147</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>46147</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>46147</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>46147</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>46147</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>46147</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>46147</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>46147</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>46147</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>46147</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>46147</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>46147</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>46147</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>46147</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>46147</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>46147</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>46147</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>46147</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>46147</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>46147</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>46147</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>46147</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>46147</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>46147</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>46147</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>46147</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>46147</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>46147</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>46147</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>46148</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>46148</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>46148</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>46148</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>46148</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>46148</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>46148</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>46148</v>
       </c>
@@ -5851,7 +5851,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>46148</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>46148</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>46148</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>46148</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>46148</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>46148</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>46148</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>46148</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>46148</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>46148</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>46148</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>46148</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>46148</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>46148</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>46148</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>46148</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>46148</v>
       </c>
@@ -6811,7 +6811,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>46148</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>46148</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>46148</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>46148</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>46148</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>46148</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>46148</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>46148</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>46148</v>
       </c>
@@ -7387,7 +7387,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>46148</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>46149</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>46149</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>46149</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>46149</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>46149</v>
       </c>
@@ -7771,7 +7771,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>46149</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>46149</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>46149</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>46149</v>
       </c>
@@ -8011,7 +8011,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>46149</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>46149</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>46149</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>46149</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>46149</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>46149</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>46149</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>46149</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>46149</v>
       </c>
@@ -8587,7 +8587,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>46149</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>46149</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>46149</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>46149</v>
       </c>
@@ -8827,7 +8827,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>46149</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>46149</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>46149</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>46149</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>46149</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>46149</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>46149</v>
       </c>
@@ -9307,7 +9307,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>46149</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>46149</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>46149</v>
       </c>
@@ -9451,7 +9451,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>46149</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>46153</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>46153</v>
       </c>
@@ -11867,6 +11867,9 @@
       <c r="E226" s="3">
         <v>16</v>
       </c>
+      <c r="G226" s="3">
+        <v>0</v>
+      </c>
       <c r="H226" s="3">
         <v>0</v>
       </c>
@@ -11896,7 +11899,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>46153</v>
       </c>
@@ -11944,7 +11947,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>46153</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>46153</v>
       </c>
@@ -12056,6 +12059,9 @@
       <c r="E230" s="3">
         <v>35</v>
       </c>
+      <c r="G230" s="3">
+        <v>0</v>
+      </c>
       <c r="H230" s="3">
         <v>0</v>
       </c>
@@ -12085,7 +12091,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>46153</v>
       </c>
@@ -12133,7 +12139,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>46153</v>
       </c>
@@ -12197,6 +12203,9 @@
       <c r="E233" s="3">
         <v>25</v>
       </c>
+      <c r="G233" s="3">
+        <v>0</v>
+      </c>
       <c r="H233" s="3">
         <v>0</v>
       </c>
@@ -12290,6 +12299,9 @@
       <c r="E235" s="3">
         <v>1</v>
       </c>
+      <c r="G235" s="3">
+        <v>0</v>
+      </c>
       <c r="H235" s="3">
         <v>0</v>
       </c>
@@ -12335,6 +12347,9 @@
       <c r="E236" s="3">
         <v>5</v>
       </c>
+      <c r="G236" s="3">
+        <v>0</v>
+      </c>
       <c r="H236" s="3">
         <v>0</v>
       </c>
@@ -12364,7 +12379,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>46153</v>
       </c>
@@ -12572,6 +12587,9 @@
       <c r="E241" s="3">
         <v>7</v>
       </c>
+      <c r="G241" s="3">
+        <v>0</v>
+      </c>
       <c r="H241" s="3">
         <v>0</v>
       </c>
@@ -12617,6 +12635,9 @@
       <c r="E242" s="3">
         <v>16</v>
       </c>
+      <c r="G242" s="3">
+        <v>0</v>
+      </c>
       <c r="H242" s="3">
         <v>0</v>
       </c>
@@ -12646,7 +12667,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>46153</v>
       </c>
@@ -12710,6 +12731,9 @@
       <c r="E244" s="3">
         <v>24</v>
       </c>
+      <c r="G244" s="3">
+        <v>0</v>
+      </c>
       <c r="H244" s="3">
         <v>0</v>
       </c>
@@ -12739,7 +12763,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>46153</v>
       </c>
@@ -12787,7 +12811,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>46153</v>
       </c>
@@ -12835,7 +12859,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
         <v>46153</v>
       </c>
@@ -12931,7 +12955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>46153</v>
       </c>
@@ -12979,7 +13003,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>46153</v>
       </c>
@@ -13027,7 +13051,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>46153</v>
       </c>
@@ -13075,7 +13099,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>46153</v>
       </c>
@@ -13123,7 +13147,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>46153</v>
       </c>
@@ -13187,6 +13211,9 @@
       <c r="E254" s="3">
         <v>30</v>
       </c>
+      <c r="G254" s="3">
+        <v>0</v>
+      </c>
       <c r="H254" s="3">
         <v>0</v>
       </c>
@@ -13264,7 +13291,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>46153</v>
       </c>
@@ -13357,7 +13384,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>46153</v>
       </c>
@@ -13421,6 +13448,9 @@
       <c r="E259" s="3">
         <v>23</v>
       </c>
+      <c r="G259" s="3">
+        <v>0</v>
+      </c>
       <c r="H259" s="3">
         <v>0</v>
       </c>
@@ -13466,6 +13496,9 @@
       <c r="E260" s="3">
         <v>8</v>
       </c>
+      <c r="G260" s="3">
+        <v>0</v>
+      </c>
       <c r="H260" s="3">
         <v>0</v>
       </c>
@@ -13511,6 +13544,9 @@
       <c r="E261" s="3">
         <v>11</v>
       </c>
+      <c r="G261" s="3">
+        <v>0</v>
+      </c>
       <c r="H261" s="3">
         <v>0</v>
       </c>
@@ -13540,7 +13576,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>46153</v>
       </c>
@@ -13588,7 +13624,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>46153</v>
       </c>
@@ -13636,7 +13672,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>46153</v>
       </c>
@@ -13684,7 +13720,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>46153</v>
       </c>
@@ -13748,6 +13784,9 @@
       <c r="E266" s="3">
         <v>21</v>
       </c>
+      <c r="G266" s="3">
+        <v>0</v>
+      </c>
       <c r="H266" s="3">
         <v>0</v>
       </c>
@@ -13777,7 +13816,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>46154</v>
       </c>
@@ -13873,7 +13912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>46154</v>
       </c>
@@ -13921,7 +13960,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>46154</v>
       </c>
@@ -13969,7 +14008,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>46154</v>
       </c>
@@ -14033,6 +14072,9 @@
       <c r="E272" s="3">
         <v>26</v>
       </c>
+      <c r="G272" s="3">
+        <v>0</v>
+      </c>
       <c r="H272" s="3">
         <v>0</v>
       </c>
@@ -14062,7 +14104,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>46154</v>
       </c>
@@ -14126,6 +14168,9 @@
       <c r="E274" s="3">
         <v>39</v>
       </c>
+      <c r="G274" s="3">
+        <v>0</v>
+      </c>
       <c r="H274" s="3">
         <v>0</v>
       </c>
@@ -14171,6 +14216,9 @@
       <c r="E275" s="3">
         <v>30</v>
       </c>
+      <c r="G275" s="3">
+        <v>0</v>
+      </c>
       <c r="H275" s="3">
         <v>0</v>
       </c>
@@ -14216,6 +14264,9 @@
       <c r="E276" s="3">
         <v>26</v>
       </c>
+      <c r="G276" s="3">
+        <v>0</v>
+      </c>
       <c r="H276" s="3">
         <v>0</v>
       </c>
@@ -14245,7 +14296,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>46154</v>
       </c>
@@ -14293,7 +14344,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>46154</v>
       </c>
@@ -14453,6 +14504,9 @@
       <c r="E281" s="3">
         <v>25</v>
       </c>
+      <c r="G281" s="3">
+        <v>0</v>
+      </c>
       <c r="H281" s="3">
         <v>0</v>
       </c>
@@ -14543,6 +14597,9 @@
       <c r="E283" s="3">
         <v>24</v>
       </c>
+      <c r="G283" s="3">
+        <v>0</v>
+      </c>
       <c r="H283" s="3">
         <v>0</v>
       </c>
@@ -14572,7 +14629,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>46154</v>
       </c>
@@ -14620,7 +14677,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>46154</v>
       </c>
@@ -14668,7 +14725,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>46154</v>
       </c>
@@ -14780,6 +14837,9 @@
       <c r="E288" s="3">
         <v>22</v>
       </c>
+      <c r="G288" s="3">
+        <v>0</v>
+      </c>
       <c r="H288" s="3">
         <v>0</v>
       </c>
@@ -14809,7 +14869,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>46154</v>
       </c>
@@ -14857,7 +14917,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>46154</v>
       </c>
@@ -14905,7 +14965,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>46154</v>
       </c>
@@ -14953,7 +15013,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>46154</v>
       </c>
@@ -15017,6 +15077,9 @@
       <c r="E293" s="3">
         <v>24</v>
       </c>
+      <c r="G293" s="3">
+        <v>0</v>
+      </c>
       <c r="H293" s="3">
         <v>0</v>
       </c>
@@ -15094,7 +15157,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5">
         <v>46154</v>
       </c>
@@ -15158,6 +15221,9 @@
       <c r="E296" s="3">
         <v>7</v>
       </c>
+      <c r="G296" s="3">
+        <v>0</v>
+      </c>
       <c r="H296" s="3">
         <v>0</v>
       </c>
@@ -15203,6 +15269,9 @@
       <c r="E297" s="3">
         <v>16</v>
       </c>
+      <c r="G297" s="3">
+        <v>0</v>
+      </c>
       <c r="H297" s="3">
         <v>0</v>
       </c>
@@ -15248,6 +15317,9 @@
       <c r="E298" s="3">
         <v>27</v>
       </c>
+      <c r="G298" s="3">
+        <v>0</v>
+      </c>
       <c r="H298" s="3">
         <v>0</v>
       </c>
@@ -15293,6 +15365,9 @@
       <c r="E299" s="3">
         <v>7</v>
       </c>
+      <c r="G299" s="3">
+        <v>0</v>
+      </c>
       <c r="H299" s="3">
         <v>0</v>
       </c>
@@ -15415,7 +15490,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>46154</v>
       </c>
@@ -15479,6 +15554,9 @@
       <c r="E303" s="3">
         <v>23</v>
       </c>
+      <c r="G303" s="3">
+        <v>0</v>
+      </c>
       <c r="H303" s="3">
         <v>0</v>
       </c>
@@ -15524,6 +15602,9 @@
       <c r="E304" s="3">
         <v>26</v>
       </c>
+      <c r="G304" s="3">
+        <v>0</v>
+      </c>
       <c r="H304" s="3">
         <v>0</v>
       </c>
@@ -15569,6 +15650,9 @@
       <c r="E305" s="3">
         <v>21</v>
       </c>
+      <c r="G305" s="3">
+        <v>0</v>
+      </c>
       <c r="H305" s="3">
         <v>0</v>
       </c>
@@ -15614,6 +15698,9 @@
       <c r="E306" s="3">
         <v>12</v>
       </c>
+      <c r="G306" s="3">
+        <v>0</v>
+      </c>
       <c r="H306" s="3">
         <v>0</v>
       </c>
@@ -15643,7 +15730,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>46154</v>
       </c>
@@ -15691,7 +15778,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>46154</v>
       </c>
@@ -15755,6 +15842,9 @@
       <c r="E309" s="3">
         <v>19</v>
       </c>
+      <c r="G309" s="3">
+        <v>0</v>
+      </c>
       <c r="H309" s="3">
         <v>0</v>
       </c>
@@ -15784,7 +15874,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>46154</v>
       </c>
@@ -15832,7 +15922,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5">
         <v>46155</v>
       </c>
@@ -15928,7 +16018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="5">
         <v>46155</v>
       </c>
@@ -15992,6 +16082,9 @@
       <c r="E314" s="3">
         <v>23</v>
       </c>
+      <c r="G314" s="3">
+        <v>0</v>
+      </c>
       <c r="H314" s="3">
         <v>0</v>
       </c>
@@ -16021,7 +16114,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5">
         <v>46155</v>
       </c>
@@ -16069,7 +16162,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="5">
         <v>46155</v>
       </c>
@@ -16117,7 +16210,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
         <v>46155</v>
       </c>
@@ -16181,6 +16274,9 @@
       <c r="E318" s="3">
         <v>30</v>
       </c>
+      <c r="G318" s="3">
+        <v>0</v>
+      </c>
       <c r="H318" s="3">
         <v>0</v>
       </c>
@@ -16210,7 +16306,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
         <v>46155</v>
       </c>
@@ -16258,7 +16354,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
         <v>46155</v>
       </c>
@@ -16322,6 +16418,9 @@
       <c r="E321" s="3">
         <v>23</v>
       </c>
+      <c r="G321" s="3">
+        <v>0</v>
+      </c>
       <c r="H321" s="3">
         <v>0</v>
       </c>
@@ -16351,7 +16450,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="5">
         <v>46155</v>
       </c>
@@ -16543,7 +16642,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
         <v>46155</v>
       </c>
@@ -16591,7 +16690,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
         <v>46155</v>
       </c>
@@ -16639,7 +16738,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
         <v>46155</v>
       </c>
@@ -16703,6 +16802,9 @@
       <c r="E329" s="3">
         <v>27</v>
       </c>
+      <c r="G329" s="3">
+        <v>0</v>
+      </c>
       <c r="H329" s="3">
         <v>0</v>
       </c>
@@ -16780,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
         <v>46155</v>
       </c>
@@ -16844,6 +16946,9 @@
       <c r="E332" s="3">
         <v>26</v>
       </c>
+      <c r="G332" s="3">
+        <v>0</v>
+      </c>
       <c r="H332" s="3">
         <v>0</v>
       </c>
@@ -16921,7 +17026,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
         <v>46155</v>
       </c>
@@ -16969,7 +17074,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
         <v>46155</v>
       </c>
@@ -17017,7 +17122,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
         <v>46155</v>
       </c>
@@ -17113,7 +17218,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
         <v>46155</v>
       </c>
@@ -17225,6 +17330,9 @@
       <c r="E340" s="3">
         <v>5</v>
       </c>
+      <c r="G340" s="3">
+        <v>0</v>
+      </c>
       <c r="H340" s="3">
         <v>0</v>
       </c>
@@ -17270,6 +17378,9 @@
       <c r="E341" s="3">
         <v>19</v>
       </c>
+      <c r="G341" s="3">
+        <v>0</v>
+      </c>
       <c r="H341" s="3">
         <v>0</v>
       </c>
@@ -17363,6 +17474,9 @@
       <c r="E343" s="3">
         <v>6</v>
       </c>
+      <c r="G343" s="3">
+        <v>0</v>
+      </c>
       <c r="H343" s="3">
         <v>0</v>
       </c>
@@ -17408,6 +17522,9 @@
       <c r="E344" s="3">
         <v>18</v>
       </c>
+      <c r="G344" s="3">
+        <v>0</v>
+      </c>
       <c r="H344" s="3">
         <v>0</v>
       </c>
@@ -17485,7 +17602,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
         <v>46155</v>
       </c>
@@ -17533,7 +17650,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
         <v>46155</v>
       </c>
@@ -17597,6 +17714,9 @@
       <c r="E348" s="3">
         <v>22</v>
       </c>
+      <c r="G348" s="3">
+        <v>0</v>
+      </c>
       <c r="H348" s="3">
         <v>0</v>
       </c>
@@ -17642,6 +17762,9 @@
       <c r="E349" s="3">
         <v>11</v>
       </c>
+      <c r="G349" s="3">
+        <v>0</v>
+      </c>
       <c r="H349" s="3">
         <v>0</v>
       </c>
@@ -17671,7 +17794,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
         <v>46155</v>
       </c>
@@ -17719,7 +17842,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>46155</v>
       </c>
@@ -17767,7 +17890,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
         <v>46155</v>
       </c>
@@ -17815,7 +17938,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
         <v>46155</v>
       </c>
@@ -17879,6 +18002,9 @@
       <c r="E354" s="3">
         <v>23</v>
       </c>
+      <c r="G354" s="3">
+        <v>0</v>
+      </c>
       <c r="H354" s="3">
         <v>0</v>
       </c>
@@ -30906,7 +31032,7 @@
         <v>15.805471124620061</v>
       </c>
     </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="10">
         <v>46164</v>
       </c>
@@ -30957,7 +31083,7 @@
         <v>19.614147909967851</v>
       </c>
     </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="10">
         <v>46164</v>
       </c>
@@ -31007,7 +31133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="10">
         <v>46164</v>
       </c>
@@ -31058,7 +31184,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="10">
         <v>46164</v>
       </c>
@@ -31109,7 +31235,7 @@
         <v>17.571884984025559</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="10">
         <v>46164</v>
       </c>
@@ -31160,7 +31286,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="10">
         <v>46164</v>
       </c>
@@ -31211,7 +31337,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="10">
         <v>46164</v>
       </c>
@@ -31262,7 +31388,7 @@
         <v>16.897506925207761</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="10">
         <v>46164</v>
       </c>
@@ -31313,7 +31439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="10">
         <v>46164</v>
       </c>
@@ -31364,7 +31490,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="10">
         <v>46164</v>
       </c>
@@ -31463,7 +31589,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="10">
         <v>46164</v>
       </c>
@@ -31562,7 +31688,7 @@
         <v>22.95719844357977</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="10">
         <v>46164</v>
       </c>
@@ -31613,7 +31739,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="10">
         <v>46164</v>
       </c>
@@ -31763,7 +31889,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="10">
         <v>46164</v>
       </c>
@@ -31814,7 +31940,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="10">
         <v>46164</v>
       </c>
@@ -31865,7 +31991,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="10">
         <v>46164</v>
       </c>
@@ -31916,7 +32042,7 @@
         <v>15.75757575757576</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="10">
         <v>46164</v>
       </c>
@@ -31967,7 +32093,7 @@
         <v>16.638370118845501</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="10">
         <v>46164</v>
       </c>
@@ -32018,7 +32144,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="10">
         <v>46164</v>
       </c>
@@ -32069,7 +32195,7 @@
         <v>16.97530864197531</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="10">
         <v>46164</v>
       </c>
@@ -32120,7 +32246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="10">
         <v>46164</v>
       </c>
@@ -32171,7 +32297,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="10">
         <v>46164</v>
       </c>
@@ -32222,7 +32348,7 @@
         <v>10.561056105610559</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="10">
         <v>46164</v>
       </c>
@@ -32273,7 +32399,7 @@
         <v>16.959064327485379</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="10">
         <v>46164</v>
       </c>
@@ -32324,7 +32450,7 @@
         <v>15.584415584415581</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="10">
         <v>46164</v>
       </c>
@@ -32423,7 +32549,7 @@
         <v>20.820189274447952</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="10">
         <v>46164</v>
       </c>
@@ -32474,7 +32600,7 @@
         <v>4.3478260869565224</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="10">
         <v>46164</v>
       </c>
@@ -32525,7 +32651,7 @@
         <v>19.93957703927493</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="10">
         <v>46164</v>
       </c>
@@ -32624,7 +32750,7 @@
         <v>9.037900874635568</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="10">
         <v>46164</v>
       </c>
@@ -32675,7 +32801,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="10">
         <v>46164</v>
       </c>
@@ -32726,7 +32852,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="10">
         <v>46164</v>
       </c>
@@ -32777,7 +32903,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="10">
         <v>46164</v>
       </c>
@@ -32828,7 +32954,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="10">
         <v>46164</v>
       </c>
@@ -32879,7 +33005,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="10">
         <v>46164</v>
       </c>
@@ -32930,7 +33056,7 @@
         <v>15.02145922746781</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="10">
         <v>46164</v>
       </c>
@@ -32981,7 +33107,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="10">
         <v>46164</v>
       </c>
@@ -33032,7 +33158,7 @@
         <v>19.28783382789317</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="10">
         <v>46164</v>
       </c>
@@ -33083,7 +33209,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="10">
         <v>46164</v>
       </c>
@@ -33134,7 +33260,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="10">
         <v>46164</v>
       </c>
@@ -34856,6 +34982,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O729" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters blank="1"/>
+    </filterColumn>
     <filterColumn colId="7">
       <filters blank="1"/>
     </filterColumn>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esther.queiroz\Desktop\PainelProdutividade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D51CBA-2C38-4C69-9789-838F8F547CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99011A9-E9B6-460A-A4D6-A4633039340F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1726,7 +1726,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46146</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>46147</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>46148</v>
       </c>
@@ -8395,7 +8395,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>46149</v>
       </c>
@@ -10219,7 +10219,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>46150</v>
       </c>
@@ -10555,7 +10555,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>46150</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>46153</v>
       </c>
@@ -12043,7 +12043,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>46153</v>
       </c>
@@ -12187,7 +12187,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>46153</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>46153</v>
       </c>
@@ -12331,7 +12331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>46153</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>46153</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>46153</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>20.408163265306118</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>46153</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>46153</v>
       </c>
@@ -13195,7 +13195,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>46153</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>46153</v>
       </c>
@@ -13480,7 +13480,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>46153</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>46153</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>46153</v>
       </c>
@@ -14056,7 +14056,7 @@
         <v>14.7239263803681</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>46154</v>
       </c>
@@ -14152,7 +14152,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>46154</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>20.87155963302752</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>46154</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>46154</v>
       </c>
@@ -14488,7 +14488,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>46154</v>
       </c>
@@ -14536,7 +14536,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>46154</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>15.41353383458646</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>46154</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>46154</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>16.867469879518069</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5">
         <v>46154</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>19.93957703927493</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5">
         <v>46154</v>
       </c>
@@ -15253,7 +15253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5">
         <v>46154</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5">
         <v>46154</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="5">
         <v>46154</v>
       </c>
@@ -15538,7 +15538,7 @@
         <v>19.095477386934672</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>46154</v>
       </c>
@@ -15586,7 +15586,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>46154</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>46154</v>
       </c>
@@ -15682,7 +15682,7 @@
         <v>19.138755980861241</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>46154</v>
       </c>
@@ -15826,7 +15826,7 @@
         <v>22.49443207126949</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>46154</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>21.5962441314554</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="5">
         <v>46155</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>19.526627218934909</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
         <v>46155</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>18.14516129032258</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>46155</v>
       </c>
@@ -16594,7 +16594,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A325" s="5">
         <v>46155</v>
       </c>
@@ -16786,7 +16786,7 @@
         <v>20.533333333333331</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
         <v>46155</v>
       </c>
@@ -16930,7 +16930,7 @@
         <v>13.961038961038961</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>46155</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>17.721518987341771</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
         <v>46155</v>
       </c>
@@ -17362,7 +17362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
         <v>46155</v>
       </c>
@@ -17458,7 +17458,7 @@
         <v>11.864406779661021</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>46155</v>
       </c>
@@ -17506,7 +17506,7 @@
         <v>16.814159292035399</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>46155</v>
       </c>
@@ -17698,7 +17698,7 @@
         <v>16.43835616438356</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
         <v>46155</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>16.894977168949769</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
         <v>46155</v>
       </c>
@@ -17986,7 +17986,7 @@
         <v>16.97247706422019</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="5">
         <v>46155</v>
       </c>
@@ -18706,7 +18706,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" s="5">
         <v>46156</v>
       </c>
@@ -20770,7 +20770,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A412" s="5">
         <v>46157</v>
       </c>
@@ -21634,7 +21634,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430" s="5">
         <v>46157</v>
       </c>
@@ -22882,7 +22882,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A456" s="5">
         <v>46160</v>
       </c>
@@ -23938,7 +23938,7 @@
         <v>29.032258064516132</v>
       </c>
     </row>
-    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A478" s="5">
         <v>46160</v>
       </c>
@@ -25141,7 +25141,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A503" s="7">
         <v>46161</v>
       </c>
@@ -25189,7 +25189,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A504" s="7">
         <v>46161</v>
       </c>
@@ -27337,7 +27337,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="548" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A548" s="7">
         <v>46162</v>
       </c>
@@ -27388,7 +27388,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="549" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A549" s="7">
         <v>46162</v>
       </c>
@@ -29613,7 +29613,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="593" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A593" s="5">
         <v>46163</v>
       </c>
@@ -29661,7 +29661,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="594" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A594" s="5">
         <v>46163</v>
       </c>
@@ -31889,7 +31889,7 @@
         <v>17.241379310344829</v>
       </c>
     </row>
-    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A638" s="10">
         <v>46164</v>
       </c>
@@ -31940,7 +31940,7 @@
         <v>14.285714285714279</v>
       </c>
     </row>
-    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A639" s="10">
         <v>46164</v>
       </c>
@@ -34982,15 +34982,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O729" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters blank="1"/>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Gabriel Alves"/>
+        <filter val="Gabriel Gomes de Andrade"/>
+      </filters>
     </filterColumn>
-    <filterColumn colId="7">
-      <filters blank="1"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A590:O590">
-      <sortCondition ref="B1:B620"/>
-    </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -34162,13 +34162,13 @@
         </is>
       </c>
       <c r="D638" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E638" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F638" s="3" t="n">
-        <v>18.34</v>
+        <v>0</v>
       </c>
       <c r="G638" s="3" t="n">
         <v>0</v>
@@ -39445,11 +39445,7 @@
           <t>Gabriel Alves</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Gabriel Andrade</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Gabriel Alves de Andrade</t>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -34176,17 +34176,14 @@
       <c r="H638" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I638" s="3">
-        <f>E638+G638+H638</f>
-        <v/>
-      </c>
-      <c r="J638" s="3">
-        <f>ROUND(MIN(IF(C638="Técnico III",35,IF(C638="Técnico II",28,IF(C638="Técnico I",23,IF(C638="JR",20,IF(C638="Estágio",10,0))))),IF(C638="Técnico III",SUMIFS($D:$D,$A:$A,$A638,$B:$B,"&lt;&gt;Patrícia Karla de Sousa Araújo",$B:$B,"&lt;&gt;Lorena Dias de Araujo",$B:$B,"&lt;&gt;Lucas Luiz Romero")*(35/1083),IF(C638="Técnico II",SUMIFS($D:$D,$A:$A,$A638,$B:$B,"&lt;&gt;Patrícia Karla de Sousa Araújo",$B:$B,"&lt;&gt;Lorena Dias de Araujo",$B:$B,"&lt;&gt;Lucas Luiz Romero")*(28/1083),IF(C638="Técnico I",SUMIFS($D:$D,$A:$A,$A638,$B:$B,"&lt;&gt;Patrícia Karla de Sousa Araújo",$B:$B,"&lt;&gt;Lorena Dias de Araujo",$B:$B,"&lt;&gt;Lucas Luiz Romero")*(23/1083),IF(C638="JR",SUMIFS($D:$D,$A:$A,$A638,$B:$B,"&lt;&gt;Patrícia Karla de Sousa Araújo",$B:$B,"&lt;&gt;Lorena Dias de Araujo",$B:$B,"&lt;&gt;Lucas Luiz Romero")*(20/1083),IF(C638="Estágio",SUMIFS($D:$D,$A:$A,$A638,$B:$B,"&lt;&gt;Patrícia Karla de Sousa Araújo",$B:$B,"&lt;&gt;Lorena Dias de Araujo",$B:$B,"&lt;&gt;Lucas Luiz Romero")*(10/1083),0)))))),0)</f>
-        <v/>
-      </c>
-      <c r="K638" s="3">
-        <f>I638-J638</f>
-        <v/>
+      <c r="I638" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J638" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K638" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L638" s="3">
         <f>IF(K638&lt;-5,"CRÍTICO",IF(K638&lt;0,"ATENÇÃO",IF(K638&lt;=5,"OPORTUNO","MUITO BOM")))</f>
@@ -39341,6 +39338,7 @@
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Damyllis Lorraine de Oliveira Gonçalves</t>
@@ -39370,6 +39368,7 @@
           <t>Davylla Rodrigues Freitas Silva</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Davylla Rodrigues Freitas Silva</t>
@@ -39433,6 +39432,11 @@
           <t>Francilene Ferreira de Jesus</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Francilene Jesus</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>Francilene Ferreira de Jesus</t>
@@ -39640,6 +39644,7 @@
           <t>Lorena Dias de Araujo</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Lorena Dias de Araujo</t>
@@ -39703,6 +39708,7 @@
           <t>Matheus Farias De Souza</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Matheus Farias De Souza</t>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -39708,7 +39708,11 @@
           <t>Matheus Farias De Souza</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Matheus Farias</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>Matheus Farias De Souza</t>

--- a/produtividade.xlsx
+++ b/produtividade.xlsx
@@ -39449,7 +39449,11 @@
           <t>Gabriel Alves</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gabriel Alves (Estagio)</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>Gabriel Alves de Andrade</t>
